--- a/data/parahumandle_design.xlsx
+++ b/data/parahumandle_design.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Research\Worm Wordle clone\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0373739-F63A-4088-B900-D7ADA74801FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4F88BCE-6067-462D-9CA3-9DCF1DB1C0A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9345" uniqueCount="1872">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9352" uniqueCount="1872">
   <si>
     <t>Parahumandle – design workbook</t>
   </si>
@@ -14897,7 +14897,7 @@
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="2" width="26" customWidth="1"/>
-    <col min="3" max="3" width="9" customWidth="1"/>
+    <col min="3" max="3" width="7.85546875" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
     <col min="6" max="6" width="11" customWidth="1"/>
@@ -41751,8 +41751,12 @@
       <c r="D476" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="E476" s="5"/>
-      <c r="F476" s="5"/>
+      <c r="E476" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F476" s="5" t="s">
+        <v>107</v>
+      </c>
       <c r="G476" s="5" t="s">
         <v>47</v>
       </c>
@@ -41776,11 +41780,11 @@
       <c r="O476" s="5"/>
       <c r="P476" s="6">
         <f t="shared" si="14"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q476" s="6" t="str">
         <f t="shared" si="15"/>
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R476" s="5" t="s">
         <v>51</v>
@@ -42149,7 +42153,9 @@
       <c r="E483" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="F483" s="5"/>
+      <c r="F483" s="5" t="s">
+        <v>107</v>
+      </c>
       <c r="G483" s="5" t="s">
         <v>47</v>
       </c>
@@ -42171,11 +42177,11 @@
       <c r="O483" s="5"/>
       <c r="P483" s="6">
         <f t="shared" si="14"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q483" s="6" t="str">
         <f t="shared" si="15"/>
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R483" s="5" t="s">
         <v>51</v>
@@ -42666,9 +42672,15 @@
       <c r="C492" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="D492" s="5"/>
-      <c r="E492" s="5"/>
-      <c r="F492" s="5"/>
+      <c r="D492" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="E492" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F492" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="G492" s="5" t="s">
         <v>57</v>
       </c>
@@ -42686,7 +42698,7 @@
       <c r="O492" s="5"/>
       <c r="P492" s="6">
         <f t="shared" si="14"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Q492" s="6" t="str">
         <f t="shared" si="15"/>
@@ -44848,7 +44860,9 @@
       <c r="D531" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="E531" s="5"/>
+      <c r="E531" s="5" t="s">
+        <v>45</v>
+      </c>
       <c r="F531" s="5" t="s">
         <v>46</v>
       </c>
@@ -44875,11 +44889,11 @@
       <c r="O531" s="5"/>
       <c r="P531" s="6">
         <f t="shared" si="16"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q531" s="6" t="str">
         <f t="shared" si="17"/>
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R531" s="5" t="s">
         <v>51</v>
@@ -49895,7 +49909,7 @@
         <v/>
       </c>
       <c r="Q642" s="6" t="str">
-        <f t="shared" ref="Q642:Q705" si="21">IF(A642="","",IF(AND(P642=6,UPPER(L642)&lt;&gt;"Y",C642&lt;&gt;""),"Yes","No"))</f>
+        <f t="shared" ref="Q642:Q701" si="21">IF(A642="","",IF(AND(P642=6,UPPER(L642)&lt;&gt;"Y",C642&lt;&gt;""),"Yes","No"))</f>
         <v/>
       </c>
       <c r="R642" s="5"/>
@@ -51990,11 +52004,11 @@
       </c>
       <c r="E2" s="8">
         <f>COUNTA(Roster!D2:D701)</f>
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F2" s="9">
         <f>IF(COUNTA(Roster!A2:A701)=0,0,E2/COUNTA(Roster!A2:A701))</f>
-        <v>0.52542372881355937</v>
+        <v>0.52711864406779663</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -52012,11 +52026,11 @@
       </c>
       <c r="E3" s="8">
         <f>COUNTA(Roster!E2:E701)</f>
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="F3" s="9">
         <f>IF(COUNTA(Roster!A2:A701)=0,0,E3/COUNTA(Roster!A2:A701))</f>
-        <v>0.3559322033898305</v>
+        <v>0.3610169491525424</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -52034,11 +52048,11 @@
       </c>
       <c r="E4" s="8">
         <f>COUNTA(Roster!F2:F701)</f>
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="F4" s="9">
         <f>IF(COUNTA(Roster!A2:A701)=0,0,E4/COUNTA(Roster!A2:A701))</f>
-        <v>0.36949152542372882</v>
+        <v>0.37457627118644066</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -52475,7 +52489,7 @@
       </c>
       <c r="B11" s="8">
         <f>COUNTIF(Roster!Q2:Q701,"Yes")</f>
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C11" s="8" t="s">
         <v>1741</v>
@@ -52487,7 +52501,7 @@
       </c>
       <c r="B12" s="9">
         <f>IF(B5=0,0,B11/B5)</f>
-        <v>0.65333333333333332</v>
+        <v>0.67333333333333334</v>
       </c>
       <c r="C12" s="8" t="s">
         <v>1741</v>
@@ -52499,7 +52513,7 @@
       </c>
       <c r="B13" s="13">
         <f>IFERROR(AVERAGE(Roster!P2:P701),0)</f>
-        <v>3.0677966101694913</v>
+        <v>3.0796610169491525</v>
       </c>
       <c r="C13" s="8" t="s">
         <v>1741</v>

--- a/data/parahumandle_design.xlsx
+++ b/data/parahumandle_design.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Research\Worm Wordle clone\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4F88BCE-6067-462D-9CA3-9DCF1DB1C0A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1104C53C-D245-4811-9037-9ECCF6E4C879}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9352" uniqueCount="1872">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9356" uniqueCount="1872">
   <si>
     <t>Parahumandle – design workbook</t>
   </si>
@@ -46992,7 +46992,9 @@
       <c r="D569" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="E569" s="5"/>
+      <c r="E569" s="5" t="s">
+        <v>45</v>
+      </c>
       <c r="F569" s="5" t="s">
         <v>46</v>
       </c>
@@ -47017,11 +47019,11 @@
       <c r="O569" s="5"/>
       <c r="P569" s="6">
         <f t="shared" si="16"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q569" s="6" t="str">
         <f t="shared" si="17"/>
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R569" s="5" t="s">
         <v>51</v>
@@ -47055,8 +47057,12 @@
       <c r="D570" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="E570" s="5"/>
-      <c r="F570" s="5"/>
+      <c r="E570" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F570" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="G570" s="5" t="s">
         <v>47</v>
       </c>
@@ -47072,7 +47078,7 @@
       <c r="O570" s="5"/>
       <c r="P570" s="6">
         <f t="shared" si="16"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q570" s="6" t="str">
         <f t="shared" si="17"/>
@@ -47872,7 +47878,9 @@
       <c r="D585" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="E585" s="5"/>
+      <c r="E585" s="5" t="s">
+        <v>45</v>
+      </c>
       <c r="F585" s="5" t="s">
         <v>46</v>
       </c>
@@ -47897,11 +47905,11 @@
       <c r="O585" s="5"/>
       <c r="P585" s="6">
         <f t="shared" si="18"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q585" s="6" t="str">
         <f t="shared" si="19"/>
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R585" s="5" t="s">
         <v>125</v>
@@ -52026,11 +52034,11 @@
       </c>
       <c r="E3" s="8">
         <f>COUNTA(Roster!E2:E701)</f>
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="F3" s="9">
         <f>IF(COUNTA(Roster!A2:A701)=0,0,E3/COUNTA(Roster!A2:A701))</f>
-        <v>0.3610169491525424</v>
+        <v>0.36610169491525424</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -52048,11 +52056,11 @@
       </c>
       <c r="E4" s="8">
         <f>COUNTA(Roster!F2:F701)</f>
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F4" s="9">
         <f>IF(COUNTA(Roster!A2:A701)=0,0,E4/COUNTA(Roster!A2:A701))</f>
-        <v>0.37457627118644066</v>
+        <v>0.37627118644067797</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -52489,7 +52497,7 @@
       </c>
       <c r="B11" s="8">
         <f>COUNTIF(Roster!Q2:Q701,"Yes")</f>
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C11" s="8" t="s">
         <v>1741</v>
@@ -52501,7 +52509,7 @@
       </c>
       <c r="B12" s="9">
         <f>IF(B5=0,0,B11/B5)</f>
-        <v>0.67333333333333334</v>
+        <v>0.68666666666666665</v>
       </c>
       <c r="C12" s="8" t="s">
         <v>1741</v>
@@ -52513,7 +52521,7 @@
       </c>
       <c r="B13" s="13">
         <f>IFERROR(AVERAGE(Roster!P2:P701),0)</f>
-        <v>3.0796610169491525</v>
+        <v>3.0864406779661016</v>
       </c>
       <c r="C13" s="8" t="s">
         <v>1741</v>

--- a/data/parahumandle_design.xlsx
+++ b/data/parahumandle_design.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Research\Worm Wordle clone\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1104C53C-D245-4811-9037-9ECCF6E4C879}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3671D077-13D9-41FD-BDCC-0A1E2314A797}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9356" uniqueCount="1872">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9379" uniqueCount="1873">
   <si>
     <t>Parahumandle – design workbook</t>
   </si>
@@ -5668,6 +5668,9 @@
   </si>
   <si>
     <t>Decision</t>
+  </si>
+  <si>
+    <t>The Huntsmen</t>
   </si>
 </sst>
 </file>
@@ -14896,8 +14899,8 @@
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
-    <col min="2" max="2" width="26" customWidth="1"/>
-    <col min="3" max="3" width="7.85546875" customWidth="1"/>
+    <col min="2" max="2" width="14.140625" customWidth="1"/>
+    <col min="3" max="3" width="19" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
     <col min="6" max="6" width="11" customWidth="1"/>
@@ -23224,8 +23227,12 @@
       <c r="D143" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="E143" s="5"/>
-      <c r="F143" s="5"/>
+      <c r="E143" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F143" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="G143" s="5"/>
       <c r="H143" s="5" t="s">
         <v>574</v>
@@ -23243,7 +23250,7 @@
       <c r="O143" s="5"/>
       <c r="P143" s="6">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q143" s="6" t="str">
         <f t="shared" si="5"/>
@@ -23277,7 +23284,9 @@
       <c r="D144" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="E144" s="5"/>
+      <c r="E144" s="5" t="s">
+        <v>45</v>
+      </c>
       <c r="F144" s="5" t="s">
         <v>107</v>
       </c>
@@ -23300,7 +23309,7 @@
       <c r="O144" s="5"/>
       <c r="P144" s="6">
         <f t="shared" si="4"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q144" s="6" t="str">
         <f t="shared" si="5"/>
@@ -24264,11 +24273,15 @@
         <v>70</v>
       </c>
       <c r="D161" s="5"/>
-      <c r="E161" s="5"/>
+      <c r="E161" s="5" t="s">
+        <v>45</v>
+      </c>
       <c r="F161" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="G161" s="5"/>
+      <c r="G161" s="5" t="s">
+        <v>57</v>
+      </c>
       <c r="H161" s="5" t="s">
         <v>639</v>
       </c>
@@ -24285,7 +24298,7 @@
       <c r="O161" s="5"/>
       <c r="P161" s="6">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q161" s="6" t="str">
         <f t="shared" si="5"/>
@@ -24315,7 +24328,9 @@
         <v>70</v>
       </c>
       <c r="D162" s="5"/>
-      <c r="E162" s="5"/>
+      <c r="E162" s="5" t="s">
+        <v>45</v>
+      </c>
       <c r="F162" s="5" t="s">
         <v>107</v>
       </c>
@@ -24338,7 +24353,7 @@
       </c>
       <c r="P162" s="6">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q162" s="6" t="str">
         <f t="shared" si="5"/>
@@ -24683,13 +24698,21 @@
       <c r="C169" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="D169" s="5"/>
-      <c r="E169" s="5"/>
-      <c r="F169" s="5"/>
+      <c r="D169" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="E169" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F169" s="5" t="s">
+        <v>107</v>
+      </c>
       <c r="G169" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H169" s="5"/>
+      <c r="H169" s="5" t="s">
+        <v>1872</v>
+      </c>
       <c r="I169" s="5"/>
       <c r="J169" s="5"/>
       <c r="K169" s="5"/>
@@ -24701,7 +24724,7 @@
       <c r="O169" s="5"/>
       <c r="P169" s="6">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q169" s="6" t="str">
         <f t="shared" si="5"/>
@@ -25666,8 +25689,12 @@
       <c r="D187" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="E187" s="5"/>
-      <c r="F187" s="5"/>
+      <c r="E187" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F187" s="5" t="s">
+        <v>107</v>
+      </c>
       <c r="G187" s="5" t="s">
         <v>47</v>
       </c>
@@ -25689,11 +25716,11 @@
       <c r="O187" s="5"/>
       <c r="P187" s="6">
         <f t="shared" si="4"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q187" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R187" s="5" t="s">
         <v>51</v>
@@ -25849,7 +25876,7 @@
         <v>47</v>
       </c>
       <c r="H190" s="5" t="s">
-        <v>706</v>
+        <v>517</v>
       </c>
       <c r="I190" s="5" t="s">
         <v>178</v>
@@ -26025,9 +26052,15 @@
       <c r="C193" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="D193" s="5"/>
-      <c r="E193" s="5"/>
-      <c r="F193" s="5"/>
+      <c r="D193" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="E193" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F193" s="5" t="s">
+        <v>107</v>
+      </c>
       <c r="G193" s="5" t="s">
         <v>57</v>
       </c>
@@ -26045,7 +26078,7 @@
       <c r="O193" s="5"/>
       <c r="P193" s="6">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Q193" s="6" t="str">
         <f t="shared" si="5"/>
@@ -26080,11 +26113,17 @@
       <c r="C194" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="D194" s="5"/>
-      <c r="E194" s="5"/>
-      <c r="F194" s="5"/>
+      <c r="D194" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="E194" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F194" s="5" t="s">
+        <v>107</v>
+      </c>
       <c r="G194" s="5" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="H194" s="5" t="s">
         <v>319</v>
@@ -26100,7 +26139,7 @@
       <c r="O194" s="5"/>
       <c r="P194" s="6">
         <f t="shared" ref="P194:P257" si="6">IF(A194="","",COUNTA(D194:F194)+COUNTA(G194:G194)+COUNTA(H194:H194)+COUNTA(I194:I194))</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Q194" s="6" t="str">
         <f t="shared" ref="Q194:Q257" si="7">IF(A194="","",IF(AND(P194=6,UPPER(L194)&lt;&gt;"Y",C194&lt;&gt;""),"Yes","No"))</f>
@@ -26446,7 +26485,9 @@
         <v>737</v>
       </c>
       <c r="B201" s="5"/>
-      <c r="C201" s="5"/>
+      <c r="C201" s="5" t="s">
+        <v>43</v>
+      </c>
       <c r="D201" s="5"/>
       <c r="E201" s="5" t="s">
         <v>45</v>
@@ -26454,7 +26495,9 @@
       <c r="F201" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="G201" s="5"/>
+      <c r="G201" s="5" t="s">
+        <v>57</v>
+      </c>
       <c r="H201" s="5" t="s">
         <v>77</v>
       </c>
@@ -26477,7 +26520,7 @@
       </c>
       <c r="P201" s="6">
         <f t="shared" si="6"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q201" s="6" t="str">
         <f t="shared" si="7"/>
@@ -26559,9 +26602,15 @@
       <c r="C203" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="D203" s="5"/>
-      <c r="E203" s="5"/>
-      <c r="F203" s="5"/>
+      <c r="D203" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="E203" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F203" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="G203" s="5" t="s">
         <v>47</v>
       </c>
@@ -26585,11 +26634,11 @@
       <c r="O203" s="5"/>
       <c r="P203" s="6">
         <f t="shared" si="6"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q203" s="6" t="str">
         <f t="shared" si="7"/>
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R203" s="5" t="s">
         <v>51</v>
@@ -52012,11 +52061,11 @@
       </c>
       <c r="E2" s="8">
         <f>COUNTA(Roster!D2:D701)</f>
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="F2" s="9">
         <f>IF(COUNTA(Roster!A2:A701)=0,0,E2/COUNTA(Roster!A2:A701))</f>
-        <v>0.52711864406779663</v>
+        <v>0.53389830508474578</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -52034,11 +52083,11 @@
       </c>
       <c r="E3" s="8">
         <f>COUNTA(Roster!E2:E701)</f>
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="F3" s="9">
         <f>IF(COUNTA(Roster!A2:A701)=0,0,E3/COUNTA(Roster!A2:A701))</f>
-        <v>0.36610169491525424</v>
+        <v>0.38135593220338981</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -52056,11 +52105,11 @@
       </c>
       <c r="E4" s="8">
         <f>COUNTA(Roster!F2:F701)</f>
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="F4" s="9">
         <f>IF(COUNTA(Roster!A2:A701)=0,0,E4/COUNTA(Roster!A2:A701))</f>
-        <v>0.37627118644067797</v>
+        <v>0.38644067796610171</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -52078,11 +52127,11 @@
       </c>
       <c r="E5" s="8">
         <f>COUNTA(Roster!G2:G701)</f>
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="F5" s="9">
         <f>IF(COUNTA(Roster!A2:A701)=0,0,E5/COUNTA(Roster!A2:A701))</f>
-        <v>0.52372881355932199</v>
+        <v>0.52711864406779663</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -52100,11 +52149,11 @@
       </c>
       <c r="E6" s="8">
         <f>COUNTA(Roster!H2:H701)</f>
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="F6" s="9">
         <f>IF(COUNTA(Roster!A2:A701)=0,0,E6/COUNTA(Roster!A2:A701))</f>
-        <v>0.76271186440677963</v>
+        <v>0.764406779661017</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
@@ -52497,7 +52546,7 @@
       </c>
       <c r="B11" s="8">
         <f>COUNTIF(Roster!Q2:Q701,"Yes")</f>
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C11" s="8" t="s">
         <v>1741</v>
@@ -52509,7 +52558,7 @@
       </c>
       <c r="B12" s="9">
         <f>IF(B5=0,0,B11/B5)</f>
-        <v>0.68666666666666665</v>
+        <v>0.7</v>
       </c>
       <c r="C12" s="8" t="s">
         <v>1741</v>
@@ -52521,7 +52570,7 @@
       </c>
       <c r="B13" s="13">
         <f>IFERROR(AVERAGE(Roster!P2:P701),0)</f>
-        <v>3.0864406779661016</v>
+        <v>3.123728813559322</v>
       </c>
       <c r="C13" s="8" t="s">
         <v>1741</v>

--- a/data/parahumandle_design.xlsx
+++ b/data/parahumandle_design.xlsx
@@ -14828,6 +14828,9 @@
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="8" t="s">
+        <v>1866</v>
+      </c>
       <c r="B5" s="8" t="s">
         <v>1869</v>
       </c>
@@ -14845,6 +14848,11 @@
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Non-cape</t>
+        </is>
+      </c>
       <c r="B6" s="8" t="s">
         <v>595</v>
       </c>
@@ -51948,7 +51956,7 @@
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0100-000001000000}">
           <x14:formula1>
-            <xm:f>Lists!$A$2:$A$4</xm:f>
+            <xm:f>Lists!$A$2:$A$6</xm:f>
           </x14:formula1>
           <x14:formula2>
             <xm:f>0</xm:f>
@@ -52053,8 +52061,10 @@
       <c r="B2" s="7" t="s">
         <v>1687</v>
       </c>
-      <c r="C2" s="7" t="s">
-        <v>1688</v>
+      <c r="C2" s="7" t="inlineStr">
+        <is>
+          <t>Hero / Villain / Rogue / Unknown / Non-cape</t>
+        </is>
       </c>
       <c r="D2" s="7" t="s">
         <v>1689</v>

--- a/data/parahumandle_design.xlsx
+++ b/data/parahumandle_design.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Research\Worm Wordle clone\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3671D077-13D9-41FD-BDCC-0A1E2314A797}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB0CAD6E-C2B5-40D6-9222-4F7948D89EBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6870" yWindow="6705" windowWidth="28800" windowHeight="15345" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9379" uniqueCount="1873">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9386" uniqueCount="1874">
   <si>
     <t>Parahumandle – design workbook</t>
   </si>
@@ -5118,9 +5118,6 @@
     <t>Disposition</t>
   </si>
   <si>
-    <t>Hero / Villain / Rogue</t>
-  </si>
-  <si>
     <t>Final disposition in canon; original in-universe label shown in tooltip</t>
   </si>
   <si>
@@ -5671,6 +5668,12 @@
   </si>
   <si>
     <t>The Huntsmen</t>
+  </si>
+  <si>
+    <t>Hero / Villain / Rogue / Unknown / Non-cape</t>
+  </si>
+  <si>
+    <t>Non-cape</t>
   </si>
 </sst>
 </file>
@@ -6162,84 +6165,84 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>1825</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>1826</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>1827</v>
-      </c>
       <c r="C1" s="4" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
+        <v>1827</v>
+      </c>
+      <c r="B2" s="7" t="s">
         <v>1828</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>1829</v>
       </c>
       <c r="C2" s="14"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
+        <v>1829</v>
+      </c>
+      <c r="B3" s="7" t="s">
         <v>1830</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>1831</v>
       </c>
       <c r="C3" s="14"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
+        <v>1831</v>
+      </c>
+      <c r="B4" s="7" t="s">
         <v>1832</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>1833</v>
       </c>
       <c r="C4" s="14"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
+        <v>1833</v>
+      </c>
+      <c r="B5" s="7" t="s">
         <v>1834</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>1835</v>
       </c>
       <c r="C5" s="14"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>1836</v>
+        <v>1835</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>1835</v>
+        <v>1834</v>
       </c>
       <c r="C6" s="14"/>
     </row>
     <row r="7" spans="1:3" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
+        <v>1836</v>
+      </c>
+      <c r="B7" s="7" t="s">
         <v>1837</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>1838</v>
       </c>
       <c r="C7" s="14"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>1839</v>
+        <v>1838</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>1835</v>
+        <v>1834</v>
       </c>
       <c r="C8" s="14"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
+        <v>1839</v>
+      </c>
+      <c r="B9" s="7" t="s">
         <v>1840</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>1841</v>
       </c>
       <c r="C9" s="14"/>
     </row>
@@ -6263,22 +6266,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
+        <v>1841</v>
+      </c>
+      <c r="B1" s="16" t="s">
+        <v>1779</v>
+      </c>
+      <c r="C1" s="16" t="s">
         <v>1842</v>
       </c>
-      <c r="B1" s="16" t="s">
-        <v>1780</v>
-      </c>
-      <c r="C1" s="16" t="s">
+      <c r="D1" s="16" t="s">
         <v>1843</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="E1" s="16" t="s">
         <v>1844</v>
       </c>
-      <c r="E1" s="16" t="s">
+      <c r="F1" s="16" t="s">
         <v>1845</v>
-      </c>
-      <c r="F1" s="16" t="s">
-        <v>1846</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -6293,7 +6296,7 @@
         <v>44</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F2" s="8"/>
     </row>
@@ -6309,7 +6312,7 @@
         <v>44</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F3" s="8"/>
     </row>
@@ -6318,14 +6321,14 @@
         <v>56</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="8" t="s">
         <v>57</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F4" s="8"/>
     </row>
@@ -6341,7 +6344,7 @@
         <v>76</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F5" s="8"/>
     </row>
@@ -6350,14 +6353,14 @@
         <v>75</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C6" s="8"/>
       <c r="D6" s="8" t="s">
         <v>57</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F6" s="8"/>
     </row>
@@ -6366,14 +6369,14 @@
         <v>75</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="C7" s="8"/>
       <c r="D7" s="8" t="s">
         <v>78</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F7" s="8"/>
     </row>
@@ -6382,7 +6385,7 @@
         <v>82</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="C8" s="8" t="s">
         <v>72</v>
@@ -6391,7 +6394,7 @@
         <v>71</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="F8" s="8"/>
     </row>
@@ -6407,7 +6410,7 @@
         <v>44</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F9" s="8"/>
     </row>
@@ -6416,14 +6419,14 @@
         <v>89</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C10" s="8"/>
       <c r="D10" s="8" t="s">
         <v>47</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F10" s="8"/>
     </row>
@@ -6432,14 +6435,14 @@
         <v>89</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="C11" s="8"/>
       <c r="D11" s="8" t="s">
         <v>91</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F11" s="8"/>
     </row>
@@ -6448,14 +6451,14 @@
         <v>95</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C12" s="8"/>
       <c r="D12" s="8" t="s">
         <v>47</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F12" s="8"/>
     </row>
@@ -6464,7 +6467,7 @@
         <v>106</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="C13" s="8" t="s">
         <v>115</v>
@@ -6473,7 +6476,7 @@
         <v>77</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>1849</v>
+        <v>1848</v>
       </c>
       <c r="F13" s="8"/>
     </row>
@@ -6482,7 +6485,7 @@
         <v>106</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="C14" s="8" t="s">
         <v>72</v>
@@ -6491,7 +6494,7 @@
         <v>71</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="F14" s="8"/>
     </row>
@@ -6507,7 +6510,7 @@
         <v>44</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F15" s="8"/>
     </row>
@@ -6516,7 +6519,7 @@
         <v>131</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="C16" s="8" t="s">
         <v>133</v>
@@ -6525,7 +6528,7 @@
         <v>178</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="F16" s="8"/>
     </row>
@@ -6534,14 +6537,14 @@
         <v>142</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C17" s="8"/>
       <c r="D17" s="8" t="s">
         <v>47</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F17" s="8"/>
     </row>
@@ -6557,7 +6560,7 @@
         <v>76</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F18" s="8"/>
     </row>
@@ -6566,14 +6569,14 @@
         <v>148</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="C19" s="8"/>
       <c r="D19" s="8" t="s">
         <v>149</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F19" s="8"/>
     </row>
@@ -6582,14 +6585,14 @@
         <v>168</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C20" s="8"/>
       <c r="D20" s="8" t="s">
         <v>57</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F20" s="8"/>
     </row>
@@ -6605,7 +6608,7 @@
         <v>76</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F21" s="8"/>
     </row>
@@ -6614,14 +6617,14 @@
         <v>174</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="C22" s="8"/>
       <c r="D22" s="8" t="s">
         <v>149</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F22" s="8"/>
     </row>
@@ -6637,7 +6640,7 @@
         <v>44</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F23" s="8"/>
     </row>
@@ -6653,7 +6656,7 @@
         <v>76</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F24" s="8"/>
     </row>
@@ -6662,7 +6665,7 @@
         <v>188</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="C25" s="8" t="s">
         <v>83</v>
@@ -6671,7 +6674,7 @@
         <v>77</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="F25" s="8"/>
     </row>
@@ -6687,7 +6690,7 @@
         <v>44</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F26" s="8"/>
     </row>
@@ -6703,7 +6706,7 @@
         <v>44</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F27" s="8"/>
     </row>
@@ -6712,14 +6715,14 @@
         <v>213</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C28" s="8"/>
       <c r="D28" s="8" t="s">
         <v>57</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F28" s="8"/>
     </row>
@@ -6728,7 +6731,7 @@
         <v>213</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="C29" s="8" t="s">
         <v>78</v>
@@ -6737,7 +6740,7 @@
         <v>119</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="F29" s="8"/>
     </row>
@@ -6753,7 +6756,7 @@
         <v>44</v>
       </c>
       <c r="E30" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F30" s="8"/>
     </row>
@@ -6762,7 +6765,7 @@
         <v>196</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="C31" s="8" t="s">
         <v>58</v>
@@ -6771,7 +6774,7 @@
         <v>191</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="F31" s="8"/>
     </row>
@@ -6787,7 +6790,7 @@
         <v>44</v>
       </c>
       <c r="E32" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F32" s="8"/>
     </row>
@@ -6796,14 +6799,14 @@
         <v>223</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C33" s="8"/>
       <c r="D33" s="8" t="s">
         <v>57</v>
       </c>
       <c r="E33" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F33" s="8"/>
     </row>
@@ -6812,7 +6815,7 @@
         <v>223</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="C34" s="8" t="s">
         <v>227</v>
@@ -6821,7 +6824,7 @@
         <v>224</v>
       </c>
       <c r="E34" s="8" t="s">
-        <v>1849</v>
+        <v>1848</v>
       </c>
       <c r="F34" s="8"/>
     </row>
@@ -6830,14 +6833,14 @@
         <v>223</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="C35" s="8"/>
       <c r="D35" s="8" t="s">
         <v>119</v>
       </c>
       <c r="E35" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F35" s="8"/>
     </row>
@@ -6853,7 +6856,7 @@
         <v>44</v>
       </c>
       <c r="E36" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F36" s="8"/>
     </row>
@@ -6862,14 +6865,14 @@
         <v>235</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C37" s="8"/>
       <c r="D37" s="8" t="s">
         <v>47</v>
       </c>
       <c r="E37" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F37" s="8"/>
     </row>
@@ -6878,7 +6881,7 @@
         <v>235</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="C38" s="8" t="s">
         <v>71</v>
@@ -6887,7 +6890,7 @@
         <v>91</v>
       </c>
       <c r="E38" s="8" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="F38" s="8"/>
     </row>
@@ -6903,7 +6906,7 @@
         <v>245</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F39" s="8"/>
     </row>
@@ -6912,14 +6915,14 @@
         <v>244</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C40" s="8"/>
       <c r="D40" s="8" t="s">
         <v>47</v>
       </c>
       <c r="E40" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F40" s="8"/>
     </row>
@@ -6928,14 +6931,14 @@
         <v>251</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C41" s="8"/>
       <c r="D41" s="8" t="s">
         <v>47</v>
       </c>
       <c r="E41" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F41" s="8"/>
     </row>
@@ -6951,7 +6954,7 @@
         <v>245</v>
       </c>
       <c r="E42" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F42" s="8"/>
     </row>
@@ -6960,14 +6963,14 @@
         <v>266</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C43" s="8"/>
       <c r="D43" s="8" t="s">
         <v>47</v>
       </c>
       <c r="E43" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F43" s="8"/>
     </row>
@@ -6983,7 +6986,7 @@
         <v>44</v>
       </c>
       <c r="E44" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F44" s="8"/>
     </row>
@@ -6999,7 +7002,7 @@
         <v>44</v>
       </c>
       <c r="E45" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F45" s="8"/>
     </row>
@@ -7008,7 +7011,7 @@
         <v>277</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="C46" s="8" t="s">
         <v>227</v>
@@ -7017,7 +7020,7 @@
         <v>224</v>
       </c>
       <c r="E46" s="8" t="s">
-        <v>1849</v>
+        <v>1848</v>
       </c>
       <c r="F46" s="8"/>
     </row>
@@ -7033,7 +7036,7 @@
         <v>44</v>
       </c>
       <c r="E47" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F47" s="8"/>
     </row>
@@ -7042,14 +7045,14 @@
         <v>280</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C48" s="8"/>
       <c r="D48" s="8" t="s">
         <v>57</v>
       </c>
       <c r="E48" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F48" s="8"/>
     </row>
@@ -7065,7 +7068,7 @@
         <v>44</v>
       </c>
       <c r="E49" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F49" s="8"/>
     </row>
@@ -7081,7 +7084,7 @@
         <v>76</v>
       </c>
       <c r="E50" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F50" s="8"/>
     </row>
@@ -7090,14 +7093,14 @@
         <v>299</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="C51" s="8"/>
       <c r="D51" s="8" t="s">
         <v>78</v>
       </c>
       <c r="E51" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F51" s="8"/>
     </row>
@@ -7113,7 +7116,7 @@
         <v>44</v>
       </c>
       <c r="E52" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F52" s="8"/>
     </row>
@@ -7122,14 +7125,14 @@
         <v>313</v>
       </c>
       <c r="B53" s="8" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C53" s="8"/>
       <c r="D53" s="8" t="s">
         <v>57</v>
       </c>
       <c r="E53" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F53" s="8"/>
     </row>
@@ -7138,14 +7141,14 @@
         <v>322</v>
       </c>
       <c r="B54" s="8" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C54" s="8"/>
       <c r="D54" s="8" t="s">
         <v>57</v>
       </c>
       <c r="E54" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F54" s="8"/>
     </row>
@@ -7161,7 +7164,7 @@
         <v>76</v>
       </c>
       <c r="E55" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F55" s="8"/>
     </row>
@@ -7170,14 +7173,14 @@
         <v>327</v>
       </c>
       <c r="B56" s="8" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="C56" s="8"/>
       <c r="D56" s="8" t="s">
         <v>77</v>
       </c>
       <c r="E56" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F56" s="8"/>
     </row>
@@ -7186,14 +7189,14 @@
         <v>329</v>
       </c>
       <c r="B57" s="8" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C57" s="8"/>
       <c r="D57" s="8" t="s">
         <v>47</v>
       </c>
       <c r="E57" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F57" s="8"/>
     </row>
@@ -7209,7 +7212,7 @@
         <v>76</v>
       </c>
       <c r="E58" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F58" s="8"/>
     </row>
@@ -7225,7 +7228,7 @@
         <v>332</v>
       </c>
       <c r="E59" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F59" s="8"/>
     </row>
@@ -7241,7 +7244,7 @@
         <v>76</v>
       </c>
       <c r="E60" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F60" s="8"/>
     </row>
@@ -7250,7 +7253,7 @@
         <v>338</v>
       </c>
       <c r="B61" s="8" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="C61" s="8" t="s">
         <v>340</v>
@@ -7259,7 +7262,7 @@
         <v>83</v>
       </c>
       <c r="E61" s="8" t="s">
-        <v>1849</v>
+        <v>1848</v>
       </c>
       <c r="F61" s="8"/>
     </row>
@@ -7268,7 +7271,7 @@
         <v>338</v>
       </c>
       <c r="B62" s="8" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="C62" s="8" t="s">
         <v>72</v>
@@ -7277,7 +7280,7 @@
         <v>59</v>
       </c>
       <c r="E62" s="8" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="F62" s="8"/>
     </row>
@@ -7293,7 +7296,7 @@
         <v>44</v>
       </c>
       <c r="E63" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F63" s="8"/>
     </row>
@@ -7302,14 +7305,14 @@
         <v>343</v>
       </c>
       <c r="B64" s="8" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="C64" s="8"/>
       <c r="D64" s="8" t="s">
         <v>119</v>
       </c>
       <c r="E64" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F64" s="8"/>
     </row>
@@ -7325,7 +7328,7 @@
         <v>44</v>
       </c>
       <c r="E65" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F65" s="8"/>
     </row>
@@ -7334,14 +7337,14 @@
         <v>349</v>
       </c>
       <c r="B66" s="8" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="C66" s="8"/>
       <c r="D66" s="8" t="s">
         <v>72</v>
       </c>
       <c r="E66" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F66" s="8"/>
     </row>
@@ -7357,7 +7360,7 @@
         <v>76</v>
       </c>
       <c r="E67" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F67" s="8"/>
     </row>
@@ -7366,14 +7369,14 @@
         <v>375</v>
       </c>
       <c r="B68" s="8" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C68" s="8"/>
       <c r="D68" s="8" t="s">
         <v>57</v>
       </c>
       <c r="E68" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F68" s="8"/>
     </row>
@@ -7382,14 +7385,14 @@
         <v>375</v>
       </c>
       <c r="B69" s="8" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="C69" s="8"/>
       <c r="D69" s="8" t="s">
         <v>91</v>
       </c>
       <c r="E69" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F69" s="8"/>
     </row>
@@ -7405,7 +7408,7 @@
         <v>76</v>
       </c>
       <c r="E70" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F70" s="8"/>
     </row>
@@ -7421,7 +7424,7 @@
         <v>76</v>
       </c>
       <c r="E71" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F71" s="8"/>
     </row>
@@ -7430,7 +7433,7 @@
         <v>384</v>
       </c>
       <c r="B72" s="8" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="C72" s="8" t="s">
         <v>83</v>
@@ -7439,7 +7442,7 @@
         <v>77</v>
       </c>
       <c r="E72" s="8" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="F72" s="8"/>
     </row>
@@ -7448,14 +7451,14 @@
         <v>386</v>
       </c>
       <c r="B73" s="8" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C73" s="8"/>
       <c r="D73" s="8" t="s">
         <v>57</v>
       </c>
       <c r="E73" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F73" s="8"/>
     </row>
@@ -7471,7 +7474,7 @@
         <v>44</v>
       </c>
       <c r="E74" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F74" s="8"/>
     </row>
@@ -7480,14 +7483,14 @@
         <v>396</v>
       </c>
       <c r="B75" s="8" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="C75" s="8"/>
       <c r="D75" s="8" t="s">
         <v>72</v>
       </c>
       <c r="E75" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F75" s="8"/>
     </row>
@@ -7503,7 +7506,7 @@
         <v>76</v>
       </c>
       <c r="E76" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F76" s="8"/>
     </row>
@@ -7512,14 +7515,14 @@
         <v>409</v>
       </c>
       <c r="B77" s="8" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C77" s="8"/>
       <c r="D77" s="8" t="s">
         <v>57</v>
       </c>
       <c r="E77" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F77" s="8"/>
     </row>
@@ -7528,7 +7531,7 @@
         <v>409</v>
       </c>
       <c r="B78" s="8" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="C78" s="8" t="s">
         <v>412</v>
@@ -7537,7 +7540,7 @@
         <v>83</v>
       </c>
       <c r="E78" s="8" t="s">
-        <v>1849</v>
+        <v>1848</v>
       </c>
       <c r="F78" s="8"/>
     </row>
@@ -7546,14 +7549,14 @@
         <v>415</v>
       </c>
       <c r="B79" s="8" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C79" s="8"/>
       <c r="D79" s="8" t="s">
         <v>57</v>
       </c>
       <c r="E79" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F79" s="8"/>
     </row>
@@ -7562,14 +7565,14 @@
         <v>420</v>
       </c>
       <c r="B80" s="8" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C80" s="8"/>
       <c r="D80" s="8" t="s">
         <v>57</v>
       </c>
       <c r="E80" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F80" s="8"/>
     </row>
@@ -7578,7 +7581,7 @@
         <v>420</v>
       </c>
       <c r="B81" s="8" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="C81" s="8" t="s">
         <v>422</v>
@@ -7587,7 +7590,7 @@
         <v>77</v>
       </c>
       <c r="E81" s="8" t="s">
-        <v>1849</v>
+        <v>1848</v>
       </c>
       <c r="F81" s="8"/>
     </row>
@@ -7603,7 +7606,7 @@
         <v>76</v>
       </c>
       <c r="E82" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F82" s="8"/>
     </row>
@@ -7612,14 +7615,14 @@
         <v>428</v>
       </c>
       <c r="B83" s="8" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="C83" s="8"/>
       <c r="D83" s="8" t="s">
         <v>71</v>
       </c>
       <c r="E83" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F83" s="8"/>
     </row>
@@ -7635,7 +7638,7 @@
         <v>76</v>
       </c>
       <c r="E84" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F84" s="8"/>
     </row>
@@ -7644,14 +7647,14 @@
         <v>431</v>
       </c>
       <c r="B85" s="8" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="C85" s="8"/>
       <c r="D85" s="8" t="s">
         <v>77</v>
       </c>
       <c r="E85" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F85" s="8"/>
     </row>
@@ -7660,14 +7663,14 @@
         <v>436</v>
       </c>
       <c r="B86" s="8" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C86" s="8"/>
       <c r="D86" s="8" t="s">
         <v>47</v>
       </c>
       <c r="E86" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F86" s="8"/>
     </row>
@@ -7683,7 +7686,7 @@
         <v>44</v>
       </c>
       <c r="E87" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F87" s="8"/>
     </row>
@@ -7692,14 +7695,14 @@
         <v>445</v>
       </c>
       <c r="B88" s="8" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C88" s="8"/>
       <c r="D88" s="8" t="s">
         <v>57</v>
       </c>
       <c r="E88" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F88" s="8"/>
     </row>
@@ -7708,14 +7711,14 @@
         <v>445</v>
       </c>
       <c r="B89" s="8" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="C89" s="8"/>
       <c r="D89" s="8" t="s">
         <v>49</v>
       </c>
       <c r="E89" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F89" s="8"/>
     </row>
@@ -7731,7 +7734,7 @@
         <v>44</v>
       </c>
       <c r="E90" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F90" s="8"/>
     </row>
@@ -7747,7 +7750,7 @@
         <v>44</v>
       </c>
       <c r="E91" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F91" s="8"/>
     </row>
@@ -7756,14 +7759,14 @@
         <v>454</v>
       </c>
       <c r="B92" s="8" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C92" s="8"/>
       <c r="D92" s="8" t="s">
         <v>57</v>
       </c>
       <c r="E92" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F92" s="8"/>
     </row>
@@ -7779,7 +7782,7 @@
         <v>76</v>
       </c>
       <c r="E93" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F93" s="8"/>
     </row>
@@ -7788,7 +7791,7 @@
         <v>461</v>
       </c>
       <c r="B94" s="8" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="C94" s="8" t="s">
         <v>77</v>
@@ -7797,7 +7800,7 @@
         <v>149</v>
       </c>
       <c r="E94" s="8" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="F94" s="8"/>
     </row>
@@ -7806,7 +7809,7 @@
         <v>469</v>
       </c>
       <c r="B95" s="8" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="C95" s="8" t="s">
         <v>83</v>
@@ -7815,7 +7818,7 @@
         <v>77</v>
       </c>
       <c r="E95" s="8" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="F95" s="8"/>
     </row>
@@ -7831,7 +7834,7 @@
         <v>76</v>
       </c>
       <c r="E96" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F96" s="8"/>
     </row>
@@ -7840,14 +7843,14 @@
         <v>474</v>
       </c>
       <c r="B97" s="8" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="C97" s="8"/>
       <c r="D97" s="8" t="s">
         <v>149</v>
       </c>
       <c r="E97" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F97" s="8"/>
     </row>
@@ -7863,7 +7866,7 @@
         <v>44</v>
       </c>
       <c r="E98" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F98" s="8"/>
     </row>
@@ -7872,7 +7875,7 @@
         <v>481</v>
       </c>
       <c r="B99" s="8" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="C99" s="8" t="s">
         <v>58</v>
@@ -7881,7 +7884,7 @@
         <v>639</v>
       </c>
       <c r="E99" s="8" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="F99" s="8"/>
     </row>
@@ -7897,7 +7900,7 @@
         <v>44</v>
       </c>
       <c r="E100" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F100" s="8"/>
     </row>
@@ -7906,14 +7909,14 @@
         <v>485</v>
       </c>
       <c r="B101" s="8" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C101" s="8"/>
       <c r="D101" s="8" t="s">
         <v>57</v>
       </c>
       <c r="E101" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F101" s="8"/>
     </row>
@@ -7929,7 +7932,7 @@
         <v>44</v>
       </c>
       <c r="E102" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F102" s="8"/>
     </row>
@@ -7938,14 +7941,14 @@
         <v>494</v>
       </c>
       <c r="B103" s="8" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C103" s="8"/>
       <c r="D103" s="8" t="s">
         <v>57</v>
       </c>
       <c r="E103" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F103" s="8"/>
     </row>
@@ -7961,7 +7964,7 @@
         <v>44</v>
       </c>
       <c r="E104" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F104" s="8"/>
     </row>
@@ -7970,14 +7973,14 @@
         <v>497</v>
       </c>
       <c r="B105" s="8" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C105" s="8"/>
       <c r="D105" s="8" t="s">
         <v>47</v>
       </c>
       <c r="E105" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F105" s="8"/>
     </row>
@@ -7986,7 +7989,7 @@
         <v>497</v>
       </c>
       <c r="B106" s="8" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="C106" s="8" t="s">
         <v>91</v>
@@ -7995,7 +7998,7 @@
         <v>49</v>
       </c>
       <c r="E106" s="8" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="F106" s="8"/>
     </row>
@@ -8011,7 +8014,7 @@
         <v>245</v>
       </c>
       <c r="E107" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F107" s="8"/>
     </row>
@@ -8020,14 +8023,14 @@
         <v>501</v>
       </c>
       <c r="B108" s="8" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C108" s="8"/>
       <c r="D108" s="8" t="s">
         <v>47</v>
       </c>
       <c r="E108" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F108" s="8"/>
     </row>
@@ -8036,7 +8039,7 @@
         <v>503</v>
       </c>
       <c r="B109" s="8" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="C109" s="8" t="s">
         <v>72</v>
@@ -8045,7 +8048,7 @@
         <v>178</v>
       </c>
       <c r="E109" s="8" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="F109" s="8"/>
     </row>
@@ -8054,7 +8057,7 @@
         <v>508</v>
       </c>
       <c r="B110" s="8" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="C110" s="8" t="s">
         <v>96</v>
@@ -8063,7 +8066,7 @@
         <v>1137</v>
       </c>
       <c r="E110" s="8" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="F110" s="8"/>
     </row>
@@ -8072,7 +8075,7 @@
         <v>508</v>
       </c>
       <c r="B111" s="8" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="C111" s="8" t="s">
         <v>59</v>
@@ -8081,7 +8084,7 @@
         <v>91</v>
       </c>
       <c r="E111" s="8" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="F111" s="8"/>
     </row>
@@ -8090,14 +8093,14 @@
         <v>511</v>
       </c>
       <c r="B112" s="8" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C112" s="8"/>
       <c r="D112" s="8" t="s">
         <v>47</v>
       </c>
       <c r="E112" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F112" s="8"/>
     </row>
@@ -8113,7 +8116,7 @@
         <v>76</v>
       </c>
       <c r="E113" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F113" s="8"/>
     </row>
@@ -8122,17 +8125,17 @@
         <v>516</v>
       </c>
       <c r="B114" s="8" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C114" s="8"/>
       <c r="D114" s="8" t="s">
         <v>47</v>
       </c>
       <c r="E114" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F114" s="8" t="s">
-        <v>1850</v>
+        <v>1849</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
@@ -8140,7 +8143,7 @@
         <v>516</v>
       </c>
       <c r="B115" s="8" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="C115" s="8" t="s">
         <v>1156</v>
@@ -8149,7 +8152,7 @@
         <v>517</v>
       </c>
       <c r="E115" s="8" t="s">
-        <v>1849</v>
+        <v>1848</v>
       </c>
       <c r="F115" s="8"/>
     </row>
@@ -8165,7 +8168,7 @@
         <v>76</v>
       </c>
       <c r="E116" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F116" s="8"/>
     </row>
@@ -8174,14 +8177,14 @@
         <v>527</v>
       </c>
       <c r="B117" s="8" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="C117" s="8"/>
       <c r="D117" s="8" t="s">
         <v>78</v>
       </c>
       <c r="E117" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F117" s="8"/>
     </row>
@@ -8197,7 +8200,7 @@
         <v>44</v>
       </c>
       <c r="E118" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F118" s="8"/>
     </row>
@@ -8206,16 +8209,16 @@
         <v>533</v>
       </c>
       <c r="B119" s="8" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="C119" s="8" t="s">
         <v>58</v>
       </c>
       <c r="D119" s="8" t="s">
-        <v>1851</v>
+        <v>1850</v>
       </c>
       <c r="E119" s="8" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="F119" s="8"/>
     </row>
@@ -8224,16 +8227,16 @@
         <v>536</v>
       </c>
       <c r="B120" s="8" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="C120" s="8" t="s">
-        <v>1852</v>
+        <v>1851</v>
       </c>
       <c r="D120" s="8" t="s">
         <v>314</v>
       </c>
       <c r="E120" s="8" t="s">
-        <v>1849</v>
+        <v>1848</v>
       </c>
       <c r="F120" s="8"/>
     </row>
@@ -8242,7 +8245,7 @@
         <v>536</v>
       </c>
       <c r="B121" s="8" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="C121" s="8" t="s">
         <v>71</v>
@@ -8251,7 +8254,7 @@
         <v>91</v>
       </c>
       <c r="E121" s="8" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="F121" s="8"/>
     </row>
@@ -8260,14 +8263,14 @@
         <v>548</v>
       </c>
       <c r="B122" s="8" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C122" s="8"/>
       <c r="D122" s="8" t="s">
         <v>47</v>
       </c>
       <c r="E122" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F122" s="8"/>
     </row>
@@ -8276,14 +8279,14 @@
         <v>550</v>
       </c>
       <c r="B123" s="8" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C123" s="8"/>
       <c r="D123" s="8" t="s">
         <v>47</v>
       </c>
       <c r="E123" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F123" s="8"/>
     </row>
@@ -8299,7 +8302,7 @@
         <v>44</v>
       </c>
       <c r="E124" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F124" s="8"/>
     </row>
@@ -8308,14 +8311,14 @@
         <v>557</v>
       </c>
       <c r="B125" s="8" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C125" s="8"/>
       <c r="D125" s="8" t="s">
         <v>47</v>
       </c>
       <c r="E125" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F125" s="8"/>
     </row>
@@ -8324,7 +8327,7 @@
         <v>168</v>
       </c>
       <c r="B126" s="8" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="C126" s="8" t="s">
         <v>77</v>
@@ -8333,7 +8336,7 @@
         <v>596</v>
       </c>
       <c r="E126" s="8" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="F126" s="8"/>
     </row>
@@ -8349,7 +8352,7 @@
         <v>76</v>
       </c>
       <c r="E127" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F127" s="8"/>
     </row>
@@ -8358,14 +8361,14 @@
         <v>569</v>
       </c>
       <c r="B128" s="8" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="C128" s="8"/>
       <c r="D128" s="8" t="s">
         <v>72</v>
       </c>
       <c r="E128" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F128" s="8"/>
     </row>
@@ -8381,7 +8384,7 @@
         <v>245</v>
       </c>
       <c r="E129" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F129" s="8"/>
     </row>
@@ -8390,14 +8393,14 @@
         <v>566</v>
       </c>
       <c r="B130" s="8" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C130" s="8"/>
       <c r="D130" s="8" t="s">
         <v>57</v>
       </c>
       <c r="E130" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F130" s="8"/>
     </row>
@@ -8413,7 +8416,7 @@
         <v>245</v>
       </c>
       <c r="E131" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F131" s="8"/>
     </row>
@@ -8422,14 +8425,14 @@
         <v>578</v>
       </c>
       <c r="B132" s="8" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C132" s="8"/>
       <c r="D132" s="8" t="s">
         <v>47</v>
       </c>
       <c r="E132" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F132" s="8"/>
     </row>
@@ -8438,14 +8441,14 @@
         <v>586</v>
       </c>
       <c r="B133" s="8" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="C133" s="8"/>
       <c r="D133" s="8" t="s">
         <v>71</v>
       </c>
       <c r="E133" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F133" s="8"/>
     </row>
@@ -8461,7 +8464,7 @@
         <v>76</v>
       </c>
       <c r="E134" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F134" s="8"/>
     </row>
@@ -8470,7 +8473,7 @@
         <v>590</v>
       </c>
       <c r="B135" s="8" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="C135" s="8" t="s">
         <v>149</v>
@@ -8479,7 +8482,7 @@
         <v>77</v>
       </c>
       <c r="E135" s="8" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="F135" s="8"/>
     </row>
@@ -8488,14 +8491,14 @@
         <v>590</v>
       </c>
       <c r="B136" s="8" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="C136" s="8"/>
       <c r="D136" s="8" t="s">
         <v>71</v>
       </c>
       <c r="E136" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F136" s="8"/>
     </row>
@@ -8504,16 +8507,16 @@
         <v>594</v>
       </c>
       <c r="B137" s="8" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="C137" s="8" t="s">
-        <v>1853</v>
+        <v>1852</v>
       </c>
       <c r="D137" s="8" t="s">
         <v>596</v>
       </c>
       <c r="E137" s="8" t="s">
-        <v>1849</v>
+        <v>1848</v>
       </c>
       <c r="F137" s="8"/>
     </row>
@@ -8522,7 +8525,7 @@
         <v>607</v>
       </c>
       <c r="B138" s="8" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="C138" s="8" t="s">
         <v>613</v>
@@ -8531,7 +8534,7 @@
         <v>77</v>
       </c>
       <c r="E138" s="8" t="s">
-        <v>1849</v>
+        <v>1848</v>
       </c>
       <c r="F138" s="8"/>
     </row>
@@ -8540,7 +8543,7 @@
         <v>607</v>
       </c>
       <c r="B139" s="8" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="C139" s="8" t="s">
         <v>78</v>
@@ -8549,7 +8552,7 @@
         <v>192</v>
       </c>
       <c r="E139" s="8" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="F139" s="8"/>
     </row>
@@ -8565,7 +8568,7 @@
         <v>76</v>
       </c>
       <c r="E140" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F140" s="8"/>
     </row>
@@ -8574,7 +8577,7 @@
         <v>619</v>
       </c>
       <c r="B141" s="8" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="C141" s="8" t="s">
         <v>58</v>
@@ -8583,7 +8586,7 @@
         <v>77</v>
       </c>
       <c r="E141" s="8" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="F141" s="8"/>
     </row>
@@ -8592,7 +8595,7 @@
         <v>626</v>
       </c>
       <c r="B142" s="8" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="C142" s="8" t="s">
         <v>115</v>
@@ -8601,7 +8604,7 @@
         <v>77</v>
       </c>
       <c r="E142" s="8" t="s">
-        <v>1849</v>
+        <v>1848</v>
       </c>
       <c r="F142" s="8"/>
     </row>
@@ -8617,7 +8620,7 @@
         <v>44</v>
       </c>
       <c r="E143" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F143" s="8"/>
     </row>
@@ -8626,14 +8629,14 @@
         <v>634</v>
       </c>
       <c r="B144" s="8" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="C144" s="8"/>
       <c r="D144" s="8" t="s">
         <v>119</v>
       </c>
       <c r="E144" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F144" s="8"/>
     </row>
@@ -8649,7 +8652,7 @@
         <v>44</v>
       </c>
       <c r="E145" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F145" s="8"/>
     </row>
@@ -8665,7 +8668,7 @@
         <v>76</v>
       </c>
       <c r="E146" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F146" s="8"/>
     </row>
@@ -8681,7 +8684,7 @@
         <v>44</v>
       </c>
       <c r="E147" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F147" s="8"/>
     </row>
@@ -8697,7 +8700,7 @@
         <v>44</v>
       </c>
       <c r="E148" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F148" s="8"/>
     </row>
@@ -8713,7 +8716,7 @@
         <v>44</v>
       </c>
       <c r="E149" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F149" s="8"/>
     </row>
@@ -8722,14 +8725,14 @@
         <v>673</v>
       </c>
       <c r="B150" s="8" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="C150" s="8"/>
       <c r="D150" s="8" t="s">
         <v>59</v>
       </c>
       <c r="E150" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F150" s="8"/>
     </row>
@@ -8745,7 +8748,7 @@
         <v>76</v>
       </c>
       <c r="E151" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F151" s="8"/>
     </row>
@@ -8754,7 +8757,7 @@
         <v>680</v>
       </c>
       <c r="B152" s="8" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="C152" s="8" t="s">
         <v>83</v>
@@ -8763,7 +8766,7 @@
         <v>77</v>
       </c>
       <c r="E152" s="8" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="F152" s="8"/>
     </row>
@@ -8779,7 +8782,7 @@
         <v>76</v>
       </c>
       <c r="E153" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F153" s="8"/>
     </row>
@@ -8788,14 +8791,14 @@
         <v>683</v>
       </c>
       <c r="B154" s="8" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="C154" s="8"/>
       <c r="D154" s="8" t="s">
         <v>119</v>
       </c>
       <c r="E154" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F154" s="8"/>
     </row>
@@ -8813,10 +8816,10 @@
         <v>44</v>
       </c>
       <c r="E155" s="8" t="s">
+        <v>1853</v>
+      </c>
+      <c r="F155" s="8" t="s">
         <v>1854</v>
-      </c>
-      <c r="F155" s="8" t="s">
-        <v>1855</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
@@ -8824,7 +8827,7 @@
         <v>689</v>
       </c>
       <c r="B156" s="8" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="C156" s="8" t="s">
         <v>695</v>
@@ -8833,7 +8836,7 @@
         <v>83</v>
       </c>
       <c r="E156" s="8" t="s">
-        <v>1849</v>
+        <v>1848</v>
       </c>
       <c r="F156" s="8"/>
     </row>
@@ -8849,7 +8852,7 @@
         <v>76</v>
       </c>
       <c r="E157" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F157" s="8"/>
     </row>
@@ -8858,7 +8861,7 @@
         <v>699</v>
       </c>
       <c r="B158" s="8" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="C158" s="8" t="s">
         <v>700</v>
@@ -8867,7 +8870,7 @@
         <v>323</v>
       </c>
       <c r="E158" s="8" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="F158" s="8"/>
     </row>
@@ -8883,7 +8886,7 @@
         <v>76</v>
       </c>
       <c r="E159" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F159" s="8"/>
     </row>
@@ -8892,14 +8895,14 @@
         <v>703</v>
       </c>
       <c r="B160" s="8" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="C160" s="8"/>
       <c r="D160" s="8" t="s">
         <v>49</v>
       </c>
       <c r="E160" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F160" s="8"/>
     </row>
@@ -8908,14 +8911,14 @@
         <v>712</v>
       </c>
       <c r="B161" s="8" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="C161" s="8"/>
       <c r="D161" s="8" t="s">
         <v>517</v>
       </c>
       <c r="E161" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F161" s="8"/>
     </row>
@@ -8931,7 +8934,7 @@
         <v>44</v>
       </c>
       <c r="E162" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F162" s="8"/>
     </row>
@@ -8940,17 +8943,17 @@
         <v>705</v>
       </c>
       <c r="B163" s="8" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C163" s="8"/>
       <c r="D163" s="8" t="s">
         <v>47</v>
       </c>
       <c r="E163" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F163" s="8" t="s">
-        <v>1850</v>
+        <v>1849</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
@@ -8958,14 +8961,14 @@
         <v>689</v>
       </c>
       <c r="B164" s="8" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C164" s="8"/>
       <c r="D164" s="8" t="s">
         <v>57</v>
       </c>
       <c r="E164" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F164" s="8"/>
     </row>
@@ -8974,7 +8977,7 @@
         <v>689</v>
       </c>
       <c r="B165" s="8" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="C165" s="8" t="s">
         <v>83</v>
@@ -8983,7 +8986,7 @@
         <v>272</v>
       </c>
       <c r="E165" s="8" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="F165" s="8"/>
     </row>
@@ -8999,7 +9002,7 @@
         <v>76</v>
       </c>
       <c r="E166" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F166" s="8"/>
     </row>
@@ -9008,14 +9011,14 @@
         <v>725</v>
       </c>
       <c r="B167" s="8" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="C167" s="8"/>
       <c r="D167" s="8" t="s">
         <v>119</v>
       </c>
       <c r="E167" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F167" s="8"/>
     </row>
@@ -9031,7 +9034,7 @@
         <v>44</v>
       </c>
       <c r="E168" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F168" s="8"/>
     </row>
@@ -9040,16 +9043,16 @@
         <v>729</v>
       </c>
       <c r="B169" s="8" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="C169" s="8" t="s">
         <v>58</v>
       </c>
       <c r="D169" s="8" t="s">
-        <v>1856</v>
+        <v>1855</v>
       </c>
       <c r="E169" s="8" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="F169" s="8"/>
     </row>
@@ -9058,14 +9061,14 @@
         <v>729</v>
       </c>
       <c r="B170" s="8" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="C170" s="8"/>
       <c r="D170" s="8" t="s">
         <v>133</v>
       </c>
       <c r="E170" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F170" s="8"/>
     </row>
@@ -9081,7 +9084,7 @@
         <v>76</v>
       </c>
       <c r="E171" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F171" s="8"/>
     </row>
@@ -9090,14 +9093,14 @@
         <v>741</v>
       </c>
       <c r="B172" s="8" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="C172" s="8"/>
       <c r="D172" s="8" t="s">
         <v>77</v>
       </c>
       <c r="E172" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F172" s="8"/>
     </row>
@@ -9106,7 +9109,7 @@
         <v>742</v>
       </c>
       <c r="B173" s="8" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="C173" s="8" t="s">
         <v>72</v>
@@ -9115,7 +9118,7 @@
         <v>78</v>
       </c>
       <c r="E173" s="8" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="F173" s="8"/>
     </row>
@@ -9131,7 +9134,7 @@
         <v>44</v>
       </c>
       <c r="E174" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F174" s="8"/>
     </row>
@@ -9140,14 +9143,14 @@
         <v>745</v>
       </c>
       <c r="B175" s="8" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C175" s="8"/>
       <c r="D175" s="8" t="s">
         <v>57</v>
       </c>
       <c r="E175" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F175" s="8"/>
     </row>
@@ -9163,7 +9166,7 @@
         <v>76</v>
       </c>
       <c r="E176" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F176" s="8"/>
     </row>
@@ -9172,7 +9175,7 @@
         <v>751</v>
       </c>
       <c r="B177" s="8" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="C177" s="8" t="s">
         <v>752</v>
@@ -9181,7 +9184,7 @@
         <v>333</v>
       </c>
       <c r="E177" s="8" t="s">
-        <v>1849</v>
+        <v>1848</v>
       </c>
       <c r="F177" s="8"/>
     </row>
@@ -9190,14 +9193,14 @@
         <v>751</v>
       </c>
       <c r="B178" s="8" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="C178" s="8"/>
       <c r="D178" s="8" t="s">
         <v>72</v>
       </c>
       <c r="E178" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F178" s="8"/>
     </row>
@@ -9213,7 +9216,7 @@
         <v>44</v>
       </c>
       <c r="E179" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F179" s="8"/>
     </row>
@@ -9222,14 +9225,14 @@
         <v>758</v>
       </c>
       <c r="B180" s="8" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="C180" s="8"/>
       <c r="D180" s="8" t="s">
         <v>71</v>
       </c>
       <c r="E180" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F180" s="8"/>
     </row>
@@ -9245,7 +9248,7 @@
         <v>245</v>
       </c>
       <c r="E181" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F181" s="8"/>
     </row>
@@ -9254,14 +9257,14 @@
         <v>760</v>
       </c>
       <c r="B182" s="8" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C182" s="8"/>
       <c r="D182" s="8" t="s">
         <v>47</v>
       </c>
       <c r="E182" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F182" s="8"/>
     </row>
@@ -9277,10 +9280,10 @@
         <v>76</v>
       </c>
       <c r="E183" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F183" s="8" t="s">
-        <v>1855</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
@@ -9288,7 +9291,7 @@
         <v>762</v>
       </c>
       <c r="B184" s="8" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="C184" s="8" t="s">
         <v>767</v>
@@ -9297,7 +9300,7 @@
         <v>58</v>
       </c>
       <c r="E184" s="8" t="s">
-        <v>1849</v>
+        <v>1848</v>
       </c>
       <c r="F184" s="8"/>
     </row>
@@ -9306,7 +9309,7 @@
         <v>769</v>
       </c>
       <c r="B185" s="8" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="C185" s="8" t="s">
         <v>775</v>
@@ -9315,7 +9318,7 @@
         <v>83</v>
       </c>
       <c r="E185" s="8" t="s">
-        <v>1849</v>
+        <v>1848</v>
       </c>
       <c r="F185" s="8"/>
     </row>
@@ -9324,7 +9327,7 @@
         <v>769</v>
       </c>
       <c r="B186" s="8" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="C186" s="8" t="s">
         <v>72</v>
@@ -9333,7 +9336,7 @@
         <v>71</v>
       </c>
       <c r="E186" s="8" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="F186" s="8"/>
     </row>
@@ -9349,7 +9352,7 @@
         <v>76</v>
       </c>
       <c r="E187" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F187" s="8"/>
     </row>
@@ -9365,7 +9368,7 @@
         <v>76</v>
       </c>
       <c r="E188" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F188" s="8"/>
     </row>
@@ -9374,14 +9377,14 @@
         <v>779</v>
       </c>
       <c r="B189" s="8" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="C189" s="8"/>
       <c r="D189" s="8" t="s">
         <v>91</v>
       </c>
       <c r="E189" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F189" s="8"/>
     </row>
@@ -9390,14 +9393,14 @@
         <v>793</v>
       </c>
       <c r="B190" s="8" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C190" s="8"/>
       <c r="D190" s="8" t="s">
         <v>47</v>
       </c>
       <c r="E190" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F190" s="8"/>
     </row>
@@ -9413,7 +9416,7 @@
         <v>76</v>
       </c>
       <c r="E191" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F191" s="8"/>
     </row>
@@ -9422,16 +9425,16 @@
         <v>798</v>
       </c>
       <c r="B192" s="8" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="C192" s="8" t="s">
         <v>664</v>
       </c>
       <c r="D192" s="8" t="s">
-        <v>1857</v>
+        <v>1856</v>
       </c>
       <c r="E192" s="8" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="F192" s="8"/>
     </row>
@@ -9440,14 +9443,14 @@
         <v>798</v>
       </c>
       <c r="B193" s="8" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="C193" s="8"/>
       <c r="D193" s="8" t="s">
         <v>119</v>
       </c>
       <c r="E193" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F193" s="8"/>
     </row>
@@ -9463,7 +9466,7 @@
         <v>44</v>
       </c>
       <c r="E194" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F194" s="8"/>
     </row>
@@ -9472,7 +9475,7 @@
         <v>814</v>
       </c>
       <c r="B195" s="8" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="C195" s="8" t="s">
         <v>752</v>
@@ -9481,7 +9484,7 @@
         <v>333</v>
       </c>
       <c r="E195" s="8" t="s">
-        <v>1849</v>
+        <v>1848</v>
       </c>
       <c r="F195" s="8"/>
     </row>
@@ -9497,7 +9500,7 @@
         <v>76</v>
       </c>
       <c r="E196" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F196" s="8"/>
     </row>
@@ -9506,14 +9509,14 @@
         <v>823</v>
       </c>
       <c r="B197" s="8" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="C197" s="8"/>
       <c r="D197" s="8" t="s">
         <v>149</v>
       </c>
       <c r="E197" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F197" s="8"/>
     </row>
@@ -9529,7 +9532,7 @@
         <v>76</v>
       </c>
       <c r="E198" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F198" s="8"/>
     </row>
@@ -9538,14 +9541,14 @@
         <v>1179</v>
       </c>
       <c r="B199" s="8" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C199" s="8"/>
       <c r="D199" s="8" t="s">
         <v>57</v>
       </c>
       <c r="E199" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F199" s="8"/>
     </row>
@@ -9554,14 +9557,14 @@
         <v>828</v>
       </c>
       <c r="B200" s="8" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C200" s="8"/>
       <c r="D200" s="8" t="s">
         <v>47</v>
       </c>
       <c r="E200" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F200" s="8"/>
     </row>
@@ -9570,7 +9573,7 @@
         <v>829</v>
       </c>
       <c r="B201" s="8" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="C201" s="8" t="s">
         <v>72</v>
@@ -9579,7 +9582,7 @@
         <v>133</v>
       </c>
       <c r="E201" s="8" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="F201" s="8"/>
     </row>
@@ -9595,7 +9598,7 @@
         <v>44</v>
       </c>
       <c r="E202" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F202" s="8"/>
     </row>
@@ -9611,7 +9614,7 @@
         <v>76</v>
       </c>
       <c r="E203" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F203" s="8"/>
     </row>
@@ -9620,14 +9623,14 @@
         <v>848</v>
       </c>
       <c r="B204" s="8" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C204" s="8"/>
       <c r="D204" s="8" t="s">
         <v>47</v>
       </c>
       <c r="E204" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F204" s="8"/>
     </row>
@@ -9643,7 +9646,7 @@
         <v>44</v>
       </c>
       <c r="E205" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F205" s="8"/>
     </row>
@@ -9659,10 +9662,10 @@
         <v>44</v>
       </c>
       <c r="E206" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F206" s="8" t="s">
-        <v>1855</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
@@ -9670,7 +9673,7 @@
         <v>1320</v>
       </c>
       <c r="B207" s="8" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="C207" s="8" t="s">
         <v>272</v>
@@ -9679,7 +9682,7 @@
         <v>702</v>
       </c>
       <c r="E207" s="8" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="F207" s="8"/>
     </row>
@@ -9688,16 +9691,16 @@
         <v>851</v>
       </c>
       <c r="B208" s="8" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="C208" s="8" t="s">
-        <v>1858</v>
+        <v>1857</v>
       </c>
       <c r="D208" s="8" t="s">
         <v>314</v>
       </c>
       <c r="E208" s="8" t="s">
-        <v>1849</v>
+        <v>1848</v>
       </c>
       <c r="F208" s="8"/>
     </row>
@@ -9706,7 +9709,7 @@
         <v>851</v>
       </c>
       <c r="B209" s="8" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="C209" s="8" t="s">
         <v>178</v>
@@ -9715,7 +9718,7 @@
         <v>72</v>
       </c>
       <c r="E209" s="8" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="F209" s="8"/>
     </row>
@@ -9731,7 +9734,7 @@
         <v>44</v>
       </c>
       <c r="E210" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F210" s="8"/>
     </row>
@@ -9740,14 +9743,14 @@
         <v>857</v>
       </c>
       <c r="B211" s="8" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C211" s="8"/>
       <c r="D211" s="8" t="s">
         <v>57</v>
       </c>
       <c r="E211" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F211" s="8"/>
     </row>
@@ -9763,7 +9766,7 @@
         <v>76</v>
       </c>
       <c r="E212" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F212" s="8"/>
     </row>
@@ -9779,7 +9782,7 @@
         <v>76</v>
       </c>
       <c r="E213" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F213" s="8"/>
     </row>
@@ -9795,7 +9798,7 @@
         <v>332</v>
       </c>
       <c r="E214" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F214" s="8"/>
     </row>
@@ -9811,7 +9814,7 @@
         <v>44</v>
       </c>
       <c r="E215" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F215" s="8"/>
     </row>
@@ -9820,7 +9823,7 @@
         <v>876</v>
       </c>
       <c r="B216" s="8" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="C216" s="8" t="s">
         <v>881</v>
@@ -9829,7 +9832,7 @@
         <v>272</v>
       </c>
       <c r="E216" s="8" t="s">
-        <v>1849</v>
+        <v>1848</v>
       </c>
       <c r="F216" s="8"/>
     </row>
@@ -9845,7 +9848,7 @@
         <v>44</v>
       </c>
       <c r="E217" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F217" s="8"/>
     </row>
@@ -9854,14 +9857,14 @@
         <v>886</v>
       </c>
       <c r="B218" s="8" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C218" s="8"/>
       <c r="D218" s="8" t="s">
         <v>57</v>
       </c>
       <c r="E218" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F218" s="8"/>
     </row>
@@ -9877,7 +9880,7 @@
         <v>76</v>
       </c>
       <c r="E219" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F219" s="8"/>
     </row>
@@ -9893,7 +9896,7 @@
         <v>76</v>
       </c>
       <c r="E220" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F220" s="8"/>
     </row>
@@ -9902,14 +9905,14 @@
         <v>893</v>
       </c>
       <c r="B221" s="8" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C221" s="8"/>
       <c r="D221" s="8" t="s">
         <v>57</v>
       </c>
       <c r="E221" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F221" s="8"/>
     </row>
@@ -9918,14 +9921,14 @@
         <v>1439</v>
       </c>
       <c r="B222" s="8" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C222" s="8"/>
       <c r="D222" s="8" t="s">
         <v>57</v>
       </c>
       <c r="E222" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F222" s="8"/>
     </row>
@@ -9941,7 +9944,7 @@
         <v>44</v>
       </c>
       <c r="E223" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F223" s="8"/>
     </row>
@@ -9950,14 +9953,14 @@
         <v>901</v>
       </c>
       <c r="B224" s="8" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="C224" s="8"/>
       <c r="D224" s="8" t="s">
         <v>119</v>
       </c>
       <c r="E224" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F224" s="8"/>
     </row>
@@ -9966,17 +9969,17 @@
         <v>895</v>
       </c>
       <c r="B225" s="8" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C225" s="8"/>
       <c r="D225" s="8" t="s">
         <v>47</v>
       </c>
       <c r="E225" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F225" s="8" t="s">
-        <v>1850</v>
+        <v>1849</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
@@ -9984,7 +9987,7 @@
         <v>895</v>
       </c>
       <c r="B226" s="8" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="C226" s="8" t="s">
         <v>49</v>
@@ -9993,7 +9996,7 @@
         <v>119</v>
       </c>
       <c r="E226" s="8" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="F226" s="8"/>
     </row>
@@ -10002,14 +10005,14 @@
         <v>905</v>
       </c>
       <c r="B227" s="8" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="C227" s="8"/>
       <c r="D227" s="8" t="s">
         <v>123</v>
       </c>
       <c r="E227" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F227" s="8"/>
     </row>
@@ -10018,14 +10021,14 @@
         <v>1013</v>
       </c>
       <c r="B228" s="8" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C228" s="8"/>
       <c r="D228" s="8" t="s">
         <v>47</v>
       </c>
       <c r="E228" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F228" s="8"/>
     </row>
@@ -10041,7 +10044,7 @@
         <v>76</v>
       </c>
       <c r="E229" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F229" s="8"/>
     </row>
@@ -10057,7 +10060,7 @@
         <v>44</v>
       </c>
       <c r="E230" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F230" s="8"/>
     </row>
@@ -10066,14 +10069,14 @@
         <v>925</v>
       </c>
       <c r="B231" s="8" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="C231" s="8"/>
       <c r="D231" s="8" t="s">
         <v>91</v>
       </c>
       <c r="E231" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F231" s="8"/>
     </row>
@@ -10082,14 +10085,14 @@
         <v>929</v>
       </c>
       <c r="B232" s="8" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C232" s="8"/>
       <c r="D232" s="8" t="s">
         <v>47</v>
       </c>
       <c r="E232" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F232" s="8"/>
     </row>
@@ -10098,14 +10101,14 @@
         <v>929</v>
       </c>
       <c r="B233" s="8" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="C233" s="8"/>
       <c r="D233" s="8" t="s">
         <v>91</v>
       </c>
       <c r="E233" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F233" s="8"/>
     </row>
@@ -10121,10 +10124,10 @@
         <v>76</v>
       </c>
       <c r="E234" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F234" s="8" t="s">
-        <v>1855</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.25">
@@ -10132,14 +10135,14 @@
         <v>934</v>
       </c>
       <c r="B235" s="8" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C235" s="8"/>
       <c r="D235" s="8" t="s">
         <v>57</v>
       </c>
       <c r="E235" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F235" s="8"/>
     </row>
@@ -10148,7 +10151,7 @@
         <v>934</v>
       </c>
       <c r="B236" s="8" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="C236" s="8" t="s">
         <v>58</v>
@@ -10157,7 +10160,7 @@
         <v>272</v>
       </c>
       <c r="E236" s="8" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="F236" s="8"/>
     </row>
@@ -10166,7 +10169,7 @@
         <v>950</v>
       </c>
       <c r="B237" s="8" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="C237" s="8" t="s">
         <v>72</v>
@@ -10175,7 +10178,7 @@
         <v>78</v>
       </c>
       <c r="E237" s="8" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="F237" s="8"/>
     </row>
@@ -10191,7 +10194,7 @@
         <v>76</v>
       </c>
       <c r="E238" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F238" s="8"/>
     </row>
@@ -10200,14 +10203,14 @@
         <v>956</v>
       </c>
       <c r="B239" s="8" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="C239" s="8"/>
       <c r="D239" s="8" t="s">
         <v>192</v>
       </c>
       <c r="E239" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F239" s="8"/>
     </row>
@@ -10216,14 +10219,14 @@
         <v>965</v>
       </c>
       <c r="B240" s="8" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C240" s="8"/>
       <c r="D240" s="8" t="s">
         <v>47</v>
       </c>
       <c r="E240" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F240" s="8"/>
     </row>
@@ -10239,7 +10242,7 @@
         <v>76</v>
       </c>
       <c r="E241" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F241" s="8"/>
     </row>
@@ -10255,7 +10258,7 @@
         <v>76</v>
       </c>
       <c r="E242" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F242" s="8"/>
     </row>
@@ -10271,7 +10274,7 @@
         <v>44</v>
       </c>
       <c r="E243" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F243" s="8"/>
     </row>
@@ -10280,16 +10283,16 @@
         <v>977</v>
       </c>
       <c r="B244" s="8" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="C244" s="8" t="s">
         <v>96</v>
       </c>
       <c r="D244" s="8" t="s">
-        <v>1859</v>
+        <v>1858</v>
       </c>
       <c r="E244" s="8" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="F244" s="8"/>
     </row>
@@ -10298,14 +10301,14 @@
         <v>977</v>
       </c>
       <c r="B245" s="8" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="C245" s="8"/>
       <c r="D245" s="8" t="s">
         <v>91</v>
       </c>
       <c r="E245" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F245" s="8"/>
     </row>
@@ -10314,14 +10317,14 @@
         <v>981</v>
       </c>
       <c r="B246" s="8" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="C246" s="8"/>
       <c r="D246" s="8" t="s">
         <v>192</v>
       </c>
       <c r="E246" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F246" s="8"/>
     </row>
@@ -10337,7 +10340,7 @@
         <v>44</v>
       </c>
       <c r="E247" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F247" s="8"/>
     </row>
@@ -10346,14 +10349,14 @@
         <v>983</v>
       </c>
       <c r="B248" s="8" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C248" s="8"/>
       <c r="D248" s="8" t="s">
         <v>47</v>
       </c>
       <c r="E248" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F248" s="8"/>
     </row>
@@ -10369,7 +10372,7 @@
         <v>44</v>
       </c>
       <c r="E249" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F249" s="8"/>
     </row>
@@ -10378,14 +10381,14 @@
         <v>985</v>
       </c>
       <c r="B250" s="8" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C250" s="8"/>
       <c r="D250" s="8" t="s">
         <v>57</v>
       </c>
       <c r="E250" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F250" s="8"/>
     </row>
@@ -10394,7 +10397,7 @@
         <v>989</v>
       </c>
       <c r="B251" s="8" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="C251" s="8" t="s">
         <v>119</v>
@@ -10403,7 +10406,7 @@
         <v>71</v>
       </c>
       <c r="E251" s="8" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="F251" s="8"/>
     </row>
@@ -10419,7 +10422,7 @@
         <v>76</v>
       </c>
       <c r="E252" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F252" s="8"/>
     </row>
@@ -10428,7 +10431,7 @@
         <v>994</v>
       </c>
       <c r="B253" s="8" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="C253" s="8" t="s">
         <v>998</v>
@@ -10437,7 +10440,7 @@
         <v>323</v>
       </c>
       <c r="E253" s="8" t="s">
-        <v>1849</v>
+        <v>1848</v>
       </c>
       <c r="F253" s="8"/>
     </row>
@@ -10446,14 +10449,14 @@
         <v>994</v>
       </c>
       <c r="B254" s="8" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="C254" s="8"/>
       <c r="D254" s="8" t="s">
         <v>71</v>
       </c>
       <c r="E254" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F254" s="8"/>
     </row>
@@ -10469,7 +10472,7 @@
         <v>44</v>
       </c>
       <c r="E255" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F255" s="8"/>
     </row>
@@ -10478,16 +10481,16 @@
         <v>1002</v>
       </c>
       <c r="B256" s="8" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="C256" s="8" t="s">
         <v>58</v>
       </c>
       <c r="D256" s="8" t="s">
-        <v>1860</v>
+        <v>1859</v>
       </c>
       <c r="E256" s="8" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="F256" s="8"/>
     </row>
@@ -10496,14 +10499,14 @@
         <v>1002</v>
       </c>
       <c r="B257" s="8" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="C257" s="8"/>
       <c r="D257" s="8" t="s">
         <v>123</v>
       </c>
       <c r="E257" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F257" s="8"/>
     </row>
@@ -10512,7 +10515,7 @@
         <v>1004</v>
       </c>
       <c r="B258" s="8" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="C258" s="8" t="s">
         <v>422</v>
@@ -10521,7 +10524,7 @@
         <v>77</v>
       </c>
       <c r="E258" s="8" t="s">
-        <v>1849</v>
+        <v>1848</v>
       </c>
       <c r="F258" s="8"/>
     </row>
@@ -10530,7 +10533,7 @@
         <v>1004</v>
       </c>
       <c r="B259" s="8" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="C259" s="8" t="s">
         <v>59</v>
@@ -10539,7 +10542,7 @@
         <v>119</v>
       </c>
       <c r="E259" s="8" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="F259" s="8"/>
     </row>
@@ -10555,7 +10558,7 @@
         <v>76</v>
       </c>
       <c r="E260" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F260" s="8"/>
     </row>
@@ -10564,7 +10567,7 @@
         <v>1007</v>
       </c>
       <c r="B261" s="8" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="C261" s="8" t="s">
         <v>77</v>
@@ -10573,7 +10576,7 @@
         <v>83</v>
       </c>
       <c r="E261" s="8" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="F261" s="8"/>
     </row>
@@ -10589,7 +10592,7 @@
         <v>76</v>
       </c>
       <c r="E262" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F262" s="8"/>
     </row>
@@ -10598,14 +10601,14 @@
         <v>1009</v>
       </c>
       <c r="B263" s="8" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="C263" s="8"/>
       <c r="D263" s="8" t="s">
         <v>49</v>
       </c>
       <c r="E263" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F263" s="8"/>
     </row>
@@ -10621,7 +10624,7 @@
         <v>76</v>
       </c>
       <c r="E264" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F264" s="8"/>
     </row>
@@ -10630,7 +10633,7 @@
         <v>1016</v>
       </c>
       <c r="B265" s="8" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="C265" s="8" t="s">
         <v>58</v>
@@ -10639,7 +10642,7 @@
         <v>77</v>
       </c>
       <c r="E265" s="8" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="F265" s="8"/>
     </row>
@@ -10648,14 +10651,14 @@
         <v>1016</v>
       </c>
       <c r="B266" s="8" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="C266" s="8"/>
       <c r="D266" s="8" t="s">
         <v>91</v>
       </c>
       <c r="E266" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F266" s="8"/>
     </row>
@@ -10671,7 +10674,7 @@
         <v>44</v>
       </c>
       <c r="E267" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F267" s="8"/>
     </row>
@@ -10680,14 +10683,14 @@
         <v>1019</v>
       </c>
       <c r="B268" s="8" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C268" s="8"/>
       <c r="D268" s="8" t="s">
         <v>47</v>
       </c>
       <c r="E268" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F268" s="8"/>
     </row>
@@ -10696,14 +10699,14 @@
         <v>1019</v>
       </c>
       <c r="B269" s="8" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="C269" s="8"/>
       <c r="D269" s="8" t="s">
         <v>119</v>
       </c>
       <c r="E269" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F269" s="8"/>
     </row>
@@ -10719,7 +10722,7 @@
         <v>76</v>
       </c>
       <c r="E270" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F270" s="8"/>
     </row>
@@ -10728,14 +10731,14 @@
         <v>1025</v>
       </c>
       <c r="B271" s="8" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C271" s="8"/>
       <c r="D271" s="8" t="s">
         <v>57</v>
       </c>
       <c r="E271" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F271" s="8"/>
     </row>
@@ -10744,7 +10747,7 @@
         <v>1025</v>
       </c>
       <c r="B272" s="8" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="C272" s="8" t="s">
         <v>700</v>
@@ -10753,7 +10756,7 @@
         <v>58</v>
       </c>
       <c r="E272" s="8" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="F272" s="8"/>
     </row>
@@ -10762,14 +10765,14 @@
         <v>1025</v>
       </c>
       <c r="B273" s="8" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="C273" s="8"/>
       <c r="D273" s="8" t="s">
         <v>119</v>
       </c>
       <c r="E273" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F273" s="8"/>
     </row>
@@ -10785,7 +10788,7 @@
         <v>44</v>
       </c>
       <c r="E274" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F274" s="8"/>
     </row>
@@ -10794,7 +10797,7 @@
         <v>1033</v>
       </c>
       <c r="B275" s="8" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="C275" s="8" t="s">
         <v>119</v>
@@ -10803,7 +10806,7 @@
         <v>91</v>
       </c>
       <c r="E275" s="8" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="F275" s="8"/>
     </row>
@@ -10819,7 +10822,7 @@
         <v>44</v>
       </c>
       <c r="E276" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F276" s="8"/>
     </row>
@@ -10828,14 +10831,14 @@
         <v>1045</v>
       </c>
       <c r="B277" s="8" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C277" s="8"/>
       <c r="D277" s="8" t="s">
         <v>57</v>
       </c>
       <c r="E277" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F277" s="8"/>
     </row>
@@ -10851,7 +10854,7 @@
         <v>44</v>
       </c>
       <c r="E278" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F278" s="8"/>
     </row>
@@ -10860,14 +10863,14 @@
         <v>1049</v>
       </c>
       <c r="B279" s="8" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C279" s="8"/>
       <c r="D279" s="8" t="s">
         <v>47</v>
       </c>
       <c r="E279" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F279" s="8"/>
     </row>
@@ -10876,14 +10879,14 @@
         <v>1049</v>
       </c>
       <c r="B280" s="8" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="C280" s="8"/>
       <c r="D280" s="8" t="s">
         <v>59</v>
       </c>
       <c r="E280" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F280" s="8"/>
     </row>
@@ -10899,7 +10902,7 @@
         <v>332</v>
       </c>
       <c r="E281" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F281" s="8"/>
     </row>
@@ -10908,14 +10911,14 @@
         <v>1056</v>
       </c>
       <c r="B282" s="8" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C282" s="8"/>
       <c r="D282" s="8" t="s">
         <v>47</v>
       </c>
       <c r="E282" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F282" s="8"/>
     </row>
@@ -10924,14 +10927,14 @@
         <v>1065</v>
       </c>
       <c r="B283" s="8" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C283" s="8"/>
       <c r="D283" s="8" t="s">
         <v>47</v>
       </c>
       <c r="E283" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F283" s="8"/>
     </row>
@@ -10940,14 +10943,14 @@
         <v>1065</v>
       </c>
       <c r="B284" s="8" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="C284" s="8"/>
       <c r="D284" s="8" t="s">
         <v>91</v>
       </c>
       <c r="E284" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F284" s="8"/>
     </row>
@@ -10963,7 +10966,7 @@
         <v>44</v>
       </c>
       <c r="E285" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F285" s="8"/>
     </row>
@@ -10972,14 +10975,14 @@
         <v>439</v>
       </c>
       <c r="B286" s="8" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="C286" s="8"/>
       <c r="D286" s="8" t="s">
         <v>91</v>
       </c>
       <c r="E286" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F286" s="8"/>
     </row>
@@ -10995,7 +10998,7 @@
         <v>76</v>
       </c>
       <c r="E287" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F287" s="8"/>
     </row>
@@ -11011,7 +11014,7 @@
         <v>76</v>
       </c>
       <c r="E288" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F288" s="8"/>
     </row>
@@ -11020,7 +11023,7 @@
         <v>1076</v>
       </c>
       <c r="B289" s="8" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="C289" s="8" t="s">
         <v>58</v>
@@ -11029,7 +11032,7 @@
         <v>333</v>
       </c>
       <c r="E289" s="8" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="F289" s="8"/>
     </row>
@@ -11045,7 +11048,7 @@
         <v>44</v>
       </c>
       <c r="E290" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F290" s="8"/>
     </row>
@@ -11054,7 +11057,7 @@
         <v>1080</v>
       </c>
       <c r="B291" s="8" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="C291" s="8" t="s">
         <v>96</v>
@@ -11063,7 +11066,7 @@
         <v>1137</v>
       </c>
       <c r="E291" s="8" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="F291" s="8"/>
     </row>
@@ -11072,14 +11075,14 @@
         <v>1080</v>
       </c>
       <c r="B292" s="8" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="C292" s="8"/>
       <c r="D292" s="8" t="s">
         <v>59</v>
       </c>
       <c r="E292" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F292" s="8"/>
     </row>
@@ -11088,14 +11091,14 @@
         <v>1084</v>
       </c>
       <c r="B293" s="8" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C293" s="8"/>
       <c r="D293" s="8" t="s">
         <v>47</v>
       </c>
       <c r="E293" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F293" s="8"/>
     </row>
@@ -11104,7 +11107,7 @@
         <v>1084</v>
       </c>
       <c r="B294" s="8" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="C294" s="8" t="s">
         <v>193</v>
@@ -11113,7 +11116,7 @@
         <v>59</v>
       </c>
       <c r="E294" s="8" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="F294" s="8"/>
     </row>
@@ -11122,7 +11125,7 @@
         <v>1092</v>
       </c>
       <c r="B295" s="8" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="C295" s="8" t="s">
         <v>422</v>
@@ -11131,7 +11134,7 @@
         <v>77</v>
       </c>
       <c r="E295" s="8" t="s">
-        <v>1849</v>
+        <v>1848</v>
       </c>
       <c r="F295" s="8"/>
     </row>
@@ -11147,10 +11150,10 @@
         <v>76</v>
       </c>
       <c r="E296" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F296" s="8" t="s">
-        <v>1855</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.25">
@@ -11165,7 +11168,7 @@
         <v>44</v>
       </c>
       <c r="E297" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F297" s="8"/>
     </row>
@@ -11174,14 +11177,14 @@
         <v>1115</v>
       </c>
       <c r="B298" s="8" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C298" s="8"/>
       <c r="D298" s="8" t="s">
         <v>57</v>
       </c>
       <c r="E298" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F298" s="8"/>
     </row>
@@ -11197,7 +11200,7 @@
         <v>76</v>
       </c>
       <c r="E299" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F299" s="8"/>
     </row>
@@ -11206,14 +11209,14 @@
         <v>1119</v>
       </c>
       <c r="B300" s="8" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="C300" s="8"/>
       <c r="D300" s="8" t="s">
         <v>71</v>
       </c>
       <c r="E300" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F300" s="8"/>
     </row>
@@ -11229,7 +11232,7 @@
         <v>332</v>
       </c>
       <c r="E301" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F301" s="8"/>
     </row>
@@ -11245,7 +11248,7 @@
         <v>44</v>
       </c>
       <c r="E302" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F302" s="8"/>
     </row>
@@ -11254,14 +11257,14 @@
         <v>1127</v>
       </c>
       <c r="B303" s="8" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C303" s="8"/>
       <c r="D303" s="8" t="s">
         <v>47</v>
       </c>
       <c r="E303" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F303" s="8"/>
     </row>
@@ -11270,14 +11273,14 @@
         <v>1127</v>
       </c>
       <c r="B304" s="8" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="C304" s="8"/>
       <c r="D304" s="8" t="s">
         <v>78</v>
       </c>
       <c r="E304" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F304" s="8"/>
     </row>
@@ -11286,14 +11289,14 @@
         <v>1132</v>
       </c>
       <c r="B305" s="8" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C305" s="8"/>
       <c r="D305" s="8" t="s">
         <v>47</v>
       </c>
       <c r="E305" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F305" s="8"/>
     </row>
@@ -11309,7 +11312,7 @@
         <v>76</v>
       </c>
       <c r="E306" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F306" s="8"/>
     </row>
@@ -11318,14 +11321,14 @@
         <v>1138</v>
       </c>
       <c r="B307" s="8" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C307" s="8"/>
       <c r="D307" s="8" t="s">
         <v>47</v>
       </c>
       <c r="E307" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F307" s="8"/>
     </row>
@@ -11334,14 +11337,14 @@
         <v>1138</v>
       </c>
       <c r="B308" s="8" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="C308" s="8"/>
       <c r="D308" s="8" t="s">
         <v>91</v>
       </c>
       <c r="E308" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F308" s="8"/>
     </row>
@@ -11357,7 +11360,7 @@
         <v>76</v>
       </c>
       <c r="E309" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F309" s="8"/>
     </row>
@@ -11366,14 +11369,14 @@
         <v>1143</v>
       </c>
       <c r="B310" s="8" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="C310" s="8"/>
       <c r="D310" s="8" t="s">
         <v>91</v>
       </c>
       <c r="E310" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F310" s="8"/>
     </row>
@@ -11389,7 +11392,7 @@
         <v>44</v>
       </c>
       <c r="E311" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F311" s="8"/>
     </row>
@@ -11405,7 +11408,7 @@
         <v>44</v>
       </c>
       <c r="E312" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F312" s="8"/>
     </row>
@@ -11414,14 +11417,14 @@
         <v>1148</v>
       </c>
       <c r="B313" s="8" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C313" s="8"/>
       <c r="D313" s="8" t="s">
         <v>57</v>
       </c>
       <c r="E313" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F313" s="8"/>
     </row>
@@ -11430,14 +11433,14 @@
         <v>1148</v>
       </c>
       <c r="B314" s="8" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="C314" s="8"/>
       <c r="D314" s="8" t="s">
         <v>78</v>
       </c>
       <c r="E314" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F314" s="8"/>
     </row>
@@ -11453,7 +11456,7 @@
         <v>76</v>
       </c>
       <c r="E315" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F315" s="8"/>
     </row>
@@ -11469,7 +11472,7 @@
         <v>44</v>
       </c>
       <c r="E316" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F316" s="8"/>
     </row>
@@ -11478,14 +11481,14 @@
         <v>1151</v>
       </c>
       <c r="B317" s="8" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="C317" s="8"/>
       <c r="D317" s="8" t="s">
         <v>193</v>
       </c>
       <c r="E317" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F317" s="8"/>
     </row>
@@ -11494,17 +11497,17 @@
         <v>1155</v>
       </c>
       <c r="B318" s="8" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C318" s="8"/>
       <c r="D318" s="8" t="s">
         <v>47</v>
       </c>
       <c r="E318" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F318" s="8" t="s">
-        <v>1850</v>
+        <v>1849</v>
       </c>
     </row>
     <row r="319" spans="1:6" x14ac:dyDescent="0.25">
@@ -11512,14 +11515,14 @@
         <v>1162</v>
       </c>
       <c r="B319" s="8" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C319" s="8"/>
       <c r="D319" s="8" t="s">
         <v>47</v>
       </c>
       <c r="E319" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F319" s="8"/>
     </row>
@@ -11535,7 +11538,7 @@
         <v>44</v>
       </c>
       <c r="E320" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F320" s="8"/>
     </row>
@@ -11544,14 +11547,14 @@
         <v>1166</v>
       </c>
       <c r="B321" s="8" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C321" s="8"/>
       <c r="D321" s="8" t="s">
         <v>57</v>
       </c>
       <c r="E321" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F321" s="8"/>
     </row>
@@ -11567,7 +11570,7 @@
         <v>76</v>
       </c>
       <c r="E322" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F322" s="8"/>
     </row>
@@ -11576,14 +11579,14 @@
         <v>1171</v>
       </c>
       <c r="B323" s="8" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="C323" s="8"/>
       <c r="D323" s="8" t="s">
         <v>193</v>
       </c>
       <c r="E323" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F323" s="8"/>
     </row>
@@ -11599,7 +11602,7 @@
         <v>76</v>
       </c>
       <c r="E324" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F324" s="8"/>
     </row>
@@ -11615,7 +11618,7 @@
         <v>44</v>
       </c>
       <c r="E325" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F325" s="8"/>
     </row>
@@ -11624,14 +11627,14 @@
         <v>1176</v>
       </c>
       <c r="B326" s="8" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="C326" s="8"/>
       <c r="D326" s="8" t="s">
         <v>133</v>
       </c>
       <c r="E326" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F326" s="8"/>
     </row>
@@ -11640,7 +11643,7 @@
         <v>1179</v>
       </c>
       <c r="B327" s="8" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="C327" s="8" t="s">
         <v>314</v>
@@ -11649,7 +11652,7 @@
         <v>458</v>
       </c>
       <c r="E327" s="8" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="F327" s="8"/>
     </row>
@@ -11665,7 +11668,7 @@
         <v>44</v>
       </c>
       <c r="E328" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F328" s="8"/>
     </row>
@@ -11674,14 +11677,14 @@
         <v>1188</v>
       </c>
       <c r="B329" s="8" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C329" s="8"/>
       <c r="D329" s="8" t="s">
         <v>47</v>
       </c>
       <c r="E329" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F329" s="8"/>
     </row>
@@ -11690,14 +11693,14 @@
         <v>1188</v>
       </c>
       <c r="B330" s="8" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="C330" s="8"/>
       <c r="D330" s="8" t="s">
         <v>193</v>
       </c>
       <c r="E330" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F330" s="8"/>
     </row>
@@ -11713,7 +11716,7 @@
         <v>44</v>
       </c>
       <c r="E331" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F331" s="8"/>
     </row>
@@ -11722,14 +11725,14 @@
         <v>1197</v>
       </c>
       <c r="B332" s="8" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C332" s="8"/>
       <c r="D332" s="8" t="s">
         <v>57</v>
       </c>
       <c r="E332" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F332" s="8"/>
     </row>
@@ -11745,7 +11748,7 @@
         <v>44</v>
       </c>
       <c r="E333" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F333" s="8"/>
     </row>
@@ -11754,14 +11757,14 @@
         <v>1202</v>
       </c>
       <c r="B334" s="8" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="C334" s="8"/>
       <c r="D334" s="8" t="s">
         <v>71</v>
       </c>
       <c r="E334" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F334" s="8"/>
     </row>
@@ -11770,7 +11773,7 @@
         <v>1204</v>
       </c>
       <c r="B335" s="8" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="C335" s="8" t="s">
         <v>96</v>
@@ -11779,7 +11782,7 @@
         <v>1137</v>
       </c>
       <c r="E335" s="8" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="F335" s="8"/>
     </row>
@@ -11788,7 +11791,7 @@
         <v>1204</v>
       </c>
       <c r="B336" s="8" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="C336" s="8" t="s">
         <v>133</v>
@@ -11797,7 +11800,7 @@
         <v>78</v>
       </c>
       <c r="E336" s="8" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="F336" s="8"/>
     </row>
@@ -11813,7 +11816,7 @@
         <v>44</v>
       </c>
       <c r="E337" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F337" s="8"/>
     </row>
@@ -11829,10 +11832,10 @@
         <v>44</v>
       </c>
       <c r="E338" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F338" s="8" t="s">
-        <v>1855</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="339" spans="1:6" x14ac:dyDescent="0.25">
@@ -11847,10 +11850,10 @@
         <v>44</v>
       </c>
       <c r="E339" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F339" s="8" t="s">
-        <v>1855</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="340" spans="1:6" x14ac:dyDescent="0.25">
@@ -11858,14 +11861,14 @@
         <v>1217</v>
       </c>
       <c r="B340" s="8" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C340" s="8"/>
       <c r="D340" s="8" t="s">
         <v>57</v>
       </c>
       <c r="E340" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F340" s="8"/>
     </row>
@@ -11874,7 +11877,7 @@
         <v>1217</v>
       </c>
       <c r="B341" s="8" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="C341" s="8" t="s">
         <v>58</v>
@@ -11883,7 +11886,7 @@
         <v>272</v>
       </c>
       <c r="E341" s="8" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="F341" s="8"/>
     </row>
@@ -11892,14 +11895,14 @@
         <v>1217</v>
       </c>
       <c r="B342" s="8" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="C342" s="8"/>
       <c r="D342" s="8" t="s">
         <v>192</v>
       </c>
       <c r="E342" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F342" s="8"/>
     </row>
@@ -11915,7 +11918,7 @@
         <v>44</v>
       </c>
       <c r="E343" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F343" s="8"/>
     </row>
@@ -11931,7 +11934,7 @@
         <v>76</v>
       </c>
       <c r="E344" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F344" s="8"/>
     </row>
@@ -11940,14 +11943,14 @@
         <v>1227</v>
       </c>
       <c r="B345" s="8" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="C345" s="8"/>
       <c r="D345" s="8" t="s">
         <v>149</v>
       </c>
       <c r="E345" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F345" s="8"/>
     </row>
@@ -11963,7 +11966,7 @@
         <v>44</v>
       </c>
       <c r="E346" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F346" s="8"/>
     </row>
@@ -11979,7 +11982,7 @@
         <v>44</v>
       </c>
       <c r="E347" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F347" s="8"/>
     </row>
@@ -11988,14 +11991,14 @@
         <v>1245</v>
       </c>
       <c r="B348" s="8" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C348" s="8"/>
       <c r="D348" s="8" t="s">
         <v>47</v>
       </c>
       <c r="E348" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F348" s="8"/>
     </row>
@@ -12011,7 +12014,7 @@
         <v>76</v>
       </c>
       <c r="E349" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F349" s="8"/>
     </row>
@@ -12027,7 +12030,7 @@
         <v>332</v>
       </c>
       <c r="E350" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F350" s="8"/>
     </row>
@@ -12036,14 +12039,14 @@
         <v>1249</v>
       </c>
       <c r="B351" s="8" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="C351" s="8"/>
       <c r="D351" s="8" t="s">
         <v>77</v>
       </c>
       <c r="E351" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F351" s="8"/>
     </row>
@@ -12059,7 +12062,7 @@
         <v>76</v>
       </c>
       <c r="E352" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F352" s="8"/>
     </row>
@@ -12075,7 +12078,7 @@
         <v>76</v>
       </c>
       <c r="E353" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F353" s="8"/>
     </row>
@@ -12084,7 +12087,7 @@
         <v>1258</v>
       </c>
       <c r="B354" s="8" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="C354" s="8" t="s">
         <v>58</v>
@@ -12093,7 +12096,7 @@
         <v>458</v>
       </c>
       <c r="E354" s="8" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="F354" s="8"/>
     </row>
@@ -12102,14 +12105,14 @@
         <v>1267</v>
       </c>
       <c r="B355" s="8" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C355" s="8"/>
       <c r="D355" s="8" t="s">
         <v>47</v>
       </c>
       <c r="E355" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F355" s="8"/>
     </row>
@@ -12125,7 +12128,7 @@
         <v>76</v>
       </c>
       <c r="E356" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F356" s="8"/>
     </row>
@@ -12141,7 +12144,7 @@
         <v>44</v>
       </c>
       <c r="E357" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F357" s="8"/>
     </row>
@@ -12157,7 +12160,7 @@
         <v>44</v>
       </c>
       <c r="E358" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F358" s="8"/>
     </row>
@@ -12166,14 +12169,14 @@
         <v>1277</v>
       </c>
       <c r="B359" s="8" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C359" s="8"/>
       <c r="D359" s="8" t="s">
         <v>47</v>
       </c>
       <c r="E359" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F359" s="8"/>
     </row>
@@ -12182,14 +12185,14 @@
         <v>1281</v>
       </c>
       <c r="B360" s="8" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C360" s="8"/>
       <c r="D360" s="8" t="s">
         <v>47</v>
       </c>
       <c r="E360" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F360" s="8"/>
     </row>
@@ -12205,7 +12208,7 @@
         <v>44</v>
       </c>
       <c r="E361" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F361" s="8"/>
     </row>
@@ -12214,17 +12217,17 @@
         <v>1286</v>
       </c>
       <c r="B362" s="8" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C362" s="8"/>
       <c r="D362" s="8" t="s">
         <v>47</v>
       </c>
       <c r="E362" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F362" s="8" t="s">
-        <v>1850</v>
+        <v>1849</v>
       </c>
     </row>
     <row r="363" spans="1:6" x14ac:dyDescent="0.25">
@@ -12239,7 +12242,7 @@
         <v>245</v>
       </c>
       <c r="E363" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F363" s="8"/>
     </row>
@@ -12248,14 +12251,14 @@
         <v>1294</v>
       </c>
       <c r="B364" s="8" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C364" s="8"/>
       <c r="D364" s="8" t="s">
         <v>47</v>
       </c>
       <c r="E364" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F364" s="8"/>
     </row>
@@ -12271,7 +12274,7 @@
         <v>44</v>
       </c>
       <c r="E365" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F365" s="8"/>
     </row>
@@ -12287,7 +12290,7 @@
         <v>76</v>
       </c>
       <c r="E366" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F366" s="8"/>
     </row>
@@ -12296,14 +12299,14 @@
         <v>1300</v>
       </c>
       <c r="B367" s="8" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="C367" s="8"/>
       <c r="D367" s="8" t="s">
         <v>133</v>
       </c>
       <c r="E367" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F367" s="8"/>
     </row>
@@ -12319,7 +12322,7 @@
         <v>44</v>
       </c>
       <c r="E368" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F368" s="8"/>
     </row>
@@ -12335,7 +12338,7 @@
         <v>76</v>
       </c>
       <c r="E369" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F369" s="8"/>
     </row>
@@ -12344,14 +12347,14 @@
         <v>1316</v>
       </c>
       <c r="B370" s="8" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C370" s="8"/>
       <c r="D370" s="8" t="s">
         <v>47</v>
       </c>
       <c r="E370" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F370" s="8"/>
     </row>
@@ -12360,14 +12363,14 @@
         <v>1316</v>
       </c>
       <c r="B371" s="8" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="C371" s="8"/>
       <c r="D371" s="8" t="s">
         <v>119</v>
       </c>
       <c r="E371" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F371" s="8"/>
     </row>
@@ -12383,7 +12386,7 @@
         <v>44</v>
       </c>
       <c r="E372" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F372" s="8"/>
     </row>
@@ -12399,7 +12402,7 @@
         <v>44</v>
       </c>
       <c r="E373" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F373" s="8"/>
     </row>
@@ -12408,14 +12411,14 @@
         <v>1327</v>
       </c>
       <c r="B374" s="8" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C374" s="8"/>
       <c r="D374" s="8" t="s">
         <v>47</v>
       </c>
       <c r="E374" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F374" s="8"/>
     </row>
@@ -12424,16 +12427,16 @@
         <v>1327</v>
       </c>
       <c r="B375" s="8" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="C375" s="8" t="s">
         <v>58</v>
       </c>
       <c r="D375" s="8" t="s">
-        <v>1851</v>
+        <v>1850</v>
       </c>
       <c r="E375" s="8" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="F375" s="8"/>
     </row>
@@ -12449,7 +12452,7 @@
         <v>76</v>
       </c>
       <c r="E376" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F376" s="8"/>
     </row>
@@ -12458,14 +12461,14 @@
         <v>1332</v>
       </c>
       <c r="B377" s="8" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="C377" s="8"/>
       <c r="D377" s="8" t="s">
         <v>119</v>
       </c>
       <c r="E377" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F377" s="8"/>
     </row>
@@ -12481,7 +12484,7 @@
         <v>44</v>
       </c>
       <c r="E378" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F378" s="8"/>
     </row>
@@ -12490,14 +12493,14 @@
         <v>1334</v>
       </c>
       <c r="B379" s="8" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="C379" s="8"/>
       <c r="D379" s="8" t="s">
         <v>49</v>
       </c>
       <c r="E379" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F379" s="8"/>
     </row>
@@ -12513,7 +12516,7 @@
         <v>76</v>
       </c>
       <c r="E380" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F380" s="8"/>
     </row>
@@ -12522,14 +12525,14 @@
         <v>1335</v>
       </c>
       <c r="B381" s="8" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C381" s="8"/>
       <c r="D381" s="8" t="s">
         <v>47</v>
       </c>
       <c r="E381" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F381" s="8"/>
     </row>
@@ -12538,14 +12541,14 @@
         <v>1335</v>
       </c>
       <c r="B382" s="8" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="C382" s="8"/>
       <c r="D382" s="8" t="s">
         <v>119</v>
       </c>
       <c r="E382" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F382" s="8"/>
     </row>
@@ -12561,10 +12564,10 @@
         <v>76</v>
       </c>
       <c r="E383" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F383" s="8" t="s">
-        <v>1855</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="384" spans="1:6" x14ac:dyDescent="0.25">
@@ -12572,14 +12575,14 @@
         <v>1341</v>
       </c>
       <c r="B384" s="8" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="C384" s="8"/>
       <c r="D384" s="8" t="s">
         <v>83</v>
       </c>
       <c r="E384" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F384" s="8"/>
     </row>
@@ -12588,14 +12591,14 @@
         <v>1341</v>
       </c>
       <c r="B385" s="8" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="C385" s="8"/>
       <c r="D385" s="8" t="s">
         <v>192</v>
       </c>
       <c r="E385" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F385" s="8"/>
     </row>
@@ -12611,7 +12614,7 @@
         <v>44</v>
       </c>
       <c r="E386" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F386" s="8"/>
     </row>
@@ -12620,14 +12623,14 @@
         <v>1345</v>
       </c>
       <c r="B387" s="8" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C387" s="8"/>
       <c r="D387" s="8" t="s">
         <v>47</v>
       </c>
       <c r="E387" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F387" s="8"/>
     </row>
@@ -12643,7 +12646,7 @@
         <v>76</v>
       </c>
       <c r="E388" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F388" s="8"/>
     </row>
@@ -12659,7 +12662,7 @@
         <v>44</v>
       </c>
       <c r="E389" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F389" s="8"/>
     </row>
@@ -12668,14 +12671,14 @@
         <v>1356</v>
       </c>
       <c r="B390" s="8" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C390" s="8"/>
       <c r="D390" s="8" t="s">
         <v>57</v>
       </c>
       <c r="E390" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F390" s="8"/>
     </row>
@@ -12684,7 +12687,7 @@
         <v>1356</v>
       </c>
       <c r="B391" s="8" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="C391" s="8" t="s">
         <v>96</v>
@@ -12693,7 +12696,7 @@
         <v>1137</v>
       </c>
       <c r="E391" s="8" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="F391" s="8"/>
     </row>
@@ -12702,14 +12705,14 @@
         <v>1356</v>
       </c>
       <c r="B392" s="8" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="C392" s="8"/>
       <c r="D392" s="8" t="s">
         <v>78</v>
       </c>
       <c r="E392" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F392" s="8"/>
     </row>
@@ -12725,10 +12728,10 @@
         <v>44</v>
       </c>
       <c r="E393" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F393" s="8" t="s">
-        <v>1855</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="394" spans="1:6" x14ac:dyDescent="0.25">
@@ -12736,14 +12739,14 @@
         <v>1359</v>
       </c>
       <c r="B394" s="8" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C394" s="8"/>
       <c r="D394" s="8" t="s">
         <v>57</v>
       </c>
       <c r="E394" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F394" s="8"/>
     </row>
@@ -12752,7 +12755,7 @@
         <v>1359</v>
       </c>
       <c r="B395" s="8" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="C395" s="8" t="s">
         <v>1364</v>
@@ -12761,7 +12764,7 @@
         <v>574</v>
       </c>
       <c r="E395" s="8" t="s">
-        <v>1849</v>
+        <v>1848</v>
       </c>
       <c r="F395" s="8"/>
     </row>
@@ -12777,7 +12780,7 @@
         <v>76</v>
       </c>
       <c r="E396" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F396" s="8"/>
     </row>
@@ -12793,7 +12796,7 @@
         <v>332</v>
       </c>
       <c r="E397" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F397" s="8"/>
     </row>
@@ -12809,7 +12812,7 @@
         <v>44</v>
       </c>
       <c r="E398" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F398" s="8"/>
     </row>
@@ -12818,14 +12821,14 @@
         <v>1372</v>
       </c>
       <c r="B399" s="8" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C399" s="8"/>
       <c r="D399" s="8" t="s">
         <v>57</v>
       </c>
       <c r="E399" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F399" s="8"/>
     </row>
@@ -12834,7 +12837,7 @@
         <v>1372</v>
       </c>
       <c r="B400" s="8" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="C400" s="8" t="s">
         <v>77</v>
@@ -12843,7 +12846,7 @@
         <v>1544</v>
       </c>
       <c r="E400" s="8" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="F400" s="8"/>
     </row>
@@ -12852,14 +12855,14 @@
         <v>1372</v>
       </c>
       <c r="B401" s="8" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="C401" s="8"/>
       <c r="D401" s="8" t="s">
         <v>192</v>
       </c>
       <c r="E401" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F401" s="8"/>
     </row>
@@ -12868,16 +12871,16 @@
         <v>1377</v>
       </c>
       <c r="B402" s="8" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="C402" s="8" t="s">
         <v>1378</v>
       </c>
       <c r="D402" s="8" t="s">
-        <v>1861</v>
+        <v>1860</v>
       </c>
       <c r="E402" s="8" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="F402" s="8"/>
     </row>
@@ -12886,14 +12889,14 @@
         <v>1377</v>
       </c>
       <c r="B403" s="8" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="C403" s="8"/>
       <c r="D403" s="8" t="s">
         <v>49</v>
       </c>
       <c r="E403" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F403" s="8"/>
     </row>
@@ -12909,7 +12912,7 @@
         <v>76</v>
       </c>
       <c r="E404" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F404" s="8"/>
     </row>
@@ -12918,14 +12921,14 @@
         <v>1381</v>
       </c>
       <c r="B405" s="8" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C405" s="8"/>
       <c r="D405" s="8" t="s">
         <v>57</v>
       </c>
       <c r="E405" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F405" s="8"/>
     </row>
@@ -12934,14 +12937,14 @@
         <v>1381</v>
       </c>
       <c r="B406" s="8" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="C406" s="8"/>
       <c r="D406" s="8" t="s">
         <v>78</v>
       </c>
       <c r="E406" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F406" s="8"/>
     </row>
@@ -12950,14 +12953,14 @@
         <v>1385</v>
       </c>
       <c r="B407" s="8" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C407" s="8"/>
       <c r="D407" s="8" t="s">
         <v>47</v>
       </c>
       <c r="E407" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F407" s="8"/>
     </row>
@@ -12966,14 +12969,14 @@
         <v>1386</v>
       </c>
       <c r="B408" s="8" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C408" s="8"/>
       <c r="D408" s="8" t="s">
         <v>47</v>
       </c>
       <c r="E408" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F408" s="8"/>
     </row>
@@ -12989,7 +12992,7 @@
         <v>44</v>
       </c>
       <c r="E409" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F409" s="8"/>
     </row>
@@ -12998,14 +13001,14 @@
         <v>1389</v>
       </c>
       <c r="B410" s="8" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C410" s="8"/>
       <c r="D410" s="8" t="s">
         <v>47</v>
       </c>
       <c r="E410" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F410" s="8"/>
     </row>
@@ -13014,14 +13017,14 @@
         <v>1389</v>
       </c>
       <c r="B411" s="8" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="C411" s="8"/>
       <c r="D411" s="8" t="s">
         <v>91</v>
       </c>
       <c r="E411" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F411" s="8"/>
     </row>
@@ -13030,14 +13033,14 @@
         <v>1391</v>
       </c>
       <c r="B412" s="8" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="C412" s="8"/>
       <c r="D412" s="8" t="s">
         <v>49</v>
       </c>
       <c r="E412" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F412" s="8"/>
     </row>
@@ -13046,14 +13049,14 @@
         <v>1395</v>
       </c>
       <c r="B413" s="8" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C413" s="8"/>
       <c r="D413" s="8" t="s">
         <v>57</v>
       </c>
       <c r="E413" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F413" s="8"/>
     </row>
@@ -13062,7 +13065,7 @@
         <v>1395</v>
       </c>
       <c r="B414" s="8" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="C414" s="8" t="s">
         <v>1133</v>
@@ -13071,7 +13074,7 @@
         <v>664</v>
       </c>
       <c r="E414" s="8" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="F414" s="8"/>
     </row>
@@ -13080,7 +13083,7 @@
         <v>1395</v>
       </c>
       <c r="B415" s="8" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="C415" s="8" t="s">
         <v>119</v>
@@ -13089,7 +13092,7 @@
         <v>91</v>
       </c>
       <c r="E415" s="8" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="F415" s="8"/>
     </row>
@@ -13105,7 +13108,7 @@
         <v>76</v>
       </c>
       <c r="E416" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F416" s="8"/>
     </row>
@@ -13114,14 +13117,14 @@
         <v>1399</v>
       </c>
       <c r="B417" s="8" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="C417" s="8"/>
       <c r="D417" s="8" t="s">
         <v>91</v>
       </c>
       <c r="E417" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F417" s="8"/>
     </row>
@@ -13130,14 +13133,14 @@
         <v>1401</v>
       </c>
       <c r="B418" s="8" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C418" s="8"/>
       <c r="D418" s="8" t="s">
         <v>57</v>
       </c>
       <c r="E418" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F418" s="8"/>
     </row>
@@ -13146,14 +13149,14 @@
         <v>1405</v>
       </c>
       <c r="B419" s="8" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C419" s="8"/>
       <c r="D419" s="8" t="s">
         <v>47</v>
       </c>
       <c r="E419" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F419" s="8"/>
     </row>
@@ -13169,7 +13172,7 @@
         <v>44</v>
       </c>
       <c r="E420" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F420" s="8"/>
     </row>
@@ -13178,14 +13181,14 @@
         <v>1406</v>
       </c>
       <c r="B421" s="8" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C421" s="8"/>
       <c r="D421" s="8" t="s">
         <v>57</v>
       </c>
       <c r="E421" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F421" s="8"/>
     </row>
@@ -13201,7 +13204,7 @@
         <v>44</v>
       </c>
       <c r="E422" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F422" s="8"/>
     </row>
@@ -13210,14 +13213,14 @@
         <v>1409</v>
       </c>
       <c r="B423" s="8" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C423" s="8"/>
       <c r="D423" s="8" t="s">
         <v>47</v>
       </c>
       <c r="E423" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F423" s="8"/>
     </row>
@@ -13226,14 +13229,14 @@
         <v>1409</v>
       </c>
       <c r="B424" s="8" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="C424" s="8"/>
       <c r="D424" s="8" t="s">
         <v>91</v>
       </c>
       <c r="E424" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F424" s="8"/>
     </row>
@@ -13249,7 +13252,7 @@
         <v>76</v>
       </c>
       <c r="E425" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F425" s="8"/>
     </row>
@@ -13258,14 +13261,14 @@
         <v>1417</v>
       </c>
       <c r="B426" s="8" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="C426" s="8"/>
       <c r="D426" s="8" t="s">
         <v>91</v>
       </c>
       <c r="E426" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F426" s="8"/>
     </row>
@@ -13281,7 +13284,7 @@
         <v>76</v>
       </c>
       <c r="E427" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F427" s="8"/>
     </row>
@@ -13290,14 +13293,14 @@
         <v>1424</v>
       </c>
       <c r="B428" s="8" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="C428" s="8"/>
       <c r="D428" s="8" t="s">
         <v>77</v>
       </c>
       <c r="E428" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F428" s="8"/>
     </row>
@@ -13306,14 +13309,14 @@
         <v>1424</v>
       </c>
       <c r="B429" s="8" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="C429" s="8"/>
       <c r="D429" s="8" t="s">
         <v>71</v>
       </c>
       <c r="E429" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F429" s="8"/>
     </row>
@@ -13322,7 +13325,7 @@
         <v>1427</v>
       </c>
       <c r="B430" s="8" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="C430" s="8" t="s">
         <v>192</v>
@@ -13331,7 +13334,7 @@
         <v>72</v>
       </c>
       <c r="E430" s="8" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="F430" s="8"/>
     </row>
@@ -13347,7 +13350,7 @@
         <v>44</v>
       </c>
       <c r="E431" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F431" s="8"/>
     </row>
@@ -13363,10 +13366,10 @@
         <v>76</v>
       </c>
       <c r="E432" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F432" s="8" t="s">
-        <v>1855</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="433" spans="1:6" x14ac:dyDescent="0.25">
@@ -13374,7 +13377,7 @@
         <v>1449</v>
       </c>
       <c r="B433" s="8" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="C433" s="8" t="s">
         <v>1454</v>
@@ -13383,7 +13386,7 @@
         <v>272</v>
       </c>
       <c r="E433" s="8" t="s">
-        <v>1849</v>
+        <v>1848</v>
       </c>
       <c r="F433" s="8"/>
     </row>
@@ -13392,7 +13395,7 @@
         <v>1456</v>
       </c>
       <c r="B434" s="8" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="C434" s="8" t="s">
         <v>58</v>
@@ -13401,7 +13404,7 @@
         <v>285</v>
       </c>
       <c r="E434" s="8" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="F434" s="8"/>
     </row>
@@ -13417,7 +13420,7 @@
         <v>76</v>
       </c>
       <c r="E435" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F435" s="8"/>
     </row>
@@ -13433,7 +13436,7 @@
         <v>44</v>
       </c>
       <c r="E436" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F436" s="8"/>
     </row>
@@ -13442,14 +13445,14 @@
         <v>1484</v>
       </c>
       <c r="B437" s="8" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="C437" s="8"/>
       <c r="D437" s="8" t="s">
         <v>119</v>
       </c>
       <c r="E437" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F437" s="8"/>
     </row>
@@ -13465,7 +13468,7 @@
         <v>44</v>
       </c>
       <c r="E438" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F438" s="8"/>
     </row>
@@ -13474,14 +13477,14 @@
         <v>1491</v>
       </c>
       <c r="B439" s="8" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="C439" s="8"/>
       <c r="D439" s="8" t="s">
         <v>192</v>
       </c>
       <c r="E439" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F439" s="8"/>
     </row>
@@ -13497,7 +13500,7 @@
         <v>44</v>
       </c>
       <c r="E440" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F440" s="8"/>
     </row>
@@ -13506,14 +13509,14 @@
         <v>1494</v>
       </c>
       <c r="B441" s="8" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C441" s="8"/>
       <c r="D441" s="8" t="s">
         <v>57</v>
       </c>
       <c r="E441" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F441" s="8"/>
     </row>
@@ -13529,7 +13532,7 @@
         <v>76</v>
       </c>
       <c r="E442" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F442" s="8"/>
     </row>
@@ -13538,7 +13541,7 @@
         <v>1496</v>
       </c>
       <c r="B443" s="8" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="C443" s="8" t="s">
         <v>115</v>
@@ -13547,7 +13550,7 @@
         <v>77</v>
       </c>
       <c r="E443" s="8" t="s">
-        <v>1849</v>
+        <v>1848</v>
       </c>
       <c r="F443" s="8"/>
     </row>
@@ -13556,14 +13559,14 @@
         <v>1498</v>
       </c>
       <c r="B444" s="8" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C444" s="8"/>
       <c r="D444" s="8" t="s">
         <v>47</v>
       </c>
       <c r="E444" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F444" s="8"/>
     </row>
@@ -13579,7 +13582,7 @@
         <v>44</v>
       </c>
       <c r="E445" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F445" s="8"/>
     </row>
@@ -13595,10 +13598,10 @@
         <v>44</v>
       </c>
       <c r="E446" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F446" s="8" t="s">
-        <v>1855</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="447" spans="1:6" x14ac:dyDescent="0.25">
@@ -13606,7 +13609,7 @@
         <v>1505</v>
       </c>
       <c r="B447" s="8" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="C447" s="8" t="s">
         <v>647</v>
@@ -13615,7 +13618,7 @@
         <v>83</v>
       </c>
       <c r="E447" s="8" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="F447" s="8"/>
     </row>
@@ -13624,14 +13627,14 @@
         <v>1505</v>
       </c>
       <c r="B448" s="8" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="C448" s="8"/>
       <c r="D448" s="8" t="s">
         <v>192</v>
       </c>
       <c r="E448" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F448" s="8"/>
     </row>
@@ -13647,7 +13650,7 @@
         <v>76</v>
       </c>
       <c r="E449" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F449" s="8"/>
     </row>
@@ -13656,14 +13659,14 @@
         <v>1508</v>
       </c>
       <c r="B450" s="8" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C450" s="8"/>
       <c r="D450" s="8" t="s">
         <v>47</v>
       </c>
       <c r="E450" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F450" s="8"/>
     </row>
@@ -13679,7 +13682,7 @@
         <v>44</v>
       </c>
       <c r="E451" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F451" s="8"/>
     </row>
@@ -13695,7 +13698,7 @@
         <v>44</v>
       </c>
       <c r="E452" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F452" s="8"/>
     </row>
@@ -13704,7 +13707,7 @@
         <v>1516</v>
       </c>
       <c r="B453" s="8" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="C453" s="8" t="s">
         <v>96</v>
@@ -13713,7 +13716,7 @@
         <v>1137</v>
       </c>
       <c r="E453" s="8" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="F453" s="8"/>
     </row>
@@ -13722,14 +13725,14 @@
         <v>1516</v>
       </c>
       <c r="B454" s="8" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="C454" s="8"/>
       <c r="D454" s="8" t="s">
         <v>91</v>
       </c>
       <c r="E454" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F454" s="8"/>
     </row>
@@ -13745,7 +13748,7 @@
         <v>76</v>
       </c>
       <c r="E455" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F455" s="8"/>
     </row>
@@ -13761,7 +13764,7 @@
         <v>44</v>
       </c>
       <c r="E456" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F456" s="8"/>
     </row>
@@ -13770,14 +13773,14 @@
         <v>1524</v>
       </c>
       <c r="B457" s="8" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C457" s="8"/>
       <c r="D457" s="8" t="s">
         <v>47</v>
       </c>
       <c r="E457" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F457" s="8"/>
     </row>
@@ -13795,7 +13798,7 @@
         <v>332</v>
       </c>
       <c r="E458" s="8" t="s">
-        <v>1854</v>
+        <v>1853</v>
       </c>
       <c r="F458" s="8"/>
     </row>
@@ -13811,7 +13814,7 @@
         <v>44</v>
       </c>
       <c r="E459" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F459" s="8"/>
     </row>
@@ -13820,14 +13823,14 @@
         <v>1533</v>
       </c>
       <c r="B460" s="8" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C460" s="8"/>
       <c r="D460" s="8" t="s">
         <v>57</v>
       </c>
       <c r="E460" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F460" s="8"/>
     </row>
@@ -13836,7 +13839,7 @@
         <v>1533</v>
       </c>
       <c r="B461" s="8" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="C461" s="8" t="s">
         <v>119</v>
@@ -13845,7 +13848,7 @@
         <v>91</v>
       </c>
       <c r="E461" s="8" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="F461" s="8"/>
     </row>
@@ -13861,7 +13864,7 @@
         <v>44</v>
       </c>
       <c r="E462" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F462" s="8"/>
     </row>
@@ -13877,7 +13880,7 @@
         <v>44</v>
       </c>
       <c r="E463" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F463" s="8"/>
     </row>
@@ -13886,14 +13889,14 @@
         <v>1378</v>
       </c>
       <c r="B464" s="8" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="C464" s="8"/>
       <c r="D464" s="8" t="s">
         <v>1544</v>
       </c>
       <c r="E464" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F464" s="8"/>
     </row>
@@ -13902,14 +13905,14 @@
         <v>1378</v>
       </c>
       <c r="B465" s="8" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="C465" s="8"/>
       <c r="D465" s="8" t="s">
         <v>192</v>
       </c>
       <c r="E465" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F465" s="8"/>
     </row>
@@ -13918,7 +13921,7 @@
         <v>1547</v>
       </c>
       <c r="B466" s="8" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="C466" s="8" t="s">
         <v>83</v>
@@ -13927,7 +13930,7 @@
         <v>77</v>
       </c>
       <c r="E466" s="8" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="F466" s="8"/>
     </row>
@@ -13943,7 +13946,7 @@
         <v>76</v>
       </c>
       <c r="E467" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F467" s="8"/>
     </row>
@@ -13952,14 +13955,14 @@
         <v>1560</v>
       </c>
       <c r="B468" s="8" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="C468" s="8"/>
       <c r="D468" s="8" t="s">
         <v>192</v>
       </c>
       <c r="E468" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F468" s="8"/>
     </row>
@@ -13975,7 +13978,7 @@
         <v>44</v>
       </c>
       <c r="E469" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F469" s="8"/>
     </row>
@@ -13984,14 +13987,14 @@
         <v>1567</v>
       </c>
       <c r="B470" s="8" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="C470" s="8"/>
       <c r="D470" s="8" t="s">
         <v>91</v>
       </c>
       <c r="E470" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F470" s="8"/>
     </row>
@@ -14007,7 +14010,7 @@
         <v>44</v>
       </c>
       <c r="E471" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F471" s="8"/>
     </row>
@@ -14023,7 +14026,7 @@
         <v>44</v>
       </c>
       <c r="E472" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F472" s="8"/>
     </row>
@@ -14039,7 +14042,7 @@
         <v>44</v>
       </c>
       <c r="E473" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F473" s="8"/>
     </row>
@@ -14048,14 +14051,14 @@
         <v>1596</v>
       </c>
       <c r="B474" s="8" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C474" s="8"/>
       <c r="D474" s="8" t="s">
         <v>47</v>
       </c>
       <c r="E474" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F474" s="8"/>
     </row>
@@ -14064,14 +14067,14 @@
         <v>1596</v>
       </c>
       <c r="B475" s="8" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="C475" s="8"/>
       <c r="D475" s="8" t="s">
         <v>72</v>
       </c>
       <c r="E475" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F475" s="8"/>
     </row>
@@ -14080,14 +14083,14 @@
         <v>1602</v>
       </c>
       <c r="B476" s="8" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C476" s="8"/>
       <c r="D476" s="8" t="s">
         <v>47</v>
       </c>
       <c r="E476" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F476" s="8"/>
     </row>
@@ -14103,7 +14106,7 @@
         <v>76</v>
       </c>
       <c r="E477" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F477" s="8"/>
     </row>
@@ -14112,14 +14115,14 @@
         <v>1608</v>
       </c>
       <c r="B478" s="8" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="C478" s="8"/>
       <c r="D478" s="8" t="s">
         <v>192</v>
       </c>
       <c r="E478" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F478" s="8"/>
     </row>
@@ -14135,7 +14138,7 @@
         <v>76</v>
       </c>
       <c r="E479" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F479" s="8"/>
     </row>
@@ -14144,14 +14147,14 @@
         <v>1610</v>
       </c>
       <c r="B480" s="8" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C480" s="8"/>
       <c r="D480" s="8" t="s">
         <v>57</v>
       </c>
       <c r="E480" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F480" s="8"/>
     </row>
@@ -14160,14 +14163,14 @@
         <v>1612</v>
       </c>
       <c r="B481" s="8" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C481" s="8"/>
       <c r="D481" s="8" t="s">
         <v>57</v>
       </c>
       <c r="E481" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F481" s="8"/>
     </row>
@@ -14176,7 +14179,7 @@
         <v>1612</v>
       </c>
       <c r="B482" s="8" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="C482" s="8" t="s">
         <v>192</v>
@@ -14185,7 +14188,7 @@
         <v>193</v>
       </c>
       <c r="E482" s="8" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="F482" s="8"/>
     </row>
@@ -14194,7 +14197,7 @@
         <v>762</v>
       </c>
       <c r="B483" s="8" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="C483" s="8" t="s">
         <v>58</v>
@@ -14203,7 +14206,7 @@
         <v>1338</v>
       </c>
       <c r="E483" s="8" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="F483" s="8"/>
     </row>
@@ -14219,7 +14222,7 @@
         <v>76</v>
       </c>
       <c r="E484" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F484" s="8"/>
     </row>
@@ -14228,7 +14231,7 @@
         <v>1617</v>
       </c>
       <c r="B485" s="8" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="C485" s="8" t="s">
         <v>77</v>
@@ -14237,7 +14240,7 @@
         <v>83</v>
       </c>
       <c r="E485" s="8" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="F485" s="8"/>
     </row>
@@ -14246,14 +14249,14 @@
         <v>1617</v>
       </c>
       <c r="B486" s="8" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="C486" s="8"/>
       <c r="D486" s="8" t="s">
         <v>72</v>
       </c>
       <c r="E486" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F486" s="8"/>
     </row>
@@ -14269,7 +14272,7 @@
         <v>44</v>
       </c>
       <c r="E487" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F487" s="8"/>
     </row>
@@ -14278,14 +14281,14 @@
         <v>1631</v>
       </c>
       <c r="B488" s="8" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="C488" s="8"/>
       <c r="D488" s="8" t="s">
         <v>91</v>
       </c>
       <c r="E488" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F488" s="8"/>
     </row>
@@ -14301,7 +14304,7 @@
         <v>44</v>
       </c>
       <c r="E489" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F489" s="8"/>
     </row>
@@ -14310,14 +14313,14 @@
         <v>1633</v>
       </c>
       <c r="B490" s="8" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C490" s="8"/>
       <c r="D490" s="8" t="s">
         <v>57</v>
       </c>
       <c r="E490" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F490" s="8"/>
     </row>
@@ -14326,7 +14329,7 @@
         <v>1633</v>
       </c>
       <c r="B491" s="8" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="C491" s="8" t="s">
         <v>96</v>
@@ -14335,7 +14338,7 @@
         <v>1137</v>
       </c>
       <c r="E491" s="8" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="F491" s="8"/>
     </row>
@@ -14344,14 +14347,14 @@
         <v>1633</v>
       </c>
       <c r="B492" s="8" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="C492" s="8"/>
       <c r="D492" s="8" t="s">
         <v>133</v>
       </c>
       <c r="E492" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F492" s="8"/>
     </row>
@@ -14367,7 +14370,7 @@
         <v>76</v>
       </c>
       <c r="E493" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F493" s="8"/>
     </row>
@@ -14376,7 +14379,7 @@
         <v>1640</v>
       </c>
       <c r="B494" s="8" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="C494" s="8" t="s">
         <v>1644</v>
@@ -14385,7 +14388,7 @@
         <v>83</v>
       </c>
       <c r="E494" s="8" t="s">
-        <v>1849</v>
+        <v>1848</v>
       </c>
       <c r="F494" s="8"/>
     </row>
@@ -14394,14 +14397,14 @@
         <v>1646</v>
       </c>
       <c r="B495" s="8" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C495" s="8"/>
       <c r="D495" s="8" t="s">
         <v>47</v>
       </c>
       <c r="E495" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F495" s="8"/>
     </row>
@@ -14417,7 +14420,7 @@
         <v>76</v>
       </c>
       <c r="E496" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F496" s="8"/>
     </row>
@@ -14433,7 +14436,7 @@
         <v>76</v>
       </c>
       <c r="E497" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F497" s="8"/>
     </row>
@@ -14449,7 +14452,7 @@
         <v>44</v>
       </c>
       <c r="E498" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F498" s="8"/>
     </row>
@@ -14458,7 +14461,7 @@
         <v>1652</v>
       </c>
       <c r="B499" s="8" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="C499" s="8" t="s">
         <v>58</v>
@@ -14467,7 +14470,7 @@
         <v>1097</v>
       </c>
       <c r="E499" s="8" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="F499" s="8"/>
     </row>
@@ -14476,14 +14479,14 @@
         <v>1652</v>
       </c>
       <c r="B500" s="8" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="C500" s="8"/>
       <c r="D500" s="8" t="s">
         <v>49</v>
       </c>
       <c r="E500" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F500" s="8"/>
     </row>
@@ -14492,14 +14495,14 @@
         <v>1449</v>
       </c>
       <c r="B501" s="8" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C501" s="8"/>
       <c r="D501" s="8" t="s">
         <v>57</v>
       </c>
       <c r="E501" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F501" s="8"/>
     </row>
@@ -14508,7 +14511,7 @@
         <v>1449</v>
       </c>
       <c r="B502" s="8" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="C502" s="8" t="s">
         <v>272</v>
@@ -14517,7 +14520,7 @@
         <v>83</v>
       </c>
       <c r="E502" s="8" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="F502" s="8"/>
     </row>
@@ -14526,14 +14529,14 @@
         <v>1657</v>
       </c>
       <c r="B503" s="8" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C503" s="8"/>
       <c r="D503" s="8" t="s">
         <v>57</v>
       </c>
       <c r="E503" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F503" s="8"/>
     </row>
@@ -14542,7 +14545,7 @@
         <v>1657</v>
       </c>
       <c r="B504" s="8" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="C504" s="8" t="s">
         <v>752</v>
@@ -14551,7 +14554,7 @@
         <v>333</v>
       </c>
       <c r="E504" s="8" t="s">
-        <v>1849</v>
+        <v>1848</v>
       </c>
       <c r="F504" s="8"/>
     </row>
@@ -14567,7 +14570,7 @@
         <v>44</v>
       </c>
       <c r="E505" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F505" s="8"/>
     </row>
@@ -14576,14 +14579,14 @@
         <v>1664</v>
       </c>
       <c r="B506" s="8" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C506" s="8"/>
       <c r="D506" s="8" t="s">
         <v>47</v>
       </c>
       <c r="E506" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F506" s="8"/>
     </row>
@@ -14592,14 +14595,14 @@
         <v>1664</v>
       </c>
       <c r="B507" s="8" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="C507" s="8"/>
       <c r="D507" s="8" t="s">
         <v>78</v>
       </c>
       <c r="E507" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F507" s="8"/>
     </row>
@@ -14615,7 +14618,7 @@
         <v>44</v>
       </c>
       <c r="E508" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F508" s="8"/>
     </row>
@@ -14624,14 +14627,14 @@
         <v>1670</v>
       </c>
       <c r="B509" s="8" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="C509" s="8"/>
       <c r="D509" s="8" t="s">
         <v>47</v>
       </c>
       <c r="E509" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F509" s="8"/>
     </row>
@@ -14640,14 +14643,14 @@
         <v>1670</v>
       </c>
       <c r="B510" s="8" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="C510" s="8"/>
       <c r="D510" s="8" t="s">
         <v>91</v>
       </c>
       <c r="E510" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F510" s="8"/>
     </row>
@@ -14663,7 +14666,7 @@
         <v>76</v>
       </c>
       <c r="E511" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F511" s="8"/>
     </row>
@@ -14672,14 +14675,14 @@
         <v>1674</v>
       </c>
       <c r="B512" s="8" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="C512" s="8"/>
       <c r="D512" s="8" t="s">
         <v>59</v>
       </c>
       <c r="E512" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F512" s="8"/>
     </row>
@@ -14688,14 +14691,14 @@
         <v>1564</v>
       </c>
       <c r="B513" s="8" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="C513" s="8"/>
       <c r="D513" s="8" t="s">
         <v>91</v>
       </c>
       <c r="E513" s="8" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F513" s="8"/>
     </row>
@@ -14725,22 +14728,22 @@
         <v>22</v>
       </c>
       <c r="D1" s="16" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="E1" s="16" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="F1" s="16" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
       <c r="G1" s="16" t="s">
         <v>19</v>
       </c>
       <c r="H1" s="16" t="s">
+        <v>1862</v>
+      </c>
+      <c r="I1" s="16" t="s">
         <v>1863</v>
-      </c>
-      <c r="I1" s="16" t="s">
-        <v>1864</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -14769,7 +14772,7 @@
         <v>1</v>
       </c>
       <c r="I2" s="8" t="s">
-        <v>1812</v>
+        <v>1811</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -14789,7 +14792,7 @@
         <v>91</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>1865</v>
+        <v>1864</v>
       </c>
       <c r="G3" s="8" t="s">
         <v>128</v>
@@ -14798,7 +14801,7 @@
         <v>2</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>1838</v>
+        <v>1837</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -14812,30 +14815,30 @@
         <v>446</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>1866</v>
+        <v>1865</v>
       </c>
       <c r="E4" s="8" t="s">
         <v>72</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>1867</v>
+        <v>1866</v>
       </c>
       <c r="H4" s="8">
         <v>3</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>1868</v>
+        <v>1867</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>1866</v>
+        <v>1865</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>1869</v>
+        <v>1868</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>1866</v>
+        <v>1865</v>
       </c>
       <c r="E5" s="8" t="s">
         <v>59</v>
@@ -14844,14 +14847,12 @@
         <v>70</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>1870</v>
+        <v>1869</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>Non-cape</t>
-        </is>
+      <c r="A6" s="8" t="s">
+        <v>1873</v>
       </c>
       <c r="B6" s="8" t="s">
         <v>595</v>
@@ -15196,9 +15197,15 @@
       <c r="C5" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
+      <c r="D5" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="G5" s="5"/>
       <c r="H5" s="5"/>
       <c r="I5" s="5" t="s">
@@ -15218,7 +15225,7 @@
       <c r="O5" s="5"/>
       <c r="P5" s="6">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Q5" s="6" t="str">
         <f t="shared" si="1"/>
@@ -15759,7 +15766,9 @@
       <c r="C14" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="D14" s="5"/>
+      <c r="D14" s="5" t="s">
+        <v>76</v>
+      </c>
       <c r="E14" s="5" t="s">
         <v>45</v>
       </c>
@@ -15783,7 +15792,7 @@
       <c r="O14" s="5"/>
       <c r="P14" s="6">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q14" s="6" t="str">
         <f t="shared" si="1"/>
@@ -15880,7 +15889,9 @@
         <v>70</v>
       </c>
       <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
+      <c r="E16" s="5" t="s">
+        <v>45</v>
+      </c>
       <c r="F16" s="5" t="s">
         <v>107</v>
       </c>
@@ -15888,7 +15899,7 @@
         <v>47</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>138</v>
+        <v>58</v>
       </c>
       <c r="I16" s="5"/>
       <c r="J16" s="5"/>
@@ -15905,7 +15916,7 @@
       </c>
       <c r="P16" s="6">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q16" s="6" t="str">
         <f t="shared" si="1"/>
@@ -24719,7 +24730,7 @@
         <v>57</v>
       </c>
       <c r="H169" s="5" t="s">
-        <v>1872</v>
+        <v>1871</v>
       </c>
       <c r="I169" s="5"/>
       <c r="J169" s="5"/>
@@ -52061,21 +52072,19 @@
       <c r="B2" s="7" t="s">
         <v>1687</v>
       </c>
-      <c r="C2" s="7" t="inlineStr">
-        <is>
-          <t>Hero / Villain / Rogue / Unknown / Non-cape</t>
-        </is>
+      <c r="C2" s="7" t="s">
+        <v>1872</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="E2" s="8">
         <f>COUNTA(Roster!D2:D701)</f>
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="F2" s="9">
         <f>IF(COUNTA(Roster!A2:A701)=0,0,E2/COUNTA(Roster!A2:A701))</f>
-        <v>0.53389830508474578</v>
+        <v>0.53728813559322031</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -52086,18 +52095,18 @@
         <v>21</v>
       </c>
       <c r="C3" s="7" t="s">
+        <v>1689</v>
+      </c>
+      <c r="D3" s="7" t="s">
         <v>1690</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>1691</v>
       </c>
       <c r="E3" s="8">
         <f>COUNTA(Roster!E2:E701)</f>
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F3" s="9">
         <f>IF(COUNTA(Roster!A2:A701)=0,0,E3/COUNTA(Roster!A2:A701))</f>
-        <v>0.38135593220338981</v>
+        <v>0.38474576271186439</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -52108,18 +52117,18 @@
         <v>22</v>
       </c>
       <c r="C4" s="7" t="s">
+        <v>1691</v>
+      </c>
+      <c r="D4" s="7" t="s">
         <v>1692</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>1693</v>
       </c>
       <c r="E4" s="8">
         <f>COUNTA(Roster!F2:F701)</f>
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F4" s="9">
         <f>IF(COUNTA(Roster!A2:A701)=0,0,E4/COUNTA(Roster!A2:A701))</f>
-        <v>0.38644067796610171</v>
+        <v>0.38813559322033897</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -52127,13 +52136,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="7" t="s">
+        <v>1693</v>
+      </c>
+      <c r="C5" s="7" t="s">
         <v>1694</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="D5" s="7" t="s">
         <v>1695</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>1696</v>
       </c>
       <c r="E5" s="8">
         <f>COUNTA(Roster!G2:G701)</f>
@@ -52149,13 +52158,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="7" t="s">
+        <v>1696</v>
+      </c>
+      <c r="C6" s="7" t="s">
         <v>1697</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="D6" s="7" t="s">
         <v>1698</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>1699</v>
       </c>
       <c r="E6" s="8">
         <f>COUNTA(Roster!H2:H701)</f>
@@ -52171,13 +52180,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="7" t="s">
+        <v>1699</v>
+      </c>
+      <c r="C7" s="7" t="s">
         <v>1700</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="D7" s="7" t="s">
         <v>1701</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>1702</v>
       </c>
       <c r="E7" s="8">
         <f>COUNTA(Roster!I2:I701)</f>
@@ -52207,16 +52216,16 @@
   <sheetData>
     <row r="1" spans="1:4" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>1702</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>1703</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="C1" s="4" t="s">
         <v>1704</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="D1" s="4" t="s">
         <v>1705</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>1706</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -52224,7 +52233,7 @@
         <v>71</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>1707</v>
+        <v>1706</v>
       </c>
       <c r="C2" s="6">
         <f>COUNTIF(Roster!$I$2:$I$701,A2)</f>
@@ -52240,7 +52249,7 @@
         <v>91</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
       <c r="C3" s="6">
         <f>COUNTIF(Roster!$I$2:$I$701,A3)</f>
@@ -52256,7 +52265,7 @@
         <v>72</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>1709</v>
+        <v>1708</v>
       </c>
       <c r="C4" s="6">
         <f>COUNTIF(Roster!$I$2:$I$701,A4)</f>
@@ -52272,7 +52281,7 @@
         <v>59</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>1710</v>
+        <v>1709</v>
       </c>
       <c r="C5" s="6">
         <f>COUNTIF(Roster!$I$2:$I$701,A5)</f>
@@ -52288,7 +52297,7 @@
         <v>192</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>1711</v>
+        <v>1710</v>
       </c>
       <c r="C6" s="6">
         <f>COUNTIF(Roster!$I$2:$I$701,A6)</f>
@@ -52304,7 +52313,7 @@
         <v>123</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>1712</v>
+        <v>1711</v>
       </c>
       <c r="C7" s="6">
         <f>COUNTIF(Roster!$I$2:$I$701,A7)</f>
@@ -52320,7 +52329,7 @@
         <v>119</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>1713</v>
+        <v>1712</v>
       </c>
       <c r="C8" s="6">
         <f>COUNTIF(Roster!$I$2:$I$701,A8)</f>
@@ -52336,7 +52345,7 @@
         <v>49</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
       <c r="C9" s="6">
         <f>COUNTIF(Roster!$I$2:$I$701,A9)</f>
@@ -52352,7 +52361,7 @@
         <v>78</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>1715</v>
+        <v>1714</v>
       </c>
       <c r="C10" s="6">
         <f>COUNTIF(Roster!$I$2:$I$701,A10)</f>
@@ -52368,7 +52377,7 @@
         <v>178</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>1716</v>
+        <v>1715</v>
       </c>
       <c r="C11" s="6">
         <f>COUNTIF(Roster!$I$2:$I$701,A11)</f>
@@ -52384,7 +52393,7 @@
         <v>133</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>1717</v>
+        <v>1716</v>
       </c>
       <c r="C12" s="6">
         <f>COUNTIF(Roster!$I$2:$I$701,A12)</f>
@@ -52400,7 +52409,7 @@
         <v>193</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>1718</v>
+        <v>1717</v>
       </c>
       <c r="C13" s="6">
         <f>COUNTIF(Roster!$I$2:$I$701,A13)</f>
@@ -52413,7 +52422,7 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>1719</v>
+        <v>1718</v>
       </c>
       <c r="C14" s="11">
         <f>SUM(C2:C13)</f>
@@ -52422,7 +52431,7 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
-        <v>1720</v>
+        <v>1719</v>
       </c>
     </row>
   </sheetData>
@@ -52443,159 +52452,159 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>1720</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>1721</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="C1" s="4" t="s">
         <v>1722</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>1723</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>1724</v>
+        <v>1723</v>
       </c>
       <c r="B2" s="8">
         <f>COUNTA('Clue Ladder'!B2:B7)</f>
         <v>6</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>1725</v>
+        <v>1724</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>1726</v>
+        <v>1725</v>
       </c>
       <c r="B3" s="12">
         <v>0</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>1727</v>
+        <v>1726</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>1728</v>
+        <v>1727</v>
       </c>
       <c r="B4" s="8">
         <f>B2+1</f>
         <v>7</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>1729</v>
+        <v>1728</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>1730</v>
+        <v>1729</v>
       </c>
       <c r="B5" s="12">
         <v>150</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>1731</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>1732</v>
+        <v>1731</v>
       </c>
       <c r="B6" s="12">
         <v>250</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>1733</v>
+        <v>1732</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>1734</v>
+        <v>1733</v>
       </c>
       <c r="B7" s="12">
         <v>300</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>1735</v>
+        <v>1734</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
+        <v>1735</v>
+      </c>
+      <c r="B8" s="8" t="s">
         <v>1736</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="C8" s="8" t="s">
         <v>1737</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>1738</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>1739</v>
+        <v>1738</v>
       </c>
       <c r="B9" s="8"/>
       <c r="C9" s="8"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>1740</v>
+        <v>1739</v>
       </c>
       <c r="B10" s="8">
         <f>COUNTA(Roster!A2:A701)</f>
         <v>590</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>1741</v>
+        <v>1740</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="B11" s="8">
         <f>COUNTIF(Roster!Q2:Q701,"Yes")</f>
         <v>105</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>1741</v>
+        <v>1740</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>1743</v>
+        <v>1742</v>
       </c>
       <c r="B12" s="9">
         <f>IF(B5=0,0,B11/B5)</f>
         <v>0.7</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>1741</v>
+        <v>1740</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>1744</v>
+        <v>1743</v>
       </c>
       <c r="B13" s="13">
         <f>IFERROR(AVERAGE(Roster!P2:P701),0)</f>
-        <v>3.123728813559322</v>
+        <v>3.1322033898305084</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>1741</v>
+        <v>1740</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>1745</v>
+        <v>1744</v>
       </c>
       <c r="B14" s="8">
         <f>COUNTIF(Roster!L2:L701,"Y")</f>
         <v>2</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>1741</v>
+        <v>1740</v>
       </c>
     </row>
   </sheetData>
@@ -52615,18 +52624,18 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>1745</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>1746</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>1747</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>1748</v>
+        <v>1747</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="25.5" x14ac:dyDescent="0.25">
@@ -52634,23 +52643,23 @@
         <v>1687</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>1749</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>1750</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>1751</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -52658,31 +52667,31 @@
         <v>22</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>1752</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
+        <v>1752</v>
+      </c>
+      <c r="B7" s="7" t="s">
         <v>1753</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>1754</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
+        <v>1754</v>
+      </c>
+      <c r="B8" s="7" t="s">
         <v>1755</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>1756</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
+        <v>1756</v>
+      </c>
+      <c r="B9" s="7" t="s">
         <v>1757</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>1758</v>
       </c>
     </row>
   </sheetData>
@@ -52703,79 +52712,79 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>1758</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>1759</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="C1" s="4" t="s">
         <v>1760</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>1761</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
+        <v>1761</v>
+      </c>
+      <c r="B2" s="7" t="s">
         <v>1762</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="C2" s="7" t="s">
         <v>1763</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>1764</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
+        <v>1764</v>
+      </c>
+      <c r="B3" s="7" t="s">
         <v>1765</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="C3" s="7" t="s">
         <v>1766</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>1767</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
+        <v>1767</v>
+      </c>
+      <c r="B4" s="7" t="s">
         <v>1768</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="C4" s="7" t="s">
         <v>1769</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>1770</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
+        <v>1770</v>
+      </c>
+      <c r="B5" s="7" t="s">
         <v>1771</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="C5" s="7" t="s">
         <v>1772</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>1773</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
+        <v>1773</v>
+      </c>
+      <c r="B6" s="7" t="s">
         <v>1774</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="C6" s="7" t="s">
         <v>1775</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>1776</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
+        <v>1776</v>
+      </c>
+      <c r="B7" s="7" t="s">
         <v>1777</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="C7" s="7" t="s">
         <v>1778</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>1779</v>
       </c>
     </row>
   </sheetData>
@@ -52797,13 +52806,13 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>1779</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>1780</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="C1" s="4" t="s">
         <v>1781</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>1782</v>
       </c>
       <c r="D1" s="4" t="s">
         <v>31</v>
@@ -52811,98 +52820,98 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
+        <v>1782</v>
+      </c>
+      <c r="B2" s="7" t="s">
         <v>1783</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="C2" s="7" t="s">
         <v>1784</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="D2" s="7" t="s">
         <v>1785</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>1786</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="B3" s="7" t="s">
+        <v>1783</v>
+      </c>
+      <c r="C3" s="7" t="s">
         <v>1784</v>
       </c>
-      <c r="C3" s="7" t="s">
-        <v>1785</v>
-      </c>
       <c r="D3" s="7" t="s">
-        <v>1787</v>
+        <v>1786</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
+        <v>1787</v>
+      </c>
+      <c r="B4" s="7" t="s">
         <v>1788</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="C4" s="7" t="s">
         <v>1789</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="D4" s="7" t="s">
         <v>1790</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>1791</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
+        <v>1791</v>
+      </c>
+      <c r="B5" s="7" t="s">
         <v>1792</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="C5" s="7" t="s">
         <v>1793</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="D5" s="7" t="s">
         <v>1794</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>1795</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
+        <v>1795</v>
+      </c>
+      <c r="B6" s="7" t="s">
         <v>1796</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="C6" s="7" t="s">
         <v>1797</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>1798</v>
       </c>
       <c r="D6" s="7"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
+        <v>1798</v>
+      </c>
+      <c r="B7" s="7" t="s">
         <v>1799</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="C7" s="7" t="s">
         <v>1800</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="D7" s="7" t="s">
         <v>1801</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>1802</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
+        <v>1802</v>
+      </c>
+      <c r="B8" s="7" t="s">
         <v>1803</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="C8" s="7" t="s">
         <v>1804</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="D8" s="7" t="s">
         <v>1805</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>1806</v>
       </c>
     </row>
   </sheetData>
@@ -52924,159 +52933,159 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>1806</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>1807</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="C1" s="4" t="s">
+        <v>1693</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>1808</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>1694</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>1809</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
+        <v>1809</v>
+      </c>
+      <c r="B2" s="7" t="s">
         <v>1810</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="C2" s="14" t="s">
         <v>1811</v>
-      </c>
-      <c r="C2" s="14" t="s">
-        <v>1812</v>
       </c>
       <c r="D2" s="15"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>1810</v>
+        <v>1809</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>1812</v>
+        <v>1811</v>
       </c>
       <c r="D3" s="15"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>1810</v>
+        <v>1809</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>1814</v>
+        <v>1813</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>1812</v>
+        <v>1811</v>
       </c>
       <c r="D4" s="15"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>1810</v>
+        <v>1809</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>1815</v>
+        <v>1814</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>1812</v>
+        <v>1811</v>
       </c>
       <c r="D5" s="15"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>1810</v>
+        <v>1809</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>1816</v>
+        <v>1815</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>1812</v>
+        <v>1811</v>
       </c>
       <c r="D6" s="15"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
+        <v>1816</v>
+      </c>
+      <c r="B7" s="7" t="s">
         <v>1817</v>
       </c>
-      <c r="B7" s="7" t="s">
-        <v>1818</v>
-      </c>
       <c r="C7" s="14" t="s">
-        <v>1812</v>
+        <v>1811</v>
       </c>
       <c r="D7" s="15"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>1817</v>
+        <v>1816</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>1819</v>
+        <v>1818</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>1812</v>
+        <v>1811</v>
       </c>
       <c r="D8" s="15"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>1817</v>
+        <v>1816</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>1820</v>
+        <v>1819</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>1812</v>
+        <v>1811</v>
       </c>
       <c r="D9" s="15"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>1817</v>
+        <v>1816</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>1821</v>
+        <v>1820</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>1812</v>
+        <v>1811</v>
       </c>
       <c r="D10" s="15"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
+        <v>1821</v>
+      </c>
+      <c r="B11" s="7" t="s">
         <v>1822</v>
       </c>
-      <c r="B11" s="7" t="s">
-        <v>1823</v>
-      </c>
       <c r="C11" s="14" t="s">
-        <v>1812</v>
+        <v>1811</v>
       </c>
       <c r="D11" s="15"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>1822</v>
+        <v>1821</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>1824</v>
+        <v>1823</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>1812</v>
+        <v>1811</v>
       </c>
       <c r="D12" s="15"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>1822</v>
+        <v>1821</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>1825</v>
+        <v>1824</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>1812</v>
+        <v>1811</v>
       </c>
       <c r="D13" s="15"/>
     </row>

--- a/data/parahumandle_design.xlsx
+++ b/data/parahumandle_design.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Research\Worm Wordle clone\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB0CAD6E-C2B5-40D6-9222-4F7948D89EBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{851A60DF-75E6-4CAD-972E-9026055D9E8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6870" yWindow="6705" windowWidth="28800" windowHeight="15345" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9386" uniqueCount="1874">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9406" uniqueCount="1874">
   <si>
     <t>Parahumandle – design workbook</t>
   </si>
@@ -14908,7 +14908,7 @@
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
-    <col min="2" max="2" width="14.140625" customWidth="1"/>
+    <col min="2" max="2" width="9.28515625" customWidth="1"/>
     <col min="3" max="3" width="19" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
@@ -15206,8 +15206,12 @@
       <c r="F5" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
+      <c r="G5" s="5" t="s">
+        <v>1865</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>63</v>
+      </c>
       <c r="I5" s="5" t="s">
         <v>71</v>
       </c>
@@ -15225,11 +15229,11 @@
       <c r="O5" s="5"/>
       <c r="P5" s="6">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q5" s="6" t="str">
         <f t="shared" si="1"/>
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R5" s="5" t="s">
         <v>51</v>
@@ -15255,7 +15259,9 @@
       <c r="D6" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="E6" s="5"/>
+      <c r="E6" s="5" t="s">
+        <v>45</v>
+      </c>
       <c r="F6" s="5" t="s">
         <v>46</v>
       </c>
@@ -15282,11 +15288,11 @@
       <c r="O6" s="5"/>
       <c r="P6" s="6">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q6" s="6" t="str">
         <f t="shared" si="1"/>
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R6" s="5" t="s">
         <v>51</v>
@@ -15517,15 +15523,27 @@
         <v>102</v>
       </c>
       <c r="B10" s="5"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
+      <c r="C10" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>1865</v>
+      </c>
       <c r="H10" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="I10" s="5"/>
+      <c r="I10" s="5" t="s">
+        <v>71</v>
+      </c>
       <c r="J10" s="5"/>
       <c r="K10" s="5"/>
       <c r="L10" s="5"/>
@@ -15538,11 +15556,11 @@
       </c>
       <c r="P10" s="6">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Q10" s="6" t="str">
         <f t="shared" si="1"/>
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R10" s="5" t="s">
         <v>51</v>
@@ -15721,7 +15739,9 @@
       <c r="G13" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="H13" s="5"/>
+      <c r="H13" s="5" t="s">
+        <v>63</v>
+      </c>
       <c r="I13" s="5" t="s">
         <v>123</v>
       </c>
@@ -15737,11 +15757,11 @@
       <c r="O13" s="5"/>
       <c r="P13" s="6">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q13" s="6" t="str">
         <f t="shared" si="1"/>
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R13" s="5" t="s">
         <v>125</v>
@@ -15781,7 +15801,9 @@
       <c r="H14" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="I14" s="5"/>
+      <c r="I14" s="5" t="s">
+        <v>49</v>
+      </c>
       <c r="J14" s="5"/>
       <c r="K14" s="5"/>
       <c r="L14" s="5"/>
@@ -15792,11 +15814,11 @@
       <c r="O14" s="5"/>
       <c r="P14" s="6">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q14" s="6" t="str">
         <f t="shared" si="1"/>
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R14" s="5" t="s">
         <v>51</v>
@@ -15834,7 +15856,9 @@
       <c r="F15" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="G15" s="5"/>
+      <c r="G15" s="5" t="s">
+        <v>1865</v>
+      </c>
       <c r="H15" s="5" t="s">
         <v>132</v>
       </c>
@@ -15855,11 +15879,11 @@
       <c r="O15" s="5"/>
       <c r="P15" s="6">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q15" s="6" t="str">
         <f t="shared" si="1"/>
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R15" s="5" t="s">
         <v>51</v>
@@ -16011,17 +16035,30 @@
         <v>146</v>
       </c>
       <c r="B18" s="5"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
-      <c r="G18" s="5"/>
+      <c r="C18" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>1865</v>
+      </c>
       <c r="H18" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="I18" s="5"/>
-      <c r="J18" s="5"/>
-      <c r="K18" s="5"/>
+      <c r="I18" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="J18" s="5" t="s">
+        <v>78</v>
+      </c>
       <c r="L18" s="5"/>
       <c r="M18" s="5"/>
       <c r="N18" s="5" t="s">
@@ -16029,12 +16066,12 @@
       </c>
       <c r="O18" s="5"/>
       <c r="P18" s="6">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f>IF(A18="","",COUNTA(D18:F18)+COUNTA(G18:G18)+COUNTA(H18:H18)+COUNTA(#REF!))</f>
+        <v>6</v>
       </c>
       <c r="Q18" s="6" t="str">
         <f t="shared" si="1"/>
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R18" s="5" t="s">
         <v>51</v>
@@ -43425,7 +43462,9 @@
       <c r="F504" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="G504" s="5"/>
+      <c r="G504" s="5" t="s">
+        <v>57</v>
+      </c>
       <c r="H504" s="5" t="s">
         <v>664</v>
       </c>
@@ -43444,11 +43483,11 @@
       <c r="O504" s="5"/>
       <c r="P504" s="6">
         <f t="shared" si="14"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q504" s="6" t="str">
         <f t="shared" si="15"/>
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R504" s="5" t="s">
         <v>51</v>
@@ -52080,11 +52119,11 @@
       </c>
       <c r="E2" s="8">
         <f>COUNTA(Roster!D2:D701)</f>
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="F2" s="9">
         <f>IF(COUNTA(Roster!A2:A701)=0,0,E2/COUNTA(Roster!A2:A701))</f>
-        <v>0.53728813559322031</v>
+        <v>0.54067796610169494</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -52102,11 +52141,11 @@
       </c>
       <c r="E3" s="8">
         <f>COUNTA(Roster!E2:E701)</f>
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="F3" s="9">
         <f>IF(COUNTA(Roster!A2:A701)=0,0,E3/COUNTA(Roster!A2:A701))</f>
-        <v>0.38474576271186439</v>
+        <v>0.38983050847457629</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -52124,11 +52163,11 @@
       </c>
       <c r="E4" s="8">
         <f>COUNTA(Roster!F2:F701)</f>
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="F4" s="9">
         <f>IF(COUNTA(Roster!A2:A701)=0,0,E4/COUNTA(Roster!A2:A701))</f>
-        <v>0.38813559322033897</v>
+        <v>0.39152542372881355</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -52146,11 +52185,11 @@
       </c>
       <c r="E5" s="8">
         <f>COUNTA(Roster!G2:G701)</f>
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="F5" s="9">
         <f>IF(COUNTA(Roster!A2:A701)=0,0,E5/COUNTA(Roster!A2:A701))</f>
-        <v>0.52711864406779663</v>
+        <v>0.53559322033898304</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -52168,11 +52207,11 @@
       </c>
       <c r="E6" s="8">
         <f>COUNTA(Roster!H2:H701)</f>
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="F6" s="9">
         <f>IF(COUNTA(Roster!A2:A701)=0,0,E6/COUNTA(Roster!A2:A701))</f>
-        <v>0.764406779661017</v>
+        <v>0.76779661016949152</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
@@ -52190,11 +52229,11 @@
       </c>
       <c r="E7" s="8">
         <f>COUNTA(Roster!I2:I701)</f>
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="F7" s="9">
         <f>IF(COUNTA(Roster!A2:A701)=0,0,E7/COUNTA(Roster!A2:A701))</f>
-        <v>0.53050847457627115</v>
+        <v>0.53559322033898304</v>
       </c>
     </row>
   </sheetData>
@@ -52237,11 +52276,11 @@
       </c>
       <c r="C2" s="6">
         <f>COUNTIF(Roster!$I$2:$I$701,A2)</f>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D2" s="10">
         <f t="shared" ref="D2:D13" si="0">IF(SUM($C$2:$C$13)=0,0,C2/SUM($C$2:$C$13))</f>
-        <v>7.6677316293929709E-2</v>
+        <v>7.9113924050632917E-2</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -52253,11 +52292,11 @@
       </c>
       <c r="C3" s="6">
         <f>COUNTIF(Roster!$I$2:$I$701,A3)</f>
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D3" s="10">
         <f t="shared" si="0"/>
-        <v>0.12140575079872204</v>
+        <v>0.12341772151898735</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -52273,7 +52312,7 @@
       </c>
       <c r="D4" s="10">
         <f t="shared" si="0"/>
-        <v>9.5846645367412137E-2</v>
+        <v>9.49367088607595E-2</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -52289,7 +52328,7 @@
       </c>
       <c r="D5" s="10">
         <f t="shared" si="0"/>
-        <v>7.0287539936102233E-2</v>
+        <v>6.9620253164556958E-2</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -52305,7 +52344,7 @@
       </c>
       <c r="D6" s="10">
         <f t="shared" si="0"/>
-        <v>0.12140575079872204</v>
+        <v>0.12025316455696203</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -52321,7 +52360,7 @@
       </c>
       <c r="D7" s="10">
         <f t="shared" si="0"/>
-        <v>0.13418530351437699</v>
+        <v>0.13291139240506328</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -52337,7 +52376,7 @@
       </c>
       <c r="D8" s="10">
         <f t="shared" si="0"/>
-        <v>0.10223642172523961</v>
+        <v>0.10126582278481013</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -52349,11 +52388,11 @@
       </c>
       <c r="C9" s="6">
         <f>COUNTIF(Roster!$I$2:$I$701,A9)</f>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D9" s="10">
         <f t="shared" si="0"/>
-        <v>0.10543130990415335</v>
+        <v>0.10759493670886076</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -52369,7 +52408,7 @@
       </c>
       <c r="D10" s="10">
         <f t="shared" si="0"/>
-        <v>6.7092651757188496E-2</v>
+        <v>6.6455696202531639E-2</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -52385,7 +52424,7 @@
       </c>
       <c r="D11" s="10">
         <f t="shared" si="0"/>
-        <v>3.8338658146964855E-2</v>
+        <v>3.7974683544303799E-2</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -52401,7 +52440,7 @@
       </c>
       <c r="D12" s="10">
         <f t="shared" si="0"/>
-        <v>3.8338658146964855E-2</v>
+        <v>3.7974683544303799E-2</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -52417,7 +52456,7 @@
       </c>
       <c r="D13" s="10">
         <f t="shared" si="0"/>
-        <v>2.8753993610223641E-2</v>
+        <v>2.8481012658227847E-2</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -52426,7 +52465,7 @@
       </c>
       <c r="C14" s="11">
         <f>SUM(C2:C13)</f>
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -52565,7 +52604,7 @@
       </c>
       <c r="B11" s="8">
         <f>COUNTIF(Roster!Q2:Q701,"Yes")</f>
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="C11" s="8" t="s">
         <v>1740</v>
@@ -52577,7 +52616,7 @@
       </c>
       <c r="B12" s="9">
         <f>IF(B5=0,0,B11/B5)</f>
-        <v>0.7</v>
+        <v>0.7533333333333333</v>
       </c>
       <c r="C12" s="8" t="s">
         <v>1740</v>
@@ -52589,7 +52628,7 @@
       </c>
       <c r="B13" s="13">
         <f>IFERROR(AVERAGE(Roster!P2:P701),0)</f>
-        <v>3.1322033898305084</v>
+        <v>3.1610169491525424</v>
       </c>
       <c r="C13" s="8" t="s">
         <v>1740</v>

--- a/data/parahumandle_design.xlsx
+++ b/data/parahumandle_design.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Research\Worm Wordle clone\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{851A60DF-75E6-4CAD-972E-9026055D9E8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DDF6A86-3E05-48FC-91EC-80CCD93E6DDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9406" uniqueCount="1874">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9423" uniqueCount="1875">
   <si>
     <t>Parahumandle – design workbook</t>
   </si>
@@ -5674,6 +5674,9 @@
   </si>
   <si>
     <t>Non-cape</t>
+  </si>
+  <si>
+    <t>Shaker, Master</t>
   </si>
 </sst>
 </file>
@@ -14914,7 +14917,7 @@
     <col min="5" max="5" width="16" customWidth="1"/>
     <col min="6" max="6" width="11" customWidth="1"/>
     <col min="7" max="7" width="14" customWidth="1"/>
-    <col min="8" max="8" width="22" customWidth="1"/>
+    <col min="8" max="8" width="29.42578125" customWidth="1"/>
     <col min="9" max="9" width="14" customWidth="1"/>
     <col min="10" max="10" width="26" customWidth="1"/>
     <col min="11" max="11" width="28" customWidth="1"/>
@@ -23514,9 +23517,15 @@
       <c r="C147" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="D147" s="5"/>
-      <c r="E147" s="5"/>
-      <c r="F147" s="5"/>
+      <c r="D147" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="E147" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F147" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="G147" s="5" t="s">
         <v>47</v>
       </c>
@@ -23538,11 +23547,11 @@
       <c r="O147" s="5"/>
       <c r="P147" s="6">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q147" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R147" s="5" t="s">
         <v>51</v>
@@ -23576,13 +23585,17 @@
       <c r="D148" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="E148" s="5"/>
+      <c r="E148" s="5" t="s">
+        <v>45</v>
+      </c>
       <c r="F148" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="G148" s="5"/>
+      <c r="G148" s="5" t="s">
+        <v>1865</v>
+      </c>
       <c r="H148" s="5" t="s">
-        <v>149</v>
+        <v>77</v>
       </c>
       <c r="I148" s="5" t="s">
         <v>71</v>
@@ -23601,11 +23614,11 @@
       <c r="O148" s="5"/>
       <c r="P148" s="6">
         <f t="shared" si="4"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q148" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R148" s="5" t="s">
         <v>51</v>
@@ -24769,8 +24782,12 @@
       <c r="H169" s="5" t="s">
         <v>1871</v>
       </c>
-      <c r="I169" s="5"/>
-      <c r="J169" s="5"/>
+      <c r="I169" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="J169" s="5" t="s">
+        <v>71</v>
+      </c>
       <c r="K169" s="5"/>
       <c r="L169" s="5"/>
       <c r="M169" s="5"/>
@@ -24780,11 +24797,11 @@
       <c r="O169" s="5"/>
       <c r="P169" s="6">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q169" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R169" s="5" t="s">
         <v>51</v>
@@ -25018,7 +25035,9 @@
       <c r="F174" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="G174" s="5"/>
+      <c r="G174" s="5" t="s">
+        <v>57</v>
+      </c>
       <c r="H174" s="5" t="s">
         <v>664</v>
       </c>
@@ -25037,11 +25056,11 @@
       <c r="O174" s="5"/>
       <c r="P174" s="6">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q174" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R174" s="5" t="s">
         <v>51</v>
@@ -25519,7 +25538,9 @@
       <c r="F183" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="G183" s="5"/>
+      <c r="G183" s="5" t="s">
+        <v>57</v>
+      </c>
       <c r="H183" s="5" t="s">
         <v>323</v>
       </c>
@@ -25538,11 +25559,11 @@
       <c r="O183" s="5"/>
       <c r="P183" s="6">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q183" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R183" s="5" t="s">
         <v>51</v>
@@ -26123,8 +26144,12 @@
       <c r="H193" s="5" t="s">
         <v>720</v>
       </c>
-      <c r="I193" s="5"/>
-      <c r="J193" s="5"/>
+      <c r="I193" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="J193" s="5" t="s">
+        <v>1874</v>
+      </c>
       <c r="K193" s="5"/>
       <c r="L193" s="5"/>
       <c r="M193" s="5"/>
@@ -26134,11 +26159,11 @@
       <c r="O193" s="5"/>
       <c r="P193" s="6">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q193" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R193" s="5" t="s">
         <v>51</v>
@@ -26334,7 +26359,9 @@
       <c r="I197" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="J197" s="5"/>
+      <c r="J197" s="5" t="s">
+        <v>192</v>
+      </c>
       <c r="K197" s="5" t="s">
         <v>119</v>
       </c>
@@ -26388,16 +26415,24 @@
       <c r="D198" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="E198" s="5"/>
-      <c r="F198" s="5"/>
-      <c r="G198" s="5"/>
+      <c r="E198" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F198" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G198" s="5" t="s">
+        <v>1865</v>
+      </c>
       <c r="H198" s="5" t="s">
         <v>58</v>
       </c>
       <c r="I198" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="J198" s="5"/>
+      <c r="J198" s="5" t="s">
+        <v>78</v>
+      </c>
       <c r="K198" s="5" t="s">
         <v>133</v>
       </c>
@@ -26409,11 +26444,11 @@
       <c r="O198" s="5"/>
       <c r="P198" s="6">
         <f t="shared" si="6"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q198" s="6" t="str">
         <f t="shared" si="7"/>
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R198" s="5" t="s">
         <v>51</v>
@@ -26544,7 +26579,9 @@
       <c r="C201" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="D201" s="5"/>
+      <c r="D201" s="5" t="s">
+        <v>76</v>
+      </c>
       <c r="E201" s="5" t="s">
         <v>45</v>
       </c>
@@ -26576,11 +26613,11 @@
       </c>
       <c r="P201" s="6">
         <f t="shared" si="6"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q201" s="6" t="str">
         <f t="shared" si="7"/>
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R201" s="5" t="s">
         <v>51</v>
@@ -52119,11 +52156,11 @@
       </c>
       <c r="E2" s="8">
         <f>COUNTA(Roster!D2:D701)</f>
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="F2" s="9">
         <f>IF(COUNTA(Roster!A2:A701)=0,0,E2/COUNTA(Roster!A2:A701))</f>
-        <v>0.54067796610169494</v>
+        <v>0.54406779661016946</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -52141,11 +52178,11 @@
       </c>
       <c r="E3" s="8">
         <f>COUNTA(Roster!E2:E701)</f>
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="F3" s="9">
         <f>IF(COUNTA(Roster!A2:A701)=0,0,E3/COUNTA(Roster!A2:A701))</f>
-        <v>0.38983050847457629</v>
+        <v>0.39491525423728813</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -52163,11 +52200,11 @@
       </c>
       <c r="E4" s="8">
         <f>COUNTA(Roster!F2:F701)</f>
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="F4" s="9">
         <f>IF(COUNTA(Roster!A2:A701)=0,0,E4/COUNTA(Roster!A2:A701))</f>
-        <v>0.39152542372881355</v>
+        <v>0.39491525423728813</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -52185,11 +52222,11 @@
       </c>
       <c r="E5" s="8">
         <f>COUNTA(Roster!G2:G701)</f>
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="F5" s="9">
         <f>IF(COUNTA(Roster!A2:A701)=0,0,E5/COUNTA(Roster!A2:A701))</f>
-        <v>0.53559322033898304</v>
+        <v>0.5423728813559322</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -52229,11 +52266,11 @@
       </c>
       <c r="E7" s="8">
         <f>COUNTA(Roster!I2:I701)</f>
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="F7" s="9">
         <f>IF(COUNTA(Roster!A2:A701)=0,0,E7/COUNTA(Roster!A2:A701))</f>
-        <v>0.53559322033898304</v>
+        <v>0.53898305084745768</v>
       </c>
     </row>
   </sheetData>
@@ -52280,7 +52317,7 @@
       </c>
       <c r="D2" s="10">
         <f t="shared" ref="D2:D13" si="0">IF(SUM($C$2:$C$13)=0,0,C2/SUM($C$2:$C$13))</f>
-        <v>7.9113924050632917E-2</v>
+        <v>7.8616352201257858E-2</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -52296,7 +52333,7 @@
       </c>
       <c r="D3" s="10">
         <f t="shared" si="0"/>
-        <v>0.12341772151898735</v>
+        <v>0.12264150943396226</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -52312,7 +52349,7 @@
       </c>
       <c r="D4" s="10">
         <f t="shared" si="0"/>
-        <v>9.49367088607595E-2</v>
+        <v>9.4339622641509441E-2</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -52328,7 +52365,7 @@
       </c>
       <c r="D5" s="10">
         <f t="shared" si="0"/>
-        <v>6.9620253164556958E-2</v>
+        <v>6.9182389937106917E-2</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -52344,7 +52381,7 @@
       </c>
       <c r="D6" s="10">
         <f t="shared" si="0"/>
-        <v>0.12025316455696203</v>
+        <v>0.11949685534591195</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -52360,7 +52397,7 @@
       </c>
       <c r="D7" s="10">
         <f t="shared" si="0"/>
-        <v>0.13291139240506328</v>
+        <v>0.13207547169811321</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -52372,11 +52409,11 @@
       </c>
       <c r="C8" s="6">
         <f>COUNTIF(Roster!$I$2:$I$701,A8)</f>
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D8" s="10">
         <f t="shared" si="0"/>
-        <v>0.10126582278481013</v>
+        <v>0.1069182389937107</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -52392,7 +52429,7 @@
       </c>
       <c r="D9" s="10">
         <f t="shared" si="0"/>
-        <v>0.10759493670886076</v>
+        <v>0.1069182389937107</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -52408,7 +52445,7 @@
       </c>
       <c r="D10" s="10">
         <f t="shared" si="0"/>
-        <v>6.6455696202531639E-2</v>
+        <v>6.6037735849056603E-2</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -52424,7 +52461,7 @@
       </c>
       <c r="D11" s="10">
         <f t="shared" si="0"/>
-        <v>3.7974683544303799E-2</v>
+        <v>3.7735849056603772E-2</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -52440,7 +52477,7 @@
       </c>
       <c r="D12" s="10">
         <f t="shared" si="0"/>
-        <v>3.7974683544303799E-2</v>
+        <v>3.7735849056603772E-2</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -52456,7 +52493,7 @@
       </c>
       <c r="D13" s="10">
         <f t="shared" si="0"/>
-        <v>2.8481012658227847E-2</v>
+        <v>2.8301886792452831E-2</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -52465,7 +52502,7 @@
       </c>
       <c r="C14" s="11">
         <f>SUM(C2:C13)</f>
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -52604,7 +52641,7 @@
       </c>
       <c r="B11" s="8">
         <f>COUNTIF(Roster!Q2:Q701,"Yes")</f>
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="C11" s="8" t="s">
         <v>1740</v>
@@ -52616,7 +52653,7 @@
       </c>
       <c r="B12" s="9">
         <f>IF(B5=0,0,B11/B5)</f>
-        <v>0.7533333333333333</v>
+        <v>0.80666666666666664</v>
       </c>
       <c r="C12" s="8" t="s">
         <v>1740</v>
@@ -52628,7 +52665,7 @@
       </c>
       <c r="B13" s="13">
         <f>IFERROR(AVERAGE(Roster!P2:P701),0)</f>
-        <v>3.1610169491525424</v>
+        <v>3.1830508474576269</v>
       </c>
       <c r="C13" s="8" t="s">
         <v>1740</v>

--- a/data/parahumandle_design.xlsx
+++ b/data/parahumandle_design.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Research\Worm Wordle clone\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DDF6A86-3E05-48FC-91EC-80CCD93E6DDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AF6E682-F2AF-41D5-B09B-10C8CCD077E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9423" uniqueCount="1875">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9457" uniqueCount="1876">
   <si>
     <t>Parahumandle – design workbook</t>
   </si>
@@ -5677,6 +5677,9 @@
   </si>
   <si>
     <t>Shaker, Master</t>
+  </si>
+  <si>
+    <t>Unicorn IV</t>
   </si>
 </sst>
 </file>
@@ -32165,7 +32168,7 @@
         <v>107</v>
       </c>
       <c r="G301" s="5" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="H301" s="5" t="s">
         <v>323</v>
@@ -32449,7 +32452,9 @@
       <c r="D306" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="E306" s="5"/>
+      <c r="E306" s="5" t="s">
+        <v>45</v>
+      </c>
       <c r="F306" s="5" t="s">
         <v>46</v>
       </c>
@@ -32474,11 +32479,11 @@
       <c r="O306" s="5"/>
       <c r="P306" s="6">
         <f t="shared" si="8"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q306" s="6" t="str">
         <f t="shared" si="9"/>
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R306" s="5" t="s">
         <v>51</v>
@@ -33463,8 +33468,12 @@
       <c r="D324" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="E324" s="5"/>
-      <c r="F324" s="5"/>
+      <c r="E324" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F324" s="5" t="s">
+        <v>107</v>
+      </c>
       <c r="G324" s="5" t="s">
         <v>47</v>
       </c>
@@ -33486,11 +33495,11 @@
       <c r="O324" s="5"/>
       <c r="P324" s="6">
         <f t="shared" si="10"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q324" s="6" t="str">
         <f t="shared" si="11"/>
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R324" s="5" t="s">
         <v>51</v>
@@ -33814,11 +33823,15 @@
       <c r="C330" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="D330" s="5"/>
+      <c r="D330" s="5" t="s">
+        <v>44</v>
+      </c>
       <c r="E330" s="5" t="s">
         <v>332</v>
       </c>
-      <c r="F330" s="5"/>
+      <c r="F330" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="G330" s="5" t="s">
         <v>47</v>
       </c>
@@ -33840,11 +33853,11 @@
       <c r="O330" s="5"/>
       <c r="P330" s="6">
         <f t="shared" si="10"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q330" s="6" t="str">
         <f t="shared" si="11"/>
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R330" s="5" t="s">
         <v>51</v>
@@ -33937,7 +33950,9 @@
       <c r="D332" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="E332" s="5"/>
+      <c r="E332" s="5" t="s">
+        <v>45</v>
+      </c>
       <c r="F332" s="5" t="s">
         <v>46</v>
       </c>
@@ -33964,11 +33979,11 @@
       <c r="O332" s="5"/>
       <c r="P332" s="6">
         <f t="shared" si="10"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q332" s="6" t="str">
         <f t="shared" si="11"/>
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R332" s="5" t="s">
         <v>51</v>
@@ -34124,7 +34139,9 @@
       <c r="F335" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="G335" s="5"/>
+      <c r="G335" s="5" t="s">
+        <v>1865</v>
+      </c>
       <c r="H335" s="5" t="s">
         <v>96</v>
       </c>
@@ -34143,11 +34160,11 @@
       <c r="O335" s="5"/>
       <c r="P335" s="6">
         <f t="shared" si="10"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q335" s="6" t="str">
         <f t="shared" si="11"/>
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R335" s="5" t="s">
         <v>51</v>
@@ -34722,17 +34739,27 @@
       <c r="A346" s="5" t="s">
         <v>1109</v>
       </c>
-      <c r="B346" s="5"/>
-      <c r="C346" s="5"/>
-      <c r="D346" s="5"/>
+      <c r="B346" s="5" t="s">
+        <v>1875</v>
+      </c>
+      <c r="C346" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="D346" s="5" t="s">
+        <v>44</v>
+      </c>
       <c r="E346" s="5" t="s">
         <v>45</v>
       </c>
       <c r="F346" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="G346" s="5"/>
-      <c r="H346" s="5"/>
+      <c r="G346" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="H346" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="I346" s="5" t="s">
         <v>192</v>
       </c>
@@ -34750,11 +34777,11 @@
       <c r="O346" s="5"/>
       <c r="P346" s="6">
         <f t="shared" si="10"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q346" s="6" t="str">
         <f t="shared" si="11"/>
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R346" s="5" t="s">
         <v>51</v>
@@ -35210,8 +35237,12 @@
       <c r="D355" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="E355" s="5"/>
-      <c r="F355" s="5"/>
+      <c r="E355" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F355" s="5" t="s">
+        <v>107</v>
+      </c>
       <c r="G355" s="5" t="s">
         <v>47</v>
       </c>
@@ -35235,11 +35266,11 @@
       <c r="O355" s="5"/>
       <c r="P355" s="6">
         <f t="shared" si="10"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q355" s="6" t="str">
         <f t="shared" si="11"/>
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R355" s="5" t="s">
         <v>51</v>
@@ -35426,8 +35457,12 @@
       <c r="D359" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="E359" s="5"/>
-      <c r="F359" s="5"/>
+      <c r="E359" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F359" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="G359" s="5" t="s">
         <v>47</v>
       </c>
@@ -35451,11 +35486,11 @@
       <c r="O359" s="5"/>
       <c r="P359" s="6">
         <f t="shared" si="10"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q359" s="6" t="str">
         <f t="shared" si="11"/>
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R359" s="5" t="s">
         <v>51</v>
@@ -35583,8 +35618,12 @@
       <c r="D362" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="E362" s="5"/>
-      <c r="F362" s="5"/>
+      <c r="E362" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F362" s="5" t="s">
+        <v>107</v>
+      </c>
       <c r="G362" s="5" t="s">
         <v>57</v>
       </c>
@@ -35606,11 +35645,11 @@
       <c r="O362" s="5"/>
       <c r="P362" s="6">
         <f t="shared" si="10"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q362" s="6" t="str">
         <f t="shared" si="11"/>
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R362" s="5" t="s">
         <v>51</v>
@@ -35807,7 +35846,9 @@
       <c r="D366" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="E366" s="5"/>
+      <c r="E366" s="5" t="s">
+        <v>45</v>
+      </c>
       <c r="F366" s="5" t="s">
         <v>46</v>
       </c>
@@ -35834,11 +35875,11 @@
       <c r="O366" s="5"/>
       <c r="P366" s="6">
         <f t="shared" si="10"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q366" s="6" t="str">
         <f t="shared" si="11"/>
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R366" s="5" t="s">
         <v>51</v>
@@ -36847,8 +36888,12 @@
       <c r="D384" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="E384" s="5"/>
-      <c r="F384" s="5"/>
+      <c r="E384" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F384" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="G384" s="5" t="s">
         <v>47</v>
       </c>
@@ -36870,11 +36915,11 @@
       <c r="O384" s="5"/>
       <c r="P384" s="6">
         <f t="shared" si="10"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q384" s="6" t="str">
         <f t="shared" si="11"/>
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R384" s="5" t="s">
         <v>51</v>
@@ -36910,8 +36955,12 @@
       <c r="D385" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="E385" s="5"/>
-      <c r="F385" s="5"/>
+      <c r="E385" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F385" s="5" t="s">
+        <v>107</v>
+      </c>
       <c r="G385" s="5" t="s">
         <v>47</v>
       </c>
@@ -36933,11 +36982,11 @@
       <c r="O385" s="5"/>
       <c r="P385" s="6">
         <f t="shared" si="10"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q385" s="6" t="str">
         <f t="shared" si="11"/>
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R385" s="5" t="s">
         <v>51</v>
@@ -36973,9 +37022,15 @@
       <c r="D386" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="E386" s="5"/>
-      <c r="F386" s="5"/>
-      <c r="G386" s="5"/>
+      <c r="E386" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F386" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G386" s="5" t="s">
+        <v>57</v>
+      </c>
       <c r="H386" s="5" t="s">
         <v>48</v>
       </c>
@@ -36994,11 +37049,11 @@
       <c r="O386" s="5"/>
       <c r="P386" s="6">
         <f t="shared" ref="P386:P449" si="12">IF(A386="","",COUNTA(D386:F386)+COUNTA(G386:G386)+COUNTA(H386:H386)+COUNTA(I386:I386))</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q386" s="6" t="str">
         <f t="shared" ref="Q386:Q449" si="13">IF(A386="","",IF(AND(P386=6,UPPER(L386)&lt;&gt;"Y",C386&lt;&gt;""),"Yes","No"))</f>
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R386" s="5" t="s">
         <v>51</v>
@@ -37535,7 +37590,9 @@
       <c r="F396" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="G396" s="5"/>
+      <c r="G396" s="5" t="s">
+        <v>47</v>
+      </c>
       <c r="H396" s="5" t="s">
         <v>910</v>
       </c>
@@ -37554,11 +37611,11 @@
       <c r="O396" s="5"/>
       <c r="P396" s="6">
         <f t="shared" si="12"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q396" s="6" t="str">
         <f t="shared" si="13"/>
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R396" s="5" t="s">
         <v>51</v>
@@ -37750,17 +37807,27 @@
       <c r="C400" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="D400" s="5"/>
-      <c r="E400" s="5"/>
-      <c r="F400" s="5"/>
+      <c r="D400" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="E400" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F400" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="G400" s="5" t="s">
         <v>47</v>
       </c>
       <c r="H400" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="I400" s="5"/>
-      <c r="J400" s="5"/>
+        <v>205</v>
+      </c>
+      <c r="I400" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="J400" s="5" t="s">
+        <v>71</v>
+      </c>
       <c r="K400" s="5"/>
       <c r="L400" s="5"/>
       <c r="M400" s="5"/>
@@ -37770,11 +37837,11 @@
       <c r="O400" s="5"/>
       <c r="P400" s="6">
         <f t="shared" si="12"/>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Q400" s="6" t="str">
         <f t="shared" si="13"/>
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R400" s="5" t="s">
         <v>51</v>
@@ -37806,8 +37873,12 @@
       <c r="D401" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="E401" s="5"/>
-      <c r="F401" s="5"/>
+      <c r="E401" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F401" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="G401" s="5" t="s">
         <v>47</v>
       </c>
@@ -37829,11 +37900,11 @@
       <c r="O401" s="5"/>
       <c r="P401" s="6">
         <f t="shared" si="12"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q401" s="6" t="str">
         <f t="shared" si="13"/>
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R401" s="5" t="s">
         <v>125</v>
@@ -52156,11 +52227,11 @@
       </c>
       <c r="E2" s="8">
         <f>COUNTA(Roster!D2:D701)</f>
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="F2" s="9">
         <f>IF(COUNTA(Roster!A2:A701)=0,0,E2/COUNTA(Roster!A2:A701))</f>
-        <v>0.54406779661016946</v>
+        <v>0.54915254237288136</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -52178,11 +52249,11 @@
       </c>
       <c r="E3" s="8">
         <f>COUNTA(Roster!E2:E701)</f>
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="F3" s="9">
         <f>IF(COUNTA(Roster!A2:A701)=0,0,E3/COUNTA(Roster!A2:A701))</f>
-        <v>0.39491525423728813</v>
+        <v>0.4152542372881356</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -52200,11 +52271,11 @@
       </c>
       <c r="E4" s="8">
         <f>COUNTA(Roster!F2:F701)</f>
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="F4" s="9">
         <f>IF(COUNTA(Roster!A2:A701)=0,0,E4/COUNTA(Roster!A2:A701))</f>
-        <v>0.39491525423728813</v>
+        <v>0.41186440677966102</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -52222,11 +52293,11 @@
       </c>
       <c r="E5" s="8">
         <f>COUNTA(Roster!G2:G701)</f>
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="F5" s="9">
         <f>IF(COUNTA(Roster!A2:A701)=0,0,E5/COUNTA(Roster!A2:A701))</f>
-        <v>0.5423728813559322</v>
+        <v>0.54915254237288136</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -52244,11 +52315,11 @@
       </c>
       <c r="E6" s="8">
         <f>COUNTA(Roster!H2:H701)</f>
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="F6" s="9">
         <f>IF(COUNTA(Roster!A2:A701)=0,0,E6/COUNTA(Roster!A2:A701))</f>
-        <v>0.76779661016949152</v>
+        <v>0.76949152542372878</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
@@ -52266,11 +52337,11 @@
       </c>
       <c r="E7" s="8">
         <f>COUNTA(Roster!I2:I701)</f>
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F7" s="9">
         <f>IF(COUNTA(Roster!A2:A701)=0,0,E7/COUNTA(Roster!A2:A701))</f>
-        <v>0.53898305084745768</v>
+        <v>0.54067796610169494</v>
       </c>
     </row>
   </sheetData>
@@ -52317,7 +52388,7 @@
       </c>
       <c r="D2" s="10">
         <f t="shared" ref="D2:D13" si="0">IF(SUM($C$2:$C$13)=0,0,C2/SUM($C$2:$C$13))</f>
-        <v>7.8616352201257858E-2</v>
+        <v>7.8369905956112859E-2</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -52329,11 +52400,11 @@
       </c>
       <c r="C3" s="6">
         <f>COUNTIF(Roster!$I$2:$I$701,A3)</f>
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D3" s="10">
         <f t="shared" si="0"/>
-        <v>0.12264150943396226</v>
+        <v>0.12539184952978055</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -52349,7 +52420,7 @@
       </c>
       <c r="D4" s="10">
         <f t="shared" si="0"/>
-        <v>9.4339622641509441E-2</v>
+        <v>9.4043887147335428E-2</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -52365,7 +52436,7 @@
       </c>
       <c r="D5" s="10">
         <f t="shared" si="0"/>
-        <v>6.9182389937106917E-2</v>
+        <v>6.8965517241379309E-2</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -52381,7 +52452,7 @@
       </c>
       <c r="D6" s="10">
         <f t="shared" si="0"/>
-        <v>0.11949685534591195</v>
+        <v>0.11912225705329153</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -52397,7 +52468,7 @@
       </c>
       <c r="D7" s="10">
         <f t="shared" si="0"/>
-        <v>0.13207547169811321</v>
+        <v>0.13166144200626959</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -52413,7 +52484,7 @@
       </c>
       <c r="D8" s="10">
         <f t="shared" si="0"/>
-        <v>0.1069182389937107</v>
+        <v>0.10658307210031348</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -52429,7 +52500,7 @@
       </c>
       <c r="D9" s="10">
         <f t="shared" si="0"/>
-        <v>0.1069182389937107</v>
+        <v>0.10658307210031348</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -52445,7 +52516,7 @@
       </c>
       <c r="D10" s="10">
         <f t="shared" si="0"/>
-        <v>6.6037735849056603E-2</v>
+        <v>6.5830721003134793E-2</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -52461,7 +52532,7 @@
       </c>
       <c r="D11" s="10">
         <f t="shared" si="0"/>
-        <v>3.7735849056603772E-2</v>
+        <v>3.7617554858934171E-2</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -52477,7 +52548,7 @@
       </c>
       <c r="D12" s="10">
         <f t="shared" si="0"/>
-        <v>3.7735849056603772E-2</v>
+        <v>3.7617554858934171E-2</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -52493,7 +52564,7 @@
       </c>
       <c r="D13" s="10">
         <f t="shared" si="0"/>
-        <v>2.8301886792452831E-2</v>
+        <v>2.8213166144200628E-2</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -52502,7 +52573,7 @@
       </c>
       <c r="C14" s="11">
         <f>SUM(C2:C13)</f>
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -52641,7 +52712,7 @@
       </c>
       <c r="B11" s="8">
         <f>COUNTIF(Roster!Q2:Q701,"Yes")</f>
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="C11" s="8" t="s">
         <v>1740</v>
@@ -52653,7 +52724,7 @@
       </c>
       <c r="B12" s="9">
         <f>IF(B5=0,0,B11/B5)</f>
-        <v>0.80666666666666664</v>
+        <v>0.91333333333333333</v>
       </c>
       <c r="C12" s="8" t="s">
         <v>1740</v>
@@ -52665,7 +52736,7 @@
       </c>
       <c r="B13" s="13">
         <f>IFERROR(AVERAGE(Roster!P2:P701),0)</f>
-        <v>3.1830508474576269</v>
+        <v>3.2355932203389832</v>
       </c>
       <c r="C13" s="8" t="s">
         <v>1740</v>

--- a/data/parahumandle_design.xlsx
+++ b/data/parahumandle_design.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Research\Worm Wordle clone\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AF6E682-F2AF-41D5-B09B-10C8CCD077E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C8EA23C-DFE8-4D8F-A0FB-3A08FFF18A3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4290" yWindow="2805" windowWidth="28800" windowHeight="15345" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9457" uniqueCount="1876">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9465" uniqueCount="1879">
   <si>
     <t>Parahumandle – design workbook</t>
   </si>
@@ -5680,6 +5680,15 @@
   </si>
   <si>
     <t>Unicorn IV</t>
+  </si>
+  <si>
+    <t>The Flock</t>
+  </si>
+  <si>
+    <t>Erring Right</t>
+  </si>
+  <si>
+    <t>The Shepherds</t>
   </si>
 </sst>
 </file>
@@ -19950,7 +19959,7 @@
         <v>57</v>
       </c>
       <c r="H86" s="5" t="s">
-        <v>58</v>
+        <v>1876</v>
       </c>
       <c r="I86" s="5" t="s">
         <v>192</v>
@@ -20335,9 +20344,15 @@
       <c r="D93" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="E93" s="5"/>
-      <c r="F93" s="5"/>
-      <c r="G93" s="5"/>
+      <c r="E93" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F93" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="G93" s="5" t="s">
+        <v>1865</v>
+      </c>
       <c r="H93" s="5" t="s">
         <v>77</v>
       </c>
@@ -20352,7 +20367,7 @@
       <c r="O93" s="5"/>
       <c r="P93" s="6">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Q93" s="6" t="str">
         <f t="shared" si="3"/>
@@ -21298,10 +21313,10 @@
         <v>46</v>
       </c>
       <c r="G109" s="5" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="H109" s="5" t="s">
-        <v>83</v>
+        <v>1876</v>
       </c>
       <c r="I109" s="5" t="s">
         <v>78</v>
@@ -26210,7 +26225,7 @@
         <v>57</v>
       </c>
       <c r="H194" s="5" t="s">
-        <v>319</v>
+        <v>1876</v>
       </c>
       <c r="I194" s="5"/>
       <c r="J194" s="5"/>
@@ -28013,10 +28028,10 @@
         <v>46</v>
       </c>
       <c r="G226" s="5" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="H226" s="5" t="s">
-        <v>272</v>
+        <v>1876</v>
       </c>
       <c r="I226" s="5" t="s">
         <v>91</v>
@@ -31037,10 +31052,10 @@
         <v>46</v>
       </c>
       <c r="G280" s="5" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="H280" s="5" t="s">
-        <v>83</v>
+        <v>1876</v>
       </c>
       <c r="I280" s="5" t="s">
         <v>123</v>
@@ -32171,7 +32186,7 @@
         <v>57</v>
       </c>
       <c r="H301" s="5" t="s">
-        <v>323</v>
+        <v>1877</v>
       </c>
       <c r="I301" s="5" t="s">
         <v>119</v>
@@ -40654,13 +40669,21 @@
       <c r="C453" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="D453" s="5"/>
-      <c r="E453" s="5"/>
-      <c r="F453" s="5"/>
+      <c r="D453" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="E453" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F453" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="G453" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="H453" s="5"/>
+        <v>57</v>
+      </c>
+      <c r="H453" s="5" t="s">
+        <v>1876</v>
+      </c>
       <c r="I453" s="5" t="s">
         <v>49</v>
       </c>
@@ -40676,11 +40699,11 @@
       <c r="O453" s="5"/>
       <c r="P453" s="6">
         <f t="shared" si="14"/>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Q453" s="6" t="str">
         <f t="shared" si="15"/>
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R453" s="5" t="s">
         <v>125</v>
@@ -40769,7 +40792,9 @@
       <c r="D455" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="E455" s="5"/>
+      <c r="E455" s="5" t="s">
+        <v>45</v>
+      </c>
       <c r="F455" s="5" t="s">
         <v>107</v>
       </c>
@@ -40777,7 +40802,7 @@
         <v>57</v>
       </c>
       <c r="H455" s="5" t="s">
-        <v>96</v>
+        <v>1878</v>
       </c>
       <c r="I455" s="5" t="s">
         <v>78</v>
@@ -40794,11 +40819,11 @@
       <c r="O455" s="5"/>
       <c r="P455" s="6">
         <f t="shared" si="14"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q455" s="6" t="str">
         <f t="shared" si="15"/>
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R455" s="5" t="s">
         <v>51</v>
@@ -52227,11 +52252,11 @@
       </c>
       <c r="E2" s="8">
         <f>COUNTA(Roster!D2:D701)</f>
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F2" s="9">
         <f>IF(COUNTA(Roster!A2:A701)=0,0,E2/COUNTA(Roster!A2:A701))</f>
-        <v>0.54915254237288136</v>
+        <v>0.55084745762711862</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -52249,11 +52274,11 @@
       </c>
       <c r="E3" s="8">
         <f>COUNTA(Roster!E2:E701)</f>
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="F3" s="9">
         <f>IF(COUNTA(Roster!A2:A701)=0,0,E3/COUNTA(Roster!A2:A701))</f>
-        <v>0.4152542372881356</v>
+        <v>0.42033898305084744</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -52271,11 +52296,11 @@
       </c>
       <c r="E4" s="8">
         <f>COUNTA(Roster!F2:F701)</f>
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="F4" s="9">
         <f>IF(COUNTA(Roster!A2:A701)=0,0,E4/COUNTA(Roster!A2:A701))</f>
-        <v>0.41186440677966102</v>
+        <v>0.4152542372881356</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -52293,11 +52318,11 @@
       </c>
       <c r="E5" s="8">
         <f>COUNTA(Roster!G2:G701)</f>
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F5" s="9">
         <f>IF(COUNTA(Roster!A2:A701)=0,0,E5/COUNTA(Roster!A2:A701))</f>
-        <v>0.54915254237288136</v>
+        <v>0.55084745762711862</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -52315,11 +52340,11 @@
       </c>
       <c r="E6" s="8">
         <f>COUNTA(Roster!H2:H701)</f>
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="F6" s="9">
         <f>IF(COUNTA(Roster!A2:A701)=0,0,E6/COUNTA(Roster!A2:A701))</f>
-        <v>0.76949152542372878</v>
+        <v>0.77118644067796616</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
@@ -52712,7 +52737,7 @@
       </c>
       <c r="B11" s="8">
         <f>COUNTIF(Roster!Q2:Q701,"Yes")</f>
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C11" s="8" t="s">
         <v>1740</v>
@@ -52724,7 +52749,7 @@
       </c>
       <c r="B12" s="9">
         <f>IF(B5=0,0,B11/B5)</f>
-        <v>0.91333333333333333</v>
+        <v>0.92666666666666664</v>
       </c>
       <c r="C12" s="8" t="s">
         <v>1740</v>
@@ -52736,7 +52761,7 @@
       </c>
       <c r="B13" s="13">
         <f>IFERROR(AVERAGE(Roster!P2:P701),0)</f>
-        <v>3.2355932203389832</v>
+        <v>3.2491525423728813</v>
       </c>
       <c r="C13" s="8" t="s">
         <v>1740</v>

--- a/data/parahumandle_design.xlsx
+++ b/data/parahumandle_design.xlsx
@@ -5259,10 +5259,10 @@
     <t>Reset time</t>
   </si>
   <si>
-    <t>Midnight CET</t>
-  </si>
-  <si>
-    <t>As on Eldendle</t>
+    <t>Midnight local time</t>
+  </si>
+  <si>
+    <t>Each player's own midnight, as on Wordle</t>
   </si>
   <si>
     <t>— Live progress —</t>
@@ -5316,7 +5316,7 @@
     <t>Daily seed</t>
   </si>
   <si>
-    <t>Deterministic daily puzzle; resets midnight CET; progress in local storage.</t>
+    <t>Deterministic daily puzzle; resets at each player's local midnight; progress in local storage.</t>
   </si>
   <si>
     <t>Alias handling</t>

--- a/data/parahumandle_design.xlsx
+++ b/data/parahumandle_design.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Research\Worm Wordle clone\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D66D0E0F-5769-40F5-9405-AA9D170AB080}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AABEB360-545A-4B00-858A-2B9A0447D273}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9563" uniqueCount="1904">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9573" uniqueCount="1907">
   <si>
     <t>Parahumandle – design workbook</t>
   </si>
@@ -5764,6 +5764,15 @@
   </si>
   <si>
     <t>The Wardens</t>
+  </si>
+  <si>
+    <t>The Mall Cluster</t>
+  </si>
+  <si>
+    <t>Blaster, Striker</t>
+  </si>
+  <si>
+    <t>Grab-bag cape. Can treat any direction as down which allowed him to leap without jumping movement. Can create large gauntlets that fit over his arms. Can force negative emotions on people he touches with his gauntlets or apply dedicated emotions from his tinkered projectiles. Can punch through inorganic materials.</t>
   </si>
 </sst>
 </file>
@@ -41527,8 +41536,12 @@
       <c r="D465" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="E465" s="5"/>
-      <c r="F465" s="5"/>
+      <c r="E465" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F465" s="5" t="s">
+        <v>107</v>
+      </c>
       <c r="G465" s="5" t="s">
         <v>47</v>
       </c>
@@ -41550,11 +41563,11 @@
       <c r="O465" s="5"/>
       <c r="P465" s="6">
         <f t="shared" si="14"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q465" s="6" t="str">
         <f t="shared" si="15"/>
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R465" s="5" t="s">
         <v>51</v>
@@ -42908,15 +42921,27 @@
       <c r="C489" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="D489" s="5"/>
-      <c r="E489" s="5"/>
-      <c r="F489" s="5"/>
+      <c r="D489" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="E489" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F489" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="G489" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="H489" s="5"/>
-      <c r="I489" s="5"/>
-      <c r="J489" s="5"/>
+        <v>47</v>
+      </c>
+      <c r="H489" s="5" t="s">
+        <v>1904</v>
+      </c>
+      <c r="I489" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="J489" s="5" t="s">
+        <v>1905</v>
+      </c>
       <c r="K489" s="5"/>
       <c r="L489" s="5"/>
       <c r="M489" s="5"/>
@@ -42926,20 +42951,24 @@
       <c r="O489" s="5"/>
       <c r="P489" s="6">
         <f t="shared" si="16"/>
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Q489" s="6" t="str">
         <f t="shared" si="15"/>
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R489" s="5" t="s">
         <v>51</v>
       </c>
       <c r="S489" s="5"/>
-      <c r="T489" s="5"/>
-      <c r="U489" s="5"/>
+      <c r="T489" s="5" t="s">
+        <v>1906</v>
+      </c>
+      <c r="U489" s="5" t="s">
+        <v>1904</v>
+      </c>
       <c r="V489" s="5" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="W489" s="5" t="s">
         <v>128</v>
@@ -52659,11 +52688,11 @@
       </c>
       <c r="E2" s="8">
         <f>COUNTA(Roster!D2:D705)</f>
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F2" s="9">
         <f>IF(COUNTA(Roster!A2:A705)=0,0,E2/COUNTA(Roster!A2:A705))</f>
-        <v>0.55892255892255893</v>
+        <v>0.56060606060606055</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -52681,11 +52710,11 @@
       </c>
       <c r="E3" s="8">
         <f>COUNTA(Roster!E2:E705)</f>
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="F3" s="9">
         <f>IF(COUNTA(Roster!A2:A705)=0,0,E3/COUNTA(Roster!A2:A705))</f>
-        <v>0.43265993265993263</v>
+        <v>0.43602693602693604</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -52703,11 +52732,11 @@
       </c>
       <c r="E4" s="8">
         <f>COUNTA(Roster!F2:F705)</f>
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="F4" s="9">
         <f>IF(COUNTA(Roster!A2:A705)=0,0,E4/COUNTA(Roster!A2:A705))</f>
-        <v>0.42760942760942761</v>
+        <v>0.43097643097643096</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -52747,11 +52776,11 @@
       </c>
       <c r="E6" s="8">
         <f>COUNTA(Roster!H2:H705)</f>
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="F6" s="9">
         <f>IF(COUNTA(Roster!A2:A705)=0,0,E6/COUNTA(Roster!A2:A705))</f>
-        <v>0.77441077441077444</v>
+        <v>0.77609427609427606</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
@@ -52769,11 +52798,11 @@
       </c>
       <c r="E7" s="8">
         <f>COUNTA(Roster!I2:I705)</f>
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F7" s="9">
         <f>IF(COUNTA(Roster!A2:A705)=0,0,E7/COUNTA(Roster!A2:A705))</f>
-        <v>0.54882154882154888</v>
+        <v>0.5505050505050505</v>
       </c>
     </row>
   </sheetData>
@@ -52820,7 +52849,7 @@
       </c>
       <c r="D2" s="10">
         <f t="shared" ref="D2:D13" si="0">IF(SUM($C$2:$C$13)=0,0,C2/SUM($C$2:$C$13))</f>
-        <v>7.9754601226993863E-2</v>
+        <v>7.9510703363914373E-2</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -52836,7 +52865,7 @@
       </c>
       <c r="D3" s="10">
         <f t="shared" si="0"/>
-        <v>0.12576687116564417</v>
+        <v>0.12538226299694188</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -52852,7 +52881,7 @@
       </c>
       <c r="D4" s="10">
         <f t="shared" si="0"/>
-        <v>9.202453987730061E-2</v>
+        <v>9.1743119266055051E-2</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -52868,7 +52897,7 @@
       </c>
       <c r="D5" s="10">
         <f t="shared" si="0"/>
-        <v>6.7484662576687116E-2</v>
+        <v>6.7278287461773695E-2</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -52884,7 +52913,7 @@
       </c>
       <c r="D6" s="10">
         <f t="shared" si="0"/>
-        <v>0.1165644171779141</v>
+        <v>0.11620795107033639</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -52896,11 +52925,11 @@
       </c>
       <c r="C7" s="6">
         <f>COUNTIF(Roster!$I$2:$I$705,A7)</f>
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D7" s="10">
         <f t="shared" si="0"/>
-        <v>0.13496932515337423</v>
+        <v>0.13761467889908258</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -52916,7 +52945,7 @@
       </c>
       <c r="D8" s="10">
         <f t="shared" si="0"/>
-        <v>0.10736196319018405</v>
+        <v>0.10703363914373089</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -52932,7 +52961,7 @@
       </c>
       <c r="D9" s="10">
         <f t="shared" si="0"/>
-        <v>0.10429447852760736</v>
+        <v>0.10397553516819572</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -52948,7 +52977,7 @@
       </c>
       <c r="D10" s="10">
         <f t="shared" si="0"/>
-        <v>7.0552147239263799E-2</v>
+        <v>7.0336391437308868E-2</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -52964,7 +52993,7 @@
       </c>
       <c r="D11" s="10">
         <f t="shared" si="0"/>
-        <v>3.6809815950920248E-2</v>
+        <v>3.669724770642202E-2</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -52980,7 +53009,7 @@
       </c>
       <c r="D12" s="10">
         <f t="shared" si="0"/>
-        <v>3.6809815950920248E-2</v>
+        <v>3.669724770642202E-2</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -52996,7 +53025,7 @@
       </c>
       <c r="D13" s="10">
         <f t="shared" si="0"/>
-        <v>2.7607361963190184E-2</v>
+        <v>2.7522935779816515E-2</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -53005,7 +53034,7 @@
       </c>
       <c r="C14" s="11">
         <f>SUM(C2:C13)</f>
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -53144,7 +53173,7 @@
       </c>
       <c r="B11" s="8">
         <f>COUNTIF(Roster!Q2:Q705,"Yes")</f>
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C11" s="8" t="s">
         <v>1739</v>
@@ -53156,7 +53185,7 @@
       </c>
       <c r="B12" s="9">
         <f>IF(B5=0,0,B11/B5)</f>
-        <v>1.0133333333333334</v>
+        <v>1.0266666666666666</v>
       </c>
       <c r="C12" s="8" t="s">
         <v>1739</v>
@@ -53168,7 +53197,7 @@
       </c>
       <c r="B13" s="13">
         <f>IFERROR(AVERAGE(Roster!P2:P705),0)</f>
-        <v>3.3047138047138045</v>
+        <v>3.3164983164983166</v>
       </c>
       <c r="C13" s="8" t="s">
         <v>1739</v>

--- a/data/parahumandle_design.xlsx
+++ b/data/parahumandle_design.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Research\Worm Wordle clone\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AABEB360-545A-4B00-858A-2B9A0447D273}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93C419EC-746C-4259-8B59-624CBFB11E16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9573" uniqueCount="1907">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9578" uniqueCount="1908">
   <si>
     <t>Parahumandle – design workbook</t>
   </si>
@@ -5773,6 +5773,9 @@
   </si>
   <si>
     <t>Grab-bag cape. Can treat any direction as down which allowed him to leap without jumping movement. Can create large gauntlets that fit over his arms. Can force negative emotions on people he touches with his gauntlets or apply dedicated emotions from his tinkered projectiles. Can punch through inorganic materials.</t>
+  </si>
+  <si>
+    <t>Stranger, Shaker</t>
   </si>
 </sst>
 </file>
@@ -21658,7 +21661,7 @@
         <v>47</v>
       </c>
       <c r="H113" s="5" t="s">
-        <v>58</v>
+        <v>224</v>
       </c>
       <c r="I113" s="5" t="s">
         <v>49</v>
@@ -21886,16 +21889,24 @@
       <c r="D117" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="E117" s="5"/>
-      <c r="F117" s="5"/>
+      <c r="E117" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F117" s="5" t="s">
+        <v>107</v>
+      </c>
       <c r="G117" s="5" t="s">
-        <v>57</v>
+        <v>1864</v>
       </c>
       <c r="H117" s="5" t="s">
         <v>494</v>
       </c>
-      <c r="I117" s="5"/>
-      <c r="J117" s="5"/>
+      <c r="I117" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="J117" s="5" t="s">
+        <v>1907</v>
+      </c>
       <c r="K117" s="5"/>
       <c r="L117" s="5"/>
       <c r="M117" s="5"/>
@@ -21905,11 +21916,11 @@
       <c r="O117" s="5"/>
       <c r="P117" s="6">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q117" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R117" s="5" t="s">
         <v>51</v>
@@ -22189,9 +22200,11 @@
       <c r="F122" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="G122" s="5"/>
+      <c r="G122" s="5" t="s">
+        <v>1864</v>
+      </c>
       <c r="H122" s="5" t="s">
-        <v>96</v>
+        <v>1136</v>
       </c>
       <c r="I122" s="5" t="s">
         <v>59</v>
@@ -22208,11 +22221,11 @@
       <c r="O122" s="5"/>
       <c r="P122" s="6">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q122" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R122" s="5" t="s">
         <v>51</v>
@@ -23849,7 +23862,7 @@
         <v>47</v>
       </c>
       <c r="H150" s="5" t="s">
-        <v>77</v>
+        <v>214</v>
       </c>
       <c r="I150" s="5" t="s">
         <v>78</v>
@@ -52710,11 +52723,11 @@
       </c>
       <c r="E3" s="8">
         <f>COUNTA(Roster!E2:E705)</f>
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F3" s="9">
         <f>IF(COUNTA(Roster!A2:A705)=0,0,E3/COUNTA(Roster!A2:A705))</f>
-        <v>0.43602693602693604</v>
+        <v>0.43771043771043772</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -52732,11 +52745,11 @@
       </c>
       <c r="E4" s="8">
         <f>COUNTA(Roster!F2:F705)</f>
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F4" s="9">
         <f>IF(COUNTA(Roster!A2:A705)=0,0,E4/COUNTA(Roster!A2:A705))</f>
-        <v>0.43097643097643096</v>
+        <v>0.43265993265993263</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -52754,11 +52767,11 @@
       </c>
       <c r="E5" s="8">
         <f>COUNTA(Roster!G2:G705)</f>
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F5" s="9">
         <f>IF(COUNTA(Roster!A2:A705)=0,0,E5/COUNTA(Roster!A2:A705))</f>
-        <v>0.56228956228956228</v>
+        <v>0.56397306397306401</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -52798,11 +52811,11 @@
       </c>
       <c r="E7" s="8">
         <f>COUNTA(Roster!I2:I705)</f>
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F7" s="9">
         <f>IF(COUNTA(Roster!A2:A705)=0,0,E7/COUNTA(Roster!A2:A705))</f>
-        <v>0.5505050505050505</v>
+        <v>0.55218855218855223</v>
       </c>
     </row>
   </sheetData>
@@ -52845,11 +52858,11 @@
       </c>
       <c r="C2" s="6">
         <f>COUNTIF(Roster!$I$2:$I$705,A2)</f>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D2" s="10">
         <f t="shared" ref="D2:D13" si="0">IF(SUM($C$2:$C$13)=0,0,C2/SUM($C$2:$C$13))</f>
-        <v>7.9510703363914373E-2</v>
+        <v>8.2317073170731711E-2</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -52865,7 +52878,7 @@
       </c>
       <c r="D3" s="10">
         <f t="shared" si="0"/>
-        <v>0.12538226299694188</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -52881,7 +52894,7 @@
       </c>
       <c r="D4" s="10">
         <f t="shared" si="0"/>
-        <v>9.1743119266055051E-2</v>
+        <v>9.1463414634146339E-2</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -52897,7 +52910,7 @@
       </c>
       <c r="D5" s="10">
         <f t="shared" si="0"/>
-        <v>6.7278287461773695E-2</v>
+        <v>6.7073170731707321E-2</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -52913,7 +52926,7 @@
       </c>
       <c r="D6" s="10">
         <f t="shared" si="0"/>
-        <v>0.11620795107033639</v>
+        <v>0.11585365853658537</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -52929,7 +52942,7 @@
       </c>
       <c r="D7" s="10">
         <f t="shared" si="0"/>
-        <v>0.13761467889908258</v>
+        <v>0.13719512195121952</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -52945,7 +52958,7 @@
       </c>
       <c r="D8" s="10">
         <f t="shared" si="0"/>
-        <v>0.10703363914373089</v>
+        <v>0.10670731707317073</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -52961,7 +52974,7 @@
       </c>
       <c r="D9" s="10">
         <f t="shared" si="0"/>
-        <v>0.10397553516819572</v>
+        <v>0.10365853658536585</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -52977,7 +52990,7 @@
       </c>
       <c r="D10" s="10">
         <f t="shared" si="0"/>
-        <v>7.0336391437308868E-2</v>
+        <v>7.0121951219512202E-2</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -52993,7 +53006,7 @@
       </c>
       <c r="D11" s="10">
         <f t="shared" si="0"/>
-        <v>3.669724770642202E-2</v>
+        <v>3.6585365853658534E-2</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -53009,7 +53022,7 @@
       </c>
       <c r="D12" s="10">
         <f t="shared" si="0"/>
-        <v>3.669724770642202E-2</v>
+        <v>3.6585365853658534E-2</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -53025,7 +53038,7 @@
       </c>
       <c r="D13" s="10">
         <f t="shared" si="0"/>
-        <v>2.7522935779816515E-2</v>
+        <v>2.7439024390243903E-2</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -53034,7 +53047,7 @@
       </c>
       <c r="C14" s="11">
         <f>SUM(C2:C13)</f>
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -53173,7 +53186,7 @@
       </c>
       <c r="B11" s="8">
         <f>COUNTIF(Roster!Q2:Q705,"Yes")</f>
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C11" s="8" t="s">
         <v>1739</v>
@@ -53185,7 +53198,7 @@
       </c>
       <c r="B12" s="9">
         <f>IF(B5=0,0,B11/B5)</f>
-        <v>1.0266666666666666</v>
+        <v>1.04</v>
       </c>
       <c r="C12" s="8" t="s">
         <v>1739</v>
@@ -53197,7 +53210,7 @@
       </c>
       <c r="B13" s="13">
         <f>IFERROR(AVERAGE(Roster!P2:P705),0)</f>
-        <v>3.3164983164983166</v>
+        <v>3.3232323232323231</v>
       </c>
       <c r="C13" s="8" t="s">
         <v>1739</v>

--- a/data/parahumandle_design.xlsx
+++ b/data/parahumandle_design.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Research\Worm Wordle clone\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12F78AB2-0AE2-4F23-A120-A7478BC7966C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2152F47-E54C-4CFF-97C1-0F9010868C8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5925" yWindow="4785" windowWidth="28800" windowHeight="15345" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18652,7 +18652,7 @@
         <v>57</v>
       </c>
       <c r="H61" s="5" t="s">
-        <v>313</v>
+        <v>1902</v>
       </c>
       <c r="I61" s="5" t="s">
         <v>123</v>

--- a/data/parahumandle_design.xlsx
+++ b/data/parahumandle_design.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Research\Worm Wordle clone\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2152F47-E54C-4CFF-97C1-0F9010868C8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F22B0D38-A59F-48BD-BA99-1FCDE949E3D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5925" yWindow="4785" windowWidth="28800" windowHeight="15345" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9578" uniqueCount="1907">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9586" uniqueCount="1909">
   <si>
     <t>Parahumandle – design workbook</t>
   </si>
@@ -5773,6 +5773,12 @@
   </si>
   <si>
     <t>Stranger, Shaker</t>
+  </si>
+  <si>
+    <t>Unknown powers. Tended to hold his abilities back to avoid scaring people.</t>
+  </si>
+  <si>
+    <t>Andrew Hawke</t>
   </si>
 </sst>
 </file>
@@ -47801,7 +47807,9 @@
       <c r="G575" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="H575" s="5"/>
+      <c r="H575" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="I575" s="5"/>
       <c r="J575" s="5"/>
       <c r="K575" s="5"/>
@@ -47813,7 +47821,7 @@
       <c r="O575" s="5"/>
       <c r="P575" s="6">
         <f t="shared" si="18"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q575" s="6" t="str">
         <f t="shared" si="17"/>
@@ -47822,8 +47830,12 @@
       <c r="R575" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="S575" s="5"/>
-      <c r="T575" s="5"/>
+      <c r="S575" s="5" t="s">
+        <v>1908</v>
+      </c>
+      <c r="T575" s="5" t="s">
+        <v>1907</v>
+      </c>
       <c r="U575" s="5"/>
       <c r="V575" s="5" t="s">
         <v>47</v>
@@ -48124,9 +48136,15 @@
       <c r="D581" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="E581" s="5"/>
-      <c r="F581" s="5"/>
-      <c r="G581" s="5"/>
+      <c r="E581" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F581" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G581" s="5" t="s">
+        <v>57</v>
+      </c>
       <c r="H581" s="5" t="s">
         <v>83</v>
       </c>
@@ -48147,11 +48165,11 @@
       <c r="O581" s="5"/>
       <c r="P581" s="6">
         <f t="shared" si="18"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q581" s="6" t="str">
         <f t="shared" si="19"/>
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R581" s="5" t="s">
         <v>51</v>
@@ -48450,7 +48468,9 @@
       <c r="D587" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="E587" s="5"/>
+      <c r="E587" s="5" t="s">
+        <v>45</v>
+      </c>
       <c r="F587" s="5" t="s">
         <v>107</v>
       </c>
@@ -48461,11 +48481,11 @@
         <v>1131</v>
       </c>
       <c r="I587" s="5" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="J587" s="5"/>
       <c r="K587" s="5" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="L587" s="5"/>
       <c r="M587" s="5"/>
@@ -48475,11 +48495,11 @@
       <c r="O587" s="5"/>
       <c r="P587" s="6">
         <f t="shared" si="18"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q587" s="6" t="str">
         <f t="shared" si="19"/>
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R587" s="5" t="s">
         <v>51</v>
@@ -48674,7 +48694,9 @@
       <c r="D591" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="E591" s="5"/>
+      <c r="E591" s="5" t="s">
+        <v>45</v>
+      </c>
       <c r="F591" s="5" t="s">
         <v>107</v>
       </c>
@@ -48699,11 +48721,11 @@
       <c r="O591" s="5"/>
       <c r="P591" s="6">
         <f t="shared" si="18"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q591" s="6" t="str">
         <f t="shared" si="19"/>
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R591" s="5" t="s">
         <v>51</v>
@@ -52720,11 +52742,11 @@
       </c>
       <c r="E3" s="8">
         <f>COUNTA(Roster!E2:E705)</f>
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="F3" s="9">
         <f>IF(COUNTA(Roster!A2:A705)=0,0,E3/COUNTA(Roster!A2:A705))</f>
-        <v>0.43771043771043772</v>
+        <v>0.44276094276094274</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -52742,11 +52764,11 @@
       </c>
       <c r="E4" s="8">
         <f>COUNTA(Roster!F2:F705)</f>
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F4" s="9">
         <f>IF(COUNTA(Roster!A2:A705)=0,0,E4/COUNTA(Roster!A2:A705))</f>
-        <v>0.43265993265993263</v>
+        <v>0.43434343434343436</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -52764,11 +52786,11 @@
       </c>
       <c r="E5" s="8">
         <f>COUNTA(Roster!G2:G705)</f>
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="F5" s="9">
         <f>IF(COUNTA(Roster!A2:A705)=0,0,E5/COUNTA(Roster!A2:A705))</f>
-        <v>0.56397306397306401</v>
+        <v>0.56565656565656564</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -52786,11 +52808,11 @@
       </c>
       <c r="E6" s="8">
         <f>COUNTA(Roster!H2:H705)</f>
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="F6" s="9">
         <f>IF(COUNTA(Roster!A2:A705)=0,0,E6/COUNTA(Roster!A2:A705))</f>
-        <v>0.77609427609427606</v>
+        <v>0.77777777777777779</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
@@ -52871,11 +52893,11 @@
       </c>
       <c r="C3" s="6">
         <f>COUNTIF(Roster!$I$2:$I$705,A3)</f>
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D3" s="10">
         <f t="shared" si="0"/>
-        <v>0.12804878048780488</v>
+        <v>0.13109756097560976</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -52983,11 +53005,11 @@
       </c>
       <c r="C10" s="6">
         <f>COUNTIF(Roster!$I$2:$I$705,A10)</f>
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D10" s="10">
         <f t="shared" si="0"/>
-        <v>7.0121951219512202E-2</v>
+        <v>6.7073170731707321E-2</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -53183,7 +53205,7 @@
       </c>
       <c r="B11" s="8">
         <f>COUNTIF(Roster!Q2:Q705,"Yes")</f>
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C11" s="8" t="s">
         <v>1738</v>
@@ -53195,7 +53217,7 @@
       </c>
       <c r="B12" s="9">
         <f>IF(B5=0,0,B11/B5)</f>
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="C12" s="8" t="s">
         <v>1738</v>
@@ -53207,7 +53229,7 @@
       </c>
       <c r="B13" s="13">
         <f>IFERROR(AVERAGE(Roster!P2:P705),0)</f>
-        <v>3.3232323232323231</v>
+        <v>3.3333333333333335</v>
       </c>
       <c r="C13" s="8" t="s">
         <v>1738</v>

--- a/data/parahumandle_design.xlsx
+++ b/data/parahumandle_design.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Research\Worm Wordle clone\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F22B0D38-A59F-48BD-BA99-1FCDE949E3D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA572BE7-7B18-4A06-93ED-DEC5A07921F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9060" yWindow="4110" windowWidth="28800" windowHeight="15345" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9586" uniqueCount="1909">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9599" uniqueCount="1911">
   <si>
     <t>Parahumandle – design workbook</t>
   </si>
@@ -5779,6 +5779,12 @@
   </si>
   <si>
     <t>Andrew Hawke</t>
+  </si>
+  <si>
+    <t>A gravity manipulator who can create multiple conflicting gravity fields within an area, alongside a thinker-aspect that allows her to perceive gravity wells.</t>
+  </si>
+  <si>
+    <t>Brianna</t>
   </si>
 </sst>
 </file>
@@ -26810,7 +26816,7 @@
         <v>214</v>
       </c>
       <c r="I202" s="5" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="J202" s="5"/>
       <c r="K202" s="5" t="s">
@@ -29967,10 +29973,10 @@
         <v>313</v>
       </c>
       <c r="I257" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="J257" s="5" t="s">
         <v>49</v>
-      </c>
-      <c r="J257" s="5" t="s">
-        <v>78</v>
       </c>
       <c r="K257" s="5" t="s">
         <v>894</v>
@@ -34901,17 +34907,27 @@
       <c r="C345" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="D345" s="5"/>
-      <c r="E345" s="5"/>
-      <c r="F345" s="5"/>
+      <c r="D345" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="E345" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F345" s="5" t="s">
+        <v>107</v>
+      </c>
       <c r="G345" s="5" t="s">
         <v>57</v>
       </c>
       <c r="H345" s="5" t="s">
-        <v>318</v>
-      </c>
-      <c r="I345" s="5"/>
-      <c r="J345" s="5"/>
+        <v>1876</v>
+      </c>
+      <c r="I345" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="J345" s="5" t="s">
+        <v>49</v>
+      </c>
       <c r="K345" s="5"/>
       <c r="L345" s="5"/>
       <c r="M345" s="5"/>
@@ -34921,17 +34937,21 @@
       <c r="O345" s="5"/>
       <c r="P345" s="6">
         <f t="shared" si="12"/>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Q345" s="6" t="str">
         <f t="shared" si="11"/>
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R345" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="S345" s="5"/>
-      <c r="T345" s="5"/>
+      <c r="S345" s="5" t="s">
+        <v>1910</v>
+      </c>
+      <c r="T345" s="5" t="s">
+        <v>1909</v>
+      </c>
       <c r="U345" s="5" t="s">
         <v>318</v>
       </c>
@@ -34957,8 +34977,12 @@
       <c r="D346" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="E346" s="5"/>
-      <c r="F346" s="5"/>
+      <c r="E346" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F346" s="5" t="s">
+        <v>107</v>
+      </c>
       <c r="G346" s="5" t="s">
         <v>57</v>
       </c>
@@ -34980,11 +35004,11 @@
       <c r="O346" s="5"/>
       <c r="P346" s="6">
         <f t="shared" si="12"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q346" s="6" t="str">
         <f t="shared" si="11"/>
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R346" s="5" t="s">
         <v>51</v>
@@ -35116,8 +35140,12 @@
       <c r="D349" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="E349" s="5"/>
-      <c r="F349" s="5"/>
+      <c r="E349" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F349" s="5" t="s">
+        <v>107</v>
+      </c>
       <c r="G349" s="5" t="s">
         <v>47</v>
       </c>
@@ -35127,7 +35155,9 @@
       <c r="I349" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="J349" s="5"/>
+      <c r="J349" s="5" t="s">
+        <v>49</v>
+      </c>
       <c r="K349" s="5" t="s">
         <v>71</v>
       </c>
@@ -35139,11 +35169,11 @@
       <c r="O349" s="5"/>
       <c r="P349" s="6">
         <f t="shared" si="12"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q349" s="6" t="str">
         <f t="shared" si="11"/>
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R349" s="5" t="s">
         <v>51</v>
@@ -35785,7 +35815,9 @@
       <c r="E361" s="5" t="s">
         <v>331</v>
       </c>
-      <c r="F361" s="5"/>
+      <c r="F361" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="G361" s="5" t="s">
         <v>57</v>
       </c>
@@ -35809,11 +35841,11 @@
       <c r="O361" s="5"/>
       <c r="P361" s="6">
         <f t="shared" si="12"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q361" s="6" t="str">
         <f t="shared" si="11"/>
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R361" s="5" t="s">
         <v>51</v>
@@ -52648,7 +52680,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>I2:I705</xm:sqref>
+          <xm:sqref>I2:I256 I258:I705 J257</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0100-000006000000}">
           <x14:formula1>
@@ -52720,11 +52752,11 @@
       </c>
       <c r="E2" s="8">
         <f>COUNTA(Roster!D2:D705)</f>
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F2" s="9">
         <f>IF(COUNTA(Roster!A2:A705)=0,0,E2/COUNTA(Roster!A2:A705))</f>
-        <v>0.56060606060606055</v>
+        <v>0.56228956228956228</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -52742,11 +52774,11 @@
       </c>
       <c r="E3" s="8">
         <f>COUNTA(Roster!E2:E705)</f>
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="F3" s="9">
         <f>IF(COUNTA(Roster!A2:A705)=0,0,E3/COUNTA(Roster!A2:A705))</f>
-        <v>0.44276094276094274</v>
+        <v>0.44781144781144783</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -52764,11 +52796,11 @@
       </c>
       <c r="E4" s="8">
         <f>COUNTA(Roster!F2:F705)</f>
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="F4" s="9">
         <f>IF(COUNTA(Roster!A2:A705)=0,0,E4/COUNTA(Roster!A2:A705))</f>
-        <v>0.43434343434343436</v>
+        <v>0.44107744107744107</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -52830,11 +52862,11 @@
       </c>
       <c r="E7" s="8">
         <f>COUNTA(Roster!I2:I705)</f>
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F7" s="9">
         <f>IF(COUNTA(Roster!A2:A705)=0,0,E7/COUNTA(Roster!A2:A705))</f>
-        <v>0.55218855218855223</v>
+        <v>0.55387205387205385</v>
       </c>
     </row>
   </sheetData>
@@ -52881,7 +52913,7 @@
       </c>
       <c r="D2" s="10">
         <f t="shared" ref="D2:D13" si="0">IF(SUM($C$2:$C$13)=0,0,C2/SUM($C$2:$C$13))</f>
-        <v>7.926829268292683E-2</v>
+        <v>7.9027355623100301E-2</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -52893,11 +52925,11 @@
       </c>
       <c r="C3" s="6">
         <f>COUNTIF(Roster!$I$2:$I$705,A3)</f>
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D3" s="10">
         <f t="shared" si="0"/>
-        <v>0.13109756097560976</v>
+        <v>0.1337386018237082</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -52913,7 +52945,7 @@
       </c>
       <c r="D4" s="10">
         <f t="shared" si="0"/>
-        <v>9.1463414634146339E-2</v>
+        <v>9.1185410334346503E-2</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -52929,7 +52961,7 @@
       </c>
       <c r="D5" s="10">
         <f t="shared" si="0"/>
-        <v>6.7073170731707321E-2</v>
+        <v>6.6869300911854099E-2</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -52941,11 +52973,11 @@
       </c>
       <c r="C6" s="6">
         <f>COUNTIF(Roster!$I$2:$I$705,A6)</f>
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D6" s="10">
         <f t="shared" si="0"/>
-        <v>0.11585365853658537</v>
+        <v>0.11854103343465046</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -52961,7 +52993,7 @@
       </c>
       <c r="D7" s="10">
         <f t="shared" si="0"/>
-        <v>0.13719512195121952</v>
+        <v>0.13677811550151975</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -52977,7 +53009,7 @@
       </c>
       <c r="D8" s="10">
         <f t="shared" si="0"/>
-        <v>0.10670731707317073</v>
+        <v>0.10638297872340426</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -52989,11 +53021,11 @@
       </c>
       <c r="C9" s="6">
         <f>COUNTIF(Roster!$I$2:$I$705,A9)</f>
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D9" s="10">
         <f t="shared" si="0"/>
-        <v>0.10365853658536585</v>
+        <v>0.10030395136778116</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -53005,11 +53037,11 @@
       </c>
       <c r="C10" s="6">
         <f>COUNTIF(Roster!$I$2:$I$705,A10)</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D10" s="10">
         <f t="shared" si="0"/>
-        <v>6.7073170731707321E-2</v>
+        <v>6.9908814589665649E-2</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -53021,11 +53053,11 @@
       </c>
       <c r="C11" s="6">
         <f>COUNTIF(Roster!$I$2:$I$705,A11)</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D11" s="10">
         <f t="shared" si="0"/>
-        <v>3.6585365853658534E-2</v>
+        <v>3.3434650455927049E-2</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -53041,7 +53073,7 @@
       </c>
       <c r="D12" s="10">
         <f t="shared" si="0"/>
-        <v>3.6585365853658534E-2</v>
+        <v>3.64741641337386E-2</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -53057,7 +53089,7 @@
       </c>
       <c r="D13" s="10">
         <f t="shared" si="0"/>
-        <v>2.7439024390243903E-2</v>
+        <v>2.7355623100303952E-2</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -53066,7 +53098,7 @@
       </c>
       <c r="C14" s="11">
         <f>SUM(C2:C13)</f>
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -53205,7 +53237,7 @@
       </c>
       <c r="B11" s="8">
         <f>COUNTIF(Roster!Q2:Q705,"Yes")</f>
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="C11" s="8" t="s">
         <v>1738</v>
@@ -53217,7 +53249,7 @@
       </c>
       <c r="B12" s="9">
         <f>IF(B5=0,0,B11/B5)</f>
-        <v>1.06</v>
+        <v>1.0866666666666667</v>
       </c>
       <c r="C12" s="8" t="s">
         <v>1738</v>
@@ -53229,7 +53261,7 @@
       </c>
       <c r="B13" s="13">
         <f>IFERROR(AVERAGE(Roster!P2:P705),0)</f>
-        <v>3.3333333333333335</v>
+        <v>3.3484848484848486</v>
       </c>
       <c r="C13" s="8" t="s">
         <v>1738</v>

--- a/data/parahumandle_design.xlsx
+++ b/data/parahumandle_design.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Research\Worm Wordle clone\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA572BE7-7B18-4A06-93ED-DEC5A07921F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD8C4EE6-6A9F-4169-A65B-8B97BBEE42E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="9060" yWindow="4110" windowWidth="28800" windowHeight="15345" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9599" uniqueCount="1911">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9605" uniqueCount="1911">
   <si>
     <t>Parahumandle – design workbook</t>
   </si>
@@ -42450,19 +42450,29 @@
       </c>
       <c r="B480" s="5"/>
       <c r="C480" s="5" t="s">
-        <v>70</v>
+        <v>43</v>
       </c>
       <c r="D480" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="E480" s="5"/>
-      <c r="F480" s="5"/>
-      <c r="G480" s="5"/>
+      <c r="E480" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F480" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G480" s="5" t="s">
+        <v>1863</v>
+      </c>
       <c r="H480" s="5" t="s">
         <v>205</v>
       </c>
-      <c r="I480" s="5"/>
-      <c r="J480" s="5"/>
+      <c r="I480" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="J480" s="5" t="s">
+        <v>71</v>
+      </c>
       <c r="K480" s="5"/>
       <c r="L480" s="5"/>
       <c r="M480" s="5"/>
@@ -42472,11 +42482,11 @@
       <c r="O480" s="5"/>
       <c r="P480" s="6">
         <f t="shared" si="16"/>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Q480" s="6" t="str">
         <f t="shared" si="15"/>
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R480" s="5" t="s">
         <v>51</v>
@@ -42728,7 +42738,9 @@
       <c r="F485" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="G485" s="5"/>
+      <c r="G485" s="5" t="s">
+        <v>1863</v>
+      </c>
       <c r="H485" s="5" t="s">
         <v>313</v>
       </c>
@@ -42747,11 +42759,11 @@
       <c r="O485" s="5"/>
       <c r="P485" s="6">
         <f t="shared" si="16"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q485" s="6" t="str">
         <f t="shared" si="15"/>
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R485" s="5" t="s">
         <v>51</v>
@@ -42792,7 +42804,7 @@
         <v>107</v>
       </c>
       <c r="G486" s="5" t="s">
-        <v>57</v>
+        <v>1863</v>
       </c>
       <c r="H486" s="5" t="s">
         <v>271</v>
@@ -52774,11 +52786,11 @@
       </c>
       <c r="E3" s="8">
         <f>COUNTA(Roster!E2:E705)</f>
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F3" s="9">
         <f>IF(COUNTA(Roster!A2:A705)=0,0,E3/COUNTA(Roster!A2:A705))</f>
-        <v>0.44781144781144783</v>
+        <v>0.4494949494949495</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -52796,11 +52808,11 @@
       </c>
       <c r="E4" s="8">
         <f>COUNTA(Roster!F2:F705)</f>
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F4" s="9">
         <f>IF(COUNTA(Roster!A2:A705)=0,0,E4/COUNTA(Roster!A2:A705))</f>
-        <v>0.44107744107744107</v>
+        <v>0.44276094276094274</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -52818,11 +52830,11 @@
       </c>
       <c r="E5" s="8">
         <f>COUNTA(Roster!G2:G705)</f>
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="F5" s="9">
         <f>IF(COUNTA(Roster!A2:A705)=0,0,E5/COUNTA(Roster!A2:A705))</f>
-        <v>0.56565656565656564</v>
+        <v>0.56902356902356899</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -52862,11 +52874,11 @@
       </c>
       <c r="E7" s="8">
         <f>COUNTA(Roster!I2:I705)</f>
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F7" s="9">
         <f>IF(COUNTA(Roster!A2:A705)=0,0,E7/COUNTA(Roster!A2:A705))</f>
-        <v>0.55387205387205385</v>
+        <v>0.55555555555555558</v>
       </c>
     </row>
   </sheetData>
@@ -52913,7 +52925,7 @@
       </c>
       <c r="D2" s="10">
         <f t="shared" ref="D2:D13" si="0">IF(SUM($C$2:$C$13)=0,0,C2/SUM($C$2:$C$13))</f>
-        <v>7.9027355623100301E-2</v>
+        <v>7.8787878787878782E-2</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -52925,11 +52937,11 @@
       </c>
       <c r="C3" s="6">
         <f>COUNTIF(Roster!$I$2:$I$705,A3)</f>
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D3" s="10">
         <f t="shared" si="0"/>
-        <v>0.1337386018237082</v>
+        <v>0.13636363636363635</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -52945,7 +52957,7 @@
       </c>
       <c r="D4" s="10">
         <f t="shared" si="0"/>
-        <v>9.1185410334346503E-2</v>
+        <v>9.0909090909090912E-2</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -52961,7 +52973,7 @@
       </c>
       <c r="D5" s="10">
         <f t="shared" si="0"/>
-        <v>6.6869300911854099E-2</v>
+        <v>6.6666666666666666E-2</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -52977,7 +52989,7 @@
       </c>
       <c r="D6" s="10">
         <f t="shared" si="0"/>
-        <v>0.11854103343465046</v>
+        <v>0.11818181818181818</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -52993,7 +53005,7 @@
       </c>
       <c r="D7" s="10">
         <f t="shared" si="0"/>
-        <v>0.13677811550151975</v>
+        <v>0.13636363636363635</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -53009,7 +53021,7 @@
       </c>
       <c r="D8" s="10">
         <f t="shared" si="0"/>
-        <v>0.10638297872340426</v>
+        <v>0.10606060606060606</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -53025,7 +53037,7 @@
       </c>
       <c r="D9" s="10">
         <f t="shared" si="0"/>
-        <v>0.10030395136778116</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -53041,7 +53053,7 @@
       </c>
       <c r="D10" s="10">
         <f t="shared" si="0"/>
-        <v>6.9908814589665649E-2</v>
+        <v>6.9696969696969702E-2</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -53057,7 +53069,7 @@
       </c>
       <c r="D11" s="10">
         <f t="shared" si="0"/>
-        <v>3.3434650455927049E-2</v>
+        <v>3.3333333333333333E-2</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -53073,7 +53085,7 @@
       </c>
       <c r="D12" s="10">
         <f t="shared" si="0"/>
-        <v>3.64741641337386E-2</v>
+        <v>3.6363636363636362E-2</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -53089,7 +53101,7 @@
       </c>
       <c r="D13" s="10">
         <f t="shared" si="0"/>
-        <v>2.7355623100303952E-2</v>
+        <v>2.7272727272727271E-2</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -53098,7 +53110,7 @@
       </c>
       <c r="C14" s="11">
         <f>SUM(C2:C13)</f>
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -53237,7 +53249,7 @@
       </c>
       <c r="B11" s="8">
         <f>COUNTIF(Roster!Q2:Q705,"Yes")</f>
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C11" s="8" t="s">
         <v>1738</v>
@@ -53249,7 +53261,7 @@
       </c>
       <c r="B12" s="9">
         <f>IF(B5=0,0,B11/B5)</f>
-        <v>1.0866666666666667</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="C12" s="8" t="s">
         <v>1738</v>
@@ -53261,7 +53273,7 @@
       </c>
       <c r="B13" s="13">
         <f>IFERROR(AVERAGE(Roster!P2:P705),0)</f>
-        <v>3.3484848484848486</v>
+        <v>3.3569023569023568</v>
       </c>
       <c r="C13" s="8" t="s">
         <v>1738</v>

--- a/data/parahumandle_design.xlsx
+++ b/data/parahumandle_design.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Research\Worm Wordle clone\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD8C4EE6-6A9F-4169-A65B-8B97BBEE42E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCA700C5-7C2A-42E3-9061-85ED68C4BDCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="9060" yWindow="4110" windowWidth="28800" windowHeight="15345" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22650,7 +22650,7 @@
         <v>47</v>
       </c>
       <c r="H129" s="5" t="s">
-        <v>58</v>
+        <v>1848</v>
       </c>
       <c r="I129" s="5" t="s">
         <v>192</v>
@@ -48672,7 +48672,7 @@
       </c>
       <c r="B590" s="5"/>
       <c r="C590" s="5" t="s">
-        <v>70</v>
+        <v>43</v>
       </c>
       <c r="D590" s="5" t="s">
         <v>44</v>

--- a/data/parahumandle_design.xlsx
+++ b/data/parahumandle_design.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Research\Worm Wordle clone\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D03B401-2E86-4968-A38F-53D05A03A445}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{540589D3-AFC1-471A-9C44-88CBE37DC4A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="9060" yWindow="4110" windowWidth="28800" windowHeight="15345" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -47190,10 +47190,10 @@
         <v>46</v>
       </c>
       <c r="G563" s="5" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="H563" s="5" t="s">
-        <v>633</v>
+        <v>1531</v>
       </c>
       <c r="I563" s="5" t="s">
         <v>192</v>
@@ -50445,7 +50445,7 @@
         <v/>
       </c>
       <c r="Q641" s="6" t="str">
-        <f t="shared" ref="Q641:Q704" si="21">IF(A641="","",IF(AND(P641=6,UPPER(L641)&lt;&gt;"Y",C641&lt;&gt;""),"Yes","No"))</f>
+        <f t="shared" ref="Q641:Q700" si="21">IF(A641="","",IF(AND(P641=6,UPPER(L641)&lt;&gt;"Y",C641&lt;&gt;""),"Yes","No"))</f>
         <v/>
       </c>
       <c r="R641" s="5"/>

--- a/data/parahumandle_design.xlsx
+++ b/data/parahumandle_design.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Research\Worm Wordle clone\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{540589D3-AFC1-471A-9C44-88CBE37DC4A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{189AE06D-8D7B-4B9E-BDAE-478F74A5D07A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="9060" yWindow="4110" windowWidth="28800" windowHeight="15345" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Reference Merge Log'!$A$1:$F$513</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">Roadmap!$A$1:$D$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Roster!$A$1:$Y$700</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Roster!$A$1:$Y$701</definedName>
   </definedNames>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9587" uniqueCount="1905">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9606" uniqueCount="1909">
   <si>
     <t>Parahumandle – design workbook</t>
   </si>
@@ -5767,6 +5767,18 @@
   </si>
   <si>
     <t>The Heartbroken</t>
+  </si>
+  <si>
+    <t>The Slug</t>
+  </si>
+  <si>
+    <t>Two-nine-three</t>
+  </si>
+  <si>
+    <t>Case 53 who can edit brains. For example, he can brainwash individuals, erase memories, and implant knowledge of English into individuals.</t>
+  </si>
+  <si>
+    <t>Projection</t>
   </si>
 </sst>
 </file>
@@ -14997,7 +15009,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:Y700"/>
+  <dimension ref="A1:Y701"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -16819,7 +16831,9 @@
       <c r="F30" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="G30" s="5"/>
+      <c r="G30" s="5" t="s">
+        <v>1851</v>
+      </c>
       <c r="H30" s="5" t="s">
         <v>191</v>
       </c>
@@ -16840,11 +16854,11 @@
       <c r="O30" s="5"/>
       <c r="P30" s="6">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q30" s="6" t="str">
         <f t="shared" si="1"/>
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R30" s="5" t="s">
         <v>51</v>
@@ -18866,8 +18880,12 @@
       <c r="D65" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="E65" s="5"/>
-      <c r="F65" s="5"/>
+      <c r="E65" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F65" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="G65" s="5" t="s">
         <v>47</v>
       </c>
@@ -18889,11 +18907,11 @@
       <c r="O65" s="5"/>
       <c r="P65" s="6">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q65" s="6" t="str">
         <f t="shared" si="1"/>
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R65" s="5" t="s">
         <v>51</v>
@@ -22012,8 +22030,12 @@
       <c r="D119" s="5" t="s">
         <v>244</v>
       </c>
-      <c r="E119" s="5"/>
-      <c r="F119" s="5"/>
+      <c r="E119" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F119" s="5" t="s">
+        <v>107</v>
+      </c>
       <c r="G119" s="5" t="s">
         <v>47</v>
       </c>
@@ -22035,11 +22057,11 @@
       <c r="O119" s="5"/>
       <c r="P119" s="6">
         <f t="shared" si="4"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q119" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R119" s="5" t="s">
         <v>51</v>
@@ -22200,11 +22222,13 @@
         <v>1129</v>
       </c>
       <c r="I122" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="J122" s="5"/>
+        <v>91</v>
+      </c>
+      <c r="J122" s="5" t="s">
+        <v>49</v>
+      </c>
       <c r="K122" s="5" t="s">
-        <v>59</v>
+        <v>91</v>
       </c>
       <c r="L122" s="5"/>
       <c r="M122" s="5"/>
@@ -43505,9 +43529,15 @@
       <c r="D497" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="E497" s="5"/>
-      <c r="F497" s="5"/>
-      <c r="G497" s="5"/>
+      <c r="E497" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F497" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G497" s="5" t="s">
+        <v>1851</v>
+      </c>
       <c r="H497" s="5" t="s">
         <v>132</v>
       </c>
@@ -43526,11 +43556,11 @@
       <c r="O497" s="5"/>
       <c r="P497" s="6">
         <f t="shared" si="16"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q497" s="6" t="str">
         <f t="shared" si="15"/>
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R497" s="5" t="s">
         <v>51</v>
@@ -44417,7 +44447,7 @@
         <v>4</v>
       </c>
       <c r="Q513" s="6" t="str">
-        <f t="shared" ref="Q513:Q576" si="17">IF(A513="","",IF(AND(P513=6,UPPER(L513)&lt;&gt;"Y",C513&lt;&gt;""),"Yes","No"))</f>
+        <f t="shared" ref="Q513:Q577" si="17">IF(A513="","",IF(AND(P513=6,UPPER(L513)&lt;&gt;"Y",C513&lt;&gt;""),"Yes","No"))</f>
         <v>No</v>
       </c>
       <c r="R513" s="5" t="s">
@@ -45356,7 +45386,7 @@
       </c>
       <c r="O530" s="5"/>
       <c r="P530" s="6">
-        <f t="shared" ref="P530:P593" si="18">IF(A530="","",COUNTA(D530:F530)+COUNTA(G530:G530)+COUNTA(H530:H530)+COUNTA(I530:I530))</f>
+        <f t="shared" ref="P530:P594" si="18">IF(A530="","",COUNTA(D530:F530)+COUNTA(G530:G530)+COUNTA(H530:H530)+COUNTA(I530:I530))</f>
         <v>2</v>
       </c>
       <c r="Q530" s="6" t="str">
@@ -45455,7 +45485,7 @@
         <v>44</v>
       </c>
       <c r="E532" s="5" t="s">
-        <v>45</v>
+        <v>1908</v>
       </c>
       <c r="F532" s="5" t="s">
         <v>107</v>
@@ -45480,7 +45510,7 @@
       </c>
       <c r="O532" s="5"/>
       <c r="P532" s="6">
-        <f t="shared" si="18"/>
+        <f>IF(A532="","",COUNTA(D532:F532)+COUNTA(G532:G532)+COUNTA(H532:H532)+COUNTA(I532:I532))</f>
         <v>6</v>
       </c>
       <c r="Q532" s="6" t="str">
@@ -45512,91 +45542,101 @@
     </row>
     <row r="533" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A533" s="5" t="s">
-        <v>1426</v>
+        <v>1905</v>
       </c>
       <c r="B533" s="5" t="s">
-        <v>1427</v>
+        <v>1906</v>
       </c>
       <c r="C533" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="D533" s="5"/>
+        <v>43</v>
+      </c>
+      <c r="D533" s="5" t="s">
+        <v>44</v>
+      </c>
       <c r="E533" s="5" t="s">
-        <v>252</v>
-      </c>
-      <c r="F533" s="5"/>
+        <v>331</v>
+      </c>
+      <c r="F533" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="G533" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="H533" s="5"/>
+        <v>47</v>
+      </c>
+      <c r="H533" s="5" t="s">
+        <v>456</v>
+      </c>
       <c r="I533" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="J533" s="5" t="s">
-        <v>595</v>
-      </c>
-      <c r="K533" s="5" t="s">
-        <v>1428</v>
-      </c>
+        <v>192</v>
+      </c>
+      <c r="J533" s="5"/>
+      <c r="K533" s="5"/>
       <c r="L533" s="5"/>
       <c r="M533" s="5"/>
-      <c r="N533" s="5" t="s">
-        <v>254</v>
-      </c>
+      <c r="N533" s="5"/>
       <c r="O533" s="5"/>
       <c r="P533" s="6">
-        <f t="shared" si="18"/>
-        <v>3</v>
+        <f>IF(A533="","",COUNTA(D533:F533)+COUNTA(G533:G533)+COUNTA(H533:H533)+COUNTA(I533:I533))</f>
+        <v>6</v>
       </c>
       <c r="Q533" s="6" t="str">
         <f t="shared" si="17"/>
-        <v>No</v>
-      </c>
-      <c r="R533" s="5" t="s">
-        <v>255</v>
-      </c>
+        <v>Yes</v>
+      </c>
+      <c r="R533" s="5"/>
       <c r="S533" s="5"/>
-      <c r="T533" s="5"/>
+      <c r="T533" s="5" t="s">
+        <v>1907</v>
+      </c>
       <c r="U533" s="5"/>
       <c r="V533" s="5"/>
       <c r="W533" s="5"/>
       <c r="X533" s="5"/>
-      <c r="Y533" s="5" t="s">
-        <v>256</v>
-      </c>
+      <c r="Y533" s="5"/>
     </row>
     <row r="534" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A534" s="5" t="s">
-        <v>1546</v>
-      </c>
-      <c r="B534" s="5"/>
+        <v>1426</v>
+      </c>
+      <c r="B534" s="5" t="s">
+        <v>1427</v>
+      </c>
       <c r="C534" s="5" t="s">
         <v>70</v>
       </c>
       <c r="D534" s="5"/>
-      <c r="E534" s="5"/>
+      <c r="E534" s="5" t="s">
+        <v>252</v>
+      </c>
       <c r="F534" s="5"/>
-      <c r="G534" s="5"/>
+      <c r="G534" s="5" t="s">
+        <v>57</v>
+      </c>
       <c r="H534" s="5"/>
-      <c r="I534" s="5"/>
-      <c r="J534" s="5"/>
-      <c r="K534" s="5"/>
+      <c r="I534" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="J534" s="5" t="s">
+        <v>595</v>
+      </c>
+      <c r="K534" s="5" t="s">
+        <v>1428</v>
+      </c>
       <c r="L534" s="5"/>
       <c r="M534" s="5"/>
       <c r="N534" s="5" t="s">
-        <v>124</v>
+        <v>254</v>
       </c>
       <c r="O534" s="5"/>
       <c r="P534" s="6">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q534" s="6" t="str">
         <f t="shared" si="17"/>
         <v>No</v>
       </c>
       <c r="R534" s="5" t="s">
-        <v>125</v>
+        <v>255</v>
       </c>
       <c r="S534" s="5"/>
       <c r="T534" s="5"/>
@@ -45605,61 +45645,55 @@
       <c r="W534" s="5"/>
       <c r="X534" s="5"/>
       <c r="Y534" s="5" t="s">
-        <v>1105</v>
+        <v>256</v>
       </c>
     </row>
     <row r="535" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A535" s="5" t="s">
-        <v>1540</v>
+        <v>1546</v>
       </c>
       <c r="B535" s="5"/>
       <c r="C535" s="5" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="D535" s="5"/>
       <c r="E535" s="5"/>
       <c r="F535" s="5"/>
       <c r="G535" s="5"/>
-      <c r="H535" s="5" t="s">
-        <v>902</v>
-      </c>
+      <c r="H535" s="5"/>
       <c r="I535" s="5"/>
       <c r="J535" s="5"/>
       <c r="K535" s="5"/>
       <c r="L535" s="5"/>
       <c r="M535" s="5"/>
       <c r="N535" s="5" t="s">
-        <v>66</v>
+        <v>124</v>
       </c>
       <c r="O535" s="5"/>
       <c r="P535" s="6">
         <f t="shared" si="18"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q535" s="6" t="str">
         <f t="shared" si="17"/>
         <v>No</v>
       </c>
       <c r="R535" s="5" t="s">
-        <v>51</v>
+        <v>125</v>
       </c>
       <c r="S535" s="5"/>
-      <c r="T535" s="5" t="s">
-        <v>1541</v>
-      </c>
-      <c r="U535" s="5" t="s">
-        <v>903</v>
-      </c>
+      <c r="T535" s="5"/>
+      <c r="U535" s="5"/>
       <c r="V535" s="5"/>
-      <c r="W535" s="5" t="s">
-        <v>43</v>
-      </c>
+      <c r="W535" s="5"/>
       <c r="X535" s="5"/>
-      <c r="Y535" s="5"/>
+      <c r="Y535" s="5" t="s">
+        <v>1105</v>
+      </c>
     </row>
     <row r="536" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A536" s="5" t="s">
-        <v>1542</v>
+        <v>1540</v>
       </c>
       <c r="B536" s="5"/>
       <c r="C536" s="5" t="s">
@@ -45694,7 +45728,7 @@
       </c>
       <c r="S536" s="5"/>
       <c r="T536" s="5" t="s">
-        <v>1543</v>
+        <v>1541</v>
       </c>
       <c r="U536" s="5" t="s">
         <v>903</v>
@@ -45708,7 +45742,7 @@
     </row>
     <row r="537" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A537" s="5" t="s">
-        <v>1544</v>
+        <v>1542</v>
       </c>
       <c r="B537" s="5"/>
       <c r="C537" s="5" t="s">
@@ -45743,7 +45777,7 @@
       </c>
       <c r="S537" s="5"/>
       <c r="T537" s="5" t="s">
-        <v>1545</v>
+        <v>1543</v>
       </c>
       <c r="U537" s="5" t="s">
         <v>903</v>
@@ -45757,37 +45791,31 @@
     </row>
     <row r="538" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A538" s="5" t="s">
-        <v>1547</v>
+        <v>1544</v>
       </c>
       <c r="B538" s="5"/>
       <c r="C538" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="D538" s="5" t="s">
-        <v>76</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="D538" s="5"/>
       <c r="E538" s="5"/>
       <c r="F538" s="5"/>
       <c r="G538" s="5"/>
       <c r="H538" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="I538" s="5" t="s">
-        <v>192</v>
-      </c>
+        <v>902</v>
+      </c>
+      <c r="I538" s="5"/>
       <c r="J538" s="5"/>
-      <c r="K538" s="5" t="s">
-        <v>192</v>
-      </c>
+      <c r="K538" s="5"/>
       <c r="L538" s="5"/>
       <c r="M538" s="5"/>
       <c r="N538" s="5" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="O538" s="5"/>
       <c r="P538" s="6">
         <f t="shared" si="18"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q538" s="6" t="str">
         <f t="shared" si="17"/>
@@ -45797,97 +45825,99 @@
         <v>51</v>
       </c>
       <c r="S538" s="5"/>
-      <c r="T538" s="5"/>
+      <c r="T538" s="5" t="s">
+        <v>1545</v>
+      </c>
       <c r="U538" s="5" t="s">
-        <v>83</v>
+        <v>903</v>
       </c>
       <c r="V538" s="5"/>
-      <c r="W538" s="5"/>
+      <c r="W538" s="5" t="s">
+        <v>43</v>
+      </c>
       <c r="X538" s="5"/>
-      <c r="Y538" s="5" t="s">
-        <v>428</v>
-      </c>
+      <c r="Y538" s="5"/>
     </row>
     <row r="539" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A539" s="5" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="B539" s="5"/>
       <c r="C539" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="D539" s="5"/>
-      <c r="E539" s="5" t="s">
-        <v>252</v>
-      </c>
+      <c r="D539" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="E539" s="5"/>
       <c r="F539" s="5"/>
-      <c r="G539" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="H539" s="5"/>
-      <c r="I539" s="5"/>
+      <c r="G539" s="5"/>
+      <c r="H539" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="I539" s="5" t="s">
+        <v>192</v>
+      </c>
       <c r="J539" s="5"/>
-      <c r="K539" s="5"/>
+      <c r="K539" s="5" t="s">
+        <v>192</v>
+      </c>
       <c r="L539" s="5"/>
       <c r="M539" s="5"/>
       <c r="N539" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="O539" s="5" t="s">
-        <v>308</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="O539" s="5"/>
       <c r="P539" s="6">
         <f t="shared" si="18"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q539" s="6" t="str">
         <f t="shared" si="17"/>
         <v>No</v>
       </c>
       <c r="R539" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="S539" s="5" t="s">
-        <v>138</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="S539" s="5"/>
       <c r="T539" s="5"/>
       <c r="U539" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="V539" s="5" t="s">
-        <v>310</v>
-      </c>
+        <v>83</v>
+      </c>
+      <c r="V539" s="5"/>
       <c r="W539" s="5"/>
       <c r="X539" s="5"/>
       <c r="Y539" s="5" t="s">
-        <v>311</v>
+        <v>428</v>
       </c>
     </row>
     <row r="540" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A540" s="5" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
       <c r="B540" s="5"/>
-      <c r="C540" s="5"/>
+      <c r="C540" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="D540" s="5"/>
-      <c r="E540" s="5"/>
-      <c r="F540" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="G540" s="5"/>
-      <c r="H540" s="5" t="s">
-        <v>77</v>
-      </c>
+      <c r="E540" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="F540" s="5"/>
+      <c r="G540" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="H540" s="5"/>
       <c r="I540" s="5"/>
       <c r="J540" s="5"/>
       <c r="K540" s="5"/>
       <c r="L540" s="5"/>
       <c r="M540" s="5"/>
       <c r="N540" s="5" t="s">
-        <v>66</v>
+        <v>124</v>
       </c>
       <c r="O540" s="5" t="s">
-        <v>103</v>
+        <v>308</v>
       </c>
       <c r="P540" s="6">
         <f t="shared" si="18"/>
@@ -45898,54 +45928,50 @@
         <v>No</v>
       </c>
       <c r="R540" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="S540" s="5"/>
-      <c r="T540" s="5" t="s">
-        <v>1550</v>
-      </c>
+        <v>125</v>
+      </c>
+      <c r="S540" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="T540" s="5"/>
       <c r="U540" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="V540" s="5"/>
-      <c r="W540" s="5" t="s">
-        <v>105</v>
-      </c>
+        <v>309</v>
+      </c>
+      <c r="V540" s="5" t="s">
+        <v>310</v>
+      </c>
+      <c r="W540" s="5"/>
       <c r="X540" s="5"/>
       <c r="Y540" s="5" t="s">
-        <v>583</v>
+        <v>311</v>
       </c>
     </row>
     <row r="541" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A541" s="5" t="s">
-        <v>1551</v>
-      </c>
-      <c r="B541" s="5" t="s">
-        <v>1552</v>
-      </c>
-      <c r="C541" s="5" t="s">
-        <v>43</v>
-      </c>
+        <v>1549</v>
+      </c>
+      <c r="B541" s="5"/>
+      <c r="C541" s="5"/>
       <c r="D541" s="5"/>
       <c r="E541" s="5"/>
-      <c r="F541" s="5"/>
+      <c r="F541" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="G541" s="5"/>
       <c r="H541" s="5" t="s">
-        <v>902</v>
-      </c>
-      <c r="I541" s="5" t="s">
-        <v>91</v>
-      </c>
+        <v>77</v>
+      </c>
+      <c r="I541" s="5"/>
       <c r="J541" s="5"/>
-      <c r="K541" s="5" t="s">
-        <v>91</v>
-      </c>
+      <c r="K541" s="5"/>
       <c r="L541" s="5"/>
       <c r="M541" s="5"/>
       <c r="N541" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="O541" s="5"/>
+        <v>66</v>
+      </c>
+      <c r="O541" s="5" t="s">
+        <v>103</v>
+      </c>
       <c r="P541" s="6">
         <f t="shared" si="18"/>
         <v>2</v>
@@ -45959,40 +45985,36 @@
       </c>
       <c r="S541" s="5"/>
       <c r="T541" s="5" t="s">
-        <v>1553</v>
+        <v>1550</v>
       </c>
       <c r="U541" s="5" t="s">
-        <v>903</v>
+        <v>77</v>
       </c>
       <c r="V541" s="5"/>
       <c r="W541" s="5" t="s">
-        <v>43</v>
+        <v>105</v>
       </c>
       <c r="X541" s="5"/>
       <c r="Y541" s="5" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
     </row>
     <row r="542" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A542" s="5" t="s">
-        <v>1554</v>
-      </c>
-      <c r="B542" s="5"/>
+        <v>1551</v>
+      </c>
+      <c r="B542" s="5" t="s">
+        <v>1552</v>
+      </c>
       <c r="C542" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="D542" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="E542" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F542" s="5" t="s">
-        <v>46</v>
-      </c>
+      <c r="D542" s="5"/>
+      <c r="E542" s="5"/>
+      <c r="F542" s="5"/>
       <c r="G542" s="5"/>
       <c r="H542" s="5" t="s">
-        <v>1089</v>
+        <v>902</v>
       </c>
       <c r="I542" s="5" t="s">
         <v>91</v>
@@ -46009,7 +46031,7 @@
       <c r="O542" s="5"/>
       <c r="P542" s="6">
         <f t="shared" si="18"/>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Q542" s="6" t="str">
         <f t="shared" si="17"/>
@@ -46018,14 +46040,12 @@
       <c r="R542" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="S542" s="5" t="s">
-        <v>1555</v>
-      </c>
+      <c r="S542" s="5"/>
       <c r="T542" s="5" t="s">
-        <v>1556</v>
+        <v>1553</v>
       </c>
       <c r="U542" s="5" t="s">
-        <v>1093</v>
+        <v>903</v>
       </c>
       <c r="V542" s="5"/>
       <c r="W542" s="5" t="s">
@@ -46033,34 +46053,46 @@
       </c>
       <c r="X542" s="5"/>
       <c r="Y542" s="5" t="s">
-        <v>347</v>
+        <v>587</v>
       </c>
     </row>
     <row r="543" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A543" s="5" t="s">
-        <v>1557</v>
+        <v>1554</v>
       </c>
       <c r="B543" s="5"/>
-      <c r="C543" s="5"/>
-      <c r="D543" s="5"/>
-      <c r="E543" s="5"/>
-      <c r="F543" s="5"/>
+      <c r="C543" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D543" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="E543" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F543" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="G543" s="5"/>
-      <c r="H543" s="5"/>
-      <c r="I543" s="5"/>
+      <c r="H543" s="5" t="s">
+        <v>1089</v>
+      </c>
+      <c r="I543" s="5" t="s">
+        <v>91</v>
+      </c>
       <c r="J543" s="5"/>
-      <c r="K543" s="5"/>
+      <c r="K543" s="5" t="s">
+        <v>91</v>
+      </c>
       <c r="L543" s="5"/>
       <c r="M543" s="5"/>
       <c r="N543" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="O543" s="5" t="s">
-        <v>103</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="O543" s="5"/>
       <c r="P543" s="6">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q543" s="6" t="str">
         <f t="shared" si="17"/>
@@ -46069,97 +46101,87 @@
       <c r="R543" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="S543" s="5"/>
+      <c r="S543" s="5" t="s">
+        <v>1555</v>
+      </c>
       <c r="T543" s="5" t="s">
-        <v>1558</v>
-      </c>
-      <c r="U543" s="5"/>
+        <v>1556</v>
+      </c>
+      <c r="U543" s="5" t="s">
+        <v>1093</v>
+      </c>
       <c r="V543" s="5"/>
       <c r="W543" s="5" t="s">
-        <v>105</v>
+        <v>43</v>
       </c>
       <c r="X543" s="5"/>
-      <c r="Y543" s="5"/>
+      <c r="Y543" s="5" t="s">
+        <v>347</v>
+      </c>
     </row>
     <row r="544" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A544" s="5" t="s">
-        <v>1559</v>
+        <v>1557</v>
       </c>
       <c r="B544" s="5"/>
-      <c r="C544" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="D544" s="5" t="s">
-        <v>244</v>
-      </c>
+      <c r="C544" s="5"/>
+      <c r="D544" s="5"/>
       <c r="E544" s="5"/>
       <c r="F544" s="5"/>
-      <c r="G544" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="H544" s="5" t="s">
-        <v>245</v>
-      </c>
-      <c r="I544" s="5" t="s">
-        <v>123</v>
-      </c>
+      <c r="G544" s="5"/>
+      <c r="H544" s="5"/>
+      <c r="I544" s="5"/>
       <c r="J544" s="5"/>
-      <c r="K544" s="5" t="s">
-        <v>123</v>
-      </c>
+      <c r="K544" s="5"/>
       <c r="L544" s="5"/>
       <c r="M544" s="5"/>
       <c r="N544" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="O544" s="5"/>
+        <v>66</v>
+      </c>
+      <c r="O544" s="5" t="s">
+        <v>103</v>
+      </c>
       <c r="P544" s="6">
         <f t="shared" si="18"/>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q544" s="6" t="str">
         <f t="shared" si="17"/>
         <v>No</v>
       </c>
       <c r="R544" s="5" t="s">
-        <v>125</v>
+        <v>51</v>
       </c>
       <c r="S544" s="5"/>
-      <c r="T544" s="5"/>
-      <c r="U544" s="5" t="s">
-        <v>1560</v>
-      </c>
-      <c r="V544" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="W544" s="5"/>
+      <c r="T544" s="5" t="s">
+        <v>1558</v>
+      </c>
+      <c r="U544" s="5"/>
+      <c r="V544" s="5"/>
+      <c r="W544" s="5" t="s">
+        <v>105</v>
+      </c>
       <c r="X544" s="5"/>
-      <c r="Y544" s="5" t="s">
-        <v>285</v>
-      </c>
+      <c r="Y544" s="5"/>
     </row>
     <row r="545" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A545" s="5" t="s">
-        <v>1561</v>
+        <v>1559</v>
       </c>
       <c r="B545" s="5"/>
       <c r="C545" s="5" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="D545" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="E545" s="5" t="s">
-        <v>331</v>
-      </c>
-      <c r="F545" s="5" t="s">
-        <v>46</v>
-      </c>
+        <v>244</v>
+      </c>
+      <c r="E545" s="5"/>
+      <c r="F545" s="5"/>
       <c r="G545" s="5" t="s">
         <v>47</v>
       </c>
       <c r="H545" s="5" t="s">
-        <v>1125</v>
+        <v>245</v>
       </c>
       <c r="I545" s="5" t="s">
         <v>123</v>
@@ -46171,82 +46193,72 @@
       <c r="L545" s="5"/>
       <c r="M545" s="5"/>
       <c r="N545" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="O545" s="5" t="s">
-        <v>225</v>
-      </c>
+        <v>124</v>
+      </c>
+      <c r="O545" s="5"/>
       <c r="P545" s="6">
         <f t="shared" si="18"/>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q545" s="6" t="str">
         <f t="shared" si="17"/>
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R545" s="5" t="s">
-        <v>51</v>
+        <v>125</v>
       </c>
       <c r="S545" s="5"/>
-      <c r="T545" s="5" t="s">
-        <v>1563</v>
-      </c>
+      <c r="T545" s="5"/>
       <c r="U545" s="5" t="s">
-        <v>1562</v>
+        <v>1560</v>
       </c>
       <c r="V545" s="5" t="s">
-        <v>1433</v>
-      </c>
-      <c r="W545" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="X545" s="5" t="s">
-        <v>87</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="W545" s="5"/>
+      <c r="X545" s="5"/>
       <c r="Y545" s="5" t="s">
-        <v>1564</v>
+        <v>285</v>
       </c>
     </row>
     <row r="546" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A546" s="5" t="s">
-        <v>1901</v>
-      </c>
-      <c r="B546" s="5" t="s">
-        <v>730</v>
-      </c>
+        <v>1561</v>
+      </c>
+      <c r="B546" s="5"/>
       <c r="C546" s="5" t="s">
         <v>43</v>
       </c>
       <c r="D546" s="5" t="s">
-        <v>76</v>
+        <v>44</v>
       </c>
       <c r="E546" s="5" t="s">
         <v>331</v>
       </c>
       <c r="F546" s="5" t="s">
-        <v>107</v>
+        <v>46</v>
       </c>
       <c r="G546" s="5" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="H546" s="5" t="s">
-        <v>1866</v>
+        <v>1125</v>
       </c>
       <c r="I546" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="J546" s="5" t="s">
-        <v>71</v>
-      </c>
+        <v>123</v>
+      </c>
+      <c r="J546" s="5"/>
       <c r="K546" s="5" t="s">
-        <v>72</v>
+        <v>123</v>
       </c>
       <c r="L546" s="5"/>
       <c r="M546" s="5"/>
       <c r="N546" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="O546" s="5"/>
+        <v>50</v>
+      </c>
+      <c r="O546" s="5" t="s">
+        <v>225</v>
+      </c>
       <c r="P546" s="6">
         <f t="shared" si="18"/>
         <v>6</v>
@@ -46256,154 +46268,156 @@
         <v>Yes</v>
       </c>
       <c r="R546" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="S546" s="5" t="s">
-        <v>1883</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="S546" s="5"/>
       <c r="T546" s="5" t="s">
-        <v>1900</v>
+        <v>1563</v>
       </c>
       <c r="U546" s="5" t="s">
-        <v>332</v>
+        <v>1562</v>
       </c>
       <c r="V546" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="W546" s="5"/>
-      <c r="X546" s="5"/>
+        <v>1433</v>
+      </c>
+      <c r="W546" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="X546" s="5" t="s">
+        <v>87</v>
+      </c>
       <c r="Y546" s="5" t="s">
-        <v>1524</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="547" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A547" s="5" t="s">
-        <v>1565</v>
-      </c>
-      <c r="B547" s="5"/>
+        <v>1901</v>
+      </c>
+      <c r="B547" s="5" t="s">
+        <v>730</v>
+      </c>
       <c r="C547" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="D547" s="5"/>
-      <c r="E547" s="5"/>
-      <c r="F547" s="5"/>
-      <c r="G547" s="5"/>
+        <v>43</v>
+      </c>
+      <c r="D547" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="E547" s="5" t="s">
+        <v>331</v>
+      </c>
+      <c r="F547" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="G547" s="5" t="s">
+        <v>57</v>
+      </c>
       <c r="H547" s="5" t="s">
-        <v>318</v>
-      </c>
-      <c r="I547" s="5"/>
-      <c r="J547" s="5"/>
-      <c r="K547" s="5"/>
+        <v>1866</v>
+      </c>
+      <c r="I547" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="J547" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="K547" s="5" t="s">
+        <v>72</v>
+      </c>
       <c r="L547" s="5"/>
       <c r="M547" s="5"/>
       <c r="N547" s="5" t="s">
-        <v>66</v>
+        <v>124</v>
       </c>
       <c r="O547" s="5"/>
       <c r="P547" s="6">
         <f t="shared" si="18"/>
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Q547" s="6" t="str">
         <f t="shared" si="17"/>
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R547" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="S547" s="5"/>
-      <c r="T547" s="5"/>
+        <v>125</v>
+      </c>
+      <c r="S547" s="5" t="s">
+        <v>1883</v>
+      </c>
+      <c r="T547" s="5" t="s">
+        <v>1900</v>
+      </c>
       <c r="U547" s="5" t="s">
-        <v>318</v>
-      </c>
-      <c r="V547" s="5"/>
-      <c r="W547" s="5" t="s">
-        <v>319</v>
-      </c>
-      <c r="X547" s="5" t="s">
-        <v>320</v>
-      </c>
-      <c r="Y547" s="5"/>
+        <v>332</v>
+      </c>
+      <c r="V547" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="W547" s="5"/>
+      <c r="X547" s="5"/>
+      <c r="Y547" s="5" t="s">
+        <v>1524</v>
+      </c>
     </row>
     <row r="548" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A548" s="5" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="B548" s="5"/>
       <c r="C548" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="D548" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="E548" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F548" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="G548" s="5" t="s">
-        <v>47</v>
-      </c>
+        <v>128</v>
+      </c>
+      <c r="D548" s="5"/>
+      <c r="E548" s="5"/>
+      <c r="F548" s="5"/>
+      <c r="G548" s="5"/>
       <c r="H548" s="5" t="s">
-        <v>214</v>
-      </c>
-      <c r="I548" s="5" t="s">
-        <v>71</v>
-      </c>
+        <v>318</v>
+      </c>
+      <c r="I548" s="5"/>
       <c r="J548" s="5"/>
-      <c r="K548" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="K548" s="5"/>
       <c r="L548" s="5"/>
       <c r="M548" s="5"/>
       <c r="N548" s="5" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="O548" s="5"/>
       <c r="P548" s="6">
         <f t="shared" si="18"/>
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Q548" s="6" t="str">
         <f t="shared" si="17"/>
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R548" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="S548" s="5" t="s">
-        <v>1567</v>
-      </c>
-      <c r="T548" s="5" t="s">
-        <v>1568</v>
-      </c>
+      <c r="S548" s="5"/>
+      <c r="T548" s="5"/>
       <c r="U548" s="5" t="s">
-        <v>214</v>
-      </c>
-      <c r="V548" s="5" t="s">
-        <v>181</v>
-      </c>
+        <v>318</v>
+      </c>
+      <c r="V548" s="5"/>
       <c r="W548" s="5" t="s">
-        <v>43</v>
+        <v>319</v>
       </c>
       <c r="X548" s="5" t="s">
-        <v>675</v>
-      </c>
-      <c r="Y548" s="5" t="s">
-        <v>55</v>
-      </c>
+        <v>320</v>
+      </c>
+      <c r="Y548" s="5"/>
     </row>
     <row r="549" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A549" s="5" t="s">
-        <v>1569</v>
+        <v>1566</v>
       </c>
       <c r="B549" s="5"/>
       <c r="C549" s="5" t="s">
         <v>43</v>
       </c>
       <c r="D549" s="5" t="s">
-        <v>76</v>
+        <v>44</v>
       </c>
       <c r="E549" s="5" t="s">
         <v>45</v>
@@ -46412,24 +46426,22 @@
         <v>46</v>
       </c>
       <c r="G549" s="5" t="s">
-        <v>1851</v>
+        <v>47</v>
       </c>
       <c r="H549" s="5" t="s">
-        <v>77</v>
+        <v>214</v>
       </c>
       <c r="I549" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="J549" s="5" t="s">
-        <v>91</v>
-      </c>
+        <v>71</v>
+      </c>
+      <c r="J549" s="5"/>
       <c r="K549" s="5" t="s">
-        <v>1570</v>
+        <v>71</v>
       </c>
       <c r="L549" s="5"/>
       <c r="M549" s="5"/>
       <c r="N549" s="5" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="O549" s="5"/>
       <c r="P549" s="6">
@@ -46444,37 +46456,49 @@
         <v>51</v>
       </c>
       <c r="S549" s="5" t="s">
-        <v>1571</v>
+        <v>1567</v>
       </c>
       <c r="T549" s="5" t="s">
-        <v>1572</v>
+        <v>1568</v>
       </c>
       <c r="U549" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="V549" s="5"/>
+        <v>214</v>
+      </c>
+      <c r="V549" s="5" t="s">
+        <v>181</v>
+      </c>
       <c r="W549" s="5" t="s">
         <v>43</v>
       </c>
       <c r="X549" s="5" t="s">
-        <v>471</v>
+        <v>675</v>
       </c>
       <c r="Y549" s="5" t="s">
-        <v>242</v>
+        <v>55</v>
       </c>
     </row>
     <row r="550" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A550" s="5" t="s">
-        <v>1573</v>
+        <v>1569</v>
       </c>
       <c r="B550" s="5"/>
-      <c r="C550" s="5"/>
-      <c r="D550" s="5"/>
-      <c r="E550" s="5"/>
-      <c r="F550" s="5"/>
-      <c r="G550" s="5"/>
+      <c r="C550" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D550" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="E550" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F550" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G550" s="5" t="s">
+        <v>1851</v>
+      </c>
       <c r="H550" s="5" t="s">
-        <v>557</v>
+        <v>77</v>
       </c>
       <c r="I550" s="5" t="s">
         <v>119</v>
@@ -46483,68 +46507,78 @@
         <v>91</v>
       </c>
       <c r="K550" s="5" t="s">
-        <v>1574</v>
+        <v>1570</v>
       </c>
       <c r="L550" s="5"/>
       <c r="M550" s="5"/>
       <c r="N550" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="O550" s="5" t="s">
-        <v>103</v>
-      </c>
+      <c r="O550" s="5"/>
       <c r="P550" s="6">
         <f t="shared" si="18"/>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Q550" s="6" t="str">
         <f t="shared" si="17"/>
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R550" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="S550" s="5"/>
+      <c r="S550" s="5" t="s">
+        <v>1571</v>
+      </c>
       <c r="T550" s="5" t="s">
-        <v>1575</v>
+        <v>1572</v>
       </c>
       <c r="U550" s="5" t="s">
-        <v>557</v>
+        <v>77</v>
       </c>
       <c r="V550" s="5"/>
       <c r="W550" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="X550" s="5"/>
-      <c r="Y550" s="5"/>
+        <v>43</v>
+      </c>
+      <c r="X550" s="5" t="s">
+        <v>471</v>
+      </c>
+      <c r="Y550" s="5" t="s">
+        <v>242</v>
+      </c>
     </row>
     <row r="551" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A551" s="5" t="s">
-        <v>1576</v>
+        <v>1573</v>
       </c>
       <c r="B551" s="5"/>
-      <c r="C551" s="5" t="s">
-        <v>70</v>
-      </c>
+      <c r="C551" s="5"/>
       <c r="D551" s="5"/>
       <c r="E551" s="5"/>
       <c r="F551" s="5"/>
       <c r="G551" s="5"/>
       <c r="H551" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="I551" s="5"/>
-      <c r="J551" s="5"/>
-      <c r="K551" s="5"/>
+        <v>557</v>
+      </c>
+      <c r="I551" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="J551" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="K551" s="5" t="s">
+        <v>1574</v>
+      </c>
       <c r="L551" s="5"/>
       <c r="M551" s="5"/>
       <c r="N551" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="O551" s="5"/>
+        <v>66</v>
+      </c>
+      <c r="O551" s="5" t="s">
+        <v>103</v>
+      </c>
       <c r="P551" s="6">
         <f t="shared" si="18"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q551" s="6" t="str">
         <f t="shared" si="17"/>
@@ -46555,32 +46589,32 @@
       </c>
       <c r="S551" s="5"/>
       <c r="T551" s="5" t="s">
-        <v>1577</v>
+        <v>1575</v>
       </c>
       <c r="U551" s="5" t="s">
-        <v>205</v>
+        <v>557</v>
       </c>
       <c r="V551" s="5"/>
-      <c r="W551" s="5"/>
+      <c r="W551" s="5" t="s">
+        <v>105</v>
+      </c>
       <c r="X551" s="5"/>
-      <c r="Y551" s="5" t="s">
-        <v>74</v>
-      </c>
+      <c r="Y551" s="5"/>
     </row>
     <row r="552" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A552" s="5" t="s">
-        <v>1578</v>
+        <v>1576</v>
       </c>
       <c r="B552" s="5"/>
       <c r="C552" s="5" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="D552" s="5"/>
       <c r="E552" s="5"/>
       <c r="F552" s="5"/>
       <c r="G552" s="5"/>
       <c r="H552" s="5" t="s">
-        <v>902</v>
+        <v>205</v>
       </c>
       <c r="I552" s="5"/>
       <c r="J552" s="5"/>
@@ -46588,7 +46622,7 @@
       <c r="L552" s="5"/>
       <c r="M552" s="5"/>
       <c r="N552" s="5" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="O552" s="5"/>
       <c r="P552" s="6">
@@ -46604,21 +46638,21 @@
       </c>
       <c r="S552" s="5"/>
       <c r="T552" s="5" t="s">
-        <v>1579</v>
+        <v>1577</v>
       </c>
       <c r="U552" s="5" t="s">
-        <v>903</v>
+        <v>205</v>
       </c>
       <c r="V552" s="5"/>
-      <c r="W552" s="5" t="s">
-        <v>43</v>
-      </c>
+      <c r="W552" s="5"/>
       <c r="X552" s="5"/>
-      <c r="Y552" s="5"/>
+      <c r="Y552" s="5" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="553" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A553" s="5" t="s">
-        <v>1580</v>
+        <v>1578</v>
       </c>
       <c r="B553" s="5"/>
       <c r="C553" s="5" t="s">
@@ -46631,13 +46665,9 @@
       <c r="H553" s="5" t="s">
         <v>902</v>
       </c>
-      <c r="I553" s="5" t="s">
-        <v>133</v>
-      </c>
+      <c r="I553" s="5"/>
       <c r="J553" s="5"/>
-      <c r="K553" s="5" t="s">
-        <v>133</v>
-      </c>
+      <c r="K553" s="5"/>
       <c r="L553" s="5"/>
       <c r="M553" s="5"/>
       <c r="N553" s="5" t="s">
@@ -46646,7 +46676,7 @@
       <c r="O553" s="5"/>
       <c r="P553" s="6">
         <f t="shared" si="18"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q553" s="6" t="str">
         <f t="shared" si="17"/>
@@ -46657,7 +46687,7 @@
       </c>
       <c r="S553" s="5"/>
       <c r="T553" s="5" t="s">
-        <v>1581</v>
+        <v>1579</v>
       </c>
       <c r="U553" s="5" t="s">
         <v>903</v>
@@ -46671,24 +46701,26 @@
     </row>
     <row r="554" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A554" s="5" t="s">
-        <v>1582</v>
+        <v>1580</v>
       </c>
       <c r="B554" s="5"/>
       <c r="C554" s="5" t="s">
-        <v>128</v>
+        <v>43</v>
       </c>
       <c r="D554" s="5"/>
       <c r="E554" s="5"/>
       <c r="F554" s="5"/>
-      <c r="G554" s="5" t="s">
-        <v>57</v>
-      </c>
+      <c r="G554" s="5"/>
       <c r="H554" s="5" t="s">
-        <v>1325</v>
-      </c>
-      <c r="I554" s="5"/>
+        <v>902</v>
+      </c>
+      <c r="I554" s="5" t="s">
+        <v>133</v>
+      </c>
       <c r="J554" s="5"/>
-      <c r="K554" s="5"/>
+      <c r="K554" s="5" t="s">
+        <v>133</v>
+      </c>
       <c r="L554" s="5"/>
       <c r="M554" s="5"/>
       <c r="N554" s="5" t="s">
@@ -46707,58 +46739,48 @@
         <v>51</v>
       </c>
       <c r="S554" s="5"/>
-      <c r="T554" s="5"/>
+      <c r="T554" s="5" t="s">
+        <v>1581</v>
+      </c>
       <c r="U554" s="5" t="s">
-        <v>1325</v>
-      </c>
-      <c r="V554" s="5" t="s">
-        <v>57</v>
-      </c>
+        <v>903</v>
+      </c>
+      <c r="V554" s="5"/>
       <c r="W554" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="X554" s="5" t="s">
-        <v>1326</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="X554" s="5"/>
       <c r="Y554" s="5"/>
     </row>
     <row r="555" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A555" s="5" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="B555" s="5"/>
       <c r="C555" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="D555" s="5" t="s">
-        <v>44</v>
-      </c>
+        <v>128</v>
+      </c>
+      <c r="D555" s="5"/>
       <c r="E555" s="5"/>
       <c r="F555" s="5"/>
       <c r="G555" s="5" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="H555" s="5" t="s">
-        <v>313</v>
-      </c>
-      <c r="I555" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="J555" s="5" t="s">
-        <v>1584</v>
-      </c>
-      <c r="K555" s="5" t="s">
-        <v>1585</v>
-      </c>
+        <v>1325</v>
+      </c>
+      <c r="I555" s="5"/>
+      <c r="J555" s="5"/>
+      <c r="K555" s="5"/>
       <c r="L555" s="5"/>
       <c r="M555" s="5"/>
       <c r="N555" s="5" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="O555" s="5"/>
       <c r="P555" s="6">
         <f t="shared" si="18"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q555" s="6" t="str">
         <f t="shared" si="17"/>
@@ -46768,24 +46790,24 @@
         <v>51</v>
       </c>
       <c r="S555" s="5"/>
-      <c r="T555" s="5" t="s">
-        <v>1586</v>
-      </c>
+      <c r="T555" s="5"/>
       <c r="U555" s="5" t="s">
-        <v>316</v>
-      </c>
-      <c r="V555" s="5"/>
+        <v>1325</v>
+      </c>
+      <c r="V555" s="5" t="s">
+        <v>57</v>
+      </c>
       <c r="W555" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="X555" s="5"/>
-      <c r="Y555" s="5" t="s">
-        <v>94</v>
-      </c>
+        <v>128</v>
+      </c>
+      <c r="X555" s="5" t="s">
+        <v>1326</v>
+      </c>
+      <c r="Y555" s="5"/>
     </row>
     <row r="556" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A556" s="5" t="s">
-        <v>1664</v>
+        <v>1583</v>
       </c>
       <c r="B556" s="5"/>
       <c r="C556" s="5" t="s">
@@ -46794,133 +46816,145 @@
       <c r="D556" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="E556" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F556" s="5" t="s">
-        <v>46</v>
-      </c>
+      <c r="E556" s="5"/>
+      <c r="F556" s="5"/>
       <c r="G556" s="5" t="s">
-        <v>1851</v>
+        <v>47</v>
       </c>
       <c r="H556" s="5" t="s">
-        <v>1162</v>
+        <v>313</v>
       </c>
       <c r="I556" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="J556" s="5"/>
+        <v>72</v>
+      </c>
+      <c r="J556" s="5" t="s">
+        <v>1584</v>
+      </c>
       <c r="K556" s="5" t="s">
-        <v>49</v>
+        <v>1585</v>
       </c>
       <c r="L556" s="5"/>
       <c r="M556" s="5"/>
       <c r="N556" s="5" t="s">
-        <v>124</v>
+        <v>50</v>
       </c>
       <c r="O556" s="5"/>
       <c r="P556" s="6">
         <f t="shared" si="18"/>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q556" s="6" t="str">
         <f t="shared" si="17"/>
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R556" s="5" t="s">
-        <v>125</v>
+        <v>51</v>
       </c>
       <c r="S556" s="5"/>
       <c r="T556" s="5" t="s">
-        <v>1587</v>
+        <v>1586</v>
       </c>
       <c r="U556" s="5" t="s">
-        <v>1665</v>
+        <v>316</v>
       </c>
       <c r="V556" s="5"/>
       <c r="W556" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="X556" s="5" t="s">
-        <v>130</v>
-      </c>
+      <c r="X556" s="5"/>
       <c r="Y556" s="5" t="s">
-        <v>1666</v>
+        <v>94</v>
       </c>
     </row>
     <row r="557" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A557" s="5" t="s">
-        <v>1588</v>
+        <v>1664</v>
       </c>
       <c r="B557" s="5"/>
       <c r="C557" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="D557" s="5"/>
-      <c r="E557" s="5"/>
-      <c r="F557" s="5"/>
+      <c r="D557" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="E557" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F557" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="G557" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="H557" s="5"/>
-      <c r="I557" s="5"/>
+        <v>1851</v>
+      </c>
+      <c r="H557" s="5" t="s">
+        <v>1162</v>
+      </c>
+      <c r="I557" s="5" t="s">
+        <v>49</v>
+      </c>
       <c r="J557" s="5"/>
-      <c r="K557" s="5"/>
+      <c r="K557" s="5" t="s">
+        <v>49</v>
+      </c>
       <c r="L557" s="5"/>
       <c r="M557" s="5"/>
       <c r="N557" s="5" t="s">
-        <v>50</v>
+        <v>124</v>
       </c>
       <c r="O557" s="5"/>
       <c r="P557" s="6">
         <f t="shared" si="18"/>
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Q557" s="6" t="str">
         <f t="shared" si="17"/>
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R557" s="5" t="s">
-        <v>51</v>
+        <v>125</v>
       </c>
       <c r="S557" s="5"/>
-      <c r="T557" s="5"/>
-      <c r="U557" s="5"/>
+      <c r="T557" s="5" t="s">
+        <v>1587</v>
+      </c>
+      <c r="U557" s="5" t="s">
+        <v>1665</v>
+      </c>
       <c r="V557" s="5"/>
       <c r="W557" s="5" t="s">
         <v>43</v>
       </c>
       <c r="X557" s="5" t="s">
-        <v>68</v>
+        <v>130</v>
       </c>
       <c r="Y557" s="5" t="s">
-        <v>547</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="558" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A558" s="5" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="B558" s="5"/>
-      <c r="C558" s="5"/>
+      <c r="C558" s="5" t="s">
+        <v>43</v>
+      </c>
       <c r="D558" s="5"/>
       <c r="E558" s="5"/>
       <c r="F558" s="5"/>
-      <c r="G558" s="5"/>
-      <c r="H558" s="5" t="s">
-        <v>90</v>
-      </c>
+      <c r="G558" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="H558" s="5"/>
       <c r="I558" s="5"/>
       <c r="J558" s="5"/>
       <c r="K558" s="5"/>
       <c r="L558" s="5"/>
       <c r="M558" s="5"/>
       <c r="N558" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="O558" s="5" t="s">
-        <v>103</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="O558" s="5"/>
       <c r="P558" s="6">
         <f t="shared" si="18"/>
         <v>1</v>
@@ -46934,40 +46968,34 @@
       </c>
       <c r="S558" s="5"/>
       <c r="T558" s="5"/>
-      <c r="U558" s="5" t="s">
-        <v>90</v>
-      </c>
+      <c r="U558" s="5"/>
       <c r="V558" s="5"/>
       <c r="W558" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="X558" s="5"/>
-      <c r="Y558" s="5"/>
+        <v>43</v>
+      </c>
+      <c r="X558" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y558" s="5" t="s">
+        <v>547</v>
+      </c>
     </row>
     <row r="559" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A559" s="5" t="s">
-        <v>1590</v>
+        <v>1589</v>
       </c>
       <c r="B559" s="5"/>
       <c r="C559" s="5"/>
       <c r="D559" s="5"/>
-      <c r="E559" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F559" s="5" t="s">
-        <v>46</v>
-      </c>
+      <c r="E559" s="5"/>
+      <c r="F559" s="5"/>
       <c r="G559" s="5"/>
       <c r="H559" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="I559" s="5" t="s">
-        <v>133</v>
-      </c>
+      <c r="I559" s="5"/>
       <c r="J559" s="5"/>
-      <c r="K559" s="5" t="s">
-        <v>133</v>
-      </c>
+      <c r="K559" s="5"/>
       <c r="L559" s="5"/>
       <c r="M559" s="5"/>
       <c r="N559" s="5" t="s">
@@ -46978,7 +47006,7 @@
       </c>
       <c r="P559" s="6">
         <f t="shared" si="18"/>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Q559" s="6" t="str">
         <f t="shared" si="17"/>
@@ -46987,12 +47015,8 @@
       <c r="R559" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="S559" s="5" t="s">
-        <v>1591</v>
-      </c>
-      <c r="T559" s="5" t="s">
-        <v>1592</v>
-      </c>
+      <c r="S559" s="5"/>
+      <c r="T559" s="5"/>
       <c r="U559" s="5" t="s">
         <v>90</v>
       </c>
@@ -47001,26 +47025,32 @@
         <v>105</v>
       </c>
       <c r="X559" s="5"/>
-      <c r="Y559" s="5" t="s">
-        <v>203</v>
-      </c>
+      <c r="Y559" s="5"/>
     </row>
     <row r="560" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A560" s="5" t="s">
-        <v>1593</v>
+        <v>1590</v>
       </c>
       <c r="B560" s="5"/>
       <c r="C560" s="5"/>
       <c r="D560" s="5"/>
-      <c r="E560" s="5"/>
-      <c r="F560" s="5"/>
+      <c r="E560" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F560" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="G560" s="5"/>
       <c r="H560" s="5" t="s">
-        <v>259</v>
-      </c>
-      <c r="I560" s="5"/>
+        <v>90</v>
+      </c>
+      <c r="I560" s="5" t="s">
+        <v>133</v>
+      </c>
       <c r="J560" s="5"/>
-      <c r="K560" s="5"/>
+      <c r="K560" s="5" t="s">
+        <v>133</v>
+      </c>
       <c r="L560" s="5"/>
       <c r="M560" s="5"/>
       <c r="N560" s="5" t="s">
@@ -47031,7 +47061,7 @@
       </c>
       <c r="P560" s="6">
         <f t="shared" si="18"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Q560" s="6" t="str">
         <f t="shared" si="17"/>
@@ -47040,53 +47070,51 @@
       <c r="R560" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="S560" s="5"/>
-      <c r="T560" s="5"/>
+      <c r="S560" s="5" t="s">
+        <v>1591</v>
+      </c>
+      <c r="T560" s="5" t="s">
+        <v>1592</v>
+      </c>
       <c r="U560" s="5" t="s">
-        <v>261</v>
+        <v>90</v>
       </c>
       <c r="V560" s="5"/>
       <c r="W560" s="5" t="s">
         <v>105</v>
       </c>
       <c r="X560" s="5"/>
-      <c r="Y560" s="5"/>
+      <c r="Y560" s="5" t="s">
+        <v>203</v>
+      </c>
     </row>
     <row r="561" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A561" s="5" t="s">
-        <v>1594</v>
+        <v>1593</v>
       </c>
       <c r="B561" s="5"/>
-      <c r="C561" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="D561" s="5" t="s">
-        <v>76</v>
-      </c>
+      <c r="C561" s="5"/>
+      <c r="D561" s="5"/>
       <c r="E561" s="5"/>
       <c r="F561" s="5"/>
-      <c r="G561" s="5" t="s">
-        <v>57</v>
-      </c>
+      <c r="G561" s="5"/>
       <c r="H561" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="I561" s="5" t="s">
-        <v>192</v>
-      </c>
+        <v>259</v>
+      </c>
+      <c r="I561" s="5"/>
       <c r="J561" s="5"/>
-      <c r="K561" s="5" t="s">
-        <v>192</v>
-      </c>
+      <c r="K561" s="5"/>
       <c r="L561" s="5"/>
       <c r="M561" s="5"/>
       <c r="N561" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="O561" s="5"/>
+        <v>66</v>
+      </c>
+      <c r="O561" s="5" t="s">
+        <v>103</v>
+      </c>
       <c r="P561" s="6">
         <f t="shared" si="18"/>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Q561" s="6" t="str">
         <f t="shared" si="17"/>
@@ -47096,26 +47124,20 @@
         <v>51</v>
       </c>
       <c r="S561" s="5"/>
-      <c r="T561" s="5" t="s">
-        <v>1595</v>
-      </c>
+      <c r="T561" s="5"/>
       <c r="U561" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="V561" s="5" t="s">
-        <v>57</v>
-      </c>
+        <v>261</v>
+      </c>
+      <c r="V561" s="5"/>
       <c r="W561" s="5" t="s">
-        <v>43</v>
+        <v>105</v>
       </c>
       <c r="X561" s="5"/>
-      <c r="Y561" s="5" t="s">
-        <v>352</v>
-      </c>
+      <c r="Y561" s="5"/>
     </row>
     <row r="562" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A562" s="5" t="s">
-        <v>1596</v>
+        <v>1594</v>
       </c>
       <c r="B562" s="5"/>
       <c r="C562" s="5" t="s">
@@ -47133,11 +47155,11 @@
         <v>77</v>
       </c>
       <c r="I562" s="5" t="s">
-        <v>133</v>
+        <v>192</v>
       </c>
       <c r="J562" s="5"/>
       <c r="K562" s="5" t="s">
-        <v>133</v>
+        <v>192</v>
       </c>
       <c r="L562" s="5"/>
       <c r="M562" s="5"/>
@@ -47158,183 +47180,185 @@
       </c>
       <c r="S562" s="5"/>
       <c r="T562" s="5" t="s">
-        <v>1597</v>
+        <v>1595</v>
       </c>
       <c r="U562" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="V562" s="5"/>
+      <c r="V562" s="5" t="s">
+        <v>57</v>
+      </c>
       <c r="W562" s="5" t="s">
         <v>43</v>
       </c>
       <c r="X562" s="5"/>
       <c r="Y562" s="5" t="s">
-        <v>64</v>
+        <v>352</v>
       </c>
     </row>
     <row r="563" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A563" s="5" t="s">
-        <v>1598</v>
+        <v>1596</v>
       </c>
       <c r="B563" s="5"/>
       <c r="C563" s="5" t="s">
         <v>43</v>
       </c>
       <c r="D563" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="E563" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F563" s="5" t="s">
-        <v>46</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="E563" s="5"/>
+      <c r="F563" s="5"/>
       <c r="G563" s="5" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="H563" s="5" t="s">
-        <v>1531</v>
+        <v>77</v>
       </c>
       <c r="I563" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="J563" s="5" t="s">
-        <v>193</v>
-      </c>
+        <v>133</v>
+      </c>
+      <c r="J563" s="5"/>
       <c r="K563" s="5" t="s">
-        <v>1599</v>
+        <v>133</v>
       </c>
       <c r="L563" s="5"/>
       <c r="M563" s="5"/>
       <c r="N563" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="O563" s="5" t="s">
-        <v>1600</v>
-      </c>
+      <c r="O563" s="5"/>
       <c r="P563" s="6">
         <f t="shared" si="18"/>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q563" s="6" t="str">
         <f t="shared" si="17"/>
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R563" s="5" t="s">
         <v>51</v>
       </c>
       <c r="S563" s="5"/>
       <c r="T563" s="5" t="s">
-        <v>1601</v>
+        <v>1597</v>
       </c>
       <c r="U563" s="5" t="s">
-        <v>635</v>
-      </c>
-      <c r="V563" s="5" t="s">
-        <v>1602</v>
-      </c>
+        <v>77</v>
+      </c>
+      <c r="V563" s="5"/>
       <c r="W563" s="5" t="s">
         <v>43</v>
       </c>
       <c r="X563" s="5"/>
       <c r="Y563" s="5" t="s">
-        <v>390</v>
+        <v>64</v>
       </c>
     </row>
     <row r="564" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A564" s="5" t="s">
-        <v>1603</v>
+        <v>1598</v>
       </c>
       <c r="B564" s="5"/>
       <c r="C564" s="5" t="s">
-        <v>70</v>
+        <v>43</v>
       </c>
       <c r="D564" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="E564" s="5"/>
-      <c r="F564" s="5"/>
-      <c r="G564" s="5"/>
+        <v>44</v>
+      </c>
+      <c r="E564" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F564" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G564" s="5" t="s">
+        <v>47</v>
+      </c>
       <c r="H564" s="5" t="s">
-        <v>77</v>
+        <v>1531</v>
       </c>
       <c r="I564" s="5" t="s">
-        <v>72</v>
+        <v>192</v>
       </c>
       <c r="J564" s="5" t="s">
-        <v>71</v>
+        <v>193</v>
       </c>
       <c r="K564" s="5" t="s">
-        <v>1604</v>
+        <v>1599</v>
       </c>
       <c r="L564" s="5"/>
       <c r="M564" s="5"/>
       <c r="N564" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="O564" s="5"/>
+      <c r="O564" s="5" t="s">
+        <v>1600</v>
+      </c>
       <c r="P564" s="6">
         <f t="shared" si="18"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q564" s="6" t="str">
         <f t="shared" si="17"/>
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R564" s="5" t="s">
         <v>51</v>
       </c>
       <c r="S564" s="5"/>
       <c r="T564" s="5" t="s">
-        <v>1605</v>
+        <v>1601</v>
       </c>
       <c r="U564" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="V564" s="5"/>
-      <c r="W564" s="5"/>
+        <v>635</v>
+      </c>
+      <c r="V564" s="5" t="s">
+        <v>1602</v>
+      </c>
+      <c r="W564" s="5" t="s">
+        <v>43</v>
+      </c>
       <c r="X564" s="5"/>
       <c r="Y564" s="5" t="s">
-        <v>428</v>
+        <v>390</v>
       </c>
     </row>
     <row r="565" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A565" s="5" t="s">
-        <v>1606</v>
+        <v>1603</v>
       </c>
       <c r="B565" s="5"/>
-      <c r="C565" s="5"/>
-      <c r="D565" s="5"/>
-      <c r="E565" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F565" s="5" t="s">
-        <v>107</v>
-      </c>
+      <c r="C565" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="D565" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="E565" s="5"/>
+      <c r="F565" s="5"/>
       <c r="G565" s="5"/>
       <c r="H565" s="5" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="I565" s="5" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="J565" s="5" t="s">
-        <v>1607</v>
+        <v>71</v>
       </c>
       <c r="K565" s="5" t="s">
-        <v>1608</v>
+        <v>1604</v>
       </c>
       <c r="L565" s="5"/>
       <c r="M565" s="5"/>
       <c r="N565" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="O565" s="5" t="s">
-        <v>103</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="O565" s="5"/>
       <c r="P565" s="6">
         <f t="shared" si="18"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q565" s="6" t="str">
         <f t="shared" si="17"/>
@@ -47343,187 +47367,185 @@
       <c r="R565" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="S565" s="5" t="s">
-        <v>1609</v>
-      </c>
+      <c r="S565" s="5"/>
       <c r="T565" s="5" t="s">
-        <v>1610</v>
+        <v>1605</v>
       </c>
       <c r="U565" s="5" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="V565" s="5"/>
-      <c r="W565" s="5" t="s">
-        <v>105</v>
-      </c>
+      <c r="W565" s="5"/>
       <c r="X565" s="5"/>
       <c r="Y565" s="5" t="s">
-        <v>203</v>
+        <v>428</v>
       </c>
     </row>
     <row r="566" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A566" s="5" t="s">
-        <v>1611</v>
+        <v>1606</v>
       </c>
       <c r="B566" s="5"/>
-      <c r="C566" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="D566" s="5" t="s">
-        <v>76</v>
-      </c>
+      <c r="C566" s="5"/>
+      <c r="D566" s="5"/>
       <c r="E566" s="5" t="s">
         <v>45</v>
       </c>
       <c r="F566" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="G566" s="5" t="s">
-        <v>47</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="G566" s="5"/>
       <c r="H566" s="5" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="I566" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="J566" s="5"/>
+        <v>59</v>
+      </c>
+      <c r="J566" s="5" t="s">
+        <v>1607</v>
+      </c>
       <c r="K566" s="5" t="s">
-        <v>71</v>
+        <v>1608</v>
       </c>
       <c r="L566" s="5"/>
       <c r="M566" s="5"/>
       <c r="N566" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="O566" s="5"/>
+      <c r="O566" s="5" t="s">
+        <v>103</v>
+      </c>
       <c r="P566" s="6">
         <f t="shared" si="18"/>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q566" s="6" t="str">
         <f t="shared" si="17"/>
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R566" s="5" t="s">
         <v>51</v>
       </c>
       <c r="S566" s="5" t="s">
-        <v>1612</v>
+        <v>1609</v>
       </c>
       <c r="T566" s="5" t="s">
-        <v>1613</v>
+        <v>1610</v>
       </c>
       <c r="U566" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="V566" s="5" t="s">
-        <v>67</v>
-      </c>
+        <v>83</v>
+      </c>
+      <c r="V566" s="5"/>
       <c r="W566" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="X566" s="5" t="s">
-        <v>187</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="X566" s="5"/>
       <c r="Y566" s="5" t="s">
-        <v>88</v>
+        <v>203</v>
       </c>
     </row>
     <row r="567" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A567" s="5" t="s">
-        <v>1614</v>
+        <v>1611</v>
       </c>
       <c r="B567" s="5"/>
-      <c r="C567" s="5"/>
-      <c r="D567" s="5"/>
+      <c r="C567" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D567" s="5" t="s">
+        <v>76</v>
+      </c>
       <c r="E567" s="5" t="s">
         <v>45</v>
       </c>
       <c r="F567" s="5" t="s">
-        <v>107</v>
+        <v>46</v>
       </c>
       <c r="G567" s="5" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="H567" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="I567" s="5"/>
+        <v>77</v>
+      </c>
+      <c r="I567" s="5" t="s">
+        <v>71</v>
+      </c>
       <c r="J567" s="5"/>
-      <c r="K567" s="5"/>
+      <c r="K567" s="5" t="s">
+        <v>71</v>
+      </c>
       <c r="L567" s="5"/>
       <c r="M567" s="5"/>
       <c r="N567" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="O567" s="5" t="s">
-        <v>103</v>
-      </c>
+      <c r="O567" s="5"/>
       <c r="P567" s="6">
         <f t="shared" si="18"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q567" s="6" t="str">
         <f t="shared" si="17"/>
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R567" s="5" t="s">
         <v>51</v>
       </c>
       <c r="S567" s="5" t="s">
-        <v>1615</v>
+        <v>1612</v>
       </c>
       <c r="T567" s="5" t="s">
-        <v>1616</v>
+        <v>1613</v>
       </c>
       <c r="U567" s="5" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="V567" s="5" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="W567" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="X567" s="5"/>
+        <v>43</v>
+      </c>
+      <c r="X567" s="5" t="s">
+        <v>187</v>
+      </c>
       <c r="Y567" s="5" t="s">
-        <v>1468</v>
+        <v>88</v>
       </c>
     </row>
     <row r="568" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A568" s="5" t="s">
-        <v>1617</v>
+        <v>1614</v>
       </c>
       <c r="B568" s="5"/>
-      <c r="C568" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="D568" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="E568" s="5"/>
-      <c r="F568" s="5"/>
-      <c r="G568" s="5"/>
+      <c r="C568" s="5"/>
+      <c r="D568" s="5"/>
+      <c r="E568" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F568" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="G568" s="5" t="s">
+        <v>57</v>
+      </c>
       <c r="H568" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="I568" s="5" t="s">
-        <v>91</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="I568" s="5"/>
       <c r="J568" s="5"/>
-      <c r="K568" s="5" t="s">
-        <v>91</v>
-      </c>
+      <c r="K568" s="5"/>
       <c r="L568" s="5"/>
       <c r="M568" s="5"/>
       <c r="N568" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="O568" s="5"/>
+        <v>66</v>
+      </c>
+      <c r="O568" s="5" t="s">
+        <v>103</v>
+      </c>
       <c r="P568" s="6">
         <f t="shared" si="18"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q568" s="6" t="str">
         <f t="shared" si="17"/>
@@ -47532,49 +47554,49 @@
       <c r="R568" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="S568" s="5"/>
+      <c r="S568" s="5" t="s">
+        <v>1615</v>
+      </c>
       <c r="T568" s="5" t="s">
-        <v>1618</v>
+        <v>1616</v>
       </c>
       <c r="U568" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="V568" s="5"/>
-      <c r="W568" s="5"/>
+        <v>63</v>
+      </c>
+      <c r="V568" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="W568" s="5" t="s">
+        <v>105</v>
+      </c>
       <c r="X568" s="5"/>
       <c r="Y568" s="5" t="s">
-        <v>428</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="569" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A569" s="5" t="s">
-        <v>1619</v>
+        <v>1617</v>
       </c>
       <c r="B569" s="5"/>
       <c r="C569" s="5" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="D569" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="E569" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F569" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="G569" s="5" t="s">
-        <v>57</v>
-      </c>
+      <c r="E569" s="5"/>
+      <c r="F569" s="5"/>
+      <c r="G569" s="5"/>
       <c r="H569" s="5" t="s">
-        <v>96</v>
+        <v>132</v>
       </c>
       <c r="I569" s="5" t="s">
-        <v>133</v>
+        <v>91</v>
       </c>
       <c r="J569" s="5"/>
       <c r="K569" s="5" t="s">
-        <v>133</v>
+        <v>91</v>
       </c>
       <c r="L569" s="5"/>
       <c r="M569" s="5"/>
@@ -47584,43 +47606,39 @@
       <c r="O569" s="5"/>
       <c r="P569" s="6">
         <f t="shared" si="18"/>
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Q569" s="6" t="str">
         <f t="shared" si="17"/>
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R569" s="5" t="s">
         <v>51</v>
       </c>
       <c r="S569" s="5"/>
       <c r="T569" s="5" t="s">
-        <v>1620</v>
+        <v>1618</v>
       </c>
       <c r="U569" s="5" t="s">
-        <v>99</v>
+        <v>132</v>
       </c>
       <c r="V569" s="5"/>
-      <c r="W569" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="X569" s="5" t="s">
-        <v>68</v>
-      </c>
+      <c r="W569" s="5"/>
+      <c r="X569" s="5"/>
       <c r="Y569" s="5" t="s">
-        <v>81</v>
+        <v>428</v>
       </c>
     </row>
     <row r="570" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A570" s="5" t="s">
-        <v>1621</v>
+        <v>1619</v>
       </c>
       <c r="B570" s="5"/>
       <c r="C570" s="5" t="s">
         <v>43</v>
       </c>
       <c r="D570" s="5" t="s">
-        <v>76</v>
+        <v>44</v>
       </c>
       <c r="E570" s="5" t="s">
         <v>45</v>
@@ -47629,14 +47647,18 @@
         <v>46</v>
       </c>
       <c r="G570" s="5" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="H570" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="I570" s="5"/>
+        <v>96</v>
+      </c>
+      <c r="I570" s="5" t="s">
+        <v>133</v>
+      </c>
       <c r="J570" s="5"/>
-      <c r="K570" s="5"/>
+      <c r="K570" s="5" t="s">
+        <v>133</v>
+      </c>
       <c r="L570" s="5"/>
       <c r="M570" s="5"/>
       <c r="N570" s="5" t="s">
@@ -47645,66 +47667,68 @@
       <c r="O570" s="5"/>
       <c r="P570" s="6">
         <f t="shared" si="18"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q570" s="6" t="str">
         <f t="shared" si="17"/>
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R570" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="S570" s="5" t="s">
-        <v>1894</v>
-      </c>
+      <c r="S570" s="5"/>
       <c r="T570" s="5" t="s">
-        <v>1893</v>
-      </c>
-      <c r="U570" s="5"/>
-      <c r="V570" s="5" t="s">
-        <v>47</v>
-      </c>
+        <v>1620</v>
+      </c>
+      <c r="U570" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="V570" s="5"/>
       <c r="W570" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="X570" s="5"/>
+      <c r="X570" s="5" t="s">
+        <v>68</v>
+      </c>
       <c r="Y570" s="5" t="s">
-        <v>136</v>
+        <v>81</v>
       </c>
     </row>
     <row r="571" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A571" s="5" t="s">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="B571" s="5"/>
-      <c r="C571" s="5"/>
-      <c r="D571" s="5"/>
-      <c r="E571" s="5"/>
-      <c r="F571" s="5"/>
-      <c r="G571" s="5"/>
+      <c r="C571" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D571" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="E571" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F571" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G571" s="5" t="s">
+        <v>47</v>
+      </c>
       <c r="H571" s="5" t="s">
-        <v>557</v>
-      </c>
-      <c r="I571" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="J571" s="5" t="s">
-        <v>1623</v>
-      </c>
-      <c r="K571" s="5" t="s">
-        <v>1624</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="I571" s="5"/>
+      <c r="J571" s="5"/>
+      <c r="K571" s="5"/>
       <c r="L571" s="5"/>
       <c r="M571" s="5"/>
       <c r="N571" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="O571" s="5" t="s">
-        <v>103</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="O571" s="5"/>
       <c r="P571" s="6">
         <f t="shared" si="18"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Q571" s="6" t="str">
         <f t="shared" si="17"/>
@@ -47713,143 +47737,153 @@
       <c r="R571" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="S571" s="5"/>
+      <c r="S571" s="5" t="s">
+        <v>1894</v>
+      </c>
       <c r="T571" s="5" t="s">
-        <v>1625</v>
-      </c>
-      <c r="U571" s="5" t="s">
-        <v>557</v>
-      </c>
-      <c r="V571" s="5"/>
+        <v>1893</v>
+      </c>
+      <c r="U571" s="5"/>
+      <c r="V571" s="5" t="s">
+        <v>47</v>
+      </c>
       <c r="W571" s="5" t="s">
-        <v>105</v>
+        <v>43</v>
       </c>
       <c r="X571" s="5"/>
-      <c r="Y571" s="5"/>
+      <c r="Y571" s="5" t="s">
+        <v>136</v>
+      </c>
     </row>
     <row r="572" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A572" s="5" t="s">
-        <v>1626</v>
+        <v>1622</v>
       </c>
       <c r="B572" s="5"/>
-      <c r="C572" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="D572" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="E572" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F572" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="G572" s="5" t="s">
-        <v>57</v>
-      </c>
+      <c r="C572" s="5"/>
+      <c r="D572" s="5"/>
+      <c r="E572" s="5"/>
+      <c r="F572" s="5"/>
+      <c r="G572" s="5"/>
       <c r="H572" s="5" t="s">
-        <v>83</v>
+        <v>557</v>
       </c>
       <c r="I572" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="J572" s="5"/>
+        <v>71</v>
+      </c>
+      <c r="J572" s="5" t="s">
+        <v>1623</v>
+      </c>
       <c r="K572" s="5" t="s">
-        <v>1627</v>
+        <v>1624</v>
       </c>
       <c r="L572" s="5"/>
       <c r="M572" s="5"/>
       <c r="N572" s="5" t="s">
-        <v>110</v>
+        <v>66</v>
       </c>
       <c r="O572" s="5" t="s">
-        <v>225</v>
+        <v>103</v>
       </c>
       <c r="P572" s="6">
         <f t="shared" si="18"/>
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Q572" s="6" t="str">
         <f t="shared" si="17"/>
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R572" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="S572" s="5" t="s">
-        <v>1628</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="S572" s="5"/>
       <c r="T572" s="5" t="s">
-        <v>1629</v>
+        <v>1625</v>
       </c>
       <c r="U572" s="5" t="s">
-        <v>1630</v>
-      </c>
-      <c r="V572" s="5" t="s">
-        <v>57</v>
-      </c>
+        <v>557</v>
+      </c>
+      <c r="V572" s="5"/>
       <c r="W572" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="X572" s="5" t="s">
-        <v>471</v>
-      </c>
-      <c r="Y572" s="5" t="s">
-        <v>117</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="X572" s="5"/>
+      <c r="Y572" s="5"/>
     </row>
     <row r="573" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A573" s="5" t="s">
-        <v>1631</v>
+        <v>1626</v>
       </c>
       <c r="B573" s="5"/>
       <c r="C573" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="D573" s="5"/>
-      <c r="E573" s="5"/>
-      <c r="F573" s="5"/>
+      <c r="D573" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="E573" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F573" s="5" t="s">
+        <v>107</v>
+      </c>
       <c r="G573" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="H573" s="5"/>
-      <c r="I573" s="5"/>
+        <v>57</v>
+      </c>
+      <c r="H573" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="I573" s="5" t="s">
+        <v>91</v>
+      </c>
       <c r="J573" s="5"/>
-      <c r="K573" s="5"/>
+      <c r="K573" s="5" t="s">
+        <v>1627</v>
+      </c>
       <c r="L573" s="5"/>
       <c r="M573" s="5"/>
       <c r="N573" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="O573" s="5"/>
+        <v>110</v>
+      </c>
+      <c r="O573" s="5" t="s">
+        <v>225</v>
+      </c>
       <c r="P573" s="6">
         <f t="shared" si="18"/>
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Q573" s="6" t="str">
         <f t="shared" si="17"/>
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R573" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="S573" s="5"/>
-      <c r="T573" s="5"/>
-      <c r="U573" s="5"/>
+        <v>112</v>
+      </c>
+      <c r="S573" s="5" t="s">
+        <v>1628</v>
+      </c>
+      <c r="T573" s="5" t="s">
+        <v>1629</v>
+      </c>
+      <c r="U573" s="5" t="s">
+        <v>1630</v>
+      </c>
       <c r="V573" s="5" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="W573" s="5" t="s">
         <v>43</v>
       </c>
       <c r="X573" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="Y573" s="5"/>
+        <v>471</v>
+      </c>
+      <c r="Y573" s="5" t="s">
+        <v>117</v>
+      </c>
     </row>
     <row r="574" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A574" s="5" t="s">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="B574" s="5"/>
       <c r="C574" s="5" t="s">
@@ -47868,7 +47902,7 @@
       <c r="L574" s="5"/>
       <c r="M574" s="5"/>
       <c r="N574" s="5" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="O574" s="5"/>
       <c r="P574" s="6">
@@ -47885,41 +47919,35 @@
       <c r="S574" s="5"/>
       <c r="T574" s="5"/>
       <c r="U574" s="5"/>
-      <c r="V574" s="5"/>
+      <c r="V574" s="5" t="s">
+        <v>67</v>
+      </c>
       <c r="W574" s="5" t="s">
         <v>43</v>
       </c>
       <c r="X574" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="Y574" s="5" t="s">
-        <v>547</v>
-      </c>
+      <c r="Y574" s="5"/>
     </row>
     <row r="575" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A575" s="5" t="s">
-        <v>1633</v>
+        <v>1632</v>
       </c>
       <c r="B575" s="5"/>
       <c r="C575" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="D575" s="5" t="s">
-        <v>76</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="D575" s="5"/>
       <c r="E575" s="5"/>
       <c r="F575" s="5"/>
-      <c r="G575" s="5"/>
-      <c r="H575" s="5" t="s">
-        <v>1634</v>
-      </c>
-      <c r="I575" s="5" t="s">
-        <v>192</v>
-      </c>
+      <c r="G575" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="H575" s="5"/>
+      <c r="I575" s="5"/>
       <c r="J575" s="5"/>
-      <c r="K575" s="5" t="s">
-        <v>192</v>
-      </c>
+      <c r="K575" s="5"/>
       <c r="L575" s="5"/>
       <c r="M575" s="5"/>
       <c r="N575" s="5" t="s">
@@ -47928,7 +47956,7 @@
       <c r="O575" s="5"/>
       <c r="P575" s="6">
         <f t="shared" si="18"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q575" s="6" t="str">
         <f t="shared" si="17"/>
@@ -47939,47 +47967,41 @@
       </c>
       <c r="S575" s="5"/>
       <c r="T575" s="5"/>
-      <c r="U575" s="5" t="s">
-        <v>1634</v>
-      </c>
+      <c r="U575" s="5"/>
       <c r="V575" s="5"/>
-      <c r="W575" s="5"/>
-      <c r="X575" s="5"/>
+      <c r="W575" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="X575" s="5" t="s">
+        <v>68</v>
+      </c>
       <c r="Y575" s="5" t="s">
-        <v>189</v>
+        <v>547</v>
       </c>
     </row>
     <row r="576" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A576" s="5" t="s">
-        <v>1635</v>
+        <v>1633</v>
       </c>
       <c r="B576" s="5"/>
       <c r="C576" s="5" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="D576" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="E576" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F576" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="G576" s="5" t="s">
-        <v>57</v>
-      </c>
+      <c r="E576" s="5"/>
+      <c r="F576" s="5"/>
+      <c r="G576" s="5"/>
       <c r="H576" s="5" t="s">
-        <v>83</v>
+        <v>1634</v>
       </c>
       <c r="I576" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="J576" s="5" t="s">
-        <v>193</v>
-      </c>
+        <v>192</v>
+      </c>
+      <c r="J576" s="5"/>
       <c r="K576" s="5" t="s">
-        <v>1636</v>
+        <v>192</v>
       </c>
       <c r="L576" s="5"/>
       <c r="M576" s="5"/>
@@ -47989,56 +48011,58 @@
       <c r="O576" s="5"/>
       <c r="P576" s="6">
         <f t="shared" si="18"/>
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Q576" s="6" t="str">
         <f t="shared" si="17"/>
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R576" s="5" t="s">
         <v>51</v>
       </c>
       <c r="S576" s="5"/>
-      <c r="T576" s="5" t="s">
-        <v>1637</v>
-      </c>
+      <c r="T576" s="5"/>
       <c r="U576" s="5" t="s">
-        <v>83</v>
+        <v>1634</v>
       </c>
       <c r="V576" s="5"/>
-      <c r="W576" s="5" t="s">
-        <v>43</v>
-      </c>
+      <c r="W576" s="5"/>
       <c r="X576" s="5"/>
       <c r="Y576" s="5" t="s">
-        <v>136</v>
+        <v>189</v>
       </c>
     </row>
     <row r="577" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A577" s="5" t="s">
-        <v>1638</v>
+        <v>1635</v>
       </c>
       <c r="B577" s="5"/>
       <c r="C577" s="5" t="s">
-        <v>70</v>
+        <v>43</v>
       </c>
       <c r="D577" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="E577" s="5"/>
-      <c r="F577" s="5"/>
-      <c r="G577" s="5"/>
+        <v>76</v>
+      </c>
+      <c r="E577" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F577" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G577" s="5" t="s">
+        <v>57</v>
+      </c>
       <c r="H577" s="5" t="s">
-        <v>58</v>
+        <v>83</v>
       </c>
       <c r="I577" s="5" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="J577" s="5" t="s">
-        <v>1639</v>
+        <v>193</v>
       </c>
       <c r="K577" s="5" t="s">
-        <v>1640</v>
+        <v>1636</v>
       </c>
       <c r="L577" s="5"/>
       <c r="M577" s="5"/>
@@ -48048,209 +48072,219 @@
       <c r="O577" s="5"/>
       <c r="P577" s="6">
         <f t="shared" si="18"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q577" s="6" t="str">
-        <f t="shared" ref="Q577:Q640" si="19">IF(A577="","",IF(AND(P577=6,UPPER(L577)&lt;&gt;"Y",C577&lt;&gt;""),"Yes","No"))</f>
-        <v>No</v>
+        <f t="shared" si="17"/>
+        <v>Yes</v>
       </c>
       <c r="R577" s="5" t="s">
         <v>51</v>
       </c>
       <c r="S577" s="5"/>
       <c r="T577" s="5" t="s">
-        <v>1641</v>
+        <v>1637</v>
       </c>
       <c r="U577" s="5" t="s">
-        <v>63</v>
+        <v>83</v>
       </c>
       <c r="V577" s="5"/>
-      <c r="W577" s="5"/>
+      <c r="W577" s="5" t="s">
+        <v>43</v>
+      </c>
       <c r="X577" s="5"/>
       <c r="Y577" s="5" t="s">
-        <v>428</v>
+        <v>136</v>
       </c>
     </row>
     <row r="578" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A578" s="5" t="s">
-        <v>1642</v>
+        <v>1638</v>
       </c>
       <c r="B578" s="5"/>
       <c r="C578" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="D578" s="5"/>
+        <v>70</v>
+      </c>
+      <c r="D578" s="5" t="s">
+        <v>44</v>
+      </c>
       <c r="E578" s="5"/>
       <c r="F578" s="5"/>
-      <c r="G578" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="H578" s="5"/>
-      <c r="I578" s="5"/>
-      <c r="J578" s="5"/>
-      <c r="K578" s="5"/>
+      <c r="G578" s="5"/>
+      <c r="H578" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="I578" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="J578" s="5" t="s">
+        <v>1639</v>
+      </c>
+      <c r="K578" s="5" t="s">
+        <v>1640</v>
+      </c>
       <c r="L578" s="5"/>
       <c r="M578" s="5"/>
       <c r="N578" s="5" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="O578" s="5"/>
       <c r="P578" s="6">
         <f t="shared" si="18"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q578" s="6" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" ref="Q578:Q641" si="19">IF(A578="","",IF(AND(P578=6,UPPER(L578)&lt;&gt;"Y",C578&lt;&gt;""),"Yes","No"))</f>
         <v>No</v>
       </c>
       <c r="R578" s="5" t="s">
         <v>51</v>
       </c>
       <c r="S578" s="5"/>
-      <c r="T578" s="5"/>
-      <c r="U578" s="5"/>
-      <c r="V578" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="W578" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="X578" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="Y578" s="5"/>
+      <c r="T578" s="5" t="s">
+        <v>1641</v>
+      </c>
+      <c r="U578" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="V578" s="5"/>
+      <c r="W578" s="5"/>
+      <c r="X578" s="5"/>
+      <c r="Y578" s="5" t="s">
+        <v>428</v>
+      </c>
     </row>
     <row r="579" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A579" s="5" t="s">
-        <v>1643</v>
+        <v>1642</v>
       </c>
       <c r="B579" s="5"/>
       <c r="C579" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="D579" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="E579" s="5" t="s">
-        <v>331</v>
-      </c>
-      <c r="F579" s="5" t="s">
-        <v>46</v>
-      </c>
+      <c r="D579" s="5"/>
+      <c r="E579" s="5"/>
+      <c r="F579" s="5"/>
       <c r="G579" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="H579" s="5" t="s">
-        <v>332</v>
-      </c>
-      <c r="I579" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="J579" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="K579" s="5" t="s">
-        <v>1644</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="H579" s="5"/>
+      <c r="I579" s="5"/>
+      <c r="J579" s="5"/>
+      <c r="K579" s="5"/>
       <c r="L579" s="5"/>
       <c r="M579" s="5"/>
       <c r="N579" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="O579" s="5" t="s">
-        <v>225</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="O579" s="5"/>
       <c r="P579" s="6">
         <f t="shared" si="18"/>
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Q579" s="6" t="str">
         <f t="shared" si="19"/>
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R579" s="5" t="s">
-        <v>112</v>
+        <v>51</v>
       </c>
       <c r="S579" s="5"/>
-      <c r="T579" s="5" t="s">
-        <v>1645</v>
-      </c>
-      <c r="U579" s="5" t="s">
-        <v>746</v>
-      </c>
-      <c r="V579" s="5"/>
+      <c r="T579" s="5"/>
+      <c r="U579" s="5"/>
+      <c r="V579" s="5" t="s">
+        <v>67</v>
+      </c>
       <c r="W579" s="5" t="s">
         <v>43</v>
       </c>
       <c r="X579" s="5" t="s">
-        <v>1646</v>
-      </c>
-      <c r="Y579" s="5" t="s">
-        <v>1647</v>
-      </c>
+        <v>68</v>
+      </c>
+      <c r="Y579" s="5"/>
     </row>
     <row r="580" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A580" s="5" t="s">
-        <v>1648</v>
+        <v>1643</v>
       </c>
       <c r="B580" s="5"/>
-      <c r="C580" s="5"/>
-      <c r="D580" s="5"/>
+      <c r="C580" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D580" s="5" t="s">
+        <v>76</v>
+      </c>
       <c r="E580" s="5" t="s">
         <v>331</v>
       </c>
-      <c r="F580" s="5"/>
-      <c r="G580" s="5"/>
-      <c r="H580" s="5"/>
-      <c r="I580" s="5"/>
-      <c r="J580" s="5"/>
-      <c r="K580" s="5"/>
+      <c r="F580" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G580" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="H580" s="5" t="s">
+        <v>332</v>
+      </c>
+      <c r="I580" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="J580" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="K580" s="5" t="s">
+        <v>1644</v>
+      </c>
       <c r="L580" s="5"/>
       <c r="M580" s="5"/>
       <c r="N580" s="5" t="s">
-        <v>66</v>
+        <v>110</v>
       </c>
       <c r="O580" s="5" t="s">
-        <v>103</v>
+        <v>225</v>
       </c>
       <c r="P580" s="6">
         <f t="shared" si="18"/>
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Q580" s="6" t="str">
         <f t="shared" si="19"/>
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R580" s="5" t="s">
-        <v>51</v>
+        <v>112</v>
       </c>
       <c r="S580" s="5"/>
       <c r="T580" s="5" t="s">
-        <v>331</v>
-      </c>
-      <c r="U580" s="5"/>
+        <v>1645</v>
+      </c>
+      <c r="U580" s="5" t="s">
+        <v>746</v>
+      </c>
       <c r="V580" s="5"/>
       <c r="W580" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="X580" s="5"/>
+        <v>43</v>
+      </c>
+      <c r="X580" s="5" t="s">
+        <v>1646</v>
+      </c>
       <c r="Y580" s="5" t="s">
-        <v>1371</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="581" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A581" s="5" t="s">
-        <v>1649</v>
+        <v>1648</v>
       </c>
       <c r="B581" s="5"/>
       <c r="C581" s="5"/>
       <c r="D581" s="5"/>
-      <c r="E581" s="5"/>
+      <c r="E581" s="5" t="s">
+        <v>331</v>
+      </c>
       <c r="F581" s="5"/>
       <c r="G581" s="5"/>
-      <c r="H581" s="5" t="s">
-        <v>437</v>
-      </c>
+      <c r="H581" s="5"/>
       <c r="I581" s="5"/>
       <c r="J581" s="5"/>
       <c r="K581" s="5"/>
@@ -48259,7 +48293,9 @@
       <c r="N581" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="O581" s="5"/>
+      <c r="O581" s="5" t="s">
+        <v>103</v>
+      </c>
       <c r="P581" s="6">
         <f t="shared" si="18"/>
         <v>1</v>
@@ -48272,132 +48308,130 @@
         <v>51</v>
       </c>
       <c r="S581" s="5"/>
-      <c r="T581" s="5"/>
-      <c r="U581" s="5" t="s">
-        <v>437</v>
-      </c>
+      <c r="T581" s="5" t="s">
+        <v>331</v>
+      </c>
+      <c r="U581" s="5"/>
       <c r="V581" s="5"/>
-      <c r="W581" s="5"/>
+      <c r="W581" s="5" t="s">
+        <v>105</v>
+      </c>
       <c r="X581" s="5"/>
-      <c r="Y581" s="5"/>
+      <c r="Y581" s="5" t="s">
+        <v>1371</v>
+      </c>
     </row>
     <row r="582" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A582" s="5" t="s">
-        <v>1650</v>
+        <v>1649</v>
       </c>
       <c r="B582" s="5"/>
-      <c r="C582" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="D582" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="E582" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F582" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="G582" s="5" t="s">
-        <v>47</v>
-      </c>
+      <c r="C582" s="5"/>
+      <c r="D582" s="5"/>
+      <c r="E582" s="5"/>
+      <c r="F582" s="5"/>
+      <c r="G582" s="5"/>
       <c r="H582" s="5" t="s">
-        <v>1125</v>
-      </c>
-      <c r="I582" s="5" t="s">
-        <v>91</v>
-      </c>
+        <v>437</v>
+      </c>
+      <c r="I582" s="5"/>
       <c r="J582" s="5"/>
-      <c r="K582" s="5" t="s">
-        <v>91</v>
-      </c>
+      <c r="K582" s="5"/>
       <c r="L582" s="5"/>
       <c r="M582" s="5"/>
       <c r="N582" s="5" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="O582" s="5"/>
       <c r="P582" s="6">
         <f t="shared" si="18"/>
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Q582" s="6" t="str">
         <f t="shared" si="19"/>
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R582" s="5" t="s">
         <v>51</v>
       </c>
       <c r="S582" s="5"/>
-      <c r="T582" s="5" t="s">
-        <v>1651</v>
-      </c>
+      <c r="T582" s="5"/>
       <c r="U582" s="5" t="s">
-        <v>1125</v>
+        <v>437</v>
       </c>
       <c r="V582" s="5"/>
-      <c r="W582" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="X582" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="Y582" s="5" t="s">
-        <v>81</v>
-      </c>
+      <c r="W582" s="5"/>
+      <c r="X582" s="5"/>
+      <c r="Y582" s="5"/>
     </row>
     <row r="583" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A583" s="5" t="s">
-        <v>1652</v>
+        <v>1650</v>
       </c>
       <c r="B583" s="5"/>
       <c r="C583" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="D583" s="5"/>
-      <c r="E583" s="5"/>
-      <c r="F583" s="5"/>
-      <c r="G583" s="5"/>
+        <v>43</v>
+      </c>
+      <c r="D583" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="E583" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F583" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="G583" s="5" t="s">
+        <v>47</v>
+      </c>
       <c r="H583" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="I583" s="5"/>
+        <v>1125</v>
+      </c>
+      <c r="I583" s="5" t="s">
+        <v>91</v>
+      </c>
       <c r="J583" s="5"/>
-      <c r="K583" s="5"/>
+      <c r="K583" s="5" t="s">
+        <v>91</v>
+      </c>
       <c r="L583" s="5"/>
       <c r="M583" s="5"/>
       <c r="N583" s="5" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="O583" s="5"/>
       <c r="P583" s="6">
         <f t="shared" si="18"/>
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Q583" s="6" t="str">
         <f t="shared" si="19"/>
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R583" s="5" t="s">
         <v>51</v>
       </c>
       <c r="S583" s="5"/>
-      <c r="T583" s="5"/>
+      <c r="T583" s="5" t="s">
+        <v>1651</v>
+      </c>
       <c r="U583" s="5" t="s">
-        <v>63</v>
+        <v>1125</v>
       </c>
       <c r="V583" s="5"/>
       <c r="W583" s="5" t="s">
-        <v>128</v>
+        <v>43</v>
       </c>
       <c r="X583" s="5" t="s">
-        <v>268</v>
-      </c>
-      <c r="Y583" s="5"/>
+        <v>68</v>
+      </c>
+      <c r="Y583" s="5" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="584" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A584" s="5" t="s">
-        <v>1653</v>
+        <v>1652</v>
       </c>
       <c r="B584" s="5"/>
       <c r="C584" s="5" t="s">
@@ -48406,10 +48440,10 @@
       <c r="D584" s="5"/>
       <c r="E584" s="5"/>
       <c r="F584" s="5"/>
-      <c r="G584" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="H584" s="5"/>
+      <c r="G584" s="5"/>
+      <c r="H584" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="I584" s="5"/>
       <c r="J584" s="5"/>
       <c r="K584" s="5"/>
@@ -48431,85 +48465,73 @@
         <v>51</v>
       </c>
       <c r="S584" s="5"/>
-      <c r="T584" s="5" t="s">
-        <v>1654</v>
-      </c>
-      <c r="U584" s="5"/>
-      <c r="V584" s="5" t="s">
-        <v>57</v>
-      </c>
+      <c r="T584" s="5"/>
+      <c r="U584" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="V584" s="5"/>
       <c r="W584" s="5" t="s">
         <v>128</v>
       </c>
       <c r="X584" s="5" t="s">
-        <v>130</v>
+        <v>268</v>
       </c>
       <c r="Y584" s="5"/>
     </row>
     <row r="585" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A585" s="5" t="s">
-        <v>1415</v>
+        <v>1653</v>
       </c>
       <c r="B585" s="5"/>
       <c r="C585" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="D585" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="E585" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F585" s="5" t="s">
-        <v>46</v>
-      </c>
+        <v>128</v>
+      </c>
+      <c r="D585" s="5"/>
+      <c r="E585" s="5"/>
+      <c r="F585" s="5"/>
       <c r="G585" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="H585" s="5" t="s">
-        <v>313</v>
-      </c>
-      <c r="I585" s="5" t="s">
-        <v>192</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="H585" s="5"/>
+      <c r="I585" s="5"/>
       <c r="J585" s="5"/>
-      <c r="K585" s="5" t="s">
-        <v>192</v>
-      </c>
+      <c r="K585" s="5"/>
       <c r="L585" s="5"/>
       <c r="M585" s="5"/>
       <c r="N585" s="5" t="s">
-        <v>124</v>
+        <v>66</v>
       </c>
       <c r="O585" s="5"/>
       <c r="P585" s="6">
         <f t="shared" si="18"/>
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Q585" s="6" t="str">
         <f t="shared" si="19"/>
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R585" s="5" t="s">
-        <v>125</v>
+        <v>51</v>
       </c>
       <c r="S585" s="5"/>
-      <c r="T585" s="5"/>
-      <c r="U585" s="5" t="s">
-        <v>1655</v>
-      </c>
+      <c r="T585" s="5" t="s">
+        <v>1654</v>
+      </c>
+      <c r="U585" s="5"/>
       <c r="V585" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="W585" s="5"/>
-      <c r="X585" s="5"/>
-      <c r="Y585" s="5" t="s">
-        <v>575</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="W585" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="X585" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="Y585" s="5"/>
     </row>
     <row r="586" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A586" s="5" t="s">
-        <v>1656</v>
+        <v>1415</v>
       </c>
       <c r="B586" s="5"/>
       <c r="C586" s="5" t="s">
@@ -48522,7 +48544,7 @@
         <v>45</v>
       </c>
       <c r="F586" s="5" t="s">
-        <v>107</v>
+        <v>46</v>
       </c>
       <c r="G586" s="5" t="s">
         <v>47</v>
@@ -48531,16 +48553,16 @@
         <v>313</v>
       </c>
       <c r="I586" s="5" t="s">
-        <v>91</v>
+        <v>192</v>
       </c>
       <c r="J586" s="5"/>
       <c r="K586" s="5" t="s">
-        <v>91</v>
+        <v>192</v>
       </c>
       <c r="L586" s="5"/>
       <c r="M586" s="5"/>
       <c r="N586" s="5" t="s">
-        <v>50</v>
+        <v>124</v>
       </c>
       <c r="O586" s="5"/>
       <c r="P586" s="6">
@@ -48552,79 +48574,93 @@
         <v>Yes</v>
       </c>
       <c r="R586" s="5" t="s">
-        <v>51</v>
+        <v>125</v>
       </c>
       <c r="S586" s="5"/>
-      <c r="T586" s="5" t="s">
-        <v>1657</v>
-      </c>
+      <c r="T586" s="5"/>
       <c r="U586" s="5" t="s">
-        <v>316</v>
-      </c>
-      <c r="V586" s="5"/>
-      <c r="W586" s="5" t="s">
-        <v>43</v>
-      </c>
+        <v>1655</v>
+      </c>
+      <c r="V586" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="W586" s="5"/>
       <c r="X586" s="5"/>
       <c r="Y586" s="5" t="s">
-        <v>1658</v>
+        <v>575</v>
       </c>
     </row>
     <row r="587" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A587" s="5" t="s">
-        <v>1659</v>
+        <v>1656</v>
       </c>
       <c r="B587" s="5"/>
       <c r="C587" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="D587" s="5"/>
-      <c r="E587" s="5"/>
-      <c r="F587" s="5"/>
+      <c r="D587" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="E587" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F587" s="5" t="s">
+        <v>107</v>
+      </c>
       <c r="G587" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="H587" s="5"/>
-      <c r="I587" s="5"/>
+      <c r="H587" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="I587" s="5" t="s">
+        <v>91</v>
+      </c>
       <c r="J587" s="5"/>
-      <c r="K587" s="5"/>
+      <c r="K587" s="5" t="s">
+        <v>91</v>
+      </c>
       <c r="L587" s="5"/>
       <c r="M587" s="5"/>
       <c r="N587" s="5" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="O587" s="5"/>
       <c r="P587" s="6">
         <f t="shared" si="18"/>
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Q587" s="6" t="str">
         <f t="shared" si="19"/>
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R587" s="5" t="s">
         <v>51</v>
       </c>
       <c r="S587" s="5"/>
-      <c r="T587" s="5"/>
-      <c r="U587" s="5"/>
-      <c r="V587" s="5" t="s">
-        <v>67</v>
-      </c>
+      <c r="T587" s="5" t="s">
+        <v>1657</v>
+      </c>
+      <c r="U587" s="5" t="s">
+        <v>316</v>
+      </c>
+      <c r="V587" s="5"/>
       <c r="W587" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="X587" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="Y587" s="5"/>
+      <c r="X587" s="5"/>
+      <c r="Y587" s="5" t="s">
+        <v>1658</v>
+      </c>
     </row>
     <row r="588" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A588" s="5" t="s">
-        <v>43</v>
+        <v>1659</v>
       </c>
       <c r="B588" s="5"/>
-      <c r="C588" s="5"/>
+      <c r="C588" s="5" t="s">
+        <v>43</v>
+      </c>
       <c r="D588" s="5"/>
       <c r="E588" s="5"/>
       <c r="F588" s="5"/>
@@ -48658,45 +48694,39 @@
       <c r="V588" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="W588" s="5"/>
-      <c r="X588" s="5"/>
+      <c r="W588" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="X588" s="5" t="s">
+        <v>68</v>
+      </c>
       <c r="Y588" s="5"/>
     </row>
     <row r="589" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A589" s="5" t="s">
-        <v>1660</v>
+        <v>43</v>
       </c>
       <c r="B589" s="5"/>
-      <c r="C589" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="D589" s="5" t="s">
-        <v>76</v>
-      </c>
+      <c r="C589" s="5"/>
+      <c r="D589" s="5"/>
       <c r="E589" s="5"/>
       <c r="F589" s="5"/>
-      <c r="G589" s="5"/>
-      <c r="H589" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="I589" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="J589" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="K589" s="5" t="s">
-        <v>1661</v>
-      </c>
+      <c r="G589" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="H589" s="5"/>
+      <c r="I589" s="5"/>
+      <c r="J589" s="5"/>
+      <c r="K589" s="5"/>
       <c r="L589" s="5"/>
       <c r="M589" s="5"/>
       <c r="N589" s="5" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="O589" s="5"/>
       <c r="P589" s="6">
         <f t="shared" si="18"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q589" s="6" t="str">
         <f t="shared" si="19"/>
@@ -48707,47 +48737,49 @@
       </c>
       <c r="S589" s="5"/>
       <c r="T589" s="5"/>
-      <c r="U589" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="V589" s="5"/>
-      <c r="W589" s="5" t="s">
-        <v>43</v>
-      </c>
+      <c r="U589" s="5"/>
+      <c r="V589" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="W589" s="5"/>
       <c r="X589" s="5"/>
-      <c r="Y589" s="5" t="s">
-        <v>352</v>
-      </c>
+      <c r="Y589" s="5"/>
     </row>
     <row r="590" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A590" s="5" t="s">
-        <v>1662</v>
+        <v>1660</v>
       </c>
       <c r="B590" s="5"/>
       <c r="C590" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="D590" s="5"/>
-      <c r="E590" s="5" t="s">
-        <v>45</v>
-      </c>
+      <c r="D590" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="E590" s="5"/>
       <c r="F590" s="5"/>
-      <c r="G590" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="H590" s="5"/>
-      <c r="I590" s="5"/>
-      <c r="J590" s="5"/>
-      <c r="K590" s="5"/>
+      <c r="G590" s="5"/>
+      <c r="H590" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="I590" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="J590" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="K590" s="5" t="s">
+        <v>1661</v>
+      </c>
       <c r="L590" s="5"/>
       <c r="M590" s="5"/>
       <c r="N590" s="5" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="O590" s="5"/>
       <c r="P590" s="6">
         <f t="shared" si="18"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q590" s="6" t="str">
         <f t="shared" si="19"/>
@@ -48756,56 +48788,74 @@
       <c r="R590" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="S590" s="5" t="s">
-        <v>1663</v>
-      </c>
+      <c r="S590" s="5"/>
       <c r="T590" s="5"/>
-      <c r="U590" s="5"/>
-      <c r="V590" s="5" t="s">
-        <v>67</v>
-      </c>
+      <c r="U590" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="V590" s="5"/>
       <c r="W590" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="X590" s="5" t="s">
-        <v>68</v>
-      </c>
+      <c r="X590" s="5"/>
       <c r="Y590" s="5" t="s">
-        <v>336</v>
+        <v>352</v>
       </c>
     </row>
     <row r="591" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A591" s="5"/>
+      <c r="A591" s="5" t="s">
+        <v>1662</v>
+      </c>
       <c r="B591" s="5"/>
-      <c r="C591" s="5"/>
+      <c r="C591" s="5" t="s">
+        <v>43</v>
+      </c>
       <c r="D591" s="5"/>
-      <c r="E591" s="5"/>
+      <c r="E591" s="5" t="s">
+        <v>45</v>
+      </c>
       <c r="F591" s="5"/>
-      <c r="G591" s="5"/>
+      <c r="G591" s="5" t="s">
+        <v>47</v>
+      </c>
       <c r="H591" s="5"/>
       <c r="I591" s="5"/>
       <c r="J591" s="5"/>
       <c r="K591" s="5"/>
       <c r="L591" s="5"/>
       <c r="M591" s="5"/>
-      <c r="N591" s="5"/>
+      <c r="N591" s="5" t="s">
+        <v>66</v>
+      </c>
       <c r="O591" s="5"/>
-      <c r="P591" s="6" t="str">
+      <c r="P591" s="6">
         <f t="shared" si="18"/>
-        <v/>
+        <v>2</v>
       </c>
       <c r="Q591" s="6" t="str">
         <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="R591" s="5"/>
-      <c r="S591" s="5"/>
+        <v>No</v>
+      </c>
+      <c r="R591" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="S591" s="5" t="s">
+        <v>1663</v>
+      </c>
       <c r="T591" s="5"/>
       <c r="U591" s="5"/>
-      <c r="V591" s="5"/>
-      <c r="W591" s="5"/>
-      <c r="X591" s="5"/>
-      <c r="Y591" s="5"/>
+      <c r="V591" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="W591" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="X591" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y591" s="5" t="s">
+        <v>336</v>
+      </c>
     </row>
     <row r="592" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A592" s="5"/>
@@ -48890,7 +48940,7 @@
       <c r="N594" s="5"/>
       <c r="O594" s="5"/>
       <c r="P594" s="6" t="str">
-        <f t="shared" ref="P594:P657" si="20">IF(A594="","",COUNTA(D594:F594)+COUNTA(G594:G594)+COUNTA(H594:H594)+COUNTA(I594:I594))</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="Q594" s="6" t="str">
@@ -48923,7 +48973,7 @@
       <c r="N595" s="5"/>
       <c r="O595" s="5"/>
       <c r="P595" s="6" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" ref="P595:P658" si="20">IF(A595="","",COUNTA(D595:F595)+COUNTA(G595:G595)+COUNTA(H595:H595)+COUNTA(I595:I595))</f>
         <v/>
       </c>
       <c r="Q595" s="6" t="str">
@@ -50445,7 +50495,7 @@
         <v/>
       </c>
       <c r="Q641" s="6" t="str">
-        <f t="shared" ref="Q641:Q700" si="21">IF(A641="","",IF(AND(P641=6,UPPER(L641)&lt;&gt;"Y",C641&lt;&gt;""),"Yes","No"))</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="R641" s="5"/>
@@ -50478,7 +50528,7 @@
         <v/>
       </c>
       <c r="Q642" s="6" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" ref="Q642:Q701" si="21">IF(A642="","",IF(AND(P642=6,UPPER(L642)&lt;&gt;"Y",C642&lt;&gt;""),"Yes","No"))</f>
         <v/>
       </c>
       <c r="R642" s="5"/>
@@ -51002,7 +51052,7 @@
       <c r="N658" s="5"/>
       <c r="O658" s="5"/>
       <c r="P658" s="6" t="str">
-        <f t="shared" ref="P658:P700" si="22">IF(A658="","",COUNTA(D658:F658)+COUNTA(G658:G658)+COUNTA(H658:H658)+COUNTA(I658:I658))</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="Q658" s="6" t="str">
@@ -51035,7 +51085,7 @@
       <c r="N659" s="5"/>
       <c r="O659" s="5"/>
       <c r="P659" s="6" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" ref="P659:P701" si="22">IF(A659="","",COUNTA(D659:F659)+COUNTA(G659:G659)+COUNTA(H659:H659)+COUNTA(I659:I659))</f>
         <v/>
       </c>
       <c r="Q659" s="6" t="str">
@@ -52404,13 +52454,46 @@
       <c r="X700" s="5"/>
       <c r="Y700" s="5"/>
     </row>
+    <row r="701" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A701" s="5"/>
+      <c r="B701" s="5"/>
+      <c r="C701" s="5"/>
+      <c r="D701" s="5"/>
+      <c r="E701" s="5"/>
+      <c r="F701" s="5"/>
+      <c r="G701" s="5"/>
+      <c r="H701" s="5"/>
+      <c r="I701" s="5"/>
+      <c r="J701" s="5"/>
+      <c r="K701" s="5"/>
+      <c r="L701" s="5"/>
+      <c r="M701" s="5"/>
+      <c r="N701" s="5"/>
+      <c r="O701" s="5"/>
+      <c r="P701" s="6" t="str">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="Q701" s="6" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="R701" s="5"/>
+      <c r="S701" s="5"/>
+      <c r="T701" s="5"/>
+      <c r="U701" s="5"/>
+      <c r="V701" s="5"/>
+      <c r="W701" s="5"/>
+      <c r="X701" s="5"/>
+      <c r="Y701" s="5"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Y700" xr:uid="{00000000-0009-0000-0000-000001000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Y700">
-      <sortCondition ref="A1:A700"/>
+  <autoFilter ref="A1:Y701" xr:uid="{00000000-0009-0000-0000-000001000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Y701">
+      <sortCondition ref="A1:A701"/>
     </sortState>
   </autoFilter>
-  <conditionalFormatting sqref="Q2:Q700">
+  <conditionalFormatting sqref="Q2:Q701">
     <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
       <formula>"Yes"</formula>
     </cfRule>
@@ -52427,7 +52510,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>J255 J208 J302 J100 I2:I99 I303:I700 I209:I229 J230 I256:I301 I101:I194 J195 I196:I207 I231:I254</xm:sqref>
+          <xm:sqref>J255 J208 J302 J100 I2:I99 K122 I209:I229 J230 I256:I301 I231:I254 J195 I196:I207 I101:I194 I303:I701</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0100-000000000000}">
           <x14:formula1>
@@ -52436,7 +52519,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>C2:C700</xm:sqref>
+          <xm:sqref>C2:C701</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0100-000001000000}">
           <x14:formula1>
@@ -52445,7 +52528,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>D2:D700</xm:sqref>
+          <xm:sqref>D2:D701</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0100-000002000000}">
           <x14:formula1>
@@ -52454,7 +52537,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>E2:E700</xm:sqref>
+          <xm:sqref>E2:E701</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0100-000003000000}">
           <x14:formula1>
@@ -52463,7 +52546,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>F2:F700</xm:sqref>
+          <xm:sqref>F2:F701</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0100-000004000000}">
           <x14:formula1>
@@ -52472,7 +52555,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>G2:G700</xm:sqref>
+          <xm:sqref>G2:G701</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0100-000006000000}">
           <x14:formula1>
@@ -52481,7 +52564,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>L2:L700</xm:sqref>
+          <xm:sqref>L2:L701</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0100-000007000000}">
           <x14:formula1>
@@ -52490,7 +52573,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>M2:M700</xm:sqref>
+          <xm:sqref>M2:M701</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -52543,12 +52626,12 @@
         <v>1674</v>
       </c>
       <c r="E2" s="8">
-        <f>COUNTA(Roster!D2:D700)</f>
-        <v>335</v>
+        <f>COUNTA(Roster!D2:D701)</f>
+        <v>336</v>
       </c>
       <c r="F2" s="9">
-        <f>IF(COUNTA(Roster!A2:A700)=0,0,E2/COUNTA(Roster!A2:A700))</f>
-        <v>0.56876061120543298</v>
+        <f>IF(COUNTA(Roster!A2:A701)=0,0,E2/COUNTA(Roster!A2:A701))</f>
+        <v>0.56949152542372883</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -52565,12 +52648,12 @@
         <v>1676</v>
       </c>
       <c r="E3" s="8">
-        <f>COUNTA(Roster!E2:E700)</f>
-        <v>274</v>
+        <f>COUNTA(Roster!E2:E701)</f>
+        <v>278</v>
       </c>
       <c r="F3" s="9">
-        <f>IF(COUNTA(Roster!A2:A700)=0,0,E3/COUNTA(Roster!A2:A700))</f>
-        <v>0.46519524617996605</v>
+        <f>IF(COUNTA(Roster!A2:A701)=0,0,E3/COUNTA(Roster!A2:A701))</f>
+        <v>0.47118644067796611</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -52587,12 +52670,12 @@
         <v>1678</v>
       </c>
       <c r="E4" s="8">
-        <f>COUNTA(Roster!F2:F700)</f>
-        <v>266</v>
+        <f>COUNTA(Roster!F2:F701)</f>
+        <v>270</v>
       </c>
       <c r="F4" s="9">
-        <f>IF(COUNTA(Roster!A2:A700)=0,0,E4/COUNTA(Roster!A2:A700))</f>
-        <v>0.45161290322580644</v>
+        <f>IF(COUNTA(Roster!A2:A701)=0,0,E4/COUNTA(Roster!A2:A701))</f>
+        <v>0.4576271186440678</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -52609,12 +52692,12 @@
         <v>1681</v>
       </c>
       <c r="E5" s="8">
-        <f>COUNTA(Roster!G2:G700)</f>
-        <v>343</v>
+        <f>COUNTA(Roster!G2:G701)</f>
+        <v>346</v>
       </c>
       <c r="F5" s="9">
-        <f>IF(COUNTA(Roster!A2:A700)=0,0,E5/COUNTA(Roster!A2:A700))</f>
-        <v>0.58234295415959259</v>
+        <f>IF(COUNTA(Roster!A2:A701)=0,0,E5/COUNTA(Roster!A2:A701))</f>
+        <v>0.58644067796610166</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -52631,12 +52714,12 @@
         <v>1684</v>
       </c>
       <c r="E6" s="8">
-        <f>COUNTA(Roster!H2:H700)</f>
-        <v>459</v>
+        <f>COUNTA(Roster!H2:H701)</f>
+        <v>460</v>
       </c>
       <c r="F6" s="9">
-        <f>IF(COUNTA(Roster!A2:A700)=0,0,E6/COUNTA(Roster!A2:A700))</f>
-        <v>0.77928692699490665</v>
+        <f>IF(COUNTA(Roster!A2:A701)=0,0,E6/COUNTA(Roster!A2:A701))</f>
+        <v>0.77966101694915257</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
@@ -52653,12 +52736,12 @@
         <v>1687</v>
       </c>
       <c r="E7" s="8">
-        <f>COUNTA(Roster!I2:I700)</f>
-        <v>330</v>
+        <f>COUNTA(Roster!I2:I701)</f>
+        <v>331</v>
       </c>
       <c r="F7" s="9">
-        <f>IF(COUNTA(Roster!A2:A700)=0,0,E7/COUNTA(Roster!A2:A700))</f>
-        <v>0.56027164685908315</v>
+        <f>IF(COUNTA(Roster!A2:A701)=0,0,E7/COUNTA(Roster!A2:A701))</f>
+        <v>0.56101694915254241</v>
       </c>
     </row>
   </sheetData>
@@ -52700,12 +52783,12 @@
         <v>1692</v>
       </c>
       <c r="C2" s="6">
-        <f>COUNTIF(Roster!$I$2:$I$700,A2)</f>
+        <f>COUNTIF(Roster!$I$2:$I$701,A2)</f>
         <v>26</v>
       </c>
       <c r="D2" s="10">
         <f t="shared" ref="D2:D13" si="0">IF(SUM($C$2:$C$13)=0,0,C2/SUM($C$2:$C$13))</f>
-        <v>7.8787878787878782E-2</v>
+        <v>7.8549848942598186E-2</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -52716,12 +52799,12 @@
         <v>1693</v>
       </c>
       <c r="C3" s="6">
-        <f>COUNTIF(Roster!$I$2:$I$700,A3)</f>
-        <v>44</v>
+        <f>COUNTIF(Roster!$I$2:$I$701,A3)</f>
+        <v>45</v>
       </c>
       <c r="D3" s="10">
         <f t="shared" si="0"/>
-        <v>0.13333333333333333</v>
+        <v>0.13595166163141995</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -52732,12 +52815,12 @@
         <v>1694</v>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF(Roster!$I$2:$I$700,A4)</f>
+        <f>COUNTIF(Roster!$I$2:$I$701,A4)</f>
         <v>29</v>
       </c>
       <c r="D4" s="10">
         <f t="shared" si="0"/>
-        <v>8.7878787878787876E-2</v>
+        <v>8.7613293051359523E-2</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -52748,12 +52831,12 @@
         <v>1695</v>
       </c>
       <c r="C5" s="6">
-        <f>COUNTIF(Roster!$I$2:$I$700,A5)</f>
-        <v>20</v>
+        <f>COUNTIF(Roster!$I$2:$I$701,A5)</f>
+        <v>19</v>
       </c>
       <c r="D5" s="10">
         <f t="shared" si="0"/>
-        <v>6.0606060606060608E-2</v>
+        <v>5.7401812688821753E-2</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -52764,12 +52847,12 @@
         <v>1696</v>
       </c>
       <c r="C6" s="6">
-        <f>COUNTIF(Roster!$I$2:$I$700,A6)</f>
-        <v>39</v>
+        <f>COUNTIF(Roster!$I$2:$I$701,A6)</f>
+        <v>40</v>
       </c>
       <c r="D6" s="10">
         <f t="shared" si="0"/>
-        <v>0.11818181818181818</v>
+        <v>0.12084592145015106</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -52780,12 +52863,12 @@
         <v>1697</v>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIF(Roster!$I$2:$I$700,A7)</f>
+        <f>COUNTIF(Roster!$I$2:$I$701,A7)</f>
         <v>45</v>
       </c>
       <c r="D7" s="10">
         <f t="shared" si="0"/>
-        <v>0.13636363636363635</v>
+        <v>0.13595166163141995</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -52796,12 +52879,12 @@
         <v>1698</v>
       </c>
       <c r="C8" s="6">
-        <f>COUNTIF(Roster!$I$2:$I$700,A8)</f>
+        <f>COUNTIF(Roster!$I$2:$I$701,A8)</f>
         <v>36</v>
       </c>
       <c r="D8" s="10">
         <f t="shared" si="0"/>
-        <v>0.10909090909090909</v>
+        <v>0.10876132930513595</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -52812,12 +52895,12 @@
         <v>1699</v>
       </c>
       <c r="C9" s="6">
-        <f>COUNTIF(Roster!$I$2:$I$700,A9)</f>
+        <f>COUNTIF(Roster!$I$2:$I$701,A9)</f>
         <v>35</v>
       </c>
       <c r="D9" s="10">
         <f t="shared" si="0"/>
-        <v>0.10606060606060606</v>
+        <v>0.10574018126888217</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -52828,12 +52911,12 @@
         <v>1700</v>
       </c>
       <c r="C10" s="6">
-        <f>COUNTIF(Roster!$I$2:$I$700,A10)</f>
+        <f>COUNTIF(Roster!$I$2:$I$701,A10)</f>
         <v>22</v>
       </c>
       <c r="D10" s="10">
         <f t="shared" si="0"/>
-        <v>6.6666666666666666E-2</v>
+        <v>6.6465256797583083E-2</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -52844,12 +52927,12 @@
         <v>1701</v>
       </c>
       <c r="C11" s="6">
-        <f>COUNTIF(Roster!$I$2:$I$700,A11)</f>
+        <f>COUNTIF(Roster!$I$2:$I$701,A11)</f>
         <v>11</v>
       </c>
       <c r="D11" s="10">
         <f t="shared" si="0"/>
-        <v>3.3333333333333333E-2</v>
+        <v>3.3232628398791542E-2</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -52860,12 +52943,12 @@
         <v>1702</v>
       </c>
       <c r="C12" s="6">
-        <f>COUNTIF(Roster!$I$2:$I$700,A12)</f>
+        <f>COUNTIF(Roster!$I$2:$I$701,A12)</f>
         <v>14</v>
       </c>
       <c r="D12" s="10">
         <f t="shared" si="0"/>
-        <v>4.2424242424242427E-2</v>
+        <v>4.2296072507552872E-2</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -52876,12 +52959,12 @@
         <v>1703</v>
       </c>
       <c r="C13" s="6">
-        <f>COUNTIF(Roster!$I$2:$I$700,A13)</f>
+        <f>COUNTIF(Roster!$I$2:$I$701,A13)</f>
         <v>9</v>
       </c>
       <c r="D13" s="10">
         <f t="shared" si="0"/>
-        <v>2.7272727272727271E-2</v>
+        <v>2.7190332326283987E-2</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -52890,7 +52973,7 @@
       </c>
       <c r="C14" s="11">
         <f>SUM(C2:C13)</f>
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -53016,8 +53099,8 @@
         <v>1725</v>
       </c>
       <c r="B10" s="8">
-        <f>COUNTA(Roster!A2:A700)</f>
-        <v>589</v>
+        <f>COUNTA(Roster!A2:A701)</f>
+        <v>590</v>
       </c>
       <c r="C10" s="8" t="s">
         <v>1726</v>
@@ -53028,8 +53111,8 @@
         <v>1727</v>
       </c>
       <c r="B11" s="8">
-        <f>COUNTIF(Roster!Q2:Q700,"Yes")</f>
-        <v>177</v>
+        <f>COUNTIF(Roster!Q2:Q701,"Yes")</f>
+        <v>182</v>
       </c>
       <c r="C11" s="8" t="s">
         <v>1726</v>
@@ -53041,7 +53124,7 @@
       </c>
       <c r="B12" s="9">
         <f>IF(B5=0,0,B11/B5)</f>
-        <v>1.18</v>
+        <v>1.2133333333333334</v>
       </c>
       <c r="C12" s="8" t="s">
         <v>1726</v>
@@ -53052,8 +53135,8 @@
         <v>1729</v>
       </c>
       <c r="B13" s="13">
-        <f>IFERROR(AVERAGE(Roster!P2:P700),0)</f>
-        <v>3.4074702886247876</v>
+        <f>IFERROR(AVERAGE(Roster!P2:P701),0)</f>
+        <v>3.4254237288135592</v>
       </c>
       <c r="C13" s="8" t="s">
         <v>1726</v>
@@ -53064,7 +53147,7 @@
         <v>1730</v>
       </c>
       <c r="B14" s="8">
-        <f>COUNTIF(Roster!L2:L700,"Y")</f>
+        <f>COUNTIF(Roster!L2:L701,"Y")</f>
         <v>2</v>
       </c>
       <c r="C14" s="8" t="s">

--- a/data/parahumandle_design.xlsx
+++ b/data/parahumandle_design.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Research\Worm Wordle clone\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{189AE06D-8D7B-4B9E-BDAE-478F74A5D07A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA42B26E-640E-4020-8161-9A07B4F9C2B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="9060" yWindow="4110" windowWidth="28800" windowHeight="15345" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9606" uniqueCount="1909">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9607" uniqueCount="1909">
   <si>
     <t>Parahumandle – design workbook</t>
   </si>
@@ -27953,7 +27953,7 @@
         <v>43</v>
       </c>
       <c r="D222" s="5" t="s">
-        <v>44</v>
+        <v>76</v>
       </c>
       <c r="E222" s="5" t="s">
         <v>45</v>
@@ -36843,7 +36843,9 @@
       <c r="I378" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="J378" s="5"/>
+      <c r="J378" s="5" t="s">
+        <v>192</v>
+      </c>
       <c r="K378" s="5" t="s">
         <v>71</v>
       </c>

--- a/data/parahumandle_design.xlsx
+++ b/data/parahumandle_design.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Research\Worm Wordle clone\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84D1C35A-1E9A-4B7B-90FF-CAD96545A43E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED26E9CA-F7DD-4E81-841E-7BEB92F2381D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5655" yWindow="3540" windowWidth="28800" windowHeight="15345" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9731" uniqueCount="1937">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9733" uniqueCount="1937">
   <si>
     <t>Parahumandle – design workbook</t>
   </si>
@@ -44964,13 +44964,17 @@
       <c r="D519" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="E519" s="5"/>
-      <c r="F519" s="5"/>
+      <c r="E519" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F519" s="5" t="s">
+        <v>107</v>
+      </c>
       <c r="G519" s="5" t="s">
         <v>47</v>
       </c>
       <c r="H519" s="5" t="s">
-        <v>58</v>
+        <v>1923</v>
       </c>
       <c r="I519" s="5" t="s">
         <v>123</v>
@@ -44987,11 +44991,11 @@
       <c r="O519" s="5"/>
       <c r="P519" s="6">
         <f t="shared" si="20"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q519" s="6" t="str">
         <f t="shared" si="21"/>
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R519" s="5" t="s">
         <v>51</v>
@@ -53192,11 +53196,11 @@
       </c>
       <c r="E3" s="8">
         <f>COUNTA(Roster!E2:E707)</f>
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F3" s="9">
         <f>IF(COUNTA(Roster!A2:A707)=0,0,E3/COUNTA(Roster!A2:A707))</f>
-        <v>0.48825503355704697</v>
+        <v>0.48993288590604028</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -53214,11 +53218,11 @@
       </c>
       <c r="E4" s="8">
         <f>COUNTA(Roster!F2:F707)</f>
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F4" s="9">
         <f>IF(COUNTA(Roster!A2:A707)=0,0,E4/COUNTA(Roster!A2:A707))</f>
-        <v>0.47315436241610737</v>
+        <v>0.47483221476510068</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -53655,7 +53659,7 @@
       </c>
       <c r="B11" s="8">
         <f>COUNTIF(Roster!Q2:Q707,"Yes")</f>
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C11" s="8" t="s">
         <v>1726</v>
@@ -53667,7 +53671,7 @@
       </c>
       <c r="B12" s="9">
         <f>IF(B5=0,0,B11/B5)</f>
-        <v>1.32</v>
+        <v>1.3266666666666667</v>
       </c>
       <c r="C12" s="8" t="s">
         <v>1726</v>
@@ -53679,7 +53683,7 @@
       </c>
       <c r="B13" s="13">
         <f>IFERROR(AVERAGE(Roster!P2:P707),0)</f>
-        <v>3.4916107382550337</v>
+        <v>3.4949664429530203</v>
       </c>
       <c r="C13" s="8" t="s">
         <v>1726</v>

--- a/data/parahumandle_design.xlsx
+++ b/data/parahumandle_design.xlsx
@@ -29,7 +29,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Reference Merge Log'!$A$1:$F$513</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">Roadmap!$A$1:$D$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Roster!$A$1:$Y$707</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Roster!$A$1:$Z$707</definedName>
   </definedNames>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
@@ -15100,7 +15100,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:Y707"/>
+  <dimension ref="A1:Z707"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -15127,9 +15127,10 @@
     <col min="23" max="23" width="14" customWidth="1"/>
     <col min="24" max="24" width="12" customWidth="1"/>
     <col min="25" max="25" width="48" customWidth="1"/>
+    <col min="26" max="26" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:26" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>17</v>
       </c>
@@ -15205,8 +15206,13 @@
       <c r="Y1" s="4" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z1" s="4" t="inlineStr">
+        <is>
+          <t>Cluster (name, or NONE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>42</v>
       </c>
@@ -15271,7 +15277,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>56</v>
       </c>
@@ -15336,7 +15342,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>65</v>
       </c>
@@ -15385,7 +15391,7 @@
       </c>
       <c r="Y4" s="5"/>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>69</v>
       </c>
@@ -15444,7 +15450,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>75</v>
       </c>
@@ -15511,7 +15517,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>82</v>
       </c>
@@ -15582,7 +15588,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>89</v>
       </c>
@@ -15645,7 +15651,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>95</v>
       </c>
@@ -15714,7 +15720,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>102</v>
       </c>
@@ -15775,7 +15781,7 @@
       <c r="X10" s="5"/>
       <c r="Y10" s="5"/>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>106</v>
       </c>
@@ -15848,7 +15854,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>118</v>
       </c>
@@ -15915,7 +15921,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>122</v>
       </c>
@@ -15974,7 +15980,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>127</v>
       </c>
@@ -16035,7 +16041,7 @@
       </c>
       <c r="Y14" s="5"/>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
         <v>131</v>
       </c>
@@ -16100,7 +16106,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
         <v>137</v>
       </c>
@@ -16159,7 +16165,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
         <v>142</v>
       </c>
@@ -16226,7 +16232,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
         <v>146</v>
       </c>
@@ -16284,7 +16290,7 @@
       <c r="X18" s="5"/>
       <c r="Y18" s="5"/>
     </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
         <v>148</v>
       </c>
@@ -16337,7 +16343,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
         <v>151</v>
       </c>
@@ -16382,7 +16388,7 @@
       <c r="X20" s="5"/>
       <c r="Y20" s="5"/>
     </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>153</v>
       </c>
@@ -16431,7 +16437,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
         <v>156</v>
       </c>
@@ -16494,7 +16500,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
         <v>162</v>
       </c>
@@ -16555,7 +16561,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
         <v>168</v>
       </c>
@@ -16624,7 +16630,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
         <v>173</v>
       </c>
@@ -16663,7 +16669,7 @@
       <c r="X25" s="5"/>
       <c r="Y25" s="5"/>
     </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
         <v>174</v>
       </c>
@@ -16722,7 +16728,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="27" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
         <v>177</v>
       </c>
@@ -16789,7 +16795,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="28" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
         <v>182</v>
       </c>
@@ -16856,7 +16862,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="29" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
         <v>188</v>
       </c>
@@ -16905,7 +16911,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="30" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
         <v>190</v>
       </c>
@@ -16970,7 +16976,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="31" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
         <v>198</v>
       </c>
@@ -17033,7 +17039,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="32" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
         <v>204</v>
       </c>
@@ -17080,7 +17086,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="33" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
         <v>206</v>
       </c>
@@ -17147,7 +17153,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="34" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
         <v>213</v>
       </c>
@@ -17216,7 +17222,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="35" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
         <v>196</v>
       </c>
@@ -17283,7 +17289,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="36" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
         <v>1908</v>
       </c>
@@ -17350,7 +17356,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="37" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
         <v>223</v>
       </c>
@@ -17417,7 +17423,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="38" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
         <v>230</v>
       </c>
@@ -17480,7 +17486,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="39" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
         <v>233</v>
       </c>
@@ -17541,7 +17547,7 @@
       <c r="X39" s="5"/>
       <c r="Y39" s="5"/>
     </row>
-    <row r="40" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
         <v>235</v>
       </c>
@@ -17608,7 +17614,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="41" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
         <v>238</v>
       </c>
@@ -17675,7 +17681,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="42" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
         <v>243</v>
       </c>
@@ -17738,7 +17744,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="43" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
         <v>247</v>
       </c>
@@ -17781,7 +17787,7 @@
       <c r="X43" s="5"/>
       <c r="Y43" s="5"/>
     </row>
-    <row r="44" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
         <v>248</v>
       </c>
@@ -17830,7 +17836,7 @@
       </c>
       <c r="Y44" s="5"/>
     </row>
-    <row r="45" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
         <v>250</v>
       </c>
@@ -17883,7 +17889,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="46" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
         <v>257</v>
       </c>
@@ -17934,7 +17940,7 @@
       <c r="X46" s="5"/>
       <c r="Y46" s="5"/>
     </row>
-    <row r="47" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
         <v>262</v>
       </c>
@@ -17981,7 +17987,7 @@
       </c>
       <c r="Y47" s="5"/>
     </row>
-    <row r="48" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
         <v>265</v>
       </c>
@@ -18044,7 +18050,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="49" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
         <v>267</v>
       </c>
@@ -18093,7 +18099,7 @@
       </c>
       <c r="Y49" s="5"/>
     </row>
-    <row r="50" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
         <v>269</v>
       </c>
@@ -18166,7 +18172,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="51" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
         <v>276</v>
       </c>
@@ -18235,7 +18241,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="52" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
         <v>278</v>
       </c>
@@ -18284,7 +18290,7 @@
       </c>
       <c r="Y52" s="5"/>
     </row>
-    <row r="53" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
         <v>279</v>
       </c>
@@ -18349,7 +18355,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="54" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
         <v>282</v>
       </c>
@@ -18406,7 +18412,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="55" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
         <v>286</v>
       </c>
@@ -18475,7 +18481,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="56" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A56" s="5" t="s">
         <v>291</v>
       </c>
@@ -18538,7 +18544,7 @@
       </c>
       <c r="Y56" s="5"/>
     </row>
-    <row r="57" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
         <v>294</v>
       </c>
@@ -18593,7 +18599,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="58" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A58" s="5" t="s">
         <v>298</v>
       </c>
@@ -18652,7 +18658,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="59" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A59" s="5" t="s">
         <v>302</v>
       </c>
@@ -18707,7 +18713,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="60" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A60" s="5" t="s">
         <v>306</v>
       </c>
@@ -18756,7 +18762,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="61" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A61" s="5" t="s">
         <v>1912</v>
       </c>
@@ -18821,7 +18827,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="62" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A62" s="5" t="s">
         <v>307</v>
       </c>
@@ -18876,7 +18882,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="63" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A63" s="5" t="s">
         <v>312</v>
       </c>
@@ -18941,7 +18947,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="64" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A64" s="5" t="s">
         <v>317</v>
       </c>
@@ -18990,7 +18996,7 @@
       </c>
       <c r="Y64" s="5"/>
     </row>
-    <row r="65" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A65" s="5" t="s">
         <v>321</v>
       </c>
@@ -19059,7 +19065,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="66" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A66" s="5" t="s">
         <v>326</v>
       </c>
@@ -19106,7 +19112,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="67" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A67" s="5" t="s">
         <v>328</v>
       </c>
@@ -19169,7 +19175,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="68" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A68" s="5" t="s">
         <v>330</v>
       </c>
@@ -19220,7 +19226,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="69" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A69" s="5" t="s">
         <v>334</v>
       </c>
@@ -19275,7 +19281,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="70" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A70" s="5" t="s">
         <v>337</v>
       </c>
@@ -19344,7 +19350,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="71" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A71" s="5" t="s">
         <v>342</v>
       </c>
@@ -19413,7 +19419,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="72" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A72" s="5" t="s">
         <v>348</v>
       </c>
@@ -19476,7 +19482,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="73" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A73" s="5" t="s">
         <v>353</v>
       </c>
@@ -19529,7 +19535,7 @@
       <c r="X73" s="5"/>
       <c r="Y73" s="5"/>
     </row>
-    <row r="74" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A74" s="5" t="s">
         <v>355</v>
       </c>
@@ -19582,7 +19588,7 @@
       <c r="X74" s="5"/>
       <c r="Y74" s="5"/>
     </row>
-    <row r="75" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A75" s="5" t="s">
         <v>357</v>
       </c>
@@ -19635,7 +19641,7 @@
       <c r="X75" s="5"/>
       <c r="Y75" s="5"/>
     </row>
-    <row r="76" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A76" s="5" t="s">
         <v>359</v>
       </c>
@@ -19688,7 +19694,7 @@
       <c r="X76" s="5"/>
       <c r="Y76" s="5"/>
     </row>
-    <row r="77" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A77" s="5" t="s">
         <v>361</v>
       </c>
@@ -19741,7 +19747,7 @@
       <c r="X77" s="5"/>
       <c r="Y77" s="5"/>
     </row>
-    <row r="78" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A78" s="5" t="s">
         <v>363</v>
       </c>
@@ -19794,7 +19800,7 @@
       <c r="X78" s="5"/>
       <c r="Y78" s="5"/>
     </row>
-    <row r="79" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A79" s="5" t="s">
         <v>365</v>
       </c>
@@ -19847,7 +19853,7 @@
       <c r="X79" s="5"/>
       <c r="Y79" s="5"/>
     </row>
-    <row r="80" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A80" s="5" t="s">
         <v>367</v>
       </c>
@@ -19900,7 +19906,7 @@
       <c r="X80" s="5"/>
       <c r="Y80" s="5"/>
     </row>
-    <row r="81" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A81" s="5" t="s">
         <v>369</v>
       </c>
@@ -19953,7 +19959,7 @@
       <c r="X81" s="5"/>
       <c r="Y81" s="5"/>
     </row>
-    <row r="82" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A82" s="5" t="s">
         <v>370</v>
       </c>
@@ -20012,7 +20018,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="83" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A83" s="5" t="s">
         <v>374</v>
       </c>
@@ -20071,7 +20077,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="84" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A84" s="5" t="s">
         <v>376</v>
       </c>
@@ -20124,7 +20130,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="85" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A85" s="5" t="s">
         <v>379</v>
       </c>
@@ -20169,7 +20175,7 @@
       <c r="X85" s="5"/>
       <c r="Y85" s="5"/>
     </row>
-    <row r="86" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A86" s="5" t="s">
         <v>381</v>
       </c>
@@ -20222,7 +20228,7 @@
       <c r="X86" s="5"/>
       <c r="Y86" s="5"/>
     </row>
-    <row r="87" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A87" s="5" t="s">
         <v>383</v>
       </c>
@@ -20275,7 +20281,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="88" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A88" s="5" t="s">
         <v>385</v>
       </c>
@@ -20342,7 +20348,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="89" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A89" s="5" t="s">
         <v>391</v>
       </c>
@@ -20411,7 +20417,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="90" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A90" s="5" t="s">
         <v>393</v>
       </c>
@@ -20460,7 +20466,7 @@
       </c>
       <c r="Y90" s="5"/>
     </row>
-    <row r="91" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A91" s="5" t="s">
         <v>394</v>
       </c>
@@ -20519,7 +20525,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="92" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A92" s="5" t="s">
         <v>397</v>
       </c>
@@ -20568,7 +20574,7 @@
       <c r="X92" s="5"/>
       <c r="Y92" s="5"/>
     </row>
-    <row r="93" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A93" s="5" t="s">
         <v>400</v>
       </c>
@@ -20631,7 +20637,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="94" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A94" s="5" t="s">
         <v>405</v>
       </c>
@@ -20678,7 +20684,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="95" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A95" s="5" t="s">
         <v>406</v>
       </c>
@@ -20733,7 +20739,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="96" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A96" s="5" t="s">
         <v>407</v>
       </c>
@@ -20802,7 +20808,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="97" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A97" s="5" t="s">
         <v>413</v>
       </c>
@@ -20871,7 +20877,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="98" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A98" s="5" t="s">
         <v>418</v>
       </c>
@@ -20940,7 +20946,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="99" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A99" s="5" t="s">
         <v>423</v>
       </c>
@@ -20999,7 +21005,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="100" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A100" s="5" t="s">
         <v>426</v>
       </c>
@@ -21054,7 +21060,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="101" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A101" s="5" t="s">
         <v>429</v>
       </c>
@@ -21121,7 +21127,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="102" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A102" s="5" t="s">
         <v>434</v>
       </c>
@@ -21186,7 +21192,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="103" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A103" s="5" t="s">
         <v>436</v>
       </c>
@@ -21239,7 +21245,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="104" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A104" s="5" t="s">
         <v>439</v>
       </c>
@@ -21296,7 +21302,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="105" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A105" s="5" t="s">
         <v>443</v>
       </c>
@@ -21365,7 +21371,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="106" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A106" s="5" t="s">
         <v>452</v>
       </c>
@@ -21430,7 +21436,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="107" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A107" s="5" t="s">
         <v>455</v>
       </c>
@@ -21487,7 +21493,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="108" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A108" s="5" t="s">
         <v>459</v>
       </c>
@@ -21536,7 +21542,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="109" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A109" s="5" t="s">
         <v>460</v>
       </c>
@@ -21597,7 +21603,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="110" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A110" s="5" t="s">
         <v>465</v>
       </c>
@@ -21642,7 +21648,7 @@
       </c>
       <c r="Y110" s="5"/>
     </row>
-    <row r="111" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A111" s="5" t="s">
         <v>467</v>
       </c>
@@ -21711,7 +21717,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="112" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A112" s="5" t="s">
         <v>472</v>
       </c>
@@ -21772,7 +21778,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="113" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A113" s="5" t="s">
         <v>475</v>
       </c>
@@ -21839,7 +21845,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="114" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A114" s="5" t="s">
         <v>478</v>
       </c>
@@ -21892,7 +21898,7 @@
       </c>
       <c r="Y114" s="5"/>
     </row>
-    <row r="115" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A115" s="5" t="s">
         <v>479</v>
       </c>
@@ -21961,7 +21967,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="116" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A116" s="5" t="s">
         <v>1935</v>
       </c>
@@ -22026,7 +22032,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="117" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A117" s="5" t="s">
         <v>483</v>
       </c>
@@ -22091,7 +22097,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="118" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A118" s="5" t="s">
         <v>488</v>
       </c>
@@ -22144,7 +22150,7 @@
       </c>
       <c r="Y118" s="5"/>
     </row>
-    <row r="119" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A119" s="5" t="s">
         <v>489</v>
       </c>
@@ -22195,7 +22201,7 @@
       <c r="X119" s="5"/>
       <c r="Y119" s="5"/>
     </row>
-    <row r="120" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A120" s="5" t="s">
         <v>492</v>
       </c>
@@ -22258,7 +22264,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="121" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A121" s="5" t="s">
         <v>1930</v>
       </c>
@@ -22324,8 +22330,13 @@
       <c r="Y121" s="5" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="122" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>The Mall Cluster</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A122" s="5" t="s">
         <v>495</v>
       </c>
@@ -22392,7 +22403,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="123" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A123" s="5" t="s">
         <v>499</v>
       </c>
@@ -22455,7 +22466,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="124" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A124" s="5" t="s">
         <v>501</v>
       </c>
@@ -22522,7 +22533,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="125" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A125" s="5" t="s">
         <v>505</v>
       </c>
@@ -22571,7 +22582,7 @@
       </c>
       <c r="Y125" s="5"/>
     </row>
-    <row r="126" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A126" s="5" t="s">
         <v>506</v>
       </c>
@@ -22638,7 +22649,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="127" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A127" s="5" t="s">
         <v>509</v>
       </c>
@@ -22701,7 +22712,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="128" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A128" s="5" t="s">
         <v>511</v>
       </c>
@@ -22762,7 +22773,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="129" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A129" s="5" t="s">
         <v>514</v>
       </c>
@@ -22831,7 +22842,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="130" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A130" s="5" t="s">
         <v>1870</v>
       </c>
@@ -22896,7 +22907,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="131" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A131" s="5" t="s">
         <v>521</v>
       </c>
@@ -22963,7 +22974,7 @@
       </c>
       <c r="Y131" s="5"/>
     </row>
-    <row r="132" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A132" s="5" t="s">
         <v>525</v>
       </c>
@@ -23026,7 +23037,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="133" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A133" s="5" t="s">
         <v>531</v>
       </c>
@@ -23093,7 +23104,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="134" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A134" s="5" t="s">
         <v>534</v>
       </c>
@@ -23164,7 +23175,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="135" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A135" s="5" t="s">
         <v>541</v>
       </c>
@@ -23215,7 +23226,7 @@
       </c>
       <c r="Y135" s="5"/>
     </row>
-    <row r="136" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A136" s="5" t="s">
         <v>544</v>
       </c>
@@ -23272,7 +23283,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="137" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A137" s="5" t="s">
         <v>548</v>
       </c>
@@ -23343,7 +23354,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="138" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A138" s="5" t="s">
         <v>554</v>
       </c>
@@ -23388,7 +23399,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="139" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A139" s="5" t="s">
         <v>555</v>
       </c>
@@ -23437,7 +23448,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="140" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A140" s="5" t="s">
         <v>556</v>
       </c>
@@ -23486,7 +23497,7 @@
       <c r="X140" s="5"/>
       <c r="Y140" s="5"/>
     </row>
-    <row r="141" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A141" s="5" t="s">
         <v>559</v>
       </c>
@@ -23539,7 +23550,7 @@
       <c r="X141" s="5"/>
       <c r="Y141" s="5"/>
     </row>
-    <row r="142" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A142" s="5" t="s">
         <v>562</v>
       </c>
@@ -23592,7 +23603,7 @@
       </c>
       <c r="Y142" s="5"/>
     </row>
-    <row r="143" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A143" s="5" t="s">
         <v>564</v>
       </c>
@@ -23659,7 +23670,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="144" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A144" s="5" t="s">
         <v>567</v>
       </c>
@@ -23716,7 +23727,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="145" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A145" s="5" t="s">
         <v>571</v>
       </c>
@@ -23779,7 +23790,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="146" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A146" s="5" t="s">
         <v>574</v>
       </c>
@@ -23840,7 +23851,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="147" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A147" s="5" t="s">
         <v>576</v>
       </c>
@@ -23903,7 +23914,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="148" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A148" s="5" t="s">
         <v>579</v>
       </c>
@@ -23958,7 +23969,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="149" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A149" s="5" t="s">
         <v>584</v>
       </c>
@@ -24023,7 +24034,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="150" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A150" s="5" t="s">
         <v>588</v>
       </c>
@@ -24088,7 +24099,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="151" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A151" s="5" t="s">
         <v>592</v>
       </c>
@@ -24157,7 +24168,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="152" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A152" s="5" t="s">
         <v>600</v>
       </c>
@@ -24208,7 +24219,7 @@
       <c r="X152" s="5"/>
       <c r="Y152" s="5"/>
     </row>
-    <row r="153" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A153" s="5" t="s">
         <v>602</v>
       </c>
@@ -24259,7 +24270,7 @@
       <c r="X153" s="5"/>
       <c r="Y153" s="5"/>
     </row>
-    <row r="154" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A154" s="5" t="s">
         <v>605</v>
       </c>
@@ -24330,7 +24341,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="155" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A155" s="5" t="s">
         <v>613</v>
       </c>
@@ -24389,7 +24400,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="156" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A156" s="5" t="s">
         <v>617</v>
       </c>
@@ -24448,7 +24459,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="157" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A157" s="5" t="s">
         <v>620</v>
       </c>
@@ -24503,7 +24514,7 @@
       </c>
       <c r="Y157" s="5"/>
     </row>
-    <row r="158" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A158" s="5" t="s">
         <v>622</v>
       </c>
@@ -24544,7 +24555,7 @@
       <c r="X158" s="5"/>
       <c r="Y158" s="5"/>
     </row>
-    <row r="159" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A159" s="5" t="s">
         <v>1925</v>
       </c>
@@ -24611,7 +24622,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="160" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A160" s="5" t="s">
         <v>624</v>
       </c>
@@ -24682,7 +24693,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="161" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A161" s="5" t="s">
         <v>629</v>
       </c>
@@ -24739,7 +24750,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="162" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A162" s="5" t="s">
         <v>631</v>
       </c>
@@ -24792,7 +24803,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="163" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A163" s="5" t="s">
         <v>632</v>
       </c>
@@ -24849,7 +24860,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="164" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A164" s="5" t="s">
         <v>636</v>
       </c>
@@ -24904,7 +24915,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="165" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A165" s="5" t="s">
         <v>638</v>
       </c>
@@ -24959,7 +24970,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="166" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A166" s="5" t="s">
         <v>640</v>
       </c>
@@ -25016,7 +25027,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="167" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A167" s="5" t="s">
         <v>643</v>
       </c>
@@ -25065,7 +25076,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="168" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A168" s="5" t="s">
         <v>644</v>
       </c>
@@ -25118,7 +25129,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="169" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A169" s="5" t="s">
         <v>647</v>
       </c>
@@ -25173,7 +25184,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="170" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A170" s="5" t="s">
         <v>649</v>
       </c>
@@ -25230,7 +25241,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="171" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A171" s="5" t="s">
         <v>651</v>
       </c>
@@ -25275,7 +25286,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="172" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A172" s="5" t="s">
         <v>652</v>
       </c>
@@ -25336,7 +25347,7 @@
       </c>
       <c r="Y172" s="5"/>
     </row>
-    <row r="173" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A173" s="5" t="s">
         <v>653</v>
       </c>
@@ -25385,7 +25396,7 @@
       <c r="X173" s="5"/>
       <c r="Y173" s="5"/>
     </row>
-    <row r="174" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A174" s="5" t="s">
         <v>655</v>
       </c>
@@ -25436,7 +25447,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="175" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A175" s="5" t="s">
         <v>657</v>
       </c>
@@ -25489,7 +25500,7 @@
       <c r="X175" s="5"/>
       <c r="Y175" s="5"/>
     </row>
-    <row r="176" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A176" s="5" t="s">
         <v>659</v>
       </c>
@@ -25534,7 +25545,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="177" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A177" s="5" t="s">
         <v>661</v>
       </c>
@@ -25599,7 +25610,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="178" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A178" s="5" t="s">
         <v>664</v>
       </c>
@@ -25660,7 +25671,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="179" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A179" s="5" t="s">
         <v>668</v>
       </c>
@@ -25723,7 +25734,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="180" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A180" s="5" t="s">
         <v>671</v>
       </c>
@@ -25794,7 +25805,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="181" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A181" s="5" t="s">
         <v>676</v>
       </c>
@@ -25843,7 +25854,7 @@
       </c>
       <c r="Y181" s="5"/>
     </row>
-    <row r="182" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A182" s="5" t="s">
         <v>677</v>
       </c>
@@ -25896,7 +25907,7 @@
       </c>
       <c r="Y182" s="5"/>
     </row>
-    <row r="183" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A183" s="5" t="s">
         <v>678</v>
       </c>
@@ -25947,7 +25958,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="184" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A184" s="5" t="s">
         <v>679</v>
       </c>
@@ -25994,7 +26005,7 @@
       <c r="X184" s="5"/>
       <c r="Y184" s="5"/>
     </row>
-    <row r="185" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A185" s="5" t="s">
         <v>680</v>
       </c>
@@ -26037,7 +26048,7 @@
       <c r="X185" s="5"/>
       <c r="Y185" s="5"/>
     </row>
-    <row r="186" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A186" s="5" t="s">
         <v>681</v>
       </c>
@@ -26104,7 +26115,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="187" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A187" s="5" t="s">
         <v>685</v>
       </c>
@@ -26153,7 +26164,7 @@
       <c r="X187" s="5"/>
       <c r="Y187" s="5"/>
     </row>
-    <row r="188" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A188" s="5" t="s">
         <v>687</v>
       </c>
@@ -26226,7 +26237,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="189" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A189" s="5" t="s">
         <v>696</v>
       </c>
@@ -26271,7 +26282,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="190" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A190" s="5" t="s">
         <v>697</v>
       </c>
@@ -26336,7 +26347,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="191" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A191" s="5" t="s">
         <v>699</v>
       </c>
@@ -26393,7 +26404,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="192" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A192" s="5" t="s">
         <v>701</v>
       </c>
@@ -26448,7 +26459,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="193" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A193" s="5" t="s">
         <v>703</v>
       </c>
@@ -26521,7 +26532,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="194" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A194" s="5" t="s">
         <v>710</v>
       </c>
@@ -26572,7 +26583,7 @@
         <v>711</v>
       </c>
     </row>
-    <row r="195" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A195" s="5" t="s">
         <v>712</v>
       </c>
@@ -26635,7 +26646,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="196" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A196" s="5" t="s">
         <v>716</v>
       </c>
@@ -26702,7 +26713,7 @@
       </c>
       <c r="Y196" s="5"/>
     </row>
-    <row r="197" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A197" s="5" t="s">
         <v>720</v>
       </c>
@@ -26761,7 +26772,7 @@
       </c>
       <c r="Y197" s="5"/>
     </row>
-    <row r="198" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A198" s="5" t="s">
         <v>721</v>
       </c>
@@ -26800,7 +26811,7 @@
       <c r="X198" s="5"/>
       <c r="Y198" s="5"/>
     </row>
-    <row r="199" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A199" s="5" t="s">
         <v>722</v>
       </c>
@@ -26849,7 +26860,7 @@
       </c>
       <c r="Y199" s="5"/>
     </row>
-    <row r="200" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A200" s="5" t="s">
         <v>723</v>
       </c>
@@ -26920,7 +26931,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="201" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A201" s="5" t="s">
         <v>727</v>
       </c>
@@ -26985,7 +26996,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="202" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A202" s="5" t="s">
         <v>729</v>
       </c>
@@ -27028,7 +27039,7 @@
       <c r="X202" s="5"/>
       <c r="Y202" s="5"/>
     </row>
-    <row r="203" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A203" s="5" t="s">
         <v>731</v>
       </c>
@@ -27097,7 +27108,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="204" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A204" s="5" t="s">
         <v>735</v>
       </c>
@@ -27144,7 +27155,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="205" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A205" s="5" t="s">
         <v>736</v>
       </c>
@@ -27209,7 +27220,7 @@
       <c r="X205" s="5"/>
       <c r="Y205" s="5"/>
     </row>
-    <row r="206" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A206" s="5" t="s">
         <v>739</v>
       </c>
@@ -27276,7 +27287,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="207" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A207" s="5" t="s">
         <v>743</v>
       </c>
@@ -27325,7 +27336,7 @@
       <c r="X207" s="5"/>
       <c r="Y207" s="5"/>
     </row>
-    <row r="208" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A208" s="5" t="s">
         <v>745</v>
       </c>
@@ -27380,7 +27391,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="209" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A209" s="5" t="s">
         <v>749</v>
       </c>
@@ -27439,7 +27450,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="210" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A210" s="5" t="s">
         <v>752</v>
       </c>
@@ -27494,7 +27505,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="211" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A211" s="5" t="s">
         <v>753</v>
       </c>
@@ -27537,7 +27548,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="212" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A212" s="5" t="s">
         <v>754</v>
       </c>
@@ -27596,7 +27607,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="213" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A213" s="5" t="s">
         <v>756</v>
       </c>
@@ -27671,7 +27682,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="214" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A214" s="5" t="s">
         <v>762</v>
       </c>
@@ -27720,7 +27731,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="215" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A215" s="5" t="s">
         <v>763</v>
       </c>
@@ -27795,7 +27806,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="216" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A216" s="5" t="s">
         <v>770</v>
       </c>
@@ -27844,7 +27855,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="217" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A217" s="5" t="s">
         <v>771</v>
       </c>
@@ -27893,7 +27904,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="218" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A218" s="5" t="s">
         <v>773</v>
       </c>
@@ -27960,7 +27971,7 @@
         <v>777</v>
       </c>
     </row>
-    <row r="219" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A219" s="5" t="s">
         <v>778</v>
       </c>
@@ -28017,7 +28028,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="220" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A220" s="5" t="s">
         <v>780</v>
       </c>
@@ -28070,7 +28081,7 @@
       </c>
       <c r="Y220" s="5"/>
     </row>
-    <row r="221" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A221" s="5" t="s">
         <v>782</v>
       </c>
@@ -28135,7 +28146,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="222" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A222" s="5" t="s">
         <v>785</v>
       </c>
@@ -28182,7 +28193,7 @@
       <c r="X222" s="5"/>
       <c r="Y222" s="5"/>
     </row>
-    <row r="223" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A223" s="5" t="s">
         <v>787</v>
       </c>
@@ -28227,7 +28238,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="224" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A224" s="5" t="s">
         <v>788</v>
       </c>
@@ -28294,7 +28305,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="225" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A225" s="5" t="s">
         <v>791</v>
       </c>
@@ -28343,7 +28354,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="226" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A226" s="5" t="s">
         <v>792</v>
       </c>
@@ -28410,7 +28421,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="227" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A227" s="5" t="s">
         <v>796</v>
       </c>
@@ -28483,7 +28494,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="228" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A228" s="5" t="s">
         <v>803</v>
       </c>
@@ -28546,7 +28557,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="229" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A229" s="5" t="s">
         <v>808</v>
       </c>
@@ -28611,7 +28622,7 @@
         <v>810</v>
       </c>
     </row>
-    <row r="230" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A230" s="5" t="s">
         <v>811</v>
       </c>
@@ -28652,7 +28663,7 @@
       <c r="X230" s="5"/>
       <c r="Y230" s="5"/>
     </row>
-    <row r="231" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A231" s="5" t="s">
         <v>813</v>
       </c>
@@ -28717,7 +28728,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="232" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A232" s="5" t="s">
         <v>817</v>
       </c>
@@ -28772,7 +28783,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="233" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A233" s="5" t="s">
         <v>818</v>
       </c>
@@ -28833,7 +28844,7 @@
         <v>821</v>
       </c>
     </row>
-    <row r="234" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A234" s="5" t="s">
         <v>822</v>
       </c>
@@ -28882,7 +28893,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="235" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A235" s="5" t="s">
         <v>823</v>
       </c>
@@ -28949,7 +28960,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="236" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A236" s="5" t="s">
         <v>826</v>
       </c>
@@ -29018,7 +29029,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="237" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A237" s="5" t="s">
         <v>832</v>
       </c>
@@ -29081,7 +29092,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="238" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A238" s="5" t="s">
         <v>833</v>
       </c>
@@ -29120,7 +29131,7 @@
       <c r="X238" s="5"/>
       <c r="Y238" s="5"/>
     </row>
-    <row r="239" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A239" s="5" t="s">
         <v>834</v>
       </c>
@@ -29181,7 +29192,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="240" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A240" s="5" t="s">
         <v>836</v>
       </c>
@@ -29238,7 +29249,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="241" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A241" s="5" t="s">
         <v>76</v>
       </c>
@@ -29303,7 +29314,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="242" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A242" s="5" t="s">
         <v>840</v>
       </c>
@@ -29352,7 +29363,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="243" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A243" s="5" t="s">
         <v>841</v>
       </c>
@@ -29401,7 +29412,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="244" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A244" s="5" t="s">
         <v>842</v>
       </c>
@@ -29464,7 +29475,7 @@
       </c>
       <c r="Y244" s="5"/>
     </row>
-    <row r="245" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A245" s="5" t="s">
         <v>843</v>
       </c>
@@ -29537,7 +29548,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="246" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A246" s="5" t="s">
         <v>849</v>
       </c>
@@ -29592,7 +29603,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="247" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A247" s="5" t="s">
         <v>852</v>
       </c>
@@ -29655,7 +29666,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="248" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A248" s="5" t="s">
         <v>856</v>
       </c>
@@ -29720,7 +29731,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="249" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A249" s="5" t="s">
         <v>859</v>
       </c>
@@ -29769,7 +29780,7 @@
       </c>
       <c r="Y249" s="5"/>
     </row>
-    <row r="250" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A250" s="5" t="s">
         <v>860</v>
       </c>
@@ -29828,7 +29839,7 @@
         <v>862</v>
       </c>
     </row>
-    <row r="251" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A251" s="5" t="s">
         <v>863</v>
       </c>
@@ -29887,7 +29898,7 @@
       <c r="X251" s="5"/>
       <c r="Y251" s="5"/>
     </row>
-    <row r="252" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A252" s="5" t="s">
         <v>866</v>
       </c>
@@ -29940,7 +29951,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="253" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A253" s="5" t="s">
         <v>868</v>
       </c>
@@ -30009,7 +30020,7 @@
         <v>875</v>
       </c>
     </row>
-    <row r="254" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A254" s="5" t="s">
         <v>876</v>
       </c>
@@ -30064,7 +30075,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="255" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A255" s="5" t="s">
         <v>878</v>
       </c>
@@ -30123,7 +30134,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="256" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A256" s="5" t="s">
         <v>880</v>
       </c>
@@ -30178,7 +30189,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="257" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A257" s="5" t="s">
         <v>882</v>
       </c>
@@ -30235,7 +30246,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="258" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A258" s="5" t="s">
         <v>884</v>
       </c>
@@ -30286,7 +30297,7 @@
       <c r="X258" s="5"/>
       <c r="Y258" s="5"/>
     </row>
-    <row r="259" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A259" s="5" t="s">
         <v>885</v>
       </c>
@@ -30333,7 +30344,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="260" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A260" s="5" t="s">
         <v>887</v>
       </c>
@@ -30404,7 +30415,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="261" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A261" s="5" t="s">
         <v>893</v>
       </c>
@@ -30461,7 +30472,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="262" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A262" s="5" t="s">
         <v>895</v>
       </c>
@@ -30504,7 +30515,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="263" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A263" s="5" t="s">
         <v>896</v>
       </c>
@@ -30559,7 +30570,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="264" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A264" s="5" t="s">
         <v>897</v>
       </c>
@@ -30612,7 +30623,7 @@
         <v>899</v>
       </c>
     </row>
-    <row r="265" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A265" s="5" t="s">
         <v>900</v>
       </c>
@@ -30661,7 +30672,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="266" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A266" s="5" t="s">
         <v>901</v>
       </c>
@@ -30708,7 +30719,7 @@
       <c r="X266" s="5"/>
       <c r="Y266" s="5"/>
     </row>
-    <row r="267" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A267" s="5" t="s">
         <v>906</v>
       </c>
@@ -30759,7 +30770,7 @@
         <v>907</v>
       </c>
     </row>
-    <row r="268" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A268" s="5" t="s">
         <v>904</v>
       </c>
@@ -30808,7 +30819,7 @@
       <c r="X268" s="5"/>
       <c r="Y268" s="5"/>
     </row>
-    <row r="269" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A269" s="5" t="s">
         <v>908</v>
       </c>
@@ -30857,7 +30868,7 @@
       </c>
       <c r="Y269" s="5"/>
     </row>
-    <row r="270" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A270" s="5" t="s">
         <v>909</v>
       </c>
@@ -30918,7 +30929,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="271" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A271" s="5" t="s">
         <v>912</v>
       </c>
@@ -30971,7 +30982,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="272" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A272" s="5" t="s">
         <v>913</v>
       </c>
@@ -31022,7 +31033,7 @@
       <c r="X272" s="5"/>
       <c r="Y272" s="5"/>
     </row>
-    <row r="273" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A273" s="5" t="s">
         <v>917</v>
       </c>
@@ -31091,7 +31102,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="274" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A274" s="5" t="s">
         <v>920</v>
       </c>
@@ -31144,7 +31155,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="275" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A275" s="5" t="s">
         <v>921</v>
       </c>
@@ -31197,7 +31208,7 @@
         <v>923</v>
       </c>
     </row>
-    <row r="276" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A276" s="5" t="s">
         <v>924</v>
       </c>
@@ -31254,7 +31265,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="277" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A277" s="5" t="s">
         <v>926</v>
       </c>
@@ -31323,7 +31334,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="278" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A278" s="5" t="s">
         <v>932</v>
       </c>
@@ -31380,7 +31391,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="279" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A279" s="5" t="s">
         <v>935</v>
       </c>
@@ -31431,7 +31442,7 @@
       <c r="X279" s="5"/>
       <c r="Y279" s="5"/>
     </row>
-    <row r="280" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A280" s="5" t="s">
         <v>938</v>
       </c>
@@ -31500,7 +31511,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="281" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A281" s="5" t="s">
         <v>942</v>
       </c>
@@ -31567,7 +31578,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="282" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A282" s="5" t="s">
         <v>947</v>
       </c>
@@ -31616,7 +31627,7 @@
       </c>
       <c r="Y282" s="5"/>
     </row>
-    <row r="283" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A283" s="5" t="s">
         <v>948</v>
       </c>
@@ -31677,7 +31688,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="284" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A284" s="5" t="s">
         <v>950</v>
       </c>
@@ -31724,7 +31735,7 @@
       <c r="X284" s="5"/>
       <c r="Y284" s="5"/>
     </row>
-    <row r="285" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A285" s="5" t="s">
         <v>951</v>
       </c>
@@ -31771,7 +31782,7 @@
       <c r="X285" s="5"/>
       <c r="Y285" s="5"/>
     </row>
-    <row r="286" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A286" s="5" t="s">
         <v>952</v>
       </c>
@@ -31820,7 +31831,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="287" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A287" s="5" t="s">
         <v>953</v>
       </c>
@@ -31867,7 +31878,7 @@
       <c r="X287" s="5"/>
       <c r="Y287" s="5"/>
     </row>
-    <row r="288" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A288" s="5" t="s">
         <v>954</v>
       </c>
@@ -31924,7 +31935,7 @@
       </c>
       <c r="Y288" s="5"/>
     </row>
-    <row r="289" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A289" s="5" t="s">
         <v>957</v>
       </c>
@@ -31977,7 +31988,7 @@
         <v>958</v>
       </c>
     </row>
-    <row r="290" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A290" s="5" t="s">
         <v>959</v>
       </c>
@@ -32026,7 +32037,7 @@
       </c>
       <c r="Y290" s="5"/>
     </row>
-    <row r="291" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A291" s="5" t="s">
         <v>960</v>
       </c>
@@ -32077,7 +32088,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="292" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A292" s="5" t="s">
         <v>961</v>
       </c>
@@ -32128,7 +32139,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="293" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A293" s="5" t="s">
         <v>962</v>
       </c>
@@ -32175,7 +32186,7 @@
       <c r="X293" s="5"/>
       <c r="Y293" s="5"/>
     </row>
-    <row r="294" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A294" s="5" t="s">
         <v>963</v>
       </c>
@@ -32226,7 +32237,7 @@
       <c r="X294" s="5"/>
       <c r="Y294" s="5"/>
     </row>
-    <row r="295" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A295" s="5" t="s">
         <v>966</v>
       </c>
@@ -32265,7 +32276,7 @@
       <c r="X295" s="5"/>
       <c r="Y295" s="5"/>
     </row>
-    <row r="296" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A296" s="5" t="s">
         <v>967</v>
       </c>
@@ -32318,7 +32329,7 @@
       <c r="X296" s="5"/>
       <c r="Y296" s="5"/>
     </row>
-    <row r="297" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A297" s="5" t="s">
         <v>969</v>
       </c>
@@ -32387,7 +32398,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="298" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A298" s="5" t="s">
         <v>973</v>
       </c>
@@ -32438,7 +32449,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="299" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A299" s="5" t="s">
         <v>975</v>
       </c>
@@ -32501,7 +32512,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="300" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A300" s="5" t="s">
         <v>977</v>
       </c>
@@ -32568,7 +32579,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="301" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A301" s="5" t="s">
         <v>981</v>
       </c>
@@ -32639,7 +32650,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="302" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A302" s="5" t="s">
         <v>985</v>
       </c>
@@ -32692,7 +32703,7 @@
       </c>
       <c r="Y302" s="5"/>
     </row>
-    <row r="303" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A303" s="5" t="s">
         <v>986</v>
       </c>
@@ -32765,7 +32776,7 @@
         <v>991</v>
       </c>
     </row>
-    <row r="304" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A304" s="5" t="s">
         <v>992</v>
       </c>
@@ -32808,7 +32819,7 @@
       <c r="X304" s="5"/>
       <c r="Y304" s="5"/>
     </row>
-    <row r="305" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A305" s="5" t="s">
         <v>993</v>
       </c>
@@ -32859,7 +32870,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="306" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A306" s="5" t="s">
         <v>994</v>
       </c>
@@ -32925,7 +32936,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="307" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A307" s="5" t="s">
         <v>996</v>
       </c>
@@ -32996,7 +33007,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="308" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A308" s="5" t="s">
         <v>999</v>
       </c>
@@ -33047,7 +33058,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="309" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A309" s="5" t="s">
         <v>1001</v>
       </c>
@@ -33106,7 +33117,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="310" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A310" s="5" t="s">
         <v>1005</v>
       </c>
@@ -33159,7 +33170,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="311" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A311" s="5" t="s">
         <v>1008</v>
       </c>
@@ -33214,7 +33225,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="312" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A312" s="5" t="s">
         <v>1011</v>
       </c>
@@ -33273,7 +33284,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="313" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A313" s="5" t="s">
         <v>1013</v>
       </c>
@@ -33336,7 +33347,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="314" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A314" s="5" t="s">
         <v>1017</v>
       </c>
@@ -33403,7 +33414,7 @@
         <v>1020</v>
       </c>
     </row>
-    <row r="315" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A315" s="5" t="s">
         <v>1024</v>
       </c>
@@ -33442,7 +33453,7 @@
       <c r="X315" s="5"/>
       <c r="Y315" s="5"/>
     </row>
-    <row r="316" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A316" s="5" t="s">
         <v>1025</v>
       </c>
@@ -33499,7 +33510,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="317" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A317" s="5" t="s">
         <v>1027</v>
       </c>
@@ -33550,7 +33561,7 @@
       <c r="X317" s="5"/>
       <c r="Y317" s="5"/>
     </row>
-    <row r="318" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A318" s="5" t="s">
         <v>1030</v>
       </c>
@@ -33607,7 +33618,7 @@
       </c>
       <c r="Y318" s="5"/>
     </row>
-    <row r="319" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A319" s="5" t="s">
         <v>1032</v>
       </c>
@@ -33652,7 +33663,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="320" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A320" s="5" t="s">
         <v>1872</v>
       </c>
@@ -33721,7 +33732,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="321" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A321" s="5" t="s">
         <v>1033</v>
       </c>
@@ -33786,7 +33797,7 @@
       </c>
       <c r="Y321" s="5"/>
     </row>
-    <row r="322" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A322" s="5" t="s">
         <v>1916</v>
       </c>
@@ -33852,8 +33863,13 @@
         <v>1921</v>
       </c>
       <c r="Y322" s="5"/>
-    </row>
-    <row r="323" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z322" t="inlineStr">
+        <is>
+          <t>The Mall Cluster</t>
+        </is>
+      </c>
+    </row>
+    <row r="323" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A323" s="5" t="s">
         <v>1036</v>
       </c>
@@ -33898,7 +33914,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="324" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A324" s="5" t="s">
         <v>1037</v>
       </c>
@@ -33967,7 +33983,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="325" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A325" s="5" t="s">
         <v>1041</v>
       </c>
@@ -34032,7 +34048,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="326" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A326" s="5" t="s">
         <v>1043</v>
       </c>
@@ -34083,7 +34099,7 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="327" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A327" s="5" t="s">
         <v>1045</v>
       </c>
@@ -34138,7 +34154,7 @@
         <v>1047</v>
       </c>
     </row>
-    <row r="328" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A328" s="5" t="s">
         <v>1048</v>
       </c>
@@ -34187,7 +34203,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="329" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A329" s="5" t="s">
         <v>1049</v>
       </c>
@@ -34256,7 +34272,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="330" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A330" s="5" t="s">
         <v>1054</v>
       </c>
@@ -34325,7 +34341,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="331" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A331" s="5" t="s">
         <v>1057</v>
       </c>
@@ -34388,7 +34404,7 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="332" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A332" s="5" t="s">
         <v>1060</v>
       </c>
@@ -34449,7 +34465,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="333" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A333" s="5" t="s">
         <v>437</v>
       </c>
@@ -34516,7 +34532,7 @@
         <v>1065</v>
       </c>
     </row>
-    <row r="334" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A334" s="5" t="s">
         <v>1066</v>
       </c>
@@ -34573,7 +34589,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="335" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A335" s="5" t="s">
         <v>1068</v>
       </c>
@@ -34632,7 +34648,7 @@
         <v>1071</v>
       </c>
     </row>
-    <row r="336" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A336" s="5" t="s">
         <v>1072</v>
       </c>
@@ -34699,7 +34715,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="337" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A337" s="5" t="s">
         <v>1076</v>
       </c>
@@ -34760,7 +34776,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="338" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A338" s="5" t="s">
         <v>1079</v>
       </c>
@@ -34811,7 +34827,7 @@
       <c r="X338" s="5"/>
       <c r="Y338" s="5"/>
     </row>
-    <row r="339" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A339" s="5" t="s">
         <v>1082</v>
       </c>
@@ -34864,7 +34880,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="340" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A340" s="5" t="s">
         <v>1084</v>
       </c>
@@ -34935,7 +34951,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="341" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A341" s="5" t="s">
         <v>1087</v>
       </c>
@@ -34984,7 +35000,7 @@
       </c>
       <c r="Y341" s="5"/>
     </row>
-    <row r="342" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A342" s="5" t="s">
         <v>1088</v>
       </c>
@@ -35049,7 +35065,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="343" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A343" s="5" t="s">
         <v>1094</v>
       </c>
@@ -35098,7 +35114,7 @@
       <c r="X343" s="5"/>
       <c r="Y343" s="5"/>
     </row>
-    <row r="344" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A344" s="5" t="s">
         <v>1096</v>
       </c>
@@ -35153,7 +35169,7 @@
       <c r="X344" s="5"/>
       <c r="Y344" s="5"/>
     </row>
-    <row r="345" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A345" s="5" t="s">
         <v>1099</v>
       </c>
@@ -35200,7 +35216,7 @@
       <c r="X345" s="5"/>
       <c r="Y345" s="5"/>
     </row>
-    <row r="346" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A346" s="5" t="s">
         <v>1100</v>
       </c>
@@ -35245,7 +35261,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="347" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A347" s="5" t="s">
         <v>1101</v>
       </c>
@@ -35310,7 +35326,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="348" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A348" s="5" t="s">
         <v>1104</v>
       </c>
@@ -35357,7 +35373,7 @@
         <v>1105</v>
       </c>
     </row>
-    <row r="349" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A349" s="5" t="s">
         <v>1106</v>
       </c>
@@ -35424,7 +35440,7 @@
       </c>
       <c r="Y349" s="5"/>
     </row>
-    <row r="350" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A350" s="5" t="s">
         <v>1107</v>
       </c>
@@ -35487,7 +35503,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="351" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A351" s="5" t="s">
         <v>1109</v>
       </c>
@@ -35540,7 +35556,7 @@
       </c>
       <c r="Y351" s="5"/>
     </row>
-    <row r="352" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A352" s="5" t="s">
         <v>1110</v>
       </c>
@@ -35587,7 +35603,7 @@
         <v>1105</v>
       </c>
     </row>
-    <row r="353" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A353" s="5" t="s">
         <v>1111</v>
       </c>
@@ -35654,7 +35670,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="354" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A354" s="5" t="s">
         <v>1114</v>
       </c>
@@ -35711,7 +35727,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="355" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A355" s="5" t="s">
         <v>1117</v>
       </c>
@@ -35760,7 +35776,7 @@
         <v>1118</v>
       </c>
     </row>
-    <row r="356" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A356" s="5" t="s">
         <v>1119</v>
       </c>
@@ -35825,7 +35841,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="357" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A357" s="5" t="s">
         <v>1122</v>
       </c>
@@ -35872,7 +35888,7 @@
       <c r="X357" s="5"/>
       <c r="Y357" s="5"/>
     </row>
-    <row r="358" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A358" s="5" t="s">
         <v>1124</v>
       </c>
@@ -35937,7 +35953,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="359" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A359" s="5" t="s">
         <v>1128</v>
       </c>
@@ -35980,7 +35996,7 @@
       <c r="X359" s="5"/>
       <c r="Y359" s="5"/>
     </row>
-    <row r="360" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A360" s="5" t="s">
         <v>1130</v>
       </c>
@@ -36047,7 +36063,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="361" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A361" s="5" t="s">
         <v>1134</v>
       </c>
@@ -36096,7 +36112,7 @@
       </c>
       <c r="Y361" s="5"/>
     </row>
-    <row r="362" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A362" s="5" t="s">
         <v>1135</v>
       </c>
@@ -36163,7 +36179,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="363" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A363" s="5" t="s">
         <v>1137</v>
       </c>
@@ -36210,7 +36226,7 @@
       <c r="X363" s="5"/>
       <c r="Y363" s="5"/>
     </row>
-    <row r="364" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A364" s="5" t="s">
         <v>1138</v>
       </c>
@@ -36259,7 +36275,7 @@
       <c r="X364" s="5"/>
       <c r="Y364" s="5"/>
     </row>
-    <row r="365" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A365" s="5" t="s">
         <v>1140</v>
       </c>
@@ -36326,7 +36342,7 @@
         <v>1142</v>
       </c>
     </row>
-    <row r="366" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A366" s="5" t="s">
         <v>1133</v>
       </c>
@@ -36371,7 +36387,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="367" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A367" s="5" t="s">
         <v>1143</v>
       </c>
@@ -36438,7 +36454,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="368" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A368" s="5" t="s">
         <v>1146</v>
       </c>
@@ -36481,7 +36497,7 @@
       <c r="X368" s="5"/>
       <c r="Y368" s="5"/>
     </row>
-    <row r="369" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A369" s="5" t="s">
         <v>1147</v>
       </c>
@@ -36554,7 +36570,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="370" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A370" s="5" t="s">
         <v>1154</v>
       </c>
@@ -36613,7 +36629,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="371" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A371" s="5" t="s">
         <v>1156</v>
       </c>
@@ -36670,7 +36686,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="372" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A372" s="5" t="s">
         <v>1158</v>
       </c>
@@ -36741,7 +36757,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="373" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A373" s="5" t="s">
         <v>1163</v>
       </c>
@@ -36798,7 +36814,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="374" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A374" s="5" t="s">
         <v>1166</v>
       </c>
@@ -36847,7 +36863,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="375" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A375" s="5" t="s">
         <v>1167</v>
       </c>
@@ -36896,7 +36912,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="376" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A376" s="5" t="s">
         <v>1168</v>
       </c>
@@ -36953,7 +36969,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="377" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A377" s="5" t="s">
         <v>1174</v>
       </c>
@@ -37008,7 +37024,7 @@
       </c>
       <c r="Y377" s="5"/>
     </row>
-    <row r="378" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A378" s="5" t="s">
         <v>1176</v>
       </c>
@@ -37065,7 +37081,7 @@
       <c r="X378" s="5"/>
       <c r="Y378" s="5"/>
     </row>
-    <row r="379" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A379" s="5" t="s">
         <v>1178</v>
       </c>
@@ -37130,7 +37146,7 @@
         <v>1180</v>
       </c>
     </row>
-    <row r="380" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A380" s="5" t="s">
         <v>1181</v>
       </c>
@@ -37187,7 +37203,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="381" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A381" s="5" t="s">
         <v>1183</v>
       </c>
@@ -37242,7 +37258,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="382" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A382" s="5" t="s">
         <v>1187</v>
       </c>
@@ -37309,7 +37325,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="383" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A383" s="5" t="s">
         <v>1190</v>
       </c>
@@ -37358,7 +37374,7 @@
       <c r="X383" s="5"/>
       <c r="Y383" s="5"/>
     </row>
-    <row r="384" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A384" s="5" t="s">
         <v>1192</v>
       </c>
@@ -37427,7 +37443,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="385" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A385" s="5" t="s">
         <v>1194</v>
       </c>
@@ -37494,7 +37510,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="386" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A386" s="5" t="s">
         <v>1197</v>
       </c>
@@ -37557,7 +37573,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="387" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A387" s="5" t="s">
         <v>1199</v>
       </c>
@@ -37600,7 +37616,7 @@
       <c r="X387" s="5"/>
       <c r="Y387" s="5"/>
     </row>
-    <row r="388" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A388" s="5" t="s">
         <v>1200</v>
       </c>
@@ -37659,7 +37675,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="389" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A389" s="5" t="s">
         <v>1201</v>
       </c>
@@ -37708,7 +37724,7 @@
       <c r="X389" s="5"/>
       <c r="Y389" s="5"/>
     </row>
-    <row r="390" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A390" s="5" t="s">
         <v>1203</v>
       </c>
@@ -37779,7 +37795,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="391" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A391" s="5" t="s">
         <v>1207</v>
       </c>
@@ -37846,7 +37862,7 @@
         <v>1210</v>
       </c>
     </row>
-    <row r="392" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A392" s="5" t="s">
         <v>1211</v>
       </c>
@@ -37899,7 +37915,7 @@
       <c r="X392" s="5"/>
       <c r="Y392" s="5"/>
     </row>
-    <row r="393" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A393" s="5" t="s">
         <v>1214</v>
       </c>
@@ -37948,7 +37964,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="394" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A394" s="5" t="s">
         <v>1215</v>
       </c>
@@ -38005,7 +38021,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="395" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A395" s="5" t="s">
         <v>1217</v>
       </c>
@@ -38058,7 +38074,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="396" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A396" s="5" t="s">
         <v>1218</v>
       </c>
@@ -38123,7 +38139,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="397" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A397" s="5" t="s">
         <v>1221</v>
       </c>
@@ -38176,7 +38192,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="398" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A398" s="5" t="s">
         <v>1223</v>
       </c>
@@ -38235,7 +38251,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="399" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A399" s="5" t="s">
         <v>1225</v>
       </c>
@@ -38284,7 +38300,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="400" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A400" s="5" t="s">
         <v>1228</v>
       </c>
@@ -38351,7 +38367,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="401" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A401" s="5" t="s">
         <v>1229</v>
       </c>
@@ -38400,7 +38416,7 @@
       <c r="X401" s="5"/>
       <c r="Y401" s="5"/>
     </row>
-    <row r="402" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A402" s="5" t="s">
         <v>1232</v>
       </c>
@@ -38439,7 +38455,7 @@
       <c r="X402" s="5"/>
       <c r="Y402" s="5"/>
     </row>
-    <row r="403" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A403" s="5" t="s">
         <v>1283</v>
       </c>
@@ -38488,7 +38504,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="404" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A404" s="5" t="s">
         <v>1233</v>
       </c>
@@ -38533,7 +38549,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="405" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A405" s="5" t="s">
         <v>1234</v>
       </c>
@@ -38582,7 +38598,7 @@
       <c r="X405" s="5"/>
       <c r="Y405" s="5"/>
     </row>
-    <row r="406" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A406" s="5" t="s">
         <v>1236</v>
       </c>
@@ -38621,7 +38637,7 @@
       <c r="X406" s="5"/>
       <c r="Y406" s="5"/>
     </row>
-    <row r="407" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A407" s="5" t="s">
         <v>1237</v>
       </c>
@@ -38670,7 +38686,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="408" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A408" s="5" t="s">
         <v>1239</v>
       </c>
@@ -38731,7 +38747,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="409" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A409" s="5" t="s">
         <v>1879</v>
       </c>
@@ -38796,7 +38812,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="410" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A410" s="5" t="s">
         <v>1242</v>
       </c>
@@ -38849,7 +38865,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="411" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A411" s="5" t="s">
         <v>1244</v>
       </c>
@@ -38902,7 +38918,7 @@
       <c r="X411" s="5"/>
       <c r="Y411" s="5"/>
     </row>
-    <row r="412" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A412" s="5" t="s">
         <v>1246</v>
       </c>
@@ -38965,7 +38981,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="413" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A413" s="5" t="s">
         <v>1250</v>
       </c>
@@ -39016,7 +39032,7 @@
       <c r="X413" s="5"/>
       <c r="Y413" s="5"/>
     </row>
-    <row r="414" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A414" s="5" t="s">
         <v>1253</v>
       </c>
@@ -39069,7 +39085,7 @@
       <c r="X414" s="5"/>
       <c r="Y414" s="5"/>
     </row>
-    <row r="415" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A415" s="5" t="s">
         <v>1255</v>
       </c>
@@ -39118,7 +39134,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="416" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A416" s="5" t="s">
         <v>1256</v>
       </c>
@@ -39167,7 +39183,7 @@
       <c r="X416" s="5"/>
       <c r="Y416" s="5"/>
     </row>
-    <row r="417" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A417" s="5" t="s">
         <v>1258</v>
       </c>
@@ -39230,7 +39246,7 @@
         <v>1261</v>
       </c>
     </row>
-    <row r="418" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A418" s="5" t="s">
         <v>1262</v>
       </c>
@@ -39297,7 +39313,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="419" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A419" s="5" t="s">
         <v>1265</v>
       </c>
@@ -39348,7 +39364,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="420" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A420" s="5" t="s">
         <v>1267</v>
       </c>
@@ -39399,7 +39415,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="421" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A421" s="5" t="s">
         <v>1269</v>
       </c>
@@ -39460,7 +39476,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="422" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A422" s="5" t="s">
         <v>1272</v>
       </c>
@@ -39507,7 +39523,7 @@
       <c r="X422" s="5"/>
       <c r="Y422" s="5"/>
     </row>
-    <row r="423" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A423" s="5" t="s">
         <v>1274</v>
       </c>
@@ -39580,7 +39596,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="424" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A424" s="5" t="s">
         <v>1281</v>
       </c>
@@ -39643,7 +39659,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="425" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A425" s="5" t="s">
         <v>1284</v>
       </c>
@@ -39700,7 +39716,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="426" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A426" s="5" t="s">
         <v>1286</v>
       </c>
@@ -39747,7 +39763,7 @@
       <c r="X426" s="5"/>
       <c r="Y426" s="5"/>
     </row>
-    <row r="427" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A427" s="5" t="s">
         <v>1287</v>
       </c>
@@ -39808,7 +39824,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="428" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A428" s="5" t="s">
         <v>1289</v>
       </c>
@@ -39857,7 +39873,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="429" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A429" s="5" t="s">
         <v>1290</v>
       </c>
@@ -39920,7 +39936,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="430" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A430" s="5" t="s">
         <v>1294</v>
       </c>
@@ -39967,7 +39983,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="431" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A431" s="5" t="s">
         <v>1296</v>
       </c>
@@ -40010,7 +40026,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="432" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A432" s="5" t="s">
         <v>1297</v>
       </c>
@@ -40067,7 +40083,7 @@
       </c>
       <c r="Y432" s="5"/>
     </row>
-    <row r="433" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A433" s="5" t="s">
         <v>1299</v>
       </c>
@@ -40114,7 +40130,7 @@
         <v>1105</v>
       </c>
     </row>
-    <row r="434" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A434" s="5" t="s">
         <v>1300</v>
       </c>
@@ -40159,7 +40175,7 @@
       <c r="X434" s="5"/>
       <c r="Y434" s="5"/>
     </row>
-    <row r="435" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A435" s="5" t="s">
         <v>1302</v>
       </c>
@@ -40208,7 +40224,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="436" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A436" s="5" t="s">
         <v>1303</v>
       </c>
@@ -40269,7 +40285,7 @@
         <v>1305</v>
       </c>
     </row>
-    <row r="437" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A437" s="5" t="s">
         <v>1306</v>
       </c>
@@ -40318,7 +40334,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="438" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A438" s="5" t="s">
         <v>1307</v>
       </c>
@@ -40389,7 +40405,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="439" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A439" s="5" t="s">
         <v>1311</v>
       </c>
@@ -40436,7 +40452,7 @@
       <c r="X439" s="5"/>
       <c r="Y439" s="5"/>
     </row>
-    <row r="440" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A440" s="5" t="s">
         <v>1312</v>
       </c>
@@ -40491,7 +40507,7 @@
       </c>
       <c r="Y440" s="5"/>
     </row>
-    <row r="441" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A441" s="5" t="s">
         <v>1314</v>
       </c>
@@ -40550,7 +40566,7 @@
         <v>1316</v>
       </c>
     </row>
-    <row r="442" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A442" s="5" t="s">
         <v>1317</v>
       </c>
@@ -40607,7 +40623,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="443" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A443" s="5" t="s">
         <v>1319</v>
       </c>
@@ -40670,7 +40686,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="444" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A444" s="5" t="s">
         <v>1321</v>
       </c>
@@ -40725,7 +40741,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="445" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A445" s="5" t="s">
         <v>1322</v>
       </c>
@@ -40786,7 +40802,7 @@
         <v>1305</v>
       </c>
     </row>
-    <row r="446" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A446" s="5" t="s">
         <v>1324</v>
       </c>
@@ -40839,7 +40855,7 @@
       </c>
       <c r="Y446" s="5"/>
     </row>
-    <row r="447" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A447" s="5" t="s">
         <v>1327</v>
       </c>
@@ -40892,7 +40908,7 @@
       </c>
       <c r="Y447" s="5"/>
     </row>
-    <row r="448" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A448" s="5" t="s">
         <v>1328</v>
       </c>
@@ -40949,7 +40965,7 @@
         <v>1331</v>
       </c>
     </row>
-    <row r="449" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A449" s="5" t="s">
         <v>1332</v>
       </c>
@@ -41002,7 +41018,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="450" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A450" s="5" t="s">
         <v>1333</v>
       </c>
@@ -41061,7 +41077,7 @@
         <v>1336</v>
       </c>
     </row>
-    <row r="451" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A451" s="5" t="s">
         <v>1337</v>
       </c>
@@ -41110,7 +41126,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="452" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A452" s="5" t="s">
         <v>1338</v>
       </c>
@@ -41169,7 +41185,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="453" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A453" s="5" t="s">
         <v>1339</v>
       </c>
@@ -41230,7 +41246,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="454" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A454" s="5" t="s">
         <v>1343</v>
       </c>
@@ -41295,7 +41311,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="455" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A455" s="5" t="s">
         <v>1345</v>
       </c>
@@ -41342,7 +41358,7 @@
       <c r="X455" s="5"/>
       <c r="Y455" s="5"/>
     </row>
-    <row r="456" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A456" s="5" t="s">
         <v>1346</v>
       </c>
@@ -41411,7 +41427,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="457" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A457" s="5" t="s">
         <v>1353</v>
       </c>
@@ -41468,7 +41484,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="458" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A458" s="5" t="s">
         <v>1356</v>
       </c>
@@ -41525,7 +41541,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="459" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A459" s="5" t="s">
         <v>1357</v>
       </c>
@@ -41578,7 +41594,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="460" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A460" s="5" t="s">
         <v>1359</v>
       </c>
@@ -41639,7 +41655,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="461" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A461" s="5" t="s">
         <v>1362</v>
       </c>
@@ -41696,7 +41712,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="462" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A462" s="5" t="s">
         <v>1364</v>
       </c>
@@ -41753,7 +41769,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="463" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A463" s="5" t="s">
         <v>1368</v>
       </c>
@@ -41814,7 +41830,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="464" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A464" s="5" t="s">
         <v>1370</v>
       </c>
@@ -41859,7 +41875,7 @@
         <v>1371</v>
       </c>
     </row>
-    <row r="465" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A465" s="5" t="s">
         <v>1372</v>
       </c>
@@ -41904,7 +41920,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="466" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A466" s="5" t="s">
         <v>1373</v>
       </c>
@@ -41959,7 +41975,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="467" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A467" s="5" t="s">
         <v>1376</v>
       </c>
@@ -42024,7 +42040,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="468" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A468" s="5" t="s">
         <v>1378</v>
       </c>
@@ -42081,7 +42097,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="469" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A469" s="5" t="s">
         <v>1380</v>
       </c>
@@ -42130,7 +42146,7 @@
       <c r="X469" s="5"/>
       <c r="Y469" s="5"/>
     </row>
-    <row r="470" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A470" s="5" t="s">
         <v>1382</v>
       </c>
@@ -42191,7 +42207,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="471" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A471" s="5" t="s">
         <v>1386</v>
       </c>
@@ -42250,7 +42266,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="472" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A472" s="5" t="s">
         <v>1388</v>
       </c>
@@ -42319,7 +42335,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="473" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A473" s="5" t="s">
         <v>1392</v>
       </c>
@@ -42368,7 +42384,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="474" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A474" s="5" t="s">
         <v>1393</v>
       </c>
@@ -42433,7 +42449,7 @@
         <v>1395</v>
       </c>
     </row>
-    <row r="475" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A475" s="5" t="s">
         <v>1396</v>
       </c>
@@ -42498,7 +42514,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="476" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A476" s="5" t="s">
         <v>1399</v>
       </c>
@@ -42555,7 +42571,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="477" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A477" s="5" t="s">
         <v>1402</v>
       </c>
@@ -42604,7 +42620,7 @@
       <c r="X477" s="5"/>
       <c r="Y477" s="5"/>
     </row>
-    <row r="478" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A478" s="5" t="s">
         <v>1413</v>
       </c>
@@ -42655,7 +42671,7 @@
         <v>907</v>
       </c>
     </row>
-    <row r="479" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A479" s="5" t="s">
         <v>1404</v>
       </c>
@@ -42726,7 +42742,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="480" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A480" s="5" t="s">
         <v>1408</v>
       </c>
@@ -42779,7 +42795,7 @@
       </c>
       <c r="Y480" s="5"/>
     </row>
-    <row r="481" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A481" s="5" t="s">
         <v>1411</v>
       </c>
@@ -42832,7 +42848,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="482" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A482" s="5" t="s">
         <v>1419</v>
       </c>
@@ -42893,7 +42909,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="483" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A483" s="5" t="s">
         <v>1421</v>
       </c>
@@ -42942,7 +42958,7 @@
       <c r="X483" s="5"/>
       <c r="Y483" s="5"/>
     </row>
-    <row r="484" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A484" s="5" t="s">
         <v>1423</v>
       </c>
@@ -42995,7 +43011,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="485" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A485" s="5" t="s">
         <v>1424</v>
       </c>
@@ -43040,7 +43056,7 @@
       <c r="X485" s="5"/>
       <c r="Y485" s="5"/>
     </row>
-    <row r="486" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A486" s="5" t="s">
         <v>1429</v>
       </c>
@@ -43109,7 +43125,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="487" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A487" s="5" t="s">
         <v>1434</v>
       </c>
@@ -43172,7 +43188,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="488" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A488" s="5" t="s">
         <v>1436</v>
       </c>
@@ -43247,7 +43263,7 @@
         <v>1442</v>
       </c>
     </row>
-    <row r="489" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A489" s="5" t="s">
         <v>1443</v>
       </c>
@@ -43306,7 +43322,7 @@
       <c r="X489" s="5"/>
       <c r="Y489" s="5"/>
     </row>
-    <row r="490" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A490" s="5" t="s">
         <v>1445</v>
       </c>
@@ -43361,7 +43377,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="491" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A491" s="5" t="s">
         <v>1447</v>
       </c>
@@ -43425,8 +43441,13 @@
         <v>293</v>
       </c>
       <c r="Y491" s="5"/>
-    </row>
-    <row r="492" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z491" t="inlineStr">
+        <is>
+          <t>The Mall Cluster</t>
+        </is>
+      </c>
+    </row>
+    <row r="492" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A492" s="5" t="s">
         <v>1448</v>
       </c>
@@ -43489,7 +43510,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="493" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A493" s="5" t="s">
         <v>1452</v>
       </c>
@@ -43546,7 +43567,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="494" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A494" s="5" t="s">
         <v>1454</v>
       </c>
@@ -43607,7 +43628,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="495" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A495" s="5" t="s">
         <v>1456</v>
       </c>
@@ -43670,7 +43691,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="496" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A496" s="5" t="s">
         <v>1460</v>
       </c>
@@ -43719,7 +43740,7 @@
       </c>
       <c r="Y496" s="5"/>
     </row>
-    <row r="497" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A497" s="5" t="s">
         <v>1462</v>
       </c>
@@ -43780,7 +43801,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="498" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A498" s="5" t="s">
         <v>1465</v>
       </c>
@@ -43837,7 +43858,7 @@
         <v>1468</v>
       </c>
     </row>
-    <row r="499" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A499" s="5" t="s">
         <v>1469</v>
       </c>
@@ -43890,7 +43911,7 @@
       </c>
       <c r="Y499" s="5"/>
     </row>
-    <row r="500" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A500" s="5" t="s">
         <v>1470</v>
       </c>
@@ -43939,7 +43960,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="501" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A501" s="5" t="s">
         <v>1471</v>
       </c>
@@ -44006,7 +44027,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="502" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A502" s="5" t="s">
         <v>1474</v>
       </c>
@@ -44061,7 +44082,7 @@
       <c r="X502" s="5"/>
       <c r="Y502" s="5"/>
     </row>
-    <row r="503" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A503" s="5" t="s">
         <v>1478</v>
       </c>
@@ -44124,7 +44145,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="504" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A504" s="5" t="s">
         <v>1480</v>
       </c>
@@ -44177,7 +44198,7 @@
       </c>
       <c r="Y504" s="5"/>
     </row>
-    <row r="505" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A505" s="5" t="s">
         <v>1481</v>
       </c>
@@ -44232,7 +44253,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="506" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A506" s="5" t="s">
         <v>1483</v>
       </c>
@@ -44289,7 +44310,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="507" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A507" s="5" t="s">
         <v>1485</v>
       </c>
@@ -44358,7 +44379,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="508" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A508" s="5" t="s">
         <v>1489</v>
       </c>
@@ -44409,7 +44430,7 @@
       </c>
       <c r="Y508" s="5"/>
     </row>
-    <row r="509" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A509" s="5" t="s">
         <v>1491</v>
       </c>
@@ -44460,7 +44481,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="510" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A510" s="5" t="s">
         <v>1492</v>
       </c>
@@ -44521,7 +44542,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="511" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A511" s="5" t="s">
         <v>1495</v>
       </c>
@@ -44572,7 +44593,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="512" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A512" s="5" t="s">
         <v>1496</v>
       </c>
@@ -44627,7 +44648,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="513" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A513" s="5" t="s">
         <v>1498</v>
       </c>
@@ -44676,7 +44697,7 @@
       </c>
       <c r="Y513" s="5"/>
     </row>
-    <row r="514" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A514" s="5" t="s">
         <v>1499</v>
       </c>
@@ -44719,7 +44740,7 @@
       <c r="X514" s="5"/>
       <c r="Y514" s="5"/>
     </row>
-    <row r="515" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A515" s="5" t="s">
         <v>1500</v>
       </c>
@@ -44774,7 +44795,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="516" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A516" s="5" t="s">
         <v>1503</v>
       </c>
@@ -44835,7 +44856,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="517" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A517" s="5" t="s">
         <v>1507</v>
       </c>
@@ -44884,7 +44905,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="518" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A518" s="5" t="s">
         <v>1508</v>
       </c>
@@ -44953,7 +44974,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="519" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A519" s="5" t="s">
         <v>1511</v>
       </c>
@@ -45016,7 +45037,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="520" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A520" s="5" t="s">
         <v>1513</v>
       </c>
@@ -45061,7 +45082,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="521" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A521" s="5" t="s">
         <v>1514</v>
       </c>
@@ -45106,7 +45127,7 @@
       <c r="X521" s="5"/>
       <c r="Y521" s="5"/>
     </row>
-    <row r="522" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A522" s="5" t="s">
         <v>1516</v>
       </c>
@@ -45163,7 +45184,7 @@
         <v>1519</v>
       </c>
     </row>
-    <row r="523" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A523" s="5" t="s">
         <v>1520</v>
       </c>
@@ -45230,7 +45251,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="524" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A524" s="5" t="s">
         <v>1867</v>
       </c>
@@ -45301,7 +45322,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="525" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A525" s="5" t="s">
         <v>1525</v>
       </c>
@@ -45346,7 +45367,7 @@
         <v>1371</v>
       </c>
     </row>
-    <row r="526" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A526" s="5" t="s">
         <v>1526</v>
       </c>
@@ -45399,7 +45420,7 @@
       </c>
       <c r="Y526" s="5"/>
     </row>
-    <row r="527" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A527" s="5" t="s">
         <v>1527</v>
       </c>
@@ -45468,7 +45489,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="528" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A528" s="5" t="s">
         <v>1365</v>
       </c>
@@ -45533,7 +45554,7 @@
         <v>1533</v>
       </c>
     </row>
-    <row r="529" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A529" s="5" t="s">
         <v>1534</v>
       </c>
@@ -45598,7 +45619,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="530" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A530" s="5" t="s">
         <v>1538</v>
       </c>
@@ -45651,7 +45672,7 @@
       </c>
       <c r="Y530" s="5"/>
     </row>
-    <row r="531" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A531" s="5" t="s">
         <v>1539</v>
       </c>
@@ -45700,7 +45721,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="532" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A532" s="5" t="s">
         <v>528</v>
       </c>
@@ -45761,7 +45782,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="533" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A533" s="5" t="s">
         <v>546</v>
       </c>
@@ -45810,7 +45831,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="534" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A534" s="5" t="s">
         <v>551</v>
       </c>
@@ -45857,7 +45878,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="535" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A535" s="5" t="s">
         <v>748</v>
       </c>
@@ -45904,7 +45925,7 @@
       <c r="X535" s="5"/>
       <c r="Y535" s="5"/>
     </row>
-    <row r="536" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A536" s="5" t="s">
         <v>1021</v>
       </c>
@@ -45955,7 +45976,7 @@
       <c r="X536" s="5"/>
       <c r="Y536" s="5"/>
     </row>
-    <row r="537" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A537" s="5" t="s">
         <v>1171</v>
       </c>
@@ -46020,7 +46041,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="538" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A538" s="5" t="s">
         <v>1414</v>
       </c>
@@ -46087,7 +46108,7 @@
         <v>1418</v>
       </c>
     </row>
-    <row r="539" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A539" s="5" t="s">
         <v>1426</v>
       </c>
@@ -46142,7 +46163,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="540" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A540" s="5" t="s">
         <v>1904</v>
       </c>
@@ -46195,7 +46216,7 @@
       <c r="X540" s="5"/>
       <c r="Y540" s="5"/>
     </row>
-    <row r="541" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A541" s="5" t="s">
         <v>1546</v>
       </c>
@@ -46238,7 +46259,7 @@
         <v>1105</v>
       </c>
     </row>
-    <row r="542" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A542" s="5" t="s">
         <v>1540</v>
       </c>
@@ -46287,7 +46308,7 @@
       <c r="X542" s="5"/>
       <c r="Y542" s="5"/>
     </row>
-    <row r="543" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A543" s="5" t="s">
         <v>1542</v>
       </c>
@@ -46336,7 +46357,7 @@
       <c r="X543" s="5"/>
       <c r="Y543" s="5"/>
     </row>
-    <row r="544" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A544" s="5" t="s">
         <v>1544</v>
       </c>
@@ -46385,7 +46406,7 @@
       <c r="X544" s="5"/>
       <c r="Y544" s="5"/>
     </row>
-    <row r="545" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A545" s="5" t="s">
         <v>1547</v>
       </c>
@@ -46438,7 +46459,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="546" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A546" s="5" t="s">
         <v>1548</v>
       </c>
@@ -46493,7 +46514,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="547" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A547" s="5" t="s">
         <v>1549</v>
       </c>
@@ -46546,7 +46567,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="548" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A548" s="5" t="s">
         <v>1551</v>
       </c>
@@ -46603,7 +46624,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="549" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A549" s="5" t="s">
         <v>1554</v>
       </c>
@@ -46666,7 +46687,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="550" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A550" s="5" t="s">
         <v>1557</v>
       </c>
@@ -46711,7 +46732,7 @@
       <c r="X550" s="5"/>
       <c r="Y550" s="5"/>
     </row>
-    <row r="551" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A551" s="5" t="s">
         <v>1559</v>
       </c>
@@ -46768,7 +46789,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="552" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A552" s="5" t="s">
         <v>1561</v>
       </c>
@@ -46837,7 +46858,7 @@
         <v>1564</v>
       </c>
     </row>
-    <row r="553" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A553" s="5" t="s">
         <v>1900</v>
       </c>
@@ -46906,7 +46927,7 @@
         <v>1524</v>
       </c>
     </row>
-    <row r="554" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A554" s="5" t="s">
         <v>1565</v>
       </c>
@@ -46955,7 +46976,7 @@
       </c>
       <c r="Y554" s="5"/>
     </row>
-    <row r="555" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A555" s="5" t="s">
         <v>1566</v>
       </c>
@@ -47024,7 +47045,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="556" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A556" s="5" t="s">
         <v>1569</v>
       </c>
@@ -47093,7 +47114,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="557" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A557" s="5" t="s">
         <v>1573</v>
       </c>
@@ -47148,7 +47169,7 @@
       <c r="X557" s="5"/>
       <c r="Y557" s="5"/>
     </row>
-    <row r="558" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A558" s="5" t="s">
         <v>1576</v>
       </c>
@@ -47197,7 +47218,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="559" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A559" s="5" t="s">
         <v>1578</v>
       </c>
@@ -47246,7 +47267,7 @@
       <c r="X559" s="5"/>
       <c r="Y559" s="5"/>
     </row>
-    <row r="560" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A560" s="5" t="s">
         <v>1580</v>
       </c>
@@ -47299,7 +47320,7 @@
       <c r="X560" s="5"/>
       <c r="Y560" s="5"/>
     </row>
-    <row r="561" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A561" s="5" t="s">
         <v>1582</v>
       </c>
@@ -47352,7 +47373,7 @@
       </c>
       <c r="Y561" s="5"/>
     </row>
-    <row r="562" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A562" s="5" t="s">
         <v>1583</v>
       </c>
@@ -47413,7 +47434,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="563" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A563" s="5" t="s">
         <v>1664</v>
       </c>
@@ -47478,7 +47499,7 @@
         <v>1666</v>
       </c>
     </row>
-    <row r="564" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A564" s="5" t="s">
         <v>1588</v>
       </c>
@@ -47527,7 +47548,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="565" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A565" s="5" t="s">
         <v>1589</v>
       </c>
@@ -47574,7 +47595,7 @@
       <c r="X565" s="5"/>
       <c r="Y565" s="5"/>
     </row>
-    <row r="566" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A566" s="5" t="s">
         <v>1590</v>
       </c>
@@ -47635,7 +47656,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="567" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A567" s="5" t="s">
         <v>1593</v>
       </c>
@@ -47682,7 +47703,7 @@
       <c r="X567" s="5"/>
       <c r="Y567" s="5"/>
     </row>
-    <row r="568" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A568" s="5" t="s">
         <v>1594</v>
       </c>
@@ -47743,7 +47764,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="569" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A569" s="5" t="s">
         <v>1596</v>
       </c>
@@ -47802,7 +47823,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="570" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A570" s="5" t="s">
         <v>1598</v>
       </c>
@@ -47871,7 +47892,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="571" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A571" s="5" t="s">
         <v>1603</v>
       </c>
@@ -47928,7 +47949,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="572" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A572" s="5" t="s">
         <v>1606</v>
       </c>
@@ -47991,7 +48012,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="573" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A573" s="5" t="s">
         <v>1611</v>
       </c>
@@ -48060,7 +48081,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="574" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A574" s="5" t="s">
         <v>1614</v>
       </c>
@@ -48121,7 +48142,7 @@
         <v>1468</v>
       </c>
     </row>
-    <row r="575" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A575" s="5" t="s">
         <v>1617</v>
       </c>
@@ -48176,7 +48197,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="576" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A576" s="5" t="s">
         <v>1619</v>
       </c>
@@ -48241,7 +48262,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="577" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A577" s="5" t="s">
         <v>1621</v>
       </c>
@@ -48302,7 +48323,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="578" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A578" s="5" t="s">
         <v>1622</v>
       </c>
@@ -48357,7 +48378,7 @@
       <c r="X578" s="5"/>
       <c r="Y578" s="5"/>
     </row>
-    <row r="579" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A579" s="5" t="s">
         <v>1626</v>
       </c>
@@ -48428,7 +48449,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="580" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A580" s="5" t="s">
         <v>1631</v>
       </c>
@@ -48477,7 +48498,7 @@
       </c>
       <c r="Y580" s="5"/>
     </row>
-    <row r="581" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A581" s="5" t="s">
         <v>1632</v>
       </c>
@@ -48526,7 +48547,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="582" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A582" s="5" t="s">
         <v>1633</v>
       </c>
@@ -48579,7 +48600,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="583" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A583" s="5" t="s">
         <v>1635</v>
       </c>
@@ -48644,7 +48665,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="584" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A584" s="5" t="s">
         <v>1638</v>
       </c>
@@ -48701,7 +48722,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="585" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A585" s="5" t="s">
         <v>1642</v>
       </c>
@@ -48750,7 +48771,7 @@
       </c>
       <c r="Y585" s="5"/>
     </row>
-    <row r="586" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A586" s="5" t="s">
         <v>1643</v>
       </c>
@@ -48819,7 +48840,7 @@
         <v>1647</v>
       </c>
     </row>
-    <row r="587" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A587" s="5" t="s">
         <v>1648</v>
       </c>
@@ -48868,7 +48889,7 @@
         <v>1371</v>
       </c>
     </row>
-    <row r="588" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A588" s="5" t="s">
         <v>1649</v>
       </c>
@@ -48911,7 +48932,7 @@
       <c r="X588" s="5"/>
       <c r="Y588" s="5"/>
     </row>
-    <row r="589" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A589" s="5" t="s">
         <v>1650</v>
       </c>
@@ -48976,7 +48997,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="590" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A590" s="5" t="s">
         <v>1652</v>
       </c>
@@ -49025,7 +49046,7 @@
       </c>
       <c r="Y590" s="5"/>
     </row>
-    <row r="591" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A591" s="5" t="s">
         <v>1653</v>
       </c>
@@ -49076,7 +49097,7 @@
       </c>
       <c r="Y591" s="5"/>
     </row>
-    <row r="592" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A592" s="5" t="s">
         <v>1415</v>
       </c>
@@ -49137,7 +49158,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="593" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A593" s="5" t="s">
         <v>1656</v>
       </c>
@@ -49200,7 +49221,7 @@
         <v>1658</v>
       </c>
     </row>
-    <row r="594" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A594" s="5" t="s">
         <v>1659</v>
       </c>
@@ -49249,7 +49270,7 @@
       </c>
       <c r="Y594" s="5"/>
     </row>
-    <row r="595" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A595" s="5" t="s">
         <v>43</v>
       </c>
@@ -49292,7 +49313,7 @@
       <c r="X595" s="5"/>
       <c r="Y595" s="5"/>
     </row>
-    <row r="596" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A596" s="5" t="s">
         <v>1660</v>
       </c>
@@ -49349,7 +49370,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="597" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A597" s="5" t="s">
         <v>1662</v>
       </c>
@@ -49404,7 +49425,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="598" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A598" s="5"/>
       <c r="B598" s="5"/>
       <c r="C598" s="5"/>
@@ -49437,7 +49458,7 @@
       <c r="X598" s="5"/>
       <c r="Y598" s="5"/>
     </row>
-    <row r="599" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A599" s="5"/>
       <c r="B599" s="5"/>
       <c r="C599" s="5"/>
@@ -49470,7 +49491,7 @@
       <c r="X599" s="5"/>
       <c r="Y599" s="5"/>
     </row>
-    <row r="600" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A600" s="5"/>
       <c r="B600" s="5"/>
       <c r="C600" s="5"/>
@@ -49503,7 +49524,7 @@
       <c r="X600" s="5"/>
       <c r="Y600" s="5"/>
     </row>
-    <row r="601" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A601" s="5"/>
       <c r="B601" s="5"/>
       <c r="C601" s="5"/>
@@ -49536,7 +49557,7 @@
       <c r="X601" s="5"/>
       <c r="Y601" s="5"/>
     </row>
-    <row r="602" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A602" s="5"/>
       <c r="B602" s="5"/>
       <c r="C602" s="5"/>
@@ -49569,7 +49590,7 @@
       <c r="X602" s="5"/>
       <c r="Y602" s="5"/>
     </row>
-    <row r="603" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A603" s="5"/>
       <c r="B603" s="5"/>
       <c r="C603" s="5"/>
@@ -49602,7 +49623,7 @@
       <c r="X603" s="5"/>
       <c r="Y603" s="5"/>
     </row>
-    <row r="604" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A604" s="5"/>
       <c r="B604" s="5"/>
       <c r="C604" s="5"/>
@@ -49635,7 +49656,7 @@
       <c r="X604" s="5"/>
       <c r="Y604" s="5"/>
     </row>
-    <row r="605" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A605" s="5"/>
       <c r="B605" s="5"/>
       <c r="C605" s="5"/>
@@ -49668,7 +49689,7 @@
       <c r="X605" s="5"/>
       <c r="Y605" s="5"/>
     </row>
-    <row r="606" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A606" s="5"/>
       <c r="B606" s="5"/>
       <c r="C606" s="5"/>
@@ -49701,7 +49722,7 @@
       <c r="X606" s="5"/>
       <c r="Y606" s="5"/>
     </row>
-    <row r="607" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A607" s="5"/>
       <c r="B607" s="5"/>
       <c r="C607" s="5"/>
@@ -49734,7 +49755,7 @@
       <c r="X607" s="5"/>
       <c r="Y607" s="5"/>
     </row>
-    <row r="608" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A608" s="5"/>
       <c r="B608" s="5"/>
       <c r="C608" s="5"/>
@@ -49767,7 +49788,7 @@
       <c r="X608" s="5"/>
       <c r="Y608" s="5"/>
     </row>
-    <row r="609" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A609" s="5"/>
       <c r="B609" s="5"/>
       <c r="C609" s="5"/>
@@ -49800,7 +49821,7 @@
       <c r="X609" s="5"/>
       <c r="Y609" s="5"/>
     </row>
-    <row r="610" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A610" s="5"/>
       <c r="B610" s="5"/>
       <c r="C610" s="5"/>
@@ -49833,7 +49854,7 @@
       <c r="X610" s="5"/>
       <c r="Y610" s="5"/>
     </row>
-    <row r="611" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A611" s="5"/>
       <c r="B611" s="5"/>
       <c r="C611" s="5"/>
@@ -49866,7 +49887,7 @@
       <c r="X611" s="5"/>
       <c r="Y611" s="5"/>
     </row>
-    <row r="612" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A612" s="5"/>
       <c r="B612" s="5"/>
       <c r="C612" s="5"/>
@@ -49899,7 +49920,7 @@
       <c r="X612" s="5"/>
       <c r="Y612" s="5"/>
     </row>
-    <row r="613" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A613" s="5"/>
       <c r="B613" s="5"/>
       <c r="C613" s="5"/>
@@ -49932,7 +49953,7 @@
       <c r="X613" s="5"/>
       <c r="Y613" s="5"/>
     </row>
-    <row r="614" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A614" s="5"/>
       <c r="B614" s="5"/>
       <c r="C614" s="5"/>
@@ -49965,7 +49986,7 @@
       <c r="X614" s="5"/>
       <c r="Y614" s="5"/>
     </row>
-    <row r="615" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A615" s="5"/>
       <c r="B615" s="5"/>
       <c r="C615" s="5"/>
@@ -49998,7 +50019,7 @@
       <c r="X615" s="5"/>
       <c r="Y615" s="5"/>
     </row>
-    <row r="616" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A616" s="5"/>
       <c r="B616" s="5"/>
       <c r="C616" s="5"/>
@@ -50031,7 +50052,7 @@
       <c r="X616" s="5"/>
       <c r="Y616" s="5"/>
     </row>
-    <row r="617" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A617" s="5"/>
       <c r="B617" s="5"/>
       <c r="C617" s="5"/>
@@ -50064,7 +50085,7 @@
       <c r="X617" s="5"/>
       <c r="Y617" s="5"/>
     </row>
-    <row r="618" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A618" s="5"/>
       <c r="B618" s="5"/>
       <c r="C618" s="5"/>
@@ -50097,7 +50118,7 @@
       <c r="X618" s="5"/>
       <c r="Y618" s="5"/>
     </row>
-    <row r="619" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A619" s="5"/>
       <c r="B619" s="5"/>
       <c r="C619" s="5"/>
@@ -50130,7 +50151,7 @@
       <c r="X619" s="5"/>
       <c r="Y619" s="5"/>
     </row>
-    <row r="620" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A620" s="5"/>
       <c r="B620" s="5"/>
       <c r="C620" s="5"/>
@@ -50163,7 +50184,7 @@
       <c r="X620" s="5"/>
       <c r="Y620" s="5"/>
     </row>
-    <row r="621" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A621" s="5"/>
       <c r="B621" s="5"/>
       <c r="C621" s="5"/>
@@ -50196,7 +50217,7 @@
       <c r="X621" s="5"/>
       <c r="Y621" s="5"/>
     </row>
-    <row r="622" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A622" s="5"/>
       <c r="B622" s="5"/>
       <c r="C622" s="5"/>
@@ -50229,7 +50250,7 @@
       <c r="X622" s="5"/>
       <c r="Y622" s="5"/>
     </row>
-    <row r="623" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A623" s="5"/>
       <c r="B623" s="5"/>
       <c r="C623" s="5"/>
@@ -50262,7 +50283,7 @@
       <c r="X623" s="5"/>
       <c r="Y623" s="5"/>
     </row>
-    <row r="624" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A624" s="5"/>
       <c r="B624" s="5"/>
       <c r="C624" s="5"/>
@@ -50295,7 +50316,7 @@
       <c r="X624" s="5"/>
       <c r="Y624" s="5"/>
     </row>
-    <row r="625" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A625" s="5"/>
       <c r="B625" s="5"/>
       <c r="C625" s="5"/>
@@ -50328,7 +50349,7 @@
       <c r="X625" s="5"/>
       <c r="Y625" s="5"/>
     </row>
-    <row r="626" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A626" s="5"/>
       <c r="B626" s="5"/>
       <c r="C626" s="5"/>
@@ -50361,7 +50382,7 @@
       <c r="X626" s="5"/>
       <c r="Y626" s="5"/>
     </row>
-    <row r="627" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A627" s="5"/>
       <c r="B627" s="5"/>
       <c r="C627" s="5"/>
@@ -50394,7 +50415,7 @@
       <c r="X627" s="5"/>
       <c r="Y627" s="5"/>
     </row>
-    <row r="628" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A628" s="5"/>
       <c r="B628" s="5"/>
       <c r="C628" s="5"/>
@@ -50427,7 +50448,7 @@
       <c r="X628" s="5"/>
       <c r="Y628" s="5"/>
     </row>
-    <row r="629" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A629" s="5"/>
       <c r="B629" s="5"/>
       <c r="C629" s="5"/>
@@ -50460,7 +50481,7 @@
       <c r="X629" s="5"/>
       <c r="Y629" s="5"/>
     </row>
-    <row r="630" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A630" s="5"/>
       <c r="B630" s="5"/>
       <c r="C630" s="5"/>
@@ -50493,7 +50514,7 @@
       <c r="X630" s="5"/>
       <c r="Y630" s="5"/>
     </row>
-    <row r="631" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A631" s="5"/>
       <c r="B631" s="5"/>
       <c r="C631" s="5"/>
@@ -50526,7 +50547,7 @@
       <c r="X631" s="5"/>
       <c r="Y631" s="5"/>
     </row>
-    <row r="632" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A632" s="5"/>
       <c r="B632" s="5"/>
       <c r="C632" s="5"/>
@@ -50559,7 +50580,7 @@
       <c r="X632" s="5"/>
       <c r="Y632" s="5"/>
     </row>
-    <row r="633" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A633" s="5"/>
       <c r="B633" s="5"/>
       <c r="C633" s="5"/>
@@ -50592,7 +50613,7 @@
       <c r="X633" s="5"/>
       <c r="Y633" s="5"/>
     </row>
-    <row r="634" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A634" s="5"/>
       <c r="B634" s="5"/>
       <c r="C634" s="5"/>
@@ -50625,7 +50646,7 @@
       <c r="X634" s="5"/>
       <c r="Y634" s="5"/>
     </row>
-    <row r="635" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A635" s="5"/>
       <c r="B635" s="5"/>
       <c r="C635" s="5"/>
@@ -50658,7 +50679,7 @@
       <c r="X635" s="5"/>
       <c r="Y635" s="5"/>
     </row>
-    <row r="636" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A636" s="5"/>
       <c r="B636" s="5"/>
       <c r="C636" s="5"/>
@@ -50691,7 +50712,7 @@
       <c r="X636" s="5"/>
       <c r="Y636" s="5"/>
     </row>
-    <row r="637" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A637" s="5"/>
       <c r="B637" s="5"/>
       <c r="C637" s="5"/>
@@ -50724,7 +50745,7 @@
       <c r="X637" s="5"/>
       <c r="Y637" s="5"/>
     </row>
-    <row r="638" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A638" s="5"/>
       <c r="B638" s="5"/>
       <c r="C638" s="5"/>
@@ -50757,7 +50778,7 @@
       <c r="X638" s="5"/>
       <c r="Y638" s="5"/>
     </row>
-    <row r="639" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A639" s="5"/>
       <c r="B639" s="5"/>
       <c r="C639" s="5"/>
@@ -50790,7 +50811,7 @@
       <c r="X639" s="5"/>
       <c r="Y639" s="5"/>
     </row>
-    <row r="640" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A640" s="5"/>
       <c r="B640" s="5"/>
       <c r="C640" s="5"/>
@@ -50823,7 +50844,7 @@
       <c r="X640" s="5"/>
       <c r="Y640" s="5"/>
     </row>
-    <row r="641" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A641" s="5"/>
       <c r="B641" s="5"/>
       <c r="C641" s="5"/>
@@ -50856,7 +50877,7 @@
       <c r="X641" s="5"/>
       <c r="Y641" s="5"/>
     </row>
-    <row r="642" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A642" s="5"/>
       <c r="B642" s="5"/>
       <c r="C642" s="5"/>
@@ -50889,7 +50910,7 @@
       <c r="X642" s="5"/>
       <c r="Y642" s="5"/>
     </row>
-    <row r="643" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A643" s="5"/>
       <c r="B643" s="5"/>
       <c r="C643" s="5"/>
@@ -50922,7 +50943,7 @@
       <c r="X643" s="5"/>
       <c r="Y643" s="5"/>
     </row>
-    <row r="644" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A644" s="5"/>
       <c r="B644" s="5"/>
       <c r="C644" s="5"/>
@@ -50955,7 +50976,7 @@
       <c r="X644" s="5"/>
       <c r="Y644" s="5"/>
     </row>
-    <row r="645" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A645" s="5"/>
       <c r="B645" s="5"/>
       <c r="C645" s="5"/>
@@ -50988,7 +51009,7 @@
       <c r="X645" s="5"/>
       <c r="Y645" s="5"/>
     </row>
-    <row r="646" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A646" s="5"/>
       <c r="B646" s="5"/>
       <c r="C646" s="5"/>
@@ -51021,7 +51042,7 @@
       <c r="X646" s="5"/>
       <c r="Y646" s="5"/>
     </row>
-    <row r="647" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A647" s="5"/>
       <c r="B647" s="5"/>
       <c r="C647" s="5"/>
@@ -51054,7 +51075,7 @@
       <c r="X647" s="5"/>
       <c r="Y647" s="5"/>
     </row>
-    <row r="648" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A648" s="5"/>
       <c r="B648" s="5"/>
       <c r="C648" s="5"/>
@@ -51087,7 +51108,7 @@
       <c r="X648" s="5"/>
       <c r="Y648" s="5"/>
     </row>
-    <row r="649" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A649" s="5"/>
       <c r="B649" s="5"/>
       <c r="C649" s="5"/>
@@ -51120,7 +51141,7 @@
       <c r="X649" s="5"/>
       <c r="Y649" s="5"/>
     </row>
-    <row r="650" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A650" s="5"/>
       <c r="B650" s="5"/>
       <c r="C650" s="5"/>
@@ -51153,7 +51174,7 @@
       <c r="X650" s="5"/>
       <c r="Y650" s="5"/>
     </row>
-    <row r="651" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A651" s="5"/>
       <c r="B651" s="5"/>
       <c r="C651" s="5"/>
@@ -51186,7 +51207,7 @@
       <c r="X651" s="5"/>
       <c r="Y651" s="5"/>
     </row>
-    <row r="652" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A652" s="5"/>
       <c r="B652" s="5"/>
       <c r="C652" s="5"/>
@@ -51219,7 +51240,7 @@
       <c r="X652" s="5"/>
       <c r="Y652" s="5"/>
     </row>
-    <row r="653" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A653" s="5"/>
       <c r="B653" s="5"/>
       <c r="C653" s="5"/>
@@ -51252,7 +51273,7 @@
       <c r="X653" s="5"/>
       <c r="Y653" s="5"/>
     </row>
-    <row r="654" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A654" s="5"/>
       <c r="B654" s="5"/>
       <c r="C654" s="5"/>
@@ -51285,7 +51306,7 @@
       <c r="X654" s="5"/>
       <c r="Y654" s="5"/>
     </row>
-    <row r="655" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A655" s="5"/>
       <c r="B655" s="5"/>
       <c r="C655" s="5"/>
@@ -51318,7 +51339,7 @@
       <c r="X655" s="5"/>
       <c r="Y655" s="5"/>
     </row>
-    <row r="656" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A656" s="5"/>
       <c r="B656" s="5"/>
       <c r="C656" s="5"/>
@@ -51351,7 +51372,7 @@
       <c r="X656" s="5"/>
       <c r="Y656" s="5"/>
     </row>
-    <row r="657" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A657" s="5"/>
       <c r="B657" s="5"/>
       <c r="C657" s="5"/>
@@ -51384,7 +51405,7 @@
       <c r="X657" s="5"/>
       <c r="Y657" s="5"/>
     </row>
-    <row r="658" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A658" s="5"/>
       <c r="B658" s="5"/>
       <c r="C658" s="5"/>
@@ -51417,7 +51438,7 @@
       <c r="X658" s="5"/>
       <c r="Y658" s="5"/>
     </row>
-    <row r="659" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A659" s="5"/>
       <c r="B659" s="5"/>
       <c r="C659" s="5"/>
@@ -51450,7 +51471,7 @@
       <c r="X659" s="5"/>
       <c r="Y659" s="5"/>
     </row>
-    <row r="660" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A660" s="5"/>
       <c r="B660" s="5"/>
       <c r="C660" s="5"/>
@@ -51483,7 +51504,7 @@
       <c r="X660" s="5"/>
       <c r="Y660" s="5"/>
     </row>
-    <row r="661" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A661" s="5"/>
       <c r="B661" s="5"/>
       <c r="C661" s="5"/>
@@ -51516,7 +51537,7 @@
       <c r="X661" s="5"/>
       <c r="Y661" s="5"/>
     </row>
-    <row r="662" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A662" s="5"/>
       <c r="B662" s="5"/>
       <c r="C662" s="5"/>
@@ -51549,7 +51570,7 @@
       <c r="X662" s="5"/>
       <c r="Y662" s="5"/>
     </row>
-    <row r="663" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A663" s="5"/>
       <c r="B663" s="5"/>
       <c r="C663" s="5"/>
@@ -51582,7 +51603,7 @@
       <c r="X663" s="5"/>
       <c r="Y663" s="5"/>
     </row>
-    <row r="664" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A664" s="5"/>
       <c r="B664" s="5"/>
       <c r="C664" s="5"/>
@@ -51615,7 +51636,7 @@
       <c r="X664" s="5"/>
       <c r="Y664" s="5"/>
     </row>
-    <row r="665" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A665" s="5"/>
       <c r="B665" s="5"/>
       <c r="C665" s="5"/>
@@ -51648,7 +51669,7 @@
       <c r="X665" s="5"/>
       <c r="Y665" s="5"/>
     </row>
-    <row r="666" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A666" s="5"/>
       <c r="B666" s="5"/>
       <c r="C666" s="5"/>
@@ -51681,7 +51702,7 @@
       <c r="X666" s="5"/>
       <c r="Y666" s="5"/>
     </row>
-    <row r="667" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A667" s="5"/>
       <c r="B667" s="5"/>
       <c r="C667" s="5"/>
@@ -51714,7 +51735,7 @@
       <c r="X667" s="5"/>
       <c r="Y667" s="5"/>
     </row>
-    <row r="668" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A668" s="5"/>
       <c r="B668" s="5"/>
       <c r="C668" s="5"/>
@@ -51747,7 +51768,7 @@
       <c r="X668" s="5"/>
       <c r="Y668" s="5"/>
     </row>
-    <row r="669" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A669" s="5"/>
       <c r="B669" s="5"/>
       <c r="C669" s="5"/>
@@ -51780,7 +51801,7 @@
       <c r="X669" s="5"/>
       <c r="Y669" s="5"/>
     </row>
-    <row r="670" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A670" s="5"/>
       <c r="B670" s="5"/>
       <c r="C670" s="5"/>
@@ -51813,7 +51834,7 @@
       <c r="X670" s="5"/>
       <c r="Y670" s="5"/>
     </row>
-    <row r="671" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A671" s="5"/>
       <c r="B671" s="5"/>
       <c r="C671" s="5"/>
@@ -51846,7 +51867,7 @@
       <c r="X671" s="5"/>
       <c r="Y671" s="5"/>
     </row>
-    <row r="672" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A672" s="5"/>
       <c r="B672" s="5"/>
       <c r="C672" s="5"/>
@@ -51879,7 +51900,7 @@
       <c r="X672" s="5"/>
       <c r="Y672" s="5"/>
     </row>
-    <row r="673" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A673" s="5"/>
       <c r="B673" s="5"/>
       <c r="C673" s="5"/>
@@ -51912,7 +51933,7 @@
       <c r="X673" s="5"/>
       <c r="Y673" s="5"/>
     </row>
-    <row r="674" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A674" s="5"/>
       <c r="B674" s="5"/>
       <c r="C674" s="5"/>
@@ -51945,7 +51966,7 @@
       <c r="X674" s="5"/>
       <c r="Y674" s="5"/>
     </row>
-    <row r="675" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A675" s="5"/>
       <c r="B675" s="5"/>
       <c r="C675" s="5"/>
@@ -51978,7 +51999,7 @@
       <c r="X675" s="5"/>
       <c r="Y675" s="5"/>
     </row>
-    <row r="676" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A676" s="5"/>
       <c r="B676" s="5"/>
       <c r="C676" s="5"/>
@@ -52011,7 +52032,7 @@
       <c r="X676" s="5"/>
       <c r="Y676" s="5"/>
     </row>
-    <row r="677" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A677" s="5"/>
       <c r="B677" s="5"/>
       <c r="C677" s="5"/>
@@ -52044,7 +52065,7 @@
       <c r="X677" s="5"/>
       <c r="Y677" s="5"/>
     </row>
-    <row r="678" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A678" s="5"/>
       <c r="B678" s="5"/>
       <c r="C678" s="5"/>
@@ -52077,7 +52098,7 @@
       <c r="X678" s="5"/>
       <c r="Y678" s="5"/>
     </row>
-    <row r="679" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A679" s="5"/>
       <c r="B679" s="5"/>
       <c r="C679" s="5"/>
@@ -52110,7 +52131,7 @@
       <c r="X679" s="5"/>
       <c r="Y679" s="5"/>
     </row>
-    <row r="680" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A680" s="5"/>
       <c r="B680" s="5"/>
       <c r="C680" s="5"/>
@@ -52143,7 +52164,7 @@
       <c r="X680" s="5"/>
       <c r="Y680" s="5"/>
     </row>
-    <row r="681" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A681" s="5"/>
       <c r="B681" s="5"/>
       <c r="C681" s="5"/>
@@ -52176,7 +52197,7 @@
       <c r="X681" s="5"/>
       <c r="Y681" s="5"/>
     </row>
-    <row r="682" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A682" s="5"/>
       <c r="B682" s="5"/>
       <c r="C682" s="5"/>
@@ -52209,7 +52230,7 @@
       <c r="X682" s="5"/>
       <c r="Y682" s="5"/>
     </row>
-    <row r="683" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A683" s="5"/>
       <c r="B683" s="5"/>
       <c r="C683" s="5"/>
@@ -52242,7 +52263,7 @@
       <c r="X683" s="5"/>
       <c r="Y683" s="5"/>
     </row>
-    <row r="684" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A684" s="5"/>
       <c r="B684" s="5"/>
       <c r="C684" s="5"/>
@@ -52275,7 +52296,7 @@
       <c r="X684" s="5"/>
       <c r="Y684" s="5"/>
     </row>
-    <row r="685" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A685" s="5"/>
       <c r="B685" s="5"/>
       <c r="C685" s="5"/>
@@ -52308,7 +52329,7 @@
       <c r="X685" s="5"/>
       <c r="Y685" s="5"/>
     </row>
-    <row r="686" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A686" s="5"/>
       <c r="B686" s="5"/>
       <c r="C686" s="5"/>
@@ -52341,7 +52362,7 @@
       <c r="X686" s="5"/>
       <c r="Y686" s="5"/>
     </row>
-    <row r="687" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A687" s="5"/>
       <c r="B687" s="5"/>
       <c r="C687" s="5"/>
@@ -52374,7 +52395,7 @@
       <c r="X687" s="5"/>
       <c r="Y687" s="5"/>
     </row>
-    <row r="688" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A688" s="5"/>
       <c r="B688" s="5"/>
       <c r="C688" s="5"/>
@@ -52407,7 +52428,7 @@
       <c r="X688" s="5"/>
       <c r="Y688" s="5"/>
     </row>
-    <row r="689" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A689" s="5"/>
       <c r="B689" s="5"/>
       <c r="C689" s="5"/>
@@ -52440,7 +52461,7 @@
       <c r="X689" s="5"/>
       <c r="Y689" s="5"/>
     </row>
-    <row r="690" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A690" s="5"/>
       <c r="B690" s="5"/>
       <c r="C690" s="5"/>
@@ -52473,7 +52494,7 @@
       <c r="X690" s="5"/>
       <c r="Y690" s="5"/>
     </row>
-    <row r="691" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A691" s="5"/>
       <c r="B691" s="5"/>
       <c r="C691" s="5"/>
@@ -52506,7 +52527,7 @@
       <c r="X691" s="5"/>
       <c r="Y691" s="5"/>
     </row>
-    <row r="692" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A692" s="5"/>
       <c r="B692" s="5"/>
       <c r="C692" s="5"/>
@@ -52539,7 +52560,7 @@
       <c r="X692" s="5"/>
       <c r="Y692" s="5"/>
     </row>
-    <row r="693" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A693" s="5"/>
       <c r="B693" s="5"/>
       <c r="C693" s="5"/>
@@ -52572,7 +52593,7 @@
       <c r="X693" s="5"/>
       <c r="Y693" s="5"/>
     </row>
-    <row r="694" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A694" s="5"/>
       <c r="B694" s="5"/>
       <c r="C694" s="5"/>
@@ -52605,7 +52626,7 @@
       <c r="X694" s="5"/>
       <c r="Y694" s="5"/>
     </row>
-    <row r="695" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A695" s="5"/>
       <c r="B695" s="5"/>
       <c r="C695" s="5"/>
@@ -52638,7 +52659,7 @@
       <c r="X695" s="5"/>
       <c r="Y695" s="5"/>
     </row>
-    <row r="696" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A696" s="5"/>
       <c r="B696" s="5"/>
       <c r="C696" s="5"/>
@@ -52671,7 +52692,7 @@
       <c r="X696" s="5"/>
       <c r="Y696" s="5"/>
     </row>
-    <row r="697" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A697" s="5"/>
       <c r="B697" s="5"/>
       <c r="C697" s="5"/>
@@ -52704,7 +52725,7 @@
       <c r="X697" s="5"/>
       <c r="Y697" s="5"/>
     </row>
-    <row r="698" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A698" s="5"/>
       <c r="B698" s="5"/>
       <c r="C698" s="5"/>
@@ -52737,7 +52758,7 @@
       <c r="X698" s="5"/>
       <c r="Y698" s="5"/>
     </row>
-    <row r="699" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A699" s="5"/>
       <c r="B699" s="5"/>
       <c r="C699" s="5"/>
@@ -52770,7 +52791,7 @@
       <c r="X699" s="5"/>
       <c r="Y699" s="5"/>
     </row>
-    <row r="700" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A700" s="5"/>
       <c r="B700" s="5"/>
       <c r="C700" s="5"/>
@@ -52803,7 +52824,7 @@
       <c r="X700" s="5"/>
       <c r="Y700" s="5"/>
     </row>
-    <row r="701" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A701" s="5"/>
       <c r="B701" s="5"/>
       <c r="C701" s="5"/>
@@ -52836,7 +52857,7 @@
       <c r="X701" s="5"/>
       <c r="Y701" s="5"/>
     </row>
-    <row r="702" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A702" s="5"/>
       <c r="B702" s="5"/>
       <c r="C702" s="5"/>
@@ -52869,7 +52890,7 @@
       <c r="X702" s="5"/>
       <c r="Y702" s="5"/>
     </row>
-    <row r="703" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="703" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A703" s="5"/>
       <c r="B703" s="5"/>
       <c r="C703" s="5"/>
@@ -52902,7 +52923,7 @@
       <c r="X703" s="5"/>
       <c r="Y703" s="5"/>
     </row>
-    <row r="704" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="704" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A704" s="5"/>
       <c r="B704" s="5"/>
       <c r="C704" s="5"/>
@@ -52935,7 +52956,7 @@
       <c r="X704" s="5"/>
       <c r="Y704" s="5"/>
     </row>
-    <row r="705" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A705" s="5"/>
       <c r="B705" s="5"/>
       <c r="C705" s="5"/>
@@ -52968,7 +52989,7 @@
       <c r="X705" s="5"/>
       <c r="Y705" s="5"/>
     </row>
-    <row r="706" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A706" s="5"/>
       <c r="B706" s="5"/>
       <c r="C706" s="5"/>
@@ -53001,7 +53022,7 @@
       <c r="X706" s="5"/>
       <c r="Y706" s="5"/>
     </row>
-    <row r="707" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A707" s="5"/>
       <c r="B707" s="5"/>
       <c r="C707" s="5"/>
@@ -53035,7 +53056,7 @@
       <c r="Y707" s="5"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Y707" xr:uid="{00000000-0009-0000-0000-000001000000}">
+  <autoFilter ref="A1:Z707" xr:uid="{00000000-0009-0000-0000-000001000000}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Y707">
       <sortCondition ref="A1:A707"/>
     </sortState>

--- a/data/parahumandle_design.xlsx
+++ b/data/parahumandle_design.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Research\Worm Wordle clone\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03749663-F347-48FA-BD38-598517332492}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2253BCF-D330-44A5-B603-A5723D9972E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5910" yWindow="5340" windowWidth="28800" windowHeight="15345" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10532" uniqueCount="1970">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10539" uniqueCount="1972">
   <si>
     <t>Parahumandle – design workbook</t>
   </si>
@@ -5962,6 +5962,12 @@
   </si>
   <si>
     <t>Increased flexibility, strength, reflexes, durability, etc. Can teleport to anyone she's harmed and has the ability to prevent inflicted wounds from healing.</t>
+  </si>
+  <si>
+    <t>Power granter who could turn a person into a specialist by granting them extraordinary and inhuman levels of skill in an unconventional thing/tool/weapon, in exchange for their sanity and free will.</t>
+  </si>
+  <si>
+    <t>Case 70, can exist simultaneously and get past bars by touch teleportation.</t>
   </si>
 </sst>
 </file>
@@ -17736,7 +17742,9 @@
       <c r="F39" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="G39" s="5"/>
+      <c r="G39" s="5" t="s">
+        <v>1845</v>
+      </c>
       <c r="H39" s="5" t="s">
         <v>90</v>
       </c>
@@ -17751,14 +17759,16 @@
       </c>
       <c r="L39" s="6">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M39" s="6" t="str">
         <f t="shared" si="1"/>
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="N39" s="5"/>
-      <c r="O39" s="5"/>
+      <c r="O39" s="5" t="s">
+        <v>1970</v>
+      </c>
       <c r="P39" s="5" t="s">
         <v>105</v>
       </c>
@@ -47542,30 +47552,40 @@
       <c r="C532" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="D532" s="5"/>
-      <c r="E532" s="5"/>
-      <c r="F532" s="5"/>
+      <c r="D532" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="E532" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F532" s="5" t="s">
+        <v>107</v>
+      </c>
       <c r="G532" s="5" t="s">
         <v>57</v>
       </c>
       <c r="H532" s="5" t="s">
         <v>1406</v>
       </c>
-      <c r="I532" s="5"/>
+      <c r="I532" s="5" t="s">
+        <v>71</v>
+      </c>
       <c r="J532" s="5"/>
       <c r="K532" s="18" t="s">
         <v>1931</v>
       </c>
       <c r="L532" s="6">
         <f t="shared" ref="L532:L595" si="20">IF(A532="","",COUNTA(D532:F532)+COUNTA(G532:G532)+COUNTA(H532:H532)+COUNTA(I532:I532))</f>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M532" s="6" t="str">
         <f t="shared" si="17"/>
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="N532" s="5"/>
-      <c r="O532" s="5"/>
+      <c r="O532" s="5" t="s">
+        <v>1971</v>
+      </c>
       <c r="P532" s="5" t="s">
         <v>128</v>
       </c>
@@ -55773,11 +55793,11 @@
       </c>
       <c r="E2" s="8">
         <f>COUNTA(Roster!D2:D715)</f>
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F2" s="9">
         <f>IF(COUNTA(Roster!A2:A715)=0,0,E2/COUNTA(Roster!A2:A715))</f>
-        <v>0.58940397350993379</v>
+        <v>0.59105960264900659</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -55795,11 +55815,11 @@
       </c>
       <c r="E3" s="8">
         <f>COUNTA(Roster!E2:E715)</f>
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F3" s="9">
         <f>IF(COUNTA(Roster!A2:A715)=0,0,E3/COUNTA(Roster!A2:A715))</f>
-        <v>0.51986754966887416</v>
+        <v>0.52152317880794707</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -55817,11 +55837,11 @@
       </c>
       <c r="E4" s="8">
         <f>COUNTA(Roster!F2:F715)</f>
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F4" s="9">
         <f>IF(COUNTA(Roster!A2:A715)=0,0,E4/COUNTA(Roster!A2:A715))</f>
-        <v>0.50331125827814571</v>
+        <v>0.50496688741721851</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -55839,11 +55859,11 @@
       </c>
       <c r="E5" s="8">
         <f>COUNTA(Roster!G2:G715)</f>
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F5" s="9">
         <f>IF(COUNTA(Roster!A2:A715)=0,0,E5/COUNTA(Roster!A2:A715))</f>
-        <v>0.6258278145695364</v>
+        <v>0.62748344370860931</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -55883,11 +55903,11 @@
       </c>
       <c r="E7" s="8">
         <f>COUNTA(Roster!I2:I715)</f>
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="F7" s="9">
         <f>IF(COUNTA(Roster!A2:A715)=0,0,E7/COUNTA(Roster!A2:A715))</f>
-        <v>0.58443708609271527</v>
+        <v>0.58609271523178808</v>
       </c>
     </row>
   </sheetData>
@@ -55930,11 +55950,11 @@
       </c>
       <c r="C2" s="6">
         <f>COUNTIF(Roster!$I$2:$I$715,A2)</f>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D2" s="10">
         <f t="shared" ref="D2:D13" si="0">IF(SUM($C$2:$C$13)=0,0,C2/SUM($C$2:$C$13))</f>
-        <v>7.6487252124645896E-2</v>
+        <v>7.909604519774012E-2</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -55950,7 +55970,7 @@
       </c>
       <c r="D3" s="10">
         <f t="shared" si="0"/>
-        <v>0.1359773371104816</v>
+        <v>0.13559322033898305</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -55966,7 +55986,7 @@
       </c>
       <c r="D4" s="10">
         <f t="shared" si="0"/>
-        <v>9.0651558073654395E-2</v>
+        <v>9.03954802259887E-2</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -55982,7 +56002,7 @@
       </c>
       <c r="D5" s="10">
         <f t="shared" si="0"/>
-        <v>5.6657223796033995E-2</v>
+        <v>5.6497175141242938E-2</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -55998,7 +56018,7 @@
       </c>
       <c r="D6" s="10">
         <f t="shared" si="0"/>
-        <v>0.11898016997167139</v>
+        <v>0.11864406779661017</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -56014,7 +56034,7 @@
       </c>
       <c r="D7" s="10">
         <f t="shared" si="0"/>
-        <v>0.13031161473087818</v>
+        <v>0.12994350282485875</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -56030,7 +56050,7 @@
       </c>
       <c r="D8" s="10">
         <f t="shared" si="0"/>
-        <v>0.11048158640226628</v>
+        <v>0.11016949152542373</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -56046,7 +56066,7 @@
       </c>
       <c r="D9" s="10">
         <f t="shared" si="0"/>
-        <v>0.10764872521246459</v>
+        <v>0.10734463276836158</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -56062,7 +56082,7 @@
       </c>
       <c r="D10" s="10">
         <f t="shared" si="0"/>
-        <v>6.5155807365439092E-2</v>
+        <v>6.4971751412429377E-2</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -56078,7 +56098,7 @@
       </c>
       <c r="D11" s="10">
         <f t="shared" si="0"/>
-        <v>3.39943342776204E-2</v>
+        <v>3.3898305084745763E-2</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -56094,7 +56114,7 @@
       </c>
       <c r="D12" s="10">
         <f t="shared" si="0"/>
-        <v>3.9660056657223795E-2</v>
+        <v>3.954802259887006E-2</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -56110,7 +56130,7 @@
       </c>
       <c r="D13" s="10">
         <f t="shared" si="0"/>
-        <v>3.39943342776204E-2</v>
+        <v>3.3898305084745763E-2</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -56119,7 +56139,7 @@
       </c>
       <c r="C14" s="11">
         <f>SUM(C2:C13)</f>
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -56258,7 +56278,7 @@
       </c>
       <c r="B11" s="8">
         <f>COUNTIF(Roster!M2:M715,"Yes")</f>
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C11" s="8" t="s">
         <v>1720</v>
@@ -56270,7 +56290,7 @@
       </c>
       <c r="B12" s="9">
         <f>IF(B5=0,0,B11/B5)</f>
-        <v>1.5133333333333334</v>
+        <v>1.5266666666666666</v>
       </c>
       <c r="C12" s="8" t="s">
         <v>1720</v>
@@ -56282,7 +56302,7 @@
       </c>
       <c r="B13" s="13">
         <f>IFERROR(AVERAGE(Roster!L2:L715),0)</f>
-        <v>3.6175496688741724</v>
+        <v>3.6258278145695364</v>
       </c>
       <c r="C13" s="8" t="s">
         <v>1720</v>

--- a/data/parahumandle_design.xlsx
+++ b/data/parahumandle_design.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Research\Worm Wordle clone\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2253BCF-D330-44A5-B603-A5723D9972E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8386FCF8-958A-4767-9B7E-50149F7CB0EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5910" yWindow="5340" windowWidth="28800" windowHeight="15345" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10539" uniqueCount="1972">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10547" uniqueCount="1973">
   <si>
     <t>Parahumandle – design workbook</t>
   </si>
@@ -5968,6 +5968,9 @@
   </si>
   <si>
     <t>Case 70, can exist simultaneously and get past bars by touch teleportation.</t>
+  </si>
+  <si>
+    <t>Controlled spatial distortion by drawing out circles with his polearm and then stepping on the affected space to propel himself forward.</t>
   </si>
 </sst>
 </file>
@@ -44698,30 +44701,40 @@
       <c r="C485" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="D485" s="5"/>
-      <c r="E485" s="5"/>
-      <c r="F485" s="5"/>
+      <c r="D485" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="E485" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F485" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="G485" s="5" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="H485" s="5" t="s">
         <v>1406</v>
       </c>
-      <c r="I485" s="5"/>
+      <c r="I485" s="5" t="s">
+        <v>71</v>
+      </c>
       <c r="J485" s="5"/>
       <c r="K485" s="18" t="s">
         <v>1931</v>
       </c>
       <c r="L485" s="6">
         <f t="shared" si="16"/>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M485" s="6" t="str">
         <f t="shared" si="15"/>
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="N485" s="5"/>
-      <c r="O485" s="5"/>
+      <c r="O485" s="5" t="s">
+        <v>1972</v>
+      </c>
       <c r="P485" s="5" t="s">
         <v>128</v>
       </c>
@@ -44752,14 +44765,20 @@
       </c>
       <c r="B486" s="5"/>
       <c r="C486" s="5" t="s">
-        <v>70</v>
+        <v>43</v>
       </c>
       <c r="D486" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="E486" s="5"/>
-      <c r="F486" s="5"/>
-      <c r="G486" s="5"/>
+      <c r="E486" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F486" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G486" s="5" t="s">
+        <v>47</v>
+      </c>
       <c r="H486" s="5" t="s">
         <v>77</v>
       </c>
@@ -44772,11 +44791,11 @@
       </c>
       <c r="L486" s="6">
         <f t="shared" si="16"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M486" s="6" t="str">
         <f t="shared" si="15"/>
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="N486" s="5"/>
       <c r="O486" s="5" t="s">
@@ -55793,11 +55812,11 @@
       </c>
       <c r="E2" s="8">
         <f>COUNTA(Roster!D2:D715)</f>
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F2" s="9">
         <f>IF(COUNTA(Roster!A2:A715)=0,0,E2/COUNTA(Roster!A2:A715))</f>
-        <v>0.59105960264900659</v>
+        <v>0.5927152317880795</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -55815,11 +55834,11 @@
       </c>
       <c r="E3" s="8">
         <f>COUNTA(Roster!E2:E715)</f>
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="F3" s="9">
         <f>IF(COUNTA(Roster!A2:A715)=0,0,E3/COUNTA(Roster!A2:A715))</f>
-        <v>0.52152317880794707</v>
+        <v>0.52483443708609268</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -55837,11 +55856,11 @@
       </c>
       <c r="E4" s="8">
         <f>COUNTA(Roster!F2:F715)</f>
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="F4" s="9">
         <f>IF(COUNTA(Roster!A2:A715)=0,0,E4/COUNTA(Roster!A2:A715))</f>
-        <v>0.50496688741721851</v>
+        <v>0.50827814569536423</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -55859,11 +55878,11 @@
       </c>
       <c r="E5" s="8">
         <f>COUNTA(Roster!G2:G715)</f>
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="F5" s="9">
         <f>IF(COUNTA(Roster!A2:A715)=0,0,E5/COUNTA(Roster!A2:A715))</f>
-        <v>0.62748344370860931</v>
+        <v>0.62913907284768211</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -55903,11 +55922,11 @@
       </c>
       <c r="E7" s="8">
         <f>COUNTA(Roster!I2:I715)</f>
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F7" s="9">
         <f>IF(COUNTA(Roster!A2:A715)=0,0,E7/COUNTA(Roster!A2:A715))</f>
-        <v>0.58609271523178808</v>
+        <v>0.58774834437086088</v>
       </c>
     </row>
   </sheetData>
@@ -55950,11 +55969,11 @@
       </c>
       <c r="C2" s="6">
         <f>COUNTIF(Roster!$I$2:$I$715,A2)</f>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D2" s="10">
         <f t="shared" ref="D2:D13" si="0">IF(SUM($C$2:$C$13)=0,0,C2/SUM($C$2:$C$13))</f>
-        <v>7.909604519774012E-2</v>
+        <v>8.1690140845070425E-2</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -55970,7 +55989,7 @@
       </c>
       <c r="D3" s="10">
         <f t="shared" si="0"/>
-        <v>0.13559322033898305</v>
+        <v>0.13521126760563379</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -55986,7 +56005,7 @@
       </c>
       <c r="D4" s="10">
         <f t="shared" si="0"/>
-        <v>9.03954802259887E-2</v>
+        <v>9.014084507042254E-2</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -56002,7 +56021,7 @@
       </c>
       <c r="D5" s="10">
         <f t="shared" si="0"/>
-        <v>5.6497175141242938E-2</v>
+        <v>5.6338028169014086E-2</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -56018,7 +56037,7 @@
       </c>
       <c r="D6" s="10">
         <f t="shared" si="0"/>
-        <v>0.11864406779661017</v>
+        <v>0.11830985915492957</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -56034,7 +56053,7 @@
       </c>
       <c r="D7" s="10">
         <f t="shared" si="0"/>
-        <v>0.12994350282485875</v>
+        <v>0.12957746478873239</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -56050,7 +56069,7 @@
       </c>
       <c r="D8" s="10">
         <f t="shared" si="0"/>
-        <v>0.11016949152542373</v>
+        <v>0.10985915492957747</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -56066,7 +56085,7 @@
       </c>
       <c r="D9" s="10">
         <f t="shared" si="0"/>
-        <v>0.10734463276836158</v>
+        <v>0.10704225352112676</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -56082,7 +56101,7 @@
       </c>
       <c r="D10" s="10">
         <f t="shared" si="0"/>
-        <v>6.4971751412429377E-2</v>
+        <v>6.4788732394366194E-2</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -56098,7 +56117,7 @@
       </c>
       <c r="D11" s="10">
         <f t="shared" si="0"/>
-        <v>3.3898305084745763E-2</v>
+        <v>3.3802816901408447E-2</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -56114,7 +56133,7 @@
       </c>
       <c r="D12" s="10">
         <f t="shared" si="0"/>
-        <v>3.954802259887006E-2</v>
+        <v>3.9436619718309862E-2</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -56130,7 +56149,7 @@
       </c>
       <c r="D13" s="10">
         <f t="shared" si="0"/>
-        <v>3.3898305084745763E-2</v>
+        <v>3.3802816901408447E-2</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -56139,7 +56158,7 @@
       </c>
       <c r="C14" s="11">
         <f>SUM(C2:C13)</f>
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -56278,7 +56297,7 @@
       </c>
       <c r="B11" s="8">
         <f>COUNTIF(Roster!M2:M715,"Yes")</f>
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C11" s="8" t="s">
         <v>1720</v>
@@ -56290,7 +56309,7 @@
       </c>
       <c r="B12" s="9">
         <f>IF(B5=0,0,B11/B5)</f>
-        <v>1.5266666666666666</v>
+        <v>1.54</v>
       </c>
       <c r="C12" s="8" t="s">
         <v>1720</v>
@@ -56302,7 +56321,7 @@
       </c>
       <c r="B13" s="13">
         <f>IFERROR(AVERAGE(Roster!L2:L715),0)</f>
-        <v>3.6258278145695364</v>
+        <v>3.6374172185430464</v>
       </c>
       <c r="C13" s="8" t="s">
         <v>1720</v>

--- a/data/parahumandle_design.xlsx
+++ b/data/parahumandle_design.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Research\Worm Wordle clone\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8386FCF8-958A-4767-9B7E-50149F7CB0EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E12D1951-8FB4-44CF-B8C3-3063B54AA0E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5910" yWindow="5340" windowWidth="28800" windowHeight="15345" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -5616,9 +5616,6 @@
     <t>Non-cape</t>
   </si>
   <si>
-    <t>Shaker, Master</t>
-  </si>
-  <si>
     <t>Unicorn IV</t>
   </si>
   <si>
@@ -5971,6 +5968,9 @@
   </si>
   <si>
     <t>Controlled spatial distortion by drawing out circles with his polearm and then stepping on the affected space to propel himself forward.</t>
+  </si>
+  <si>
+    <t>The Major Malfunctions</t>
   </si>
 </sst>
 </file>
@@ -15293,7 +15293,7 @@
         <v>26</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>1930</v>
+        <v>1929</v>
       </c>
       <c r="L1" s="4" t="s">
         <v>32</v>
@@ -15369,7 +15369,7 @@
       </c>
       <c r="J2" s="5"/>
       <c r="K2" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L2" s="6">
         <f t="shared" ref="L2:L17" si="0">IF(A2="","",COUNTA(D2:F2)+COUNTA(G2:G2)+COUNTA(H2:H2)+COUNTA(I2:I2))</f>
@@ -15439,7 +15439,7 @@
         <v>60</v>
       </c>
       <c r="K3" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L3" s="6">
         <f t="shared" si="0"/>
@@ -15495,7 +15495,7 @@
       <c r="I4" s="5"/>
       <c r="J4" s="5"/>
       <c r="K4" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L4" s="6">
         <f t="shared" si="0"/>
@@ -15559,7 +15559,7 @@
         <v>72</v>
       </c>
       <c r="K5" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L5" s="6">
         <f t="shared" si="0"/>
@@ -15621,7 +15621,7 @@
         <v>78</v>
       </c>
       <c r="K6" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L6" s="6">
         <f t="shared" si="0"/>
@@ -15691,7 +15691,7 @@
         <v>71</v>
       </c>
       <c r="K7" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L7" s="6">
         <f t="shared" si="0"/>
@@ -15763,7 +15763,7 @@
       </c>
       <c r="J8" s="5"/>
       <c r="K8" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L8" s="6">
         <f t="shared" si="0"/>
@@ -15829,7 +15829,7 @@
       </c>
       <c r="J9" s="5"/>
       <c r="K9" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L9" s="6">
         <f t="shared" si="0"/>
@@ -15901,7 +15901,7 @@
       </c>
       <c r="J10" s="5"/>
       <c r="K10" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L10" s="6">
         <f t="shared" si="0"/>
@@ -15967,7 +15967,7 @@
         <v>108</v>
       </c>
       <c r="K11" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L11" s="6">
         <f t="shared" si="0"/>
@@ -16041,7 +16041,7 @@
       </c>
       <c r="J12" s="5"/>
       <c r="K12" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L12" s="6">
         <f t="shared" si="0"/>
@@ -16111,7 +16111,7 @@
       </c>
       <c r="J13" s="5"/>
       <c r="K13" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L13" s="6">
         <f t="shared" si="0"/>
@@ -16173,7 +16173,7 @@
       </c>
       <c r="J14" s="5"/>
       <c r="K14" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L14" s="6">
         <f t="shared" si="0"/>
@@ -16239,7 +16239,7 @@
         <v>119</v>
       </c>
       <c r="K15" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L15" s="6">
         <f t="shared" si="0"/>
@@ -16301,7 +16301,7 @@
       <c r="I16" s="5"/>
       <c r="J16" s="5"/>
       <c r="K16" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L16" s="6">
         <f t="shared" si="0"/>
@@ -16369,7 +16369,7 @@
         <v>91</v>
       </c>
       <c r="K17" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L17" s="6">
         <f t="shared" si="0"/>
@@ -16439,7 +16439,7 @@
         <v>78</v>
       </c>
       <c r="K18" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L18" s="6">
         <f>IF(A18="","",COUNTA(D18:F18)+COUNTA(G18:G18)+COUNTA(H18:H18)+COUNTA(#REF!))</f>
@@ -16492,7 +16492,7 @@
       <c r="I19" s="5"/>
       <c r="J19" s="5"/>
       <c r="K19" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L19" s="6">
         <f t="shared" ref="L19:L82" si="2">IF(A19="","",COUNTA(D19:F19)+COUNTA(G19:G19)+COUNTA(H19:H19)+COUNTA(I19:I19))</f>
@@ -16542,7 +16542,7 @@
       </c>
       <c r="J20" s="5"/>
       <c r="K20" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L20" s="6">
         <f t="shared" si="2"/>
@@ -16594,7 +16594,7 @@
       <c r="I21" s="5"/>
       <c r="J21" s="5"/>
       <c r="K21" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L21" s="6">
         <f t="shared" si="2"/>
@@ -16654,7 +16654,7 @@
         <v>157</v>
       </c>
       <c r="K22" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L22" s="6">
         <f t="shared" si="2"/>
@@ -16716,7 +16716,7 @@
       </c>
       <c r="J23" s="5"/>
       <c r="K23" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L23" s="6">
         <f t="shared" si="2"/>
@@ -16788,7 +16788,7 @@
       </c>
       <c r="J24" s="5"/>
       <c r="K24" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L24" s="6">
         <f t="shared" si="2"/>
@@ -16844,7 +16844,7 @@
       <c r="I25" s="5"/>
       <c r="J25" s="5"/>
       <c r="K25" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L25" s="6">
         <f t="shared" si="2"/>
@@ -16896,7 +16896,7 @@
       <c r="I26" s="5"/>
       <c r="J26" s="5"/>
       <c r="K26" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L26" s="6">
         <f t="shared" si="2"/>
@@ -16964,7 +16964,7 @@
         <v>178</v>
       </c>
       <c r="K27" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L27" s="6">
         <f t="shared" si="2"/>
@@ -17032,7 +17032,7 @@
       </c>
       <c r="J28" s="5"/>
       <c r="K28" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L28" s="6">
         <f t="shared" si="2"/>
@@ -17094,7 +17094,7 @@
       <c r="I29" s="5"/>
       <c r="J29" s="5"/>
       <c r="K29" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L29" s="6">
         <f t="shared" si="2"/>
@@ -17156,7 +17156,7 @@
         <v>193</v>
       </c>
       <c r="K30" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L30" s="6">
         <f t="shared" si="2"/>
@@ -17218,7 +17218,7 @@
         <v>199</v>
       </c>
       <c r="K31" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L31" s="6">
         <f t="shared" si="2"/>
@@ -17278,7 +17278,7 @@
       <c r="I32" s="5"/>
       <c r="J32" s="5"/>
       <c r="K32" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L32" s="6">
         <f t="shared" si="2"/>
@@ -17338,7 +17338,7 @@
       </c>
       <c r="J33" s="5"/>
       <c r="K33" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L33" s="6">
         <f t="shared" si="2"/>
@@ -17410,7 +17410,7 @@
         <v>119</v>
       </c>
       <c r="K34" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L34" s="6">
         <f t="shared" si="2"/>
@@ -17482,7 +17482,7 @@
         <v>91</v>
       </c>
       <c r="K35" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L35" s="6">
         <f t="shared" si="2"/>
@@ -17524,7 +17524,7 @@
     </row>
     <row r="36" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
-        <v>1901</v>
+        <v>1900</v>
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5" t="s">
@@ -17543,7 +17543,7 @@
         <v>57</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>1902</v>
+        <v>1901</v>
       </c>
       <c r="I36" s="5" t="s">
         <v>178</v>
@@ -17552,7 +17552,7 @@
         <v>72</v>
       </c>
       <c r="K36" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L36" s="6">
         <f t="shared" si="2"/>
@@ -17564,13 +17564,13 @@
       </c>
       <c r="N36" s="5"/>
       <c r="O36" s="5" t="s">
-        <v>1903</v>
+        <v>1902</v>
       </c>
       <c r="P36" s="5" t="s">
         <v>128</v>
       </c>
       <c r="Q36" s="5" t="s">
-        <v>1904</v>
+        <v>1903</v>
       </c>
       <c r="R36" s="5" t="s">
         <v>220</v>
@@ -17620,7 +17620,7 @@
       </c>
       <c r="J37" s="5"/>
       <c r="K37" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L37" s="6">
         <f t="shared" si="2"/>
@@ -17690,7 +17690,7 @@
       </c>
       <c r="J38" s="5"/>
       <c r="K38" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L38" s="6">
         <f t="shared" si="2"/>
@@ -17758,7 +17758,7 @@
         <v>133</v>
       </c>
       <c r="K39" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L39" s="6">
         <f t="shared" si="2"/>
@@ -17770,7 +17770,7 @@
       </c>
       <c r="N39" s="5"/>
       <c r="O39" s="5" t="s">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="P39" s="5" t="s">
         <v>105</v>
@@ -17826,7 +17826,7 @@
         <v>71</v>
       </c>
       <c r="K40" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L40" s="6">
         <f t="shared" si="2"/>
@@ -17894,7 +17894,7 @@
       </c>
       <c r="J41" s="5"/>
       <c r="K41" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L41" s="6">
         <f t="shared" si="2"/>
@@ -17964,7 +17964,7 @@
       </c>
       <c r="J42" s="5"/>
       <c r="K42" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L42" s="6">
         <f t="shared" si="2"/>
@@ -18018,7 +18018,7 @@
       <c r="I43" s="5"/>
       <c r="J43" s="5"/>
       <c r="K43" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L43" s="6">
         <f t="shared" si="2"/>
@@ -18066,7 +18066,7 @@
       <c r="I44" s="5"/>
       <c r="J44" s="5"/>
       <c r="K44" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L44" s="6">
         <f t="shared" si="2"/>
@@ -18124,7 +18124,7 @@
       </c>
       <c r="J45" s="5"/>
       <c r="K45" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L45" s="6">
         <f t="shared" si="2"/>
@@ -18174,7 +18174,7 @@
       <c r="I46" s="5"/>
       <c r="J46" s="5"/>
       <c r="K46" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L46" s="6">
         <f t="shared" si="2"/>
@@ -18226,7 +18226,7 @@
       <c r="I47" s="5"/>
       <c r="J47" s="5"/>
       <c r="K47" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L47" s="6">
         <f t="shared" si="2"/>
@@ -18288,7 +18288,7 @@
       </c>
       <c r="J48" s="5"/>
       <c r="K48" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L48" s="6">
         <f t="shared" si="2"/>
@@ -18344,7 +18344,7 @@
       <c r="I49" s="5"/>
       <c r="J49" s="5"/>
       <c r="K49" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L49" s="6">
         <f t="shared" si="2"/>
@@ -18410,7 +18410,7 @@
         <v>78</v>
       </c>
       <c r="K50" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L50" s="6">
         <f t="shared" si="2"/>
@@ -18482,7 +18482,7 @@
       </c>
       <c r="J51" s="5"/>
       <c r="K51" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L51" s="6">
         <f t="shared" si="2"/>
@@ -18544,7 +18544,7 @@
       <c r="I52" s="5"/>
       <c r="J52" s="5"/>
       <c r="K52" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L52" s="6">
         <f t="shared" si="2"/>
@@ -18608,7 +18608,7 @@
         <v>78</v>
       </c>
       <c r="K53" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L53" s="6">
         <f t="shared" si="2"/>
@@ -18668,7 +18668,7 @@
       <c r="I54" s="5"/>
       <c r="J54" s="5"/>
       <c r="K54" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L54" s="6">
         <f t="shared" si="2"/>
@@ -18727,7 +18727,7 @@
         <v>47</v>
       </c>
       <c r="H55" s="5" t="s">
-        <v>1890</v>
+        <v>1889</v>
       </c>
       <c r="I55" s="5" t="s">
         <v>123</v>
@@ -18736,7 +18736,7 @@
         <v>287</v>
       </c>
       <c r="K55" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L55" s="6">
         <f t="shared" si="2"/>
@@ -18806,7 +18806,7 @@
       </c>
       <c r="J56" s="5"/>
       <c r="K56" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L56" s="6">
         <f t="shared" si="2"/>
@@ -18866,7 +18866,7 @@
         <v>192</v>
       </c>
       <c r="K57" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L57" s="6">
         <f t="shared" si="2"/>
@@ -18928,7 +18928,7 @@
         <v>192</v>
       </c>
       <c r="K58" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L58" s="6">
         <f t="shared" si="2"/>
@@ -18986,7 +18986,7 @@
         <v>72</v>
       </c>
       <c r="K59" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L59" s="6">
         <f t="shared" si="2"/>
@@ -19042,7 +19042,7 @@
       <c r="I60" s="5"/>
       <c r="J60" s="5"/>
       <c r="K60" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L60" s="6">
         <f t="shared" si="2"/>
@@ -19076,7 +19076,7 @@
     </row>
     <row r="61" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A61" s="5" t="s">
-        <v>1905</v>
+        <v>1904</v>
       </c>
       <c r="B61" s="5"/>
       <c r="C61" s="5" t="s">
@@ -19095,14 +19095,14 @@
         <v>57</v>
       </c>
       <c r="H61" s="5" t="s">
-        <v>1906</v>
+        <v>1905</v>
       </c>
       <c r="I61" s="5" t="s">
         <v>49</v>
       </c>
       <c r="J61" s="5"/>
       <c r="K61" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L61" s="6">
         <f t="shared" si="2"/>
@@ -19114,7 +19114,7 @@
       </c>
       <c r="N61" s="5"/>
       <c r="O61" s="5" t="s">
-        <v>1907</v>
+        <v>1906</v>
       </c>
       <c r="P61" s="5" t="s">
         <v>128</v>
@@ -19133,7 +19133,7 @@
         <v>51</v>
       </c>
       <c r="X61" s="5" t="s">
-        <v>1908</v>
+        <v>1907</v>
       </c>
       <c r="Y61" s="5" t="s">
         <v>57</v>
@@ -19162,7 +19162,7 @@
       <c r="I62" s="5"/>
       <c r="J62" s="5"/>
       <c r="K62" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L62" s="6">
         <f t="shared" si="2"/>
@@ -19221,14 +19221,14 @@
         <v>57</v>
       </c>
       <c r="H63" s="5" t="s">
-        <v>1881</v>
+        <v>1880</v>
       </c>
       <c r="I63" s="5" t="s">
         <v>123</v>
       </c>
       <c r="J63" s="5"/>
       <c r="K63" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L63" s="6">
         <f t="shared" si="2"/>
@@ -19286,7 +19286,7 @@
       <c r="I64" s="5"/>
       <c r="J64" s="5"/>
       <c r="K64" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L64" s="6">
         <f t="shared" si="2"/>
@@ -19341,7 +19341,7 @@
         <v>57</v>
       </c>
       <c r="H65" s="5" t="s">
-        <v>1857</v>
+        <v>1856</v>
       </c>
       <c r="I65" s="5" t="s">
         <v>78</v>
@@ -19350,7 +19350,7 @@
         <v>178</v>
       </c>
       <c r="K65" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L65" s="6">
         <f t="shared" si="2"/>
@@ -19412,7 +19412,7 @@
       <c r="I66" s="5"/>
       <c r="J66" s="5"/>
       <c r="K66" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L66" s="6">
         <f t="shared" si="2"/>
@@ -19470,7 +19470,7 @@
       </c>
       <c r="J67" s="5"/>
       <c r="K67" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L67" s="6">
         <f t="shared" si="2"/>
@@ -19530,7 +19530,7 @@
       <c r="I68" s="5"/>
       <c r="J68" s="5"/>
       <c r="K68" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L68" s="6">
         <f t="shared" si="2"/>
@@ -19582,7 +19582,7 @@
       <c r="I69" s="5"/>
       <c r="J69" s="5"/>
       <c r="K69" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L69" s="6">
         <f t="shared" si="2"/>
@@ -19648,7 +19648,7 @@
       </c>
       <c r="J70" s="5"/>
       <c r="K70" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L70" s="6">
         <f t="shared" si="2"/>
@@ -19722,7 +19722,7 @@
         <v>71</v>
       </c>
       <c r="K71" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L71" s="6">
         <f t="shared" si="2"/>
@@ -19790,7 +19790,7 @@
         <v>349</v>
       </c>
       <c r="K72" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L72" s="6">
         <f t="shared" si="2"/>
@@ -19850,7 +19850,7 @@
       <c r="I73" s="5"/>
       <c r="J73" s="5"/>
       <c r="K73" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L73" s="6">
         <f t="shared" si="2"/>
@@ -19906,7 +19906,7 @@
       <c r="I74" s="5"/>
       <c r="J74" s="5"/>
       <c r="K74" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L74" s="6">
         <f t="shared" si="2"/>
@@ -19962,7 +19962,7 @@
       <c r="I75" s="5"/>
       <c r="J75" s="5"/>
       <c r="K75" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L75" s="6">
         <f t="shared" si="2"/>
@@ -20018,7 +20018,7 @@
       <c r="I76" s="5"/>
       <c r="J76" s="5"/>
       <c r="K76" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L76" s="6">
         <f t="shared" si="2"/>
@@ -20074,7 +20074,7 @@
       <c r="I77" s="5"/>
       <c r="J77" s="5"/>
       <c r="K77" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L77" s="6">
         <f t="shared" si="2"/>
@@ -20130,7 +20130,7 @@
       <c r="I78" s="5"/>
       <c r="J78" s="5"/>
       <c r="K78" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L78" s="6">
         <f t="shared" si="2"/>
@@ -20186,7 +20186,7 @@
       <c r="I79" s="5"/>
       <c r="J79" s="5"/>
       <c r="K79" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L79" s="6">
         <f t="shared" si="2"/>
@@ -20242,7 +20242,7 @@
       <c r="I80" s="5"/>
       <c r="J80" s="5"/>
       <c r="K80" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L80" s="6">
         <f t="shared" si="2"/>
@@ -20298,7 +20298,7 @@
       <c r="I81" s="5"/>
       <c r="J81" s="5"/>
       <c r="K81" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L81" s="6">
         <f t="shared" si="2"/>
@@ -20358,7 +20358,7 @@
       <c r="I82" s="5"/>
       <c r="J82" s="5"/>
       <c r="K82" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L82" s="6">
         <f t="shared" si="2"/>
@@ -20420,7 +20420,7 @@
       </c>
       <c r="J83" s="5"/>
       <c r="K83" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L83" s="6">
         <f t="shared" ref="L83:L146" si="4">IF(A83="","",COUNTA(D83:F83)+COUNTA(G83:G83)+COUNTA(H83:H83)+COUNTA(I83:I83))</f>
@@ -20476,7 +20476,7 @@
       <c r="I84" s="5"/>
       <c r="J84" s="5"/>
       <c r="K84" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L84" s="6">
         <f t="shared" si="4"/>
@@ -20530,7 +20530,7 @@
       <c r="I85" s="5"/>
       <c r="J85" s="5"/>
       <c r="K85" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L85" s="6">
         <f t="shared" si="4"/>
@@ -20580,7 +20580,7 @@
       </c>
       <c r="J86" s="5"/>
       <c r="K86" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L86" s="6">
         <f t="shared" si="4"/>
@@ -20638,7 +20638,7 @@
       <c r="I87" s="5"/>
       <c r="J87" s="5"/>
       <c r="K87" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L87" s="6">
         <f t="shared" si="4"/>
@@ -20695,14 +20695,14 @@
         <v>57</v>
       </c>
       <c r="H88" s="5" t="s">
-        <v>1856</v>
+        <v>1855</v>
       </c>
       <c r="I88" s="5" t="s">
         <v>192</v>
       </c>
       <c r="J88" s="5"/>
       <c r="K88" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L88" s="6">
         <f t="shared" si="4"/>
@@ -20765,7 +20765,7 @@
         <v>57</v>
       </c>
       <c r="H89" s="5" t="s">
-        <v>1860</v>
+        <v>1859</v>
       </c>
       <c r="I89" s="5" t="s">
         <v>91</v>
@@ -20774,7 +20774,7 @@
         <v>72</v>
       </c>
       <c r="K89" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L89" s="6">
         <f t="shared" si="4"/>
@@ -20785,10 +20785,10 @@
         <v>Yes</v>
       </c>
       <c r="N89" s="5" t="s">
+        <v>1876</v>
+      </c>
+      <c r="O89" s="5" t="s">
         <v>1877</v>
-      </c>
-      <c r="O89" s="5" t="s">
-        <v>1878</v>
       </c>
       <c r="P89" s="5" t="s">
         <v>319</v>
@@ -20834,7 +20834,7 @@
       <c r="I90" s="5"/>
       <c r="J90" s="5"/>
       <c r="K90" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L90" s="6">
         <f t="shared" si="4"/>
@@ -20890,7 +20890,7 @@
       </c>
       <c r="J91" s="5"/>
       <c r="K91" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L91" s="6">
         <f t="shared" si="4"/>
@@ -20946,7 +20946,7 @@
       <c r="I92" s="5"/>
       <c r="J92" s="5"/>
       <c r="K92" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L92" s="6">
         <f t="shared" si="4"/>
@@ -21006,7 +21006,7 @@
         <v>401</v>
       </c>
       <c r="K93" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L93" s="6">
         <f t="shared" si="4"/>
@@ -21066,7 +21066,7 @@
       <c r="I94" s="5"/>
       <c r="J94" s="5"/>
       <c r="K94" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L94" s="6">
         <f t="shared" si="4"/>
@@ -21124,7 +21124,7 @@
       <c r="I95" s="5"/>
       <c r="J95" s="5"/>
       <c r="K95" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L95" s="6">
         <f t="shared" si="4"/>
@@ -21184,7 +21184,7 @@
       </c>
       <c r="J96" s="5"/>
       <c r="K96" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L96" s="6">
         <f t="shared" si="4"/>
@@ -21258,7 +21258,7 @@
       </c>
       <c r="J97" s="5"/>
       <c r="K97" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L97" s="6">
         <f t="shared" si="4"/>
@@ -21330,7 +21330,7 @@
         <v>49</v>
       </c>
       <c r="K98" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L98" s="6">
         <f t="shared" si="4"/>
@@ -21392,7 +21392,7 @@
       </c>
       <c r="J99" s="5"/>
       <c r="K99" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L99" s="6">
         <f t="shared" si="4"/>
@@ -21456,7 +21456,7 @@
       </c>
       <c r="J100" s="5"/>
       <c r="K100" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L100" s="6">
         <f t="shared" si="4"/>
@@ -21520,7 +21520,7 @@
       </c>
       <c r="J101" s="5"/>
       <c r="K101" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L101" s="6">
         <f t="shared" si="4"/>
@@ -21592,7 +21592,7 @@
         <v>72</v>
       </c>
       <c r="K102" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L102" s="6">
         <f t="shared" si="4"/>
@@ -21650,7 +21650,7 @@
       <c r="I103" s="5"/>
       <c r="J103" s="5"/>
       <c r="K103" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L103" s="6">
         <f t="shared" si="4"/>
@@ -21710,7 +21710,7 @@
         <v>440</v>
       </c>
       <c r="K104" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L104" s="6">
         <f t="shared" si="4"/>
@@ -21776,7 +21776,7 @@
         <v>445</v>
       </c>
       <c r="K105" s="18" t="s">
-        <v>1932</v>
+        <v>1931</v>
       </c>
       <c r="L105" s="6">
         <f t="shared" si="4"/>
@@ -21848,7 +21848,7 @@
         <v>133</v>
       </c>
       <c r="K106" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L106" s="6">
         <f t="shared" si="4"/>
@@ -21910,7 +21910,7 @@
         <v>78</v>
       </c>
       <c r="K107" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L107" s="6">
         <f t="shared" si="4"/>
@@ -21966,7 +21966,7 @@
       <c r="I108" s="5"/>
       <c r="J108" s="5"/>
       <c r="K108" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L108" s="6">
         <f t="shared" si="4"/>
@@ -22020,7 +22020,7 @@
         <v>461</v>
       </c>
       <c r="K109" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L109" s="6">
         <f t="shared" si="4"/>
@@ -22078,7 +22078,7 @@
       <c r="I110" s="5"/>
       <c r="J110" s="5"/>
       <c r="K110" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L110" s="6">
         <f t="shared" si="4"/>
@@ -22131,14 +22131,14 @@
         <v>57</v>
       </c>
       <c r="H111" s="5" t="s">
-        <v>1856</v>
+        <v>1855</v>
       </c>
       <c r="I111" s="5" t="s">
         <v>78</v>
       </c>
       <c r="J111" s="5"/>
       <c r="K111" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L111" s="6">
         <f t="shared" si="4"/>
@@ -22208,7 +22208,7 @@
       <c r="I112" s="5"/>
       <c r="J112" s="5"/>
       <c r="K112" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L112" s="6">
         <f t="shared" si="4"/>
@@ -22276,7 +22276,7 @@
         <v>49</v>
       </c>
       <c r="K113" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L113" s="6">
         <f t="shared" si="4"/>
@@ -22336,7 +22336,7 @@
       <c r="I114" s="5"/>
       <c r="J114" s="5"/>
       <c r="K114" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L114" s="6">
         <f t="shared" si="4"/>
@@ -22400,7 +22400,7 @@
       </c>
       <c r="J115" s="5"/>
       <c r="K115" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L115" s="6">
         <f t="shared" si="4"/>
@@ -22446,7 +22446,7 @@
     </row>
     <row r="116" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A116" s="5" t="s">
-        <v>1928</v>
+        <v>1927</v>
       </c>
       <c r="B116" s="5"/>
       <c r="C116" s="5" t="s">
@@ -22471,10 +22471,10 @@
         <v>59</v>
       </c>
       <c r="J116" s="5" t="s">
-        <v>1924</v>
+        <v>1923</v>
       </c>
       <c r="K116" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L116" s="6">
         <f t="shared" si="4"/>
@@ -22486,7 +22486,7 @@
       </c>
       <c r="N116" s="5"/>
       <c r="O116" s="5" t="s">
-        <v>1929</v>
+        <v>1928</v>
       </c>
       <c r="P116" s="5" t="s">
         <v>128</v>
@@ -22540,7 +22540,7 @@
       </c>
       <c r="J117" s="5"/>
       <c r="K117" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L117" s="6">
         <f t="shared" si="4"/>
@@ -22600,7 +22600,7 @@
       <c r="I118" s="5"/>
       <c r="J118" s="5"/>
       <c r="K118" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L118" s="6">
         <f t="shared" si="4"/>
@@ -22654,7 +22654,7 @@
       <c r="I119" s="5"/>
       <c r="J119" s="5"/>
       <c r="K119" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L119" s="6">
         <f t="shared" si="4"/>
@@ -22717,10 +22717,10 @@
         <v>71</v>
       </c>
       <c r="J120" s="5" t="s">
-        <v>1884</v>
+        <v>1883</v>
       </c>
       <c r="K120" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L120" s="6">
         <f t="shared" si="4"/>
@@ -22758,7 +22758,7 @@
     </row>
     <row r="121" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A121" s="5" t="s">
-        <v>1923</v>
+        <v>1922</v>
       </c>
       <c r="B121" s="5"/>
       <c r="C121" s="5" t="s">
@@ -22777,16 +22777,16 @@
         <v>47</v>
       </c>
       <c r="H121" s="17" t="s">
-        <v>1902</v>
+        <v>1901</v>
       </c>
       <c r="I121" s="5" t="s">
         <v>123</v>
       </c>
       <c r="J121" s="5" t="s">
-        <v>1924</v>
+        <v>1923</v>
       </c>
       <c r="K121" s="18" t="s">
-        <v>1882</v>
+        <v>1881</v>
       </c>
       <c r="L121" s="6">
         <f t="shared" si="4"/>
@@ -22797,16 +22797,16 @@
         <v>Yes</v>
       </c>
       <c r="N121" s="5" t="s">
-        <v>1926</v>
+        <v>1925</v>
       </c>
       <c r="O121" s="5" t="s">
-        <v>1925</v>
+        <v>1924</v>
       </c>
       <c r="P121" s="5" t="s">
         <v>128</v>
       </c>
       <c r="Q121" s="5" t="s">
-        <v>1927</v>
+        <v>1926</v>
       </c>
       <c r="R121" s="5"/>
       <c r="S121" s="5"/>
@@ -22819,7 +22819,7 @@
         <v>51</v>
       </c>
       <c r="X121" s="5" t="s">
-        <v>1882</v>
+        <v>1881</v>
       </c>
       <c r="Y121" s="5"/>
       <c r="Z121" s="5" t="s">
@@ -22847,7 +22847,7 @@
         <v>47</v>
       </c>
       <c r="H122" s="17" t="s">
-        <v>1916</v>
+        <v>1915</v>
       </c>
       <c r="I122" s="5" t="s">
         <v>91</v>
@@ -22856,7 +22856,7 @@
         <v>49</v>
       </c>
       <c r="K122" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L122" s="6">
         <f t="shared" si="4"/>
@@ -22924,7 +22924,7 @@
       </c>
       <c r="J123" s="5"/>
       <c r="K123" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L123" s="6">
         <f t="shared" si="4"/>
@@ -22990,7 +22990,7 @@
       </c>
       <c r="J124" s="5"/>
       <c r="K124" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L124" s="6">
         <f t="shared" si="4"/>
@@ -23050,7 +23050,7 @@
       <c r="I125" s="5"/>
       <c r="J125" s="5"/>
       <c r="K125" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L125" s="6">
         <f t="shared" si="4"/>
@@ -23114,7 +23114,7 @@
         <v>49</v>
       </c>
       <c r="K126" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L126" s="6">
         <f t="shared" si="4"/>
@@ -23182,7 +23182,7 @@
       </c>
       <c r="J127" s="5"/>
       <c r="K127" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L127" s="6">
         <f t="shared" si="4"/>
@@ -23248,7 +23248,7 @@
       </c>
       <c r="J128" s="5"/>
       <c r="K128" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L128" s="6">
         <f t="shared" si="4"/>
@@ -23312,7 +23312,7 @@
       </c>
       <c r="J129" s="5"/>
       <c r="K129" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L129" s="6">
         <f t="shared" si="4"/>
@@ -23358,7 +23358,7 @@
     </row>
     <row r="130" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A130" s="5" t="s">
-        <v>1863</v>
+        <v>1862</v>
       </c>
       <c r="B130" s="5"/>
       <c r="C130" s="5" t="s">
@@ -23384,7 +23384,7 @@
       </c>
       <c r="J130" s="5"/>
       <c r="K130" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L130" s="6">
         <f t="shared" si="4"/>
@@ -23395,10 +23395,10 @@
         <v>Yes</v>
       </c>
       <c r="N130" s="5" t="s">
-        <v>1867</v>
+        <v>1866</v>
       </c>
       <c r="O130" s="5" t="s">
-        <v>1864</v>
+        <v>1863</v>
       </c>
       <c r="P130" s="5" t="s">
         <v>43</v>
@@ -23451,10 +23451,10 @@
         <v>119</v>
       </c>
       <c r="J131" s="17" t="s">
-        <v>1915</v>
+        <v>1914</v>
       </c>
       <c r="K131" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L131" s="6">
         <f t="shared" si="4"/>
@@ -23520,7 +23520,7 @@
       </c>
       <c r="J132" s="5"/>
       <c r="K132" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L132" s="6">
         <f t="shared" si="4"/>
@@ -23588,7 +23588,7 @@
       </c>
       <c r="J133" s="5"/>
       <c r="K133" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L133" s="6">
         <f t="shared" si="4"/>
@@ -23660,7 +23660,7 @@
         <v>91</v>
       </c>
       <c r="K134" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L134" s="6">
         <f t="shared" si="4"/>
@@ -23722,7 +23722,7 @@
       </c>
       <c r="J135" s="5"/>
       <c r="K135" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L135" s="6">
         <f t="shared" si="4"/>
@@ -23782,7 +23782,7 @@
       <c r="I136" s="5"/>
       <c r="J136" s="5"/>
       <c r="K136" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L136" s="6">
         <f t="shared" si="4"/>
@@ -23848,7 +23848,7 @@
         <v>133</v>
       </c>
       <c r="K137" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L137" s="6">
         <f t="shared" si="4"/>
@@ -23910,7 +23910,7 @@
       <c r="I138" s="5"/>
       <c r="J138" s="5"/>
       <c r="K138" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L138" s="6">
         <f t="shared" si="4"/>
@@ -23958,7 +23958,7 @@
       <c r="I139" s="5"/>
       <c r="J139" s="5"/>
       <c r="K139" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L139" s="6">
         <f t="shared" si="4"/>
@@ -24008,7 +24008,7 @@
       <c r="I140" s="5"/>
       <c r="J140" s="5"/>
       <c r="K140" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L140" s="6">
         <f t="shared" si="4"/>
@@ -24062,7 +24062,7 @@
       </c>
       <c r="J141" s="5"/>
       <c r="K141" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L141" s="6">
         <f t="shared" si="4"/>
@@ -24120,7 +24120,7 @@
       <c r="I142" s="5"/>
       <c r="J142" s="5"/>
       <c r="K142" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L142" s="6">
         <f t="shared" si="4"/>
@@ -24184,7 +24184,7 @@
       </c>
       <c r="J143" s="5"/>
       <c r="K143" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L143" s="6">
         <f t="shared" si="4"/>
@@ -24250,7 +24250,7 @@
         <v>568</v>
       </c>
       <c r="K144" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L144" s="6">
         <f t="shared" si="4"/>
@@ -24314,7 +24314,7 @@
       </c>
       <c r="J145" s="5"/>
       <c r="K145" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L145" s="6">
         <f t="shared" si="4"/>
@@ -24328,7 +24328,7 @@
         <v>573</v>
       </c>
       <c r="O145" s="17" t="s">
-        <v>1917</v>
+        <v>1916</v>
       </c>
       <c r="P145" s="5"/>
       <c r="Q145" s="5"/>
@@ -24378,7 +24378,7 @@
       <c r="I146" s="5"/>
       <c r="J146" s="5"/>
       <c r="K146" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L146" s="6">
         <f t="shared" si="4"/>
@@ -24446,7 +24446,7 @@
         <v>71</v>
       </c>
       <c r="K147" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L147" s="6">
         <f t="shared" ref="L147:L210" si="6">IF(A147="","",COUNTA(D147:F147)+COUNTA(G147:G147)+COUNTA(H147:H147)+COUNTA(I147:I147))</f>
@@ -24504,7 +24504,7 @@
         <v>580</v>
       </c>
       <c r="K148" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L148" s="6">
         <f t="shared" si="6"/>
@@ -24568,7 +24568,7 @@
       </c>
       <c r="J149" s="5"/>
       <c r="K149" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L149" s="6">
         <f t="shared" si="6"/>
@@ -24638,7 +24638,7 @@
         <v>91</v>
       </c>
       <c r="K150" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L150" s="6">
         <f t="shared" si="6"/>
@@ -24703,10 +24703,10 @@
         <v>123</v>
       </c>
       <c r="J151" s="5" t="s">
-        <v>1952</v>
+        <v>1951</v>
       </c>
       <c r="K151" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L151" s="6">
         <f t="shared" si="6"/>
@@ -24766,7 +24766,7 @@
       </c>
       <c r="J152" s="5"/>
       <c r="K152" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L152" s="6">
         <f t="shared" si="6"/>
@@ -24820,7 +24820,7 @@
       <c r="I153" s="5"/>
       <c r="J153" s="5"/>
       <c r="K153" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L153" s="6">
         <f t="shared" si="6"/>
@@ -24886,7 +24886,7 @@
         <v>606</v>
       </c>
       <c r="K154" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L154" s="6">
         <f t="shared" si="6"/>
@@ -24952,7 +24952,7 @@
       <c r="I155" s="5"/>
       <c r="J155" s="5"/>
       <c r="K155" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L155" s="6">
         <f t="shared" si="6"/>
@@ -25018,7 +25018,7 @@
       </c>
       <c r="J156" s="5"/>
       <c r="K156" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L156" s="6">
         <f t="shared" si="6"/>
@@ -25074,7 +25074,7 @@
       <c r="I157" s="5"/>
       <c r="J157" s="5"/>
       <c r="K157" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L157" s="6">
         <f t="shared" si="6"/>
@@ -25126,7 +25126,7 @@
       <c r="I158" s="5"/>
       <c r="J158" s="5"/>
       <c r="K158" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L158" s="6">
         <f t="shared" si="6"/>
@@ -25158,7 +25158,7 @@
     </row>
     <row r="159" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A159" s="5" t="s">
-        <v>1918</v>
+        <v>1917</v>
       </c>
       <c r="B159" s="5"/>
       <c r="C159" s="5" t="s">
@@ -25177,7 +25177,7 @@
         <v>57</v>
       </c>
       <c r="H159" s="5" t="s">
-        <v>1919</v>
+        <v>1918</v>
       </c>
       <c r="I159" s="5" t="s">
         <v>192</v>
@@ -25186,7 +25186,7 @@
         <v>59</v>
       </c>
       <c r="K159" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L159" s="6">
         <f t="shared" si="6"/>
@@ -25198,13 +25198,13 @@
       </c>
       <c r="N159" s="5"/>
       <c r="O159" s="5" t="s">
-        <v>1920</v>
+        <v>1919</v>
       </c>
       <c r="P159" s="5" t="s">
         <v>128</v>
       </c>
       <c r="Q159" s="5" t="s">
-        <v>1921</v>
+        <v>1920</v>
       </c>
       <c r="R159" s="5"/>
       <c r="S159" s="5"/>
@@ -25219,7 +25219,7 @@
         <v>112</v>
       </c>
       <c r="X159" s="5" t="s">
-        <v>1919</v>
+        <v>1918</v>
       </c>
       <c r="Y159" s="5"/>
       <c r="Z159" s="5" t="s">
@@ -25254,7 +25254,7 @@
       </c>
       <c r="J160" s="5"/>
       <c r="K160" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L160" s="6">
         <f t="shared" si="6"/>
@@ -25322,7 +25322,7 @@
       <c r="I161" s="5"/>
       <c r="J161" s="5"/>
       <c r="K161" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L161" s="6">
         <f t="shared" si="6"/>
@@ -25382,7 +25382,7 @@
       </c>
       <c r="J162" s="5"/>
       <c r="K162" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L162" s="6">
         <f t="shared" si="6"/>
@@ -25440,7 +25440,7 @@
       </c>
       <c r="J163" s="5"/>
       <c r="K163" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L163" s="6">
         <f t="shared" si="6"/>
@@ -25500,7 +25500,7 @@
       <c r="I164" s="5"/>
       <c r="J164" s="5"/>
       <c r="K164" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L164" s="6">
         <f t="shared" si="6"/>
@@ -25556,7 +25556,7 @@
       <c r="I165" s="5"/>
       <c r="J165" s="5"/>
       <c r="K165" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L165" s="6">
         <f t="shared" si="6"/>
@@ -25612,7 +25612,7 @@
       <c r="I166" s="5"/>
       <c r="J166" s="5"/>
       <c r="K166" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L166" s="6">
         <f t="shared" si="6"/>
@@ -25672,7 +25672,7 @@
       </c>
       <c r="J167" s="5"/>
       <c r="K167" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L167" s="6">
         <f t="shared" si="6"/>
@@ -25724,7 +25724,7 @@
       <c r="I168" s="5"/>
       <c r="J168" s="5"/>
       <c r="K168" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L168" s="6">
         <f t="shared" si="6"/>
@@ -25782,7 +25782,7 @@
       <c r="I169" s="5"/>
       <c r="J169" s="5"/>
       <c r="K169" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L169" s="6">
         <f t="shared" si="6"/>
@@ -25840,7 +25840,7 @@
       <c r="I170" s="5"/>
       <c r="J170" s="5"/>
       <c r="K170" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L170" s="6">
         <f t="shared" si="6"/>
@@ -25896,7 +25896,7 @@
       <c r="I171" s="5"/>
       <c r="J171" s="5"/>
       <c r="K171" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L171" s="6">
         <f t="shared" si="6"/>
@@ -25956,7 +25956,7 @@
         <v>71</v>
       </c>
       <c r="K172" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L172" s="6">
         <f t="shared" si="6"/>
@@ -26006,7 +26006,7 @@
       <c r="I173" s="5"/>
       <c r="J173" s="5"/>
       <c r="K173" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L173" s="6">
         <f t="shared" si="6"/>
@@ -26062,7 +26062,7 @@
       <c r="I174" s="5"/>
       <c r="J174" s="5"/>
       <c r="K174" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L174" s="6">
         <f t="shared" si="6"/>
@@ -26116,7 +26116,7 @@
         <v>78</v>
       </c>
       <c r="K175" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L175" s="6">
         <f t="shared" si="6"/>
@@ -26168,7 +26168,7 @@
       <c r="I176" s="5"/>
       <c r="J176" s="5"/>
       <c r="K176" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L176" s="6">
         <f t="shared" si="6"/>
@@ -26228,7 +26228,7 @@
       </c>
       <c r="J177" s="5"/>
       <c r="K177" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L177" s="6">
         <f t="shared" si="6"/>
@@ -26290,7 +26290,7 @@
         <v>91</v>
       </c>
       <c r="K178" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L178" s="6">
         <f t="shared" si="6"/>
@@ -26360,7 +26360,7 @@
         <v>119</v>
       </c>
       <c r="K179" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L179" s="6">
         <f t="shared" si="6"/>
@@ -26428,7 +26428,7 @@
         <v>72</v>
       </c>
       <c r="K180" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L180" s="6">
         <f t="shared" si="6"/>
@@ -26490,7 +26490,7 @@
       <c r="I181" s="5"/>
       <c r="J181" s="5"/>
       <c r="K181" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L181" s="6">
         <f t="shared" si="6"/>
@@ -26544,7 +26544,7 @@
       <c r="I182" s="5"/>
       <c r="J182" s="5"/>
       <c r="K182" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L182" s="6">
         <f t="shared" si="6"/>
@@ -26600,7 +26600,7 @@
       <c r="I183" s="5"/>
       <c r="J183" s="5"/>
       <c r="K183" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L183" s="6">
         <f t="shared" si="6"/>
@@ -26650,7 +26650,7 @@
       <c r="I184" s="5"/>
       <c r="J184" s="5"/>
       <c r="K184" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L184" s="6">
         <f t="shared" si="6"/>
@@ -26700,7 +26700,7 @@
       <c r="I185" s="5"/>
       <c r="J185" s="5"/>
       <c r="K185" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L185" s="6">
         <f t="shared" si="6"/>
@@ -26758,7 +26758,7 @@
       </c>
       <c r="J186" s="5"/>
       <c r="K186" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L186" s="6">
         <f t="shared" si="6"/>
@@ -26816,7 +26816,7 @@
       <c r="I187" s="5"/>
       <c r="J187" s="5"/>
       <c r="K187" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L187" s="6">
         <f t="shared" si="6"/>
@@ -26875,7 +26875,7 @@
         <v>57</v>
       </c>
       <c r="H188" s="5" t="s">
-        <v>1859</v>
+        <v>1858</v>
       </c>
       <c r="I188" s="5" t="s">
         <v>78</v>
@@ -26884,7 +26884,7 @@
         <v>689</v>
       </c>
       <c r="K188" s="18" t="s">
-        <v>1937</v>
+        <v>1936</v>
       </c>
       <c r="L188" s="6">
         <f t="shared" si="6"/>
@@ -26946,7 +26946,7 @@
       <c r="I189" s="5"/>
       <c r="J189" s="5"/>
       <c r="K189" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L189" s="6">
         <f t="shared" si="6"/>
@@ -27004,7 +27004,7 @@
       </c>
       <c r="J190" s="5"/>
       <c r="K190" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L190" s="6">
         <f t="shared" si="6"/>
@@ -27068,7 +27068,7 @@
       </c>
       <c r="J191" s="5"/>
       <c r="K191" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L191" s="6">
         <f t="shared" si="6"/>
@@ -27126,7 +27126,7 @@
       </c>
       <c r="J192" s="5"/>
       <c r="K192" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L192" s="6">
         <f t="shared" si="6"/>
@@ -27192,7 +27192,7 @@
         <v>193</v>
       </c>
       <c r="K193" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L193" s="6">
         <f t="shared" si="6"/>
@@ -27258,7 +27258,7 @@
       <c r="I194" s="5"/>
       <c r="J194" s="5"/>
       <c r="K194" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L194" s="6">
         <f t="shared" si="6"/>
@@ -27316,7 +27316,7 @@
         <v>91</v>
       </c>
       <c r="K195" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L195" s="6">
         <f t="shared" si="6"/>
@@ -27378,19 +27378,19 @@
         <v>107</v>
       </c>
       <c r="G196" s="5" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="H196" s="5" t="s">
-        <v>718</v>
+        <v>1972</v>
       </c>
       <c r="I196" s="5" t="s">
         <v>119</v>
       </c>
       <c r="J196" s="5" t="s">
-        <v>1854</v>
+        <v>91</v>
       </c>
       <c r="K196" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L196" s="6">
         <f t="shared" si="6"/>
@@ -27449,12 +27449,12 @@
         <v>57</v>
       </c>
       <c r="H197" s="5" t="s">
-        <v>1856</v>
+        <v>1855</v>
       </c>
       <c r="I197" s="5"/>
       <c r="J197" s="5"/>
       <c r="K197" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L197" s="6">
         <f t="shared" si="6"/>
@@ -27504,7 +27504,7 @@
       <c r="I198" s="5"/>
       <c r="J198" s="5"/>
       <c r="K198" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L198" s="6">
         <f t="shared" si="6"/>
@@ -27550,7 +27550,7 @@
       <c r="I199" s="5"/>
       <c r="J199" s="5"/>
       <c r="K199" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L199" s="6">
         <f t="shared" si="6"/>
@@ -27614,7 +27614,7 @@
         <v>119</v>
       </c>
       <c r="K200" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L200" s="6">
         <f t="shared" si="6"/>
@@ -27688,7 +27688,7 @@
         <v>78</v>
       </c>
       <c r="K201" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L201" s="6">
         <f t="shared" si="6"/>
@@ -27742,7 +27742,7 @@
       <c r="I202" s="5"/>
       <c r="J202" s="5"/>
       <c r="K202" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L202" s="6">
         <f t="shared" si="6"/>
@@ -27802,7 +27802,7 @@
         <v>193</v>
       </c>
       <c r="K203" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L203" s="6">
         <f t="shared" si="6"/>
@@ -27864,7 +27864,7 @@
       <c r="I204" s="5"/>
       <c r="J204" s="5"/>
       <c r="K204" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L204" s="6">
         <f t="shared" si="6"/>
@@ -27924,7 +27924,7 @@
         <v>78</v>
       </c>
       <c r="K205" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L205" s="6">
         <f t="shared" si="6"/>
@@ -27990,7 +27990,7 @@
       </c>
       <c r="J206" s="5"/>
       <c r="K206" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L206" s="6">
         <f t="shared" si="6"/>
@@ -28050,7 +28050,7 @@
       <c r="I207" s="5"/>
       <c r="J207" s="5"/>
       <c r="K207" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L207" s="6">
         <f t="shared" si="6"/>
@@ -28106,7 +28106,7 @@
       </c>
       <c r="J208" s="5"/>
       <c r="K208" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L208" s="6">
         <f t="shared" si="6"/>
@@ -28164,7 +28164,7 @@
       <c r="I209" s="5"/>
       <c r="J209" s="5"/>
       <c r="K209" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L209" s="6">
         <f t="shared" si="6"/>
@@ -28226,7 +28226,7 @@
       </c>
       <c r="J210" s="5"/>
       <c r="K210" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L210" s="6">
         <f t="shared" si="6"/>
@@ -28278,7 +28278,7 @@
       <c r="I211" s="5"/>
       <c r="J211" s="5"/>
       <c r="K211" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L211" s="6">
         <f t="shared" ref="L211:L274" si="8">IF(A211="","",COUNTA(D211:F211)+COUNTA(G211:G211)+COUNTA(H211:H211)+COUNTA(I211:I211))</f>
@@ -28332,7 +28332,7 @@
       </c>
       <c r="J212" s="5"/>
       <c r="K212" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L212" s="6">
         <f t="shared" si="8"/>
@@ -28393,16 +28393,16 @@
         <v>47</v>
       </c>
       <c r="H213" s="5" t="s">
-        <v>1881</v>
+        <v>1880</v>
       </c>
       <c r="I213" s="5" t="s">
         <v>133</v>
       </c>
       <c r="J213" s="5" t="s">
-        <v>1889</v>
+        <v>1888</v>
       </c>
       <c r="K213" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L213" s="6">
         <f t="shared" si="8"/>
@@ -28468,7 +28468,7 @@
       </c>
       <c r="J214" s="5"/>
       <c r="K214" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L214" s="6">
         <f t="shared" si="8"/>
@@ -28523,7 +28523,7 @@
         <v>57</v>
       </c>
       <c r="H215" s="5" t="s">
-        <v>1860</v>
+        <v>1859</v>
       </c>
       <c r="I215" s="5" t="s">
         <v>72</v>
@@ -28532,7 +28532,7 @@
         <v>765</v>
       </c>
       <c r="K215" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L215" s="6">
         <f t="shared" si="8"/>
@@ -28598,7 +28598,7 @@
       <c r="I216" s="5"/>
       <c r="J216" s="5"/>
       <c r="K216" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L216" s="6">
         <f t="shared" si="8"/>
@@ -28660,7 +28660,7 @@
         <v>49</v>
       </c>
       <c r="K217" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L217" s="6">
         <f t="shared" si="8"/>
@@ -28672,7 +28672,7 @@
       </c>
       <c r="N217" s="5"/>
       <c r="O217" s="5" t="s">
-        <v>1953</v>
+        <v>1952</v>
       </c>
       <c r="P217" s="5"/>
       <c r="Q217" s="5"/>
@@ -28696,7 +28696,7 @@
     </row>
     <row r="218" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A218" s="5" t="s">
-        <v>1941</v>
+        <v>1940</v>
       </c>
       <c r="B218" s="5"/>
       <c r="C218" s="5" t="s">
@@ -28715,16 +28715,16 @@
         <v>47</v>
       </c>
       <c r="H218" s="5" t="s">
-        <v>1942</v>
+        <v>1941</v>
       </c>
       <c r="I218" s="5" t="s">
         <v>192</v>
       </c>
       <c r="J218" s="5" t="s">
-        <v>1946</v>
+        <v>1945</v>
       </c>
       <c r="K218" s="18" t="s">
-        <v>1943</v>
+        <v>1942</v>
       </c>
       <c r="L218" s="6">
         <f t="shared" si="8"/>
@@ -28735,10 +28735,10 @@
         <v>Yes</v>
       </c>
       <c r="N218" s="5" t="s">
+        <v>1943</v>
+      </c>
+      <c r="O218" s="5" t="s">
         <v>1944</v>
-      </c>
-      <c r="O218" s="5" t="s">
-        <v>1945</v>
       </c>
       <c r="P218" s="5" t="s">
         <v>128</v>
@@ -28785,7 +28785,7 @@
         <v>57</v>
       </c>
       <c r="H219" s="5" t="s">
-        <v>1881</v>
+        <v>1880</v>
       </c>
       <c r="I219" s="5" t="s">
         <v>91</v>
@@ -28794,7 +28794,7 @@
         <v>78</v>
       </c>
       <c r="K219" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L219" s="6">
         <f t="shared" si="8"/>
@@ -28856,7 +28856,7 @@
       <c r="I220" s="5"/>
       <c r="J220" s="5"/>
       <c r="K220" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L220" s="6">
         <f t="shared" si="8"/>
@@ -28914,7 +28914,7 @@
       <c r="I221" s="5"/>
       <c r="J221" s="5"/>
       <c r="K221" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L221" s="6">
         <f t="shared" si="8"/>
@@ -28978,7 +28978,7 @@
       </c>
       <c r="J222" s="5"/>
       <c r="K222" s="18" t="s">
-        <v>1932</v>
+        <v>1931</v>
       </c>
       <c r="L222" s="6">
         <f t="shared" si="8"/>
@@ -29036,7 +29036,7 @@
         <v>91</v>
       </c>
       <c r="K223" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L223" s="6">
         <f t="shared" si="8"/>
@@ -29086,7 +29086,7 @@
       <c r="I224" s="5"/>
       <c r="J224" s="5"/>
       <c r="K224" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L224" s="6">
         <f t="shared" si="8"/>
@@ -29144,7 +29144,7 @@
       </c>
       <c r="J225" s="5"/>
       <c r="K225" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L225" s="6">
         <f t="shared" si="8"/>
@@ -29206,7 +29206,7 @@
       <c r="I226" s="5"/>
       <c r="J226" s="5"/>
       <c r="K226" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L226" s="6">
         <f t="shared" si="8"/>
@@ -29266,7 +29266,7 @@
       </c>
       <c r="J227" s="5"/>
       <c r="K227" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L227" s="6">
         <f t="shared" si="8"/>
@@ -29329,7 +29329,7 @@
         <v>57</v>
       </c>
       <c r="H228" s="5" t="s">
-        <v>1856</v>
+        <v>1855</v>
       </c>
       <c r="I228" s="5" t="s">
         <v>91</v>
@@ -29338,7 +29338,7 @@
         <v>797</v>
       </c>
       <c r="K228" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L228" s="6">
         <f t="shared" si="8"/>
@@ -29408,7 +29408,7 @@
         <v>804</v>
       </c>
       <c r="K229" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L229" s="6">
         <f t="shared" si="8"/>
@@ -29478,7 +29478,7 @@
       </c>
       <c r="J230" s="5"/>
       <c r="K230" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L230" s="6">
         <f t="shared" si="8"/>
@@ -29532,7 +29532,7 @@
       <c r="I231" s="5"/>
       <c r="J231" s="5"/>
       <c r="K231" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L231" s="6">
         <f t="shared" si="8"/>
@@ -29592,7 +29592,7 @@
         <v>814</v>
       </c>
       <c r="K232" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L232" s="6">
         <f t="shared" si="8"/>
@@ -29652,7 +29652,7 @@
       <c r="I233" s="5"/>
       <c r="J233" s="5"/>
       <c r="K233" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L233" s="6">
         <f t="shared" si="8"/>
@@ -29712,7 +29712,7 @@
       <c r="I234" s="5"/>
       <c r="J234" s="5"/>
       <c r="K234" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L234" s="6">
         <f t="shared" si="8"/>
@@ -29770,7 +29770,7 @@
       <c r="I235" s="5"/>
       <c r="J235" s="5"/>
       <c r="K235" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L235" s="6">
         <f t="shared" si="8"/>
@@ -29834,7 +29834,7 @@
         <v>72</v>
       </c>
       <c r="K236" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L236" s="6">
         <f t="shared" si="8"/>
@@ -29895,14 +29895,14 @@
         <v>47</v>
       </c>
       <c r="H237" s="5" t="s">
-        <v>1896</v>
+        <v>1895</v>
       </c>
       <c r="I237" s="5" t="s">
         <v>192</v>
       </c>
       <c r="J237" s="5"/>
       <c r="K237" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L237" s="6">
         <f t="shared" si="8"/>
@@ -29974,7 +29974,7 @@
       </c>
       <c r="J238" s="5"/>
       <c r="K238" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L238" s="6">
         <f t="shared" si="8"/>
@@ -30026,7 +30026,7 @@
       <c r="I239" s="5"/>
       <c r="J239" s="5"/>
       <c r="K239" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L239" s="6">
         <f t="shared" si="8"/>
@@ -30082,7 +30082,7 @@
       </c>
       <c r="J240" s="5"/>
       <c r="K240" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L240" s="6">
         <f t="shared" si="8"/>
@@ -30140,7 +30140,7 @@
       <c r="I241" s="5"/>
       <c r="J241" s="5"/>
       <c r="K241" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L241" s="6">
         <f t="shared" si="8"/>
@@ -30206,7 +30206,7 @@
       </c>
       <c r="J242" s="5"/>
       <c r="K242" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L242" s="6">
         <f t="shared" si="8"/>
@@ -30264,7 +30264,7 @@
       <c r="I243" s="5"/>
       <c r="J243" s="5"/>
       <c r="K243" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L243" s="6">
         <f t="shared" si="8"/>
@@ -30318,7 +30318,7 @@
       <c r="I244" s="5"/>
       <c r="J244" s="5"/>
       <c r="K244" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L244" s="6">
         <f t="shared" si="8"/>
@@ -30352,7 +30352,7 @@
     </row>
     <row r="245" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A245" s="5" t="s">
-        <v>1939</v>
+        <v>1938</v>
       </c>
       <c r="B245" s="5"/>
       <c r="C245" s="5" t="s">
@@ -30380,7 +30380,7 @@
         <v>78</v>
       </c>
       <c r="K245" s="18" t="s">
-        <v>1937</v>
+        <v>1936</v>
       </c>
       <c r="L245" s="6">
         <f t="shared" si="8"/>
@@ -30392,7 +30392,7 @@
       </c>
       <c r="N245" s="5"/>
       <c r="O245" s="5" t="s">
-        <v>1940</v>
+        <v>1939</v>
       </c>
       <c r="P245" s="5" t="s">
         <v>128</v>
@@ -30437,7 +30437,7 @@
         <v>57</v>
       </c>
       <c r="H246" s="5" t="s">
-        <v>1879</v>
+        <v>1878</v>
       </c>
       <c r="I246" s="5" t="s">
         <v>78</v>
@@ -30446,7 +30446,7 @@
         <v>71</v>
       </c>
       <c r="K246" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L246" s="6">
         <f t="shared" si="8"/>
@@ -30458,7 +30458,7 @@
       </c>
       <c r="N246" s="5"/>
       <c r="O246" s="5" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
       <c r="P246" s="5" t="s">
         <v>128</v>
@@ -30512,7 +30512,7 @@
         <v>72</v>
       </c>
       <c r="K247" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L247" s="6">
         <f t="shared" si="8"/>
@@ -30580,7 +30580,7 @@
       <c r="I248" s="5"/>
       <c r="J248" s="5"/>
       <c r="K248" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L248" s="6">
         <f t="shared" si="8"/>
@@ -30640,7 +30640,7 @@
         <v>78</v>
       </c>
       <c r="K249" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L249" s="6">
         <f t="shared" si="8"/>
@@ -30712,7 +30712,7 @@
         <v>72</v>
       </c>
       <c r="K250" s="18" t="s">
-        <v>1932</v>
+        <v>1931</v>
       </c>
       <c r="L250" s="6">
         <f t="shared" si="8"/>
@@ -30768,7 +30768,7 @@
       <c r="I251" s="5"/>
       <c r="J251" s="5"/>
       <c r="K251" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L251" s="6">
         <f t="shared" si="8"/>
@@ -30826,7 +30826,7 @@
       </c>
       <c r="J252" s="5"/>
       <c r="K252" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L252" s="6">
         <f t="shared" si="8"/>
@@ -30886,7 +30886,7 @@
         <v>71</v>
       </c>
       <c r="K253" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L253" s="6">
         <f t="shared" si="8"/>
@@ -30944,7 +30944,7 @@
       <c r="I254" s="5"/>
       <c r="J254" s="5"/>
       <c r="K254" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L254" s="6">
         <f t="shared" si="8"/>
@@ -31010,7 +31010,7 @@
       </c>
       <c r="J255" s="5"/>
       <c r="K255" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L255" s="6">
         <f t="shared" si="8"/>
@@ -31076,7 +31076,7 @@
       <c r="I256" s="5"/>
       <c r="J256" s="5"/>
       <c r="K256" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L256" s="6">
         <f t="shared" si="8"/>
@@ -31136,7 +31136,7 @@
       </c>
       <c r="J257" s="5"/>
       <c r="K257" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L257" s="6">
         <f t="shared" si="8"/>
@@ -31194,7 +31194,7 @@
       <c r="I258" s="5"/>
       <c r="J258" s="5"/>
       <c r="K258" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L258" s="6">
         <f t="shared" si="8"/>
@@ -31254,7 +31254,7 @@
       <c r="I259" s="5"/>
       <c r="J259" s="5"/>
       <c r="K259" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L259" s="6">
         <f t="shared" si="8"/>
@@ -31312,7 +31312,7 @@
       <c r="I260" s="5"/>
       <c r="J260" s="5"/>
       <c r="K260" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L260" s="6">
         <f t="shared" si="8"/>
@@ -31366,7 +31366,7 @@
       <c r="I261" s="5"/>
       <c r="J261" s="5"/>
       <c r="K261" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L261" s="6">
         <f t="shared" si="8"/>
@@ -31398,7 +31398,7 @@
     </row>
     <row r="262" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A262" s="5" t="s">
-        <v>1933</v>
+        <v>1932</v>
       </c>
       <c r="B262" s="5"/>
       <c r="C262" s="5" t="s">
@@ -31417,7 +31417,7 @@
         <v>57</v>
       </c>
       <c r="H262" s="5" t="s">
-        <v>1934</v>
+        <v>1933</v>
       </c>
       <c r="I262" s="5" t="s">
         <v>193</v>
@@ -31426,7 +31426,7 @@
         <v>78</v>
       </c>
       <c r="K262" s="18" t="s">
-        <v>1935</v>
+        <v>1934</v>
       </c>
       <c r="L262" s="6">
         <f t="shared" si="8"/>
@@ -31438,7 +31438,7 @@
       </c>
       <c r="N262" s="5"/>
       <c r="O262" s="5" t="s">
-        <v>1936</v>
+        <v>1935</v>
       </c>
       <c r="P262" s="5"/>
       <c r="Q262" s="5"/>
@@ -31488,7 +31488,7 @@
         <v>49</v>
       </c>
       <c r="K263" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L263" s="6">
         <f t="shared" si="8"/>
@@ -31554,7 +31554,7 @@
       </c>
       <c r="J264" s="5"/>
       <c r="K264" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L264" s="6">
         <f t="shared" si="8"/>
@@ -31608,7 +31608,7 @@
       <c r="I265" s="5"/>
       <c r="J265" s="5"/>
       <c r="K265" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L265" s="6">
         <f t="shared" si="8"/>
@@ -31660,7 +31660,7 @@
       <c r="I266" s="5"/>
       <c r="J266" s="5"/>
       <c r="K266" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L266" s="6">
         <f t="shared" si="8"/>
@@ -31716,7 +31716,7 @@
       </c>
       <c r="J267" s="5"/>
       <c r="K267" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L267" s="6">
         <f t="shared" si="8"/>
@@ -31772,7 +31772,7 @@
       <c r="I268" s="5"/>
       <c r="J268" s="5"/>
       <c r="K268" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L268" s="6">
         <f t="shared" si="8"/>
@@ -31822,7 +31822,7 @@
       </c>
       <c r="J269" s="5"/>
       <c r="K269" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L269" s="6">
         <f t="shared" si="8"/>
@@ -31874,7 +31874,7 @@
       </c>
       <c r="J270" s="5"/>
       <c r="K270" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L270" s="6">
         <f t="shared" si="8"/>
@@ -31926,7 +31926,7 @@
       </c>
       <c r="J271" s="5"/>
       <c r="K271" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L271" s="6">
         <f t="shared" si="8"/>
@@ -31990,7 +31990,7 @@
         <v>78</v>
       </c>
       <c r="K272" s="18" t="s">
-        <v>1935</v>
+        <v>1934</v>
       </c>
       <c r="L272" s="6">
         <f t="shared" si="8"/>
@@ -32056,7 +32056,7 @@
         <v>78</v>
       </c>
       <c r="K273" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L273" s="6">
         <f t="shared" si="8"/>
@@ -32114,7 +32114,7 @@
       <c r="I274" s="5"/>
       <c r="J274" s="5"/>
       <c r="K274" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L274" s="6">
         <f t="shared" si="8"/>
@@ -32166,7 +32166,7 @@
       <c r="I275" s="5"/>
       <c r="J275" s="5"/>
       <c r="K275" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L275" s="6">
         <f t="shared" ref="L275:L338" si="10">IF(A275="","",COUNTA(D275:F275)+COUNTA(G275:G275)+COUNTA(H275:H275)+COUNTA(I275:I275))</f>
@@ -32230,7 +32230,7 @@
       </c>
       <c r="J276" s="5"/>
       <c r="K276" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L276" s="6">
         <f t="shared" si="10"/>
@@ -32296,7 +32296,7 @@
       <c r="I277" s="5"/>
       <c r="J277" s="5"/>
       <c r="K277" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L277" s="6">
         <f t="shared" si="10"/>
@@ -32350,7 +32350,7 @@
       </c>
       <c r="J278" s="5"/>
       <c r="K278" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L278" s="6">
         <f t="shared" si="10"/>
@@ -32408,7 +32408,7 @@
       <c r="I279" s="5"/>
       <c r="J279" s="5"/>
       <c r="K279" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L279" s="6">
         <f t="shared" si="10"/>
@@ -32474,7 +32474,7 @@
       </c>
       <c r="J280" s="5"/>
       <c r="K280" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L280" s="6">
         <f t="shared" si="10"/>
@@ -32538,7 +32538,7 @@
       <c r="I281" s="5"/>
       <c r="J281" s="5"/>
       <c r="K281" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L281" s="6">
         <f t="shared" si="10"/>
@@ -32596,7 +32596,7 @@
       <c r="I282" s="5"/>
       <c r="J282" s="5"/>
       <c r="K282" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L282" s="6">
         <f t="shared" si="10"/>
@@ -32653,14 +32653,14 @@
         <v>57</v>
       </c>
       <c r="H283" s="5" t="s">
-        <v>1856</v>
+        <v>1855</v>
       </c>
       <c r="I283" s="5" t="s">
         <v>123</v>
       </c>
       <c r="J283" s="5"/>
       <c r="K283" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L283" s="6">
         <f t="shared" si="10"/>
@@ -32732,7 +32732,7 @@
       </c>
       <c r="J284" s="5"/>
       <c r="K284" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L284" s="6">
         <f t="shared" si="10"/>
@@ -32792,7 +32792,7 @@
       <c r="I285" s="5"/>
       <c r="J285" s="5"/>
       <c r="K285" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L285" s="6">
         <f t="shared" si="10"/>
@@ -32850,7 +32850,7 @@
       </c>
       <c r="J286" s="5"/>
       <c r="K286" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L286" s="6">
         <f t="shared" si="10"/>
@@ -32908,7 +32908,7 @@
       <c r="I287" s="5"/>
       <c r="J287" s="5"/>
       <c r="K287" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L287" s="6">
         <f t="shared" si="10"/>
@@ -32958,7 +32958,7 @@
       <c r="I288" s="5"/>
       <c r="J288" s="5"/>
       <c r="K288" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L288" s="6">
         <f t="shared" si="10"/>
@@ -33010,7 +33010,7 @@
       <c r="I289" s="5"/>
       <c r="J289" s="5"/>
       <c r="K289" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L289" s="6">
         <f t="shared" si="10"/>
@@ -33060,7 +33060,7 @@
       <c r="I290" s="5"/>
       <c r="J290" s="5"/>
       <c r="K290" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L290" s="6">
         <f t="shared" si="10"/>
@@ -33114,7 +33114,7 @@
         <v>192</v>
       </c>
       <c r="K291" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L291" s="6">
         <f t="shared" si="10"/>
@@ -33176,7 +33176,7 @@
       </c>
       <c r="J292" s="5"/>
       <c r="K292" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L292" s="6">
         <f t="shared" si="10"/>
@@ -33226,7 +33226,7 @@
       <c r="I293" s="5"/>
       <c r="J293" s="5"/>
       <c r="K293" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L293" s="6">
         <f t="shared" si="10"/>
@@ -33280,7 +33280,7 @@
       <c r="I294" s="5"/>
       <c r="J294" s="5"/>
       <c r="K294" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L294" s="6">
         <f t="shared" si="10"/>
@@ -33334,7 +33334,7 @@
       <c r="I295" s="5"/>
       <c r="J295" s="5"/>
       <c r="K295" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L295" s="6">
         <f t="shared" si="10"/>
@@ -33384,7 +33384,7 @@
       <c r="I296" s="5"/>
       <c r="J296" s="5"/>
       <c r="K296" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L296" s="6">
         <f t="shared" si="10"/>
@@ -33438,7 +33438,7 @@
         <v>59</v>
       </c>
       <c r="K297" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L297" s="6">
         <f t="shared" si="10"/>
@@ -33486,7 +33486,7 @@
       <c r="I298" s="5"/>
       <c r="J298" s="5"/>
       <c r="K298" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L298" s="6">
         <f t="shared" si="10"/>
@@ -33532,7 +33532,7 @@
       </c>
       <c r="J299" s="5"/>
       <c r="K299" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L299" s="6">
         <f t="shared" si="10"/>
@@ -33600,7 +33600,7 @@
         <v>72</v>
       </c>
       <c r="K300" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L300" s="6">
         <f t="shared" si="10"/>
@@ -33660,7 +33660,7 @@
       </c>
       <c r="J301" s="5"/>
       <c r="K301" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L301" s="6">
         <f t="shared" si="10"/>
@@ -33724,7 +33724,7 @@
       </c>
       <c r="J302" s="5"/>
       <c r="K302" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L302" s="6">
         <f t="shared" si="10"/>
@@ -33790,7 +33790,7 @@
       </c>
       <c r="J303" s="5"/>
       <c r="K303" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L303" s="6">
         <f t="shared" si="10"/>
@@ -33853,7 +33853,7 @@
         <v>57</v>
       </c>
       <c r="H304" s="5" t="s">
-        <v>1857</v>
+        <v>1856</v>
       </c>
       <c r="I304" s="5" t="s">
         <v>119</v>
@@ -33862,7 +33862,7 @@
         <v>765</v>
       </c>
       <c r="K304" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L304" s="6">
         <f t="shared" si="10"/>
@@ -33926,7 +33926,7 @@
       <c r="I305" s="5"/>
       <c r="J305" s="5"/>
       <c r="K305" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L305" s="6">
         <f t="shared" si="10"/>
@@ -33992,7 +33992,7 @@
         <v>157</v>
       </c>
       <c r="K306" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L306" s="6">
         <f t="shared" si="10"/>
@@ -34054,7 +34054,7 @@
       <c r="I307" s="5"/>
       <c r="J307" s="5"/>
       <c r="K307" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L307" s="6">
         <f t="shared" si="10"/>
@@ -34104,7 +34104,7 @@
       <c r="I308" s="5"/>
       <c r="J308" s="5"/>
       <c r="K308" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L308" s="6">
         <f t="shared" si="10"/>
@@ -34165,7 +34165,7 @@
         <v>123</v>
       </c>
       <c r="K309" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L309" s="6">
         <f t="shared" si="10"/>
@@ -34237,7 +34237,7 @@
         <v>1655</v>
       </c>
       <c r="K310" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L310" s="6">
         <f t="shared" si="10"/>
@@ -34301,7 +34301,7 @@
       <c r="I311" s="5"/>
       <c r="J311" s="5"/>
       <c r="K311" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L311" s="6">
         <f t="shared" si="10"/>
@@ -34361,7 +34361,7 @@
         <v>1002</v>
       </c>
       <c r="K312" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L312" s="6">
         <f t="shared" si="10"/>
@@ -34421,7 +34421,7 @@
       </c>
       <c r="J313" s="5"/>
       <c r="K313" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L313" s="6">
         <f t="shared" si="10"/>
@@ -34475,7 +34475,7 @@
       </c>
       <c r="J314" s="5"/>
       <c r="K314" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L314" s="6">
         <f t="shared" si="10"/>
@@ -34535,7 +34535,7 @@
       </c>
       <c r="J315" s="5"/>
       <c r="K315" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L315" s="6">
         <f t="shared" si="10"/>
@@ -34597,7 +34597,7 @@
         <v>91</v>
       </c>
       <c r="K316" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L316" s="6">
         <f t="shared" si="10"/>
@@ -34667,7 +34667,7 @@
       </c>
       <c r="J317" s="5"/>
       <c r="K317" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L317" s="6">
         <f t="shared" si="10"/>
@@ -34723,7 +34723,7 @@
       <c r="I318" s="5"/>
       <c r="J318" s="5"/>
       <c r="K318" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L318" s="6">
         <f t="shared" si="10"/>
@@ -34773,7 +34773,7 @@
       </c>
       <c r="J319" s="5"/>
       <c r="K319" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L319" s="6">
         <f t="shared" si="10"/>
@@ -34831,7 +34831,7 @@
         <v>91</v>
       </c>
       <c r="K320" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L320" s="6">
         <f t="shared" si="10"/>
@@ -34887,7 +34887,7 @@
       </c>
       <c r="J321" s="5"/>
       <c r="K321" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L321" s="6">
         <f t="shared" si="10"/>
@@ -34943,7 +34943,7 @@
       <c r="I322" s="5"/>
       <c r="J322" s="5"/>
       <c r="K322" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L322" s="6">
         <f t="shared" si="10"/>
@@ -34975,10 +34975,10 @@
     </row>
     <row r="323" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A323" s="5" t="s">
+        <v>1864</v>
+      </c>
+      <c r="B323" s="5" t="s">
         <v>1865</v>
-      </c>
-      <c r="B323" s="5" t="s">
-        <v>1866</v>
       </c>
       <c r="C323" s="5" t="s">
         <v>128</v>
@@ -34996,16 +34996,16 @@
         <v>57</v>
       </c>
       <c r="H323" s="5" t="s">
-        <v>1860</v>
+        <v>1859</v>
       </c>
       <c r="I323" s="5" t="s">
         <v>123</v>
       </c>
       <c r="J323" s="5" t="s">
-        <v>1868</v>
+        <v>1867</v>
       </c>
       <c r="K323" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L323" s="6">
         <f t="shared" si="10"/>
@@ -35016,16 +35016,16 @@
         <v>Yes</v>
       </c>
       <c r="N323" s="5" t="s">
+        <v>1868</v>
+      </c>
+      <c r="O323" s="5" t="s">
         <v>1869</v>
-      </c>
-      <c r="O323" s="5" t="s">
-        <v>1870</v>
       </c>
       <c r="P323" s="5" t="s">
         <v>128</v>
       </c>
       <c r="Q323" s="5" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
       <c r="R323" s="5"/>
       <c r="S323" s="5"/>
@@ -35038,7 +35038,7 @@
         <v>51</v>
       </c>
       <c r="X323" s="5" t="s">
-        <v>1860</v>
+        <v>1859</v>
       </c>
       <c r="Y323" s="5"/>
       <c r="Z323" s="5" t="s">
@@ -35075,7 +35075,7 @@
         <v>59</v>
       </c>
       <c r="K324" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L324" s="6">
         <f t="shared" si="10"/>
@@ -35115,7 +35115,7 @@
     </row>
     <row r="325" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A325" s="5" t="s">
-        <v>1909</v>
+        <v>1908</v>
       </c>
       <c r="B325" s="5"/>
       <c r="C325" s="5" t="s">
@@ -35140,10 +35140,10 @@
         <v>192</v>
       </c>
       <c r="J325" s="5" t="s">
-        <v>1911</v>
+        <v>1910</v>
       </c>
       <c r="K325" s="5" t="s">
-        <v>1882</v>
+        <v>1881</v>
       </c>
       <c r="L325" s="6">
         <f t="shared" si="10"/>
@@ -35154,16 +35154,16 @@
         <v>Yes</v>
       </c>
       <c r="N325" s="5" t="s">
-        <v>1910</v>
+        <v>1909</v>
       </c>
       <c r="O325" s="5" t="s">
-        <v>1912</v>
+        <v>1911</v>
       </c>
       <c r="P325" s="5" t="s">
         <v>128</v>
       </c>
       <c r="Q325" s="5" t="s">
-        <v>1914</v>
+        <v>1913</v>
       </c>
       <c r="R325" s="5"/>
       <c r="S325" s="5"/>
@@ -35176,7 +35176,7 @@
         <v>51</v>
       </c>
       <c r="X325" s="5" t="s">
-        <v>1913</v>
+        <v>1912</v>
       </c>
       <c r="Y325" s="5" t="s">
         <v>57</v>
@@ -35201,7 +35201,7 @@
       <c r="I326" s="5"/>
       <c r="J326" s="5"/>
       <c r="K326" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L326" s="6">
         <f t="shared" si="10"/>
@@ -35261,7 +35261,7 @@
         <v>119</v>
       </c>
       <c r="K327" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L327" s="6">
         <f t="shared" si="10"/>
@@ -35331,7 +35331,7 @@
       </c>
       <c r="J328" s="5"/>
       <c r="K328" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L328" s="6">
         <f t="shared" si="10"/>
@@ -35391,7 +35391,7 @@
       <c r="I329" s="5"/>
       <c r="J329" s="5"/>
       <c r="K329" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L329" s="6">
         <f t="shared" si="10"/>
@@ -35447,7 +35447,7 @@
       <c r="I330" s="5"/>
       <c r="J330" s="5"/>
       <c r="K330" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L330" s="6">
         <f t="shared" si="10"/>
@@ -35501,7 +35501,7 @@
       <c r="I331" s="5"/>
       <c r="J331" s="5"/>
       <c r="K331" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L331" s="6">
         <f t="shared" si="10"/>
@@ -35565,7 +35565,7 @@
       </c>
       <c r="J332" s="5"/>
       <c r="K332" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L332" s="6">
         <f t="shared" si="10"/>
@@ -35635,7 +35635,7 @@
       </c>
       <c r="J333" s="5"/>
       <c r="K333" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L333" s="6">
         <f t="shared" si="10"/>
@@ -35707,7 +35707,7 @@
       </c>
       <c r="J334" s="5"/>
       <c r="K334" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L334" s="6">
         <f t="shared" si="10"/>
@@ -35767,7 +35767,7 @@
       </c>
       <c r="J335" s="5"/>
       <c r="K335" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L335" s="6">
         <f t="shared" si="10"/>
@@ -35830,7 +35830,7 @@
         <v>47</v>
       </c>
       <c r="H336" s="19" t="s">
-        <v>1934</v>
+        <v>1933</v>
       </c>
       <c r="I336" s="5" t="s">
         <v>49</v>
@@ -35839,7 +35839,7 @@
         <v>78</v>
       </c>
       <c r="K336" s="18" t="s">
-        <v>1937</v>
+        <v>1936</v>
       </c>
       <c r="L336" s="6">
         <f t="shared" si="10"/>
@@ -35851,7 +35851,7 @@
       </c>
       <c r="N336" s="5"/>
       <c r="O336" s="5" t="s">
-        <v>1938</v>
+        <v>1937</v>
       </c>
       <c r="P336" s="5" t="s">
         <v>43</v>
@@ -35909,7 +35909,7 @@
         <v>178</v>
       </c>
       <c r="K337" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L337" s="6">
         <f t="shared" si="10"/>
@@ -35977,7 +35977,7 @@
       </c>
       <c r="J338" s="5"/>
       <c r="K338" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L338" s="6">
         <f t="shared" si="10"/>
@@ -36039,7 +36039,7 @@
       <c r="I339" s="5"/>
       <c r="J339" s="5"/>
       <c r="K339" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L339" s="6">
         <f t="shared" ref="L339:L402" si="12">IF(A339="","",COUNTA(D339:F339)+COUNTA(G339:G339)+COUNTA(H339:H339)+COUNTA(I339:I339))</f>
@@ -36050,7 +36050,7 @@
         <v>No</v>
       </c>
       <c r="N339" s="5" t="s">
-        <v>1951</v>
+        <v>1950</v>
       </c>
       <c r="O339" s="5" t="s">
         <v>1069</v>
@@ -36079,7 +36079,7 @@
     </row>
     <row r="340" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A340" s="5" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="B340" s="5"/>
       <c r="C340" s="5" t="s">
@@ -36098,7 +36098,7 @@
         <v>57</v>
       </c>
       <c r="H340" s="5" t="s">
-        <v>1934</v>
+        <v>1933</v>
       </c>
       <c r="I340" s="5" t="s">
         <v>133</v>
@@ -36107,7 +36107,7 @@
         <v>157</v>
       </c>
       <c r="K340" s="18" t="s">
-        <v>1943</v>
+        <v>1942</v>
       </c>
       <c r="L340" s="6">
         <f t="shared" si="12"/>
@@ -36119,7 +36119,7 @@
       </c>
       <c r="N340" s="5"/>
       <c r="O340" s="5" t="s">
-        <v>1950</v>
+        <v>1949</v>
       </c>
       <c r="P340" s="5" t="s">
         <v>43</v>
@@ -36177,7 +36177,7 @@
         <v>72</v>
       </c>
       <c r="K341" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L341" s="6">
         <f t="shared" si="12"/>
@@ -36245,7 +36245,7 @@
         <v>119</v>
       </c>
       <c r="K342" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L342" s="6">
         <f t="shared" si="12"/>
@@ -36301,7 +36301,7 @@
       <c r="I343" s="5"/>
       <c r="J343" s="5"/>
       <c r="K343" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L343" s="6">
         <f t="shared" si="12"/>
@@ -36355,7 +36355,7 @@
       <c r="I344" s="5"/>
       <c r="J344" s="5"/>
       <c r="K344" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L344" s="6">
         <f t="shared" si="12"/>
@@ -36421,7 +36421,7 @@
       </c>
       <c r="J345" s="5"/>
       <c r="K345" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L345" s="6">
         <f t="shared" si="12"/>
@@ -36485,7 +36485,7 @@
       <c r="I346" s="5"/>
       <c r="J346" s="5"/>
       <c r="K346" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L346" s="6">
         <f t="shared" si="12"/>
@@ -36549,7 +36549,7 @@
         <v>91</v>
       </c>
       <c r="K347" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L347" s="6">
         <f t="shared" si="12"/>
@@ -36605,7 +36605,7 @@
       <c r="I348" s="5"/>
       <c r="J348" s="5"/>
       <c r="K348" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L348" s="6">
         <f t="shared" si="12"/>
@@ -36661,7 +36661,7 @@
         <v>91</v>
       </c>
       <c r="K349" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L349" s="6">
         <f t="shared" si="12"/>
@@ -36715,7 +36715,7 @@
       <c r="I350" s="5"/>
       <c r="J350" s="5"/>
       <c r="K350" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L350" s="6">
         <f t="shared" si="12"/>
@@ -36767,7 +36767,7 @@
       <c r="I351" s="5"/>
       <c r="J351" s="5"/>
       <c r="K351" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L351" s="6">
         <f t="shared" si="12"/>
@@ -36802,7 +36802,7 @@
         <v>1100</v>
       </c>
       <c r="B352" s="5" t="s">
-        <v>1855</v>
+        <v>1854</v>
       </c>
       <c r="C352" s="5" t="s">
         <v>128</v>
@@ -36829,7 +36829,7 @@
         <v>133</v>
       </c>
       <c r="K352" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L352" s="6">
         <f t="shared" si="12"/>
@@ -36883,7 +36883,7 @@
       </c>
       <c r="J353" s="5"/>
       <c r="K353" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L353" s="6">
         <f t="shared" si="12"/>
@@ -36936,7 +36936,7 @@
         <v>57</v>
       </c>
       <c r="H354" s="5" t="s">
-        <v>1858</v>
+        <v>1857</v>
       </c>
       <c r="I354" s="5" t="s">
         <v>91</v>
@@ -36945,7 +36945,7 @@
         <v>49</v>
       </c>
       <c r="K354" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L354" s="6">
         <f t="shared" si="12"/>
@@ -36956,10 +36956,10 @@
         <v>Yes</v>
       </c>
       <c r="N354" s="5" t="s">
-        <v>1888</v>
+        <v>1887</v>
       </c>
       <c r="O354" s="5" t="s">
-        <v>1887</v>
+        <v>1886</v>
       </c>
       <c r="P354" s="5" t="s">
         <v>319</v>
@@ -37013,7 +37013,7 @@
       </c>
       <c r="J355" s="5"/>
       <c r="K355" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L355" s="6">
         <f t="shared" si="12"/>
@@ -37071,7 +37071,7 @@
       <c r="I356" s="5"/>
       <c r="J356" s="5"/>
       <c r="K356" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L356" s="6">
         <f t="shared" si="12"/>
@@ -37125,7 +37125,7 @@
       </c>
       <c r="J357" s="5"/>
       <c r="K357" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L357" s="6">
         <f t="shared" si="12"/>
@@ -37187,7 +37187,7 @@
         <v>49</v>
       </c>
       <c r="K358" s="18" t="s">
-        <v>1932</v>
+        <v>1931</v>
       </c>
       <c r="L358" s="6">
         <f t="shared" si="12"/>
@@ -37249,7 +37249,7 @@
       <c r="I359" s="5"/>
       <c r="J359" s="5"/>
       <c r="K359" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L359" s="6">
         <f t="shared" si="12"/>
@@ -37307,7 +37307,7 @@
       <c r="I360" s="5"/>
       <c r="J360" s="5"/>
       <c r="K360" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L360" s="6">
         <f t="shared" si="12"/>
@@ -37369,7 +37369,7 @@
         <v>71</v>
       </c>
       <c r="K361" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L361" s="6">
         <f t="shared" si="12"/>
@@ -37381,7 +37381,7 @@
       </c>
       <c r="N361" s="5"/>
       <c r="O361" s="5" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="P361" s="5" t="s">
         <v>43</v>
@@ -37425,7 +37425,7 @@
       <c r="I362" s="5"/>
       <c r="J362" s="5"/>
       <c r="K362" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L362" s="6">
         <f t="shared" si="12"/>
@@ -37485,7 +37485,7 @@
       </c>
       <c r="J363" s="5"/>
       <c r="K363" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L363" s="6">
         <f t="shared" si="12"/>
@@ -37541,7 +37541,7 @@
       <c r="I364" s="5"/>
       <c r="J364" s="5"/>
       <c r="K364" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L364" s="6">
         <f t="shared" si="12"/>
@@ -37601,7 +37601,7 @@
         <v>765</v>
       </c>
       <c r="K365" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L365" s="6">
         <f t="shared" si="12"/>
@@ -37659,7 +37659,7 @@
       <c r="I366" s="5"/>
       <c r="J366" s="5"/>
       <c r="K366" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L366" s="6">
         <f t="shared" si="12"/>
@@ -37723,7 +37723,7 @@
         <v>71</v>
       </c>
       <c r="K367" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L367" s="6">
         <f t="shared" si="12"/>
@@ -37781,7 +37781,7 @@
       <c r="I368" s="5"/>
       <c r="J368" s="5"/>
       <c r="K368" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L368" s="6">
         <f t="shared" si="12"/>
@@ -37831,7 +37831,7 @@
       <c r="I369" s="5"/>
       <c r="J369" s="5"/>
       <c r="K369" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L369" s="6">
         <f t="shared" si="12"/>
@@ -37897,7 +37897,7 @@
         <v>71</v>
       </c>
       <c r="K370" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L370" s="6">
         <f t="shared" si="12"/>
@@ -37955,7 +37955,7 @@
       <c r="I371" s="5"/>
       <c r="J371" s="5"/>
       <c r="K371" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L371" s="6">
         <f t="shared" si="12"/>
@@ -38015,7 +38015,7 @@
         <v>192</v>
       </c>
       <c r="K372" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L372" s="6">
         <f t="shared" si="12"/>
@@ -38071,7 +38071,7 @@
       <c r="I373" s="5"/>
       <c r="J373" s="5"/>
       <c r="K373" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L373" s="6">
         <f t="shared" si="12"/>
@@ -38131,7 +38131,7 @@
         <v>193</v>
       </c>
       <c r="K374" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L374" s="6">
         <f t="shared" si="12"/>
@@ -38201,7 +38201,7 @@
       </c>
       <c r="J375" s="5"/>
       <c r="K375" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L375" s="6">
         <f t="shared" si="12"/>
@@ -38263,7 +38263,7 @@
         <v>193</v>
       </c>
       <c r="K376" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L376" s="6">
         <f t="shared" si="12"/>
@@ -38327,7 +38327,7 @@
       </c>
       <c r="J377" s="5"/>
       <c r="K377" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L377" s="6">
         <f t="shared" si="12"/>
@@ -38397,7 +38397,7 @@
         <v>91</v>
       </c>
       <c r="K378" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L378" s="6">
         <f t="shared" si="12"/>
@@ -38453,7 +38453,7 @@
       <c r="I379" s="5"/>
       <c r="J379" s="5"/>
       <c r="K379" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L379" s="6">
         <f t="shared" si="12"/>
@@ -38505,7 +38505,7 @@
       <c r="I380" s="5"/>
       <c r="J380" s="5"/>
       <c r="K380" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L380" s="6">
         <f t="shared" si="12"/>
@@ -38559,7 +38559,7 @@
       </c>
       <c r="J381" s="5"/>
       <c r="K381" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L381" s="6">
         <f t="shared" si="12"/>
@@ -38617,7 +38617,7 @@
       </c>
       <c r="J382" s="5"/>
       <c r="K382" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L382" s="6">
         <f t="shared" si="12"/>
@@ -38676,14 +38676,14 @@
         <v>57</v>
       </c>
       <c r="H383" s="5" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="I383" s="5" t="s">
         <v>49</v>
       </c>
       <c r="J383" s="5"/>
       <c r="K383" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L383" s="6">
         <f t="shared" si="12"/>
@@ -38745,7 +38745,7 @@
         <v>91</v>
       </c>
       <c r="K384" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L384" s="6">
         <f t="shared" si="12"/>
@@ -38805,7 +38805,7 @@
       <c r="I385" s="5"/>
       <c r="J385" s="5"/>
       <c r="K385" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L385" s="6">
         <f t="shared" si="12"/>
@@ -38865,7 +38865,7 @@
         <v>123</v>
       </c>
       <c r="K386" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L386" s="6">
         <f t="shared" si="12"/>
@@ -38931,7 +38931,7 @@
         <v>193</v>
       </c>
       <c r="K387" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L387" s="6">
         <f t="shared" si="12"/>
@@ -38989,7 +38989,7 @@
       <c r="I388" s="5"/>
       <c r="J388" s="5"/>
       <c r="K388" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L388" s="6">
         <f t="shared" si="12"/>
@@ -39053,7 +39053,7 @@
         <v>192</v>
       </c>
       <c r="K389" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L389" s="6">
         <f t="shared" si="12"/>
@@ -39123,7 +39123,7 @@
       </c>
       <c r="J390" s="5"/>
       <c r="K390" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L390" s="6">
         <f t="shared" si="12"/>
@@ -39193,7 +39193,7 @@
       </c>
       <c r="J391" s="5"/>
       <c r="K391" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L391" s="6">
         <f t="shared" si="12"/>
@@ -39247,7 +39247,7 @@
       <c r="I392" s="5"/>
       <c r="J392" s="5"/>
       <c r="K392" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L392" s="6">
         <f t="shared" si="12"/>
@@ -39301,7 +39301,7 @@
       </c>
       <c r="J393" s="5"/>
       <c r="K393" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L393" s="6">
         <f t="shared" si="12"/>
@@ -39355,7 +39355,7 @@
       <c r="I394" s="5"/>
       <c r="J394" s="5"/>
       <c r="K394" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L394" s="6">
         <f t="shared" si="12"/>
@@ -39396,7 +39396,7 @@
         <v>1200</v>
       </c>
       <c r="B395" s="5" t="s">
-        <v>1895</v>
+        <v>1894</v>
       </c>
       <c r="C395" s="5" t="s">
         <v>43</v>
@@ -39421,7 +39421,7 @@
       </c>
       <c r="J395" s="5"/>
       <c r="K395" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L395" s="6">
         <f t="shared" si="12"/>
@@ -39486,14 +39486,14 @@
         <v>57</v>
       </c>
       <c r="H396" s="5" t="s">
-        <v>1859</v>
+        <v>1858</v>
       </c>
       <c r="I396" s="5" t="s">
         <v>192</v>
       </c>
       <c r="J396" s="5"/>
       <c r="K396" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L396" s="6">
         <f t="shared" si="12"/>
@@ -39555,7 +39555,7 @@
       </c>
       <c r="J397" s="5"/>
       <c r="K397" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L397" s="6">
         <f t="shared" si="12"/>
@@ -39611,7 +39611,7 @@
       <c r="I398" s="5"/>
       <c r="J398" s="5"/>
       <c r="K398" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L398" s="6">
         <f t="shared" si="12"/>
@@ -39665,7 +39665,7 @@
       <c r="I399" s="5"/>
       <c r="J399" s="5"/>
       <c r="K399" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L399" s="6">
         <f t="shared" si="12"/>
@@ -39725,7 +39725,7 @@
       <c r="I400" s="5"/>
       <c r="J400" s="5"/>
       <c r="K400" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L400" s="6">
         <f t="shared" si="12"/>
@@ -39787,7 +39787,7 @@
       </c>
       <c r="J401" s="5"/>
       <c r="K401" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L401" s="6">
         <f t="shared" si="12"/>
@@ -39845,7 +39845,7 @@
       <c r="I402" s="5"/>
       <c r="J402" s="5"/>
       <c r="K402" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L402" s="6">
         <f t="shared" si="12"/>
@@ -39907,7 +39907,7 @@
       <c r="I403" s="5"/>
       <c r="J403" s="5"/>
       <c r="K403" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L403" s="6">
         <f t="shared" ref="L403:L466" si="14">IF(A403="","",COUNTA(D403:F403)+COUNTA(G403:G403)+COUNTA(H403:H403)+COUNTA(I403:I403))</f>
@@ -39963,7 +39963,7 @@
       <c r="I404" s="5"/>
       <c r="J404" s="5"/>
       <c r="K404" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L404" s="6">
         <f t="shared" si="14"/>
@@ -40027,7 +40027,7 @@
         <v>71</v>
       </c>
       <c r="K405" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L405" s="6">
         <f t="shared" si="14"/>
@@ -40085,7 +40085,7 @@
       <c r="I406" s="5"/>
       <c r="J406" s="5"/>
       <c r="K406" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L406" s="6">
         <f t="shared" si="14"/>
@@ -40133,7 +40133,7 @@
       <c r="I407" s="5"/>
       <c r="J407" s="5"/>
       <c r="K407" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L407" s="6">
         <f t="shared" si="14"/>
@@ -40181,7 +40181,7 @@
       <c r="I408" s="5"/>
       <c r="J408" s="5"/>
       <c r="K408" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L408" s="6">
         <f t="shared" si="14"/>
@@ -40231,7 +40231,7 @@
       <c r="I409" s="5"/>
       <c r="J409" s="5"/>
       <c r="K409" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L409" s="6">
         <f t="shared" si="14"/>
@@ -40277,7 +40277,7 @@
       <c r="I410" s="5"/>
       <c r="J410" s="5"/>
       <c r="K410" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L410" s="6">
         <f t="shared" si="14"/>
@@ -40327,7 +40327,7 @@
       <c r="I411" s="5"/>
       <c r="J411" s="5"/>
       <c r="K411" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L411" s="6">
         <f t="shared" si="14"/>
@@ -40377,7 +40377,7 @@
       <c r="I412" s="5"/>
       <c r="J412" s="5"/>
       <c r="K412" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L412" s="6">
         <f t="shared" si="14"/>
@@ -40429,7 +40429,7 @@
       <c r="I413" s="5"/>
       <c r="J413" s="5"/>
       <c r="K413" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L413" s="6">
         <f t="shared" si="14"/>
@@ -40473,7 +40473,7 @@
     </row>
     <row r="414" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A414" s="5" t="s">
-        <v>1872</v>
+        <v>1871</v>
       </c>
       <c r="B414" s="5"/>
       <c r="C414" s="5" t="s">
@@ -40492,16 +40492,16 @@
         <v>57</v>
       </c>
       <c r="H414" s="5" t="s">
-        <v>1860</v>
+        <v>1859</v>
       </c>
       <c r="I414" s="5" t="s">
         <v>119</v>
       </c>
       <c r="J414" s="5" t="s">
-        <v>1873</v>
+        <v>1872</v>
       </c>
       <c r="K414" s="18" t="s">
-        <v>1882</v>
+        <v>1881</v>
       </c>
       <c r="L414" s="6">
         <f t="shared" si="14"/>
@@ -40512,10 +40512,10 @@
         <v>Yes</v>
       </c>
       <c r="N414" s="5" t="s">
-        <v>1875</v>
+        <v>1874</v>
       </c>
       <c r="O414" s="5" t="s">
-        <v>1874</v>
+        <v>1873</v>
       </c>
       <c r="P414" s="5" t="s">
         <v>43</v>
@@ -40559,7 +40559,7 @@
       <c r="I415" s="5"/>
       <c r="J415" s="5"/>
       <c r="K415" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L415" s="6">
         <f t="shared" si="14"/>
@@ -40613,7 +40613,7 @@
       </c>
       <c r="J416" s="5"/>
       <c r="K416" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L416" s="6">
         <f t="shared" si="14"/>
@@ -40675,7 +40675,7 @@
       </c>
       <c r="J417" s="5"/>
       <c r="K417" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L417" s="6">
         <f t="shared" si="14"/>
@@ -40735,7 +40735,7 @@
       <c r="I418" s="5"/>
       <c r="J418" s="5"/>
       <c r="K418" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L418" s="6">
         <f t="shared" si="14"/>
@@ -40789,7 +40789,7 @@
       </c>
       <c r="J419" s="5"/>
       <c r="K419" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L419" s="6">
         <f t="shared" si="14"/>
@@ -40845,7 +40845,7 @@
       <c r="I420" s="5"/>
       <c r="J420" s="5"/>
       <c r="K420" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L420" s="6">
         <f t="shared" si="14"/>
@@ -40895,7 +40895,7 @@
       <c r="I421" s="5"/>
       <c r="J421" s="5"/>
       <c r="K421" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L421" s="6">
         <f t="shared" si="14"/>
@@ -40959,7 +40959,7 @@
       </c>
       <c r="J422" s="5"/>
       <c r="K422" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L422" s="6">
         <f t="shared" si="14"/>
@@ -41025,7 +41025,7 @@
       </c>
       <c r="J423" s="5"/>
       <c r="K423" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L423" s="6">
         <f t="shared" si="14"/>
@@ -41037,7 +41037,7 @@
       </c>
       <c r="N423" s="5"/>
       <c r="O423" s="5" t="s">
-        <v>1891</v>
+        <v>1890</v>
       </c>
       <c r="P423" s="5" t="s">
         <v>43</v>
@@ -41087,7 +41087,7 @@
       <c r="I424" s="5"/>
       <c r="J424" s="5"/>
       <c r="K424" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L424" s="6">
         <f t="shared" si="14"/>
@@ -41141,7 +41141,7 @@
       </c>
       <c r="J425" s="5"/>
       <c r="K425" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L425" s="6">
         <f t="shared" si="14"/>
@@ -41201,7 +41201,7 @@
         <v>192</v>
       </c>
       <c r="K426" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L426" s="6">
         <f t="shared" si="14"/>
@@ -41255,7 +41255,7 @@
       <c r="I427" s="5"/>
       <c r="J427" s="5"/>
       <c r="K427" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L427" s="6">
         <f t="shared" si="14"/>
@@ -41319,7 +41319,7 @@
         <v>71</v>
       </c>
       <c r="K428" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L428" s="6">
         <f t="shared" si="14"/>
@@ -41393,7 +41393,7 @@
       </c>
       <c r="J429" s="5"/>
       <c r="K429" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L429" s="6">
         <f t="shared" si="14"/>
@@ -41453,7 +41453,7 @@
       <c r="I430" s="5"/>
       <c r="J430" s="5"/>
       <c r="K430" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L430" s="6">
         <f t="shared" si="14"/>
@@ -41507,7 +41507,7 @@
       <c r="I431" s="5"/>
       <c r="J431" s="5"/>
       <c r="K431" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L431" s="6">
         <f t="shared" si="14"/>
@@ -41565,7 +41565,7 @@
       </c>
       <c r="J432" s="5"/>
       <c r="K432" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L432" s="6">
         <f t="shared" si="14"/>
@@ -41625,7 +41625,7 @@
       <c r="I433" s="5"/>
       <c r="J433" s="5"/>
       <c r="K433" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L433" s="6">
         <f t="shared" si="14"/>
@@ -41681,7 +41681,7 @@
         <v>119</v>
       </c>
       <c r="K434" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L434" s="6">
         <f t="shared" si="14"/>
@@ -41741,7 +41741,7 @@
       <c r="I435" s="5"/>
       <c r="J435" s="5"/>
       <c r="K435" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L435" s="6">
         <f t="shared" si="14"/>
@@ -41789,7 +41789,7 @@
       <c r="I436" s="5"/>
       <c r="J436" s="5"/>
       <c r="K436" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L436" s="6">
         <f t="shared" si="14"/>
@@ -41847,7 +41847,7 @@
       </c>
       <c r="J437" s="5"/>
       <c r="K437" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L437" s="6">
         <f t="shared" si="14"/>
@@ -41897,7 +41897,7 @@
       </c>
       <c r="J438" s="5"/>
       <c r="K438" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L438" s="6">
         <f t="shared" si="14"/>
@@ -41959,7 +41959,7 @@
         <v>72</v>
       </c>
       <c r="K439" s="18" t="s">
-        <v>1932</v>
+        <v>1931</v>
       </c>
       <c r="L439" s="6">
         <f t="shared" si="14"/>
@@ -42011,7 +42011,7 @@
       <c r="I440" s="5"/>
       <c r="J440" s="5"/>
       <c r="K440" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L440" s="6">
         <f t="shared" si="14"/>
@@ -42071,7 +42071,7 @@
       </c>
       <c r="J441" s="5"/>
       <c r="K441" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L441" s="6">
         <f t="shared" si="14"/>
@@ -42127,7 +42127,7 @@
       <c r="I442" s="5"/>
       <c r="J442" s="5"/>
       <c r="K442" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L442" s="6">
         <f t="shared" si="14"/>
@@ -42189,7 +42189,7 @@
       </c>
       <c r="J443" s="5"/>
       <c r="K443" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L443" s="6">
         <f t="shared" si="14"/>
@@ -42249,7 +42249,7 @@
       <c r="I444" s="5"/>
       <c r="J444" s="5"/>
       <c r="K444" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L444" s="6">
         <f t="shared" si="14"/>
@@ -42303,7 +42303,7 @@
       <c r="I445" s="5"/>
       <c r="J445" s="5"/>
       <c r="K445" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L445" s="6">
         <f t="shared" si="14"/>
@@ -42365,7 +42365,7 @@
       <c r="I446" s="5"/>
       <c r="J446" s="5"/>
       <c r="K446" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L446" s="6">
         <f t="shared" si="14"/>
@@ -42425,7 +42425,7 @@
       <c r="I447" s="5"/>
       <c r="J447" s="5"/>
       <c r="K447" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L447" s="6">
         <f t="shared" si="14"/>
@@ -42489,7 +42489,7 @@
         <v>71</v>
       </c>
       <c r="K448" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L448" s="6">
         <f t="shared" si="14"/>
@@ -42551,7 +42551,7 @@
       </c>
       <c r="J449" s="5"/>
       <c r="K449" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L449" s="6">
         <f t="shared" si="14"/>
@@ -42615,7 +42615,7 @@
       </c>
       <c r="J450" s="5"/>
       <c r="K450" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L450" s="6">
         <f t="shared" si="14"/>
@@ -42671,7 +42671,7 @@
       <c r="I451" s="5"/>
       <c r="J451" s="5"/>
       <c r="K451" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L451" s="6">
         <f t="shared" si="14"/>
@@ -42727,7 +42727,7 @@
       <c r="I452" s="5"/>
       <c r="J452" s="5"/>
       <c r="K452" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L452" s="6">
         <f t="shared" si="14"/>
@@ -42787,7 +42787,7 @@
         <v>91</v>
       </c>
       <c r="K453" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L453" s="6">
         <f t="shared" si="14"/>
@@ -42845,7 +42845,7 @@
       <c r="I454" s="5"/>
       <c r="J454" s="5"/>
       <c r="K454" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L454" s="6">
         <f t="shared" si="14"/>
@@ -42903,7 +42903,7 @@
       <c r="I455" s="5"/>
       <c r="J455" s="5"/>
       <c r="K455" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L455" s="6">
         <f t="shared" si="14"/>
@@ -42961,7 +42961,7 @@
       <c r="I456" s="5"/>
       <c r="J456" s="5"/>
       <c r="K456" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L456" s="6">
         <f t="shared" si="14"/>
@@ -43014,14 +43014,14 @@
         <v>57</v>
       </c>
       <c r="H457" s="5" t="s">
-        <v>1856</v>
+        <v>1855</v>
       </c>
       <c r="I457" s="5" t="s">
         <v>49</v>
       </c>
       <c r="J457" s="5"/>
       <c r="K457" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L457" s="6">
         <f t="shared" si="14"/>
@@ -43077,7 +43077,7 @@
       </c>
       <c r="J458" s="5"/>
       <c r="K458" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L458" s="6">
         <f t="shared" si="14"/>
@@ -43140,14 +43140,14 @@
         <v>57</v>
       </c>
       <c r="H459" s="5" t="s">
-        <v>1858</v>
+        <v>1857</v>
       </c>
       <c r="I459" s="5" t="s">
         <v>78</v>
       </c>
       <c r="J459" s="5"/>
       <c r="K459" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L459" s="6">
         <f t="shared" si="14"/>
@@ -43205,7 +43205,7 @@
       <c r="I460" s="5"/>
       <c r="J460" s="5"/>
       <c r="K460" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L460" s="6">
         <f t="shared" si="14"/>
@@ -43265,7 +43265,7 @@
       </c>
       <c r="J461" s="5"/>
       <c r="K461" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L461" s="6">
         <f t="shared" si="14"/>
@@ -43329,7 +43329,7 @@
       <c r="I462" s="5"/>
       <c r="J462" s="5"/>
       <c r="K462" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L462" s="6">
         <f t="shared" si="14"/>
@@ -43393,7 +43393,7 @@
       </c>
       <c r="J463" s="5"/>
       <c r="K463" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L463" s="6">
         <f t="shared" si="14"/>
@@ -43451,7 +43451,7 @@
       <c r="I464" s="5"/>
       <c r="J464" s="5"/>
       <c r="K464" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L464" s="6">
         <f t="shared" si="14"/>
@@ -43511,7 +43511,7 @@
         <v>178</v>
       </c>
       <c r="K465" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L465" s="6">
         <f t="shared" si="14"/>
@@ -43571,7 +43571,7 @@
       <c r="I466" s="5"/>
       <c r="J466" s="5"/>
       <c r="K466" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L466" s="6">
         <f t="shared" si="14"/>
@@ -43629,7 +43629,7 @@
       </c>
       <c r="J467" s="5"/>
       <c r="K467" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L467" s="6">
         <f t="shared" ref="L467:L531" si="16">IF(A467="","",COUNTA(D467:F467)+COUNTA(G467:G467)+COUNTA(H467:H467)+COUNTA(I467:I467))</f>
@@ -43695,7 +43695,7 @@
       </c>
       <c r="J468" s="5"/>
       <c r="K468" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L468" s="6">
         <f t="shared" si="16"/>
@@ -43749,7 +43749,7 @@
       <c r="I469" s="5"/>
       <c r="J469" s="5"/>
       <c r="K469" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L469" s="6">
         <f t="shared" si="16"/>
@@ -43799,7 +43799,7 @@
       <c r="I470" s="5"/>
       <c r="J470" s="5"/>
       <c r="K470" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L470" s="6">
         <f t="shared" si="16"/>
@@ -43855,7 +43855,7 @@
         <v>133</v>
       </c>
       <c r="K471" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L471" s="6">
         <f t="shared" si="16"/>
@@ -43917,7 +43917,7 @@
         <v>193</v>
       </c>
       <c r="K472" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L472" s="6">
         <f t="shared" si="16"/>
@@ -43975,7 +43975,7 @@
       </c>
       <c r="J473" s="5"/>
       <c r="K473" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L473" s="6">
         <f t="shared" si="16"/>
@@ -44031,7 +44031,7 @@
       <c r="I474" s="5"/>
       <c r="J474" s="5"/>
       <c r="K474" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L474" s="6">
         <f t="shared" si="16"/>
@@ -44091,7 +44091,7 @@
       </c>
       <c r="J475" s="5"/>
       <c r="K475" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L475" s="6">
         <f t="shared" si="16"/>
@@ -44155,7 +44155,7 @@
       </c>
       <c r="J476" s="5"/>
       <c r="K476" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L476" s="6">
         <f t="shared" si="16"/>
@@ -44223,7 +44223,7 @@
         <v>1002</v>
       </c>
       <c r="K477" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L477" s="6">
         <f t="shared" si="16"/>
@@ -44283,7 +44283,7 @@
       <c r="I478" s="5"/>
       <c r="J478" s="5"/>
       <c r="K478" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L478" s="6">
         <f t="shared" si="16"/>
@@ -44345,7 +44345,7 @@
       </c>
       <c r="J479" s="5"/>
       <c r="K479" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L479" s="6">
         <f t="shared" si="16"/>
@@ -44415,7 +44415,7 @@
         <v>108</v>
       </c>
       <c r="K480" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L480" s="6">
         <f t="shared" si="16"/>
@@ -44473,7 +44473,7 @@
       </c>
       <c r="J481" s="5"/>
       <c r="K481" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L481" s="6">
         <f t="shared" si="16"/>
@@ -44531,7 +44531,7 @@
       <c r="I482" s="5"/>
       <c r="J482" s="5"/>
       <c r="K482" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L482" s="6">
         <f t="shared" si="16"/>
@@ -44585,7 +44585,7 @@
       </c>
       <c r="J483" s="5"/>
       <c r="K483" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L483" s="6">
         <f t="shared" si="16"/>
@@ -44649,7 +44649,7 @@
         <v>1402</v>
       </c>
       <c r="K484" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L484" s="6">
         <f t="shared" si="16"/>
@@ -44721,7 +44721,7 @@
       </c>
       <c r="J485" s="5"/>
       <c r="K485" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L485" s="6">
         <f t="shared" si="16"/>
@@ -44733,7 +44733,7 @@
       </c>
       <c r="N485" s="5"/>
       <c r="O485" s="5" t="s">
-        <v>1972</v>
+        <v>1971</v>
       </c>
       <c r="P485" s="5" t="s">
         <v>128</v>
@@ -44787,7 +44787,7 @@
       </c>
       <c r="J486" s="5"/>
       <c r="K486" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L486" s="6">
         <f t="shared" si="16"/>
@@ -44851,7 +44851,7 @@
         <v>71</v>
       </c>
       <c r="K487" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L487" s="6">
         <f t="shared" si="16"/>
@@ -44901,7 +44901,7 @@
       <c r="I488" s="5"/>
       <c r="J488" s="5"/>
       <c r="K488" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L488" s="6">
         <f t="shared" si="16"/>
@@ -44959,7 +44959,7 @@
         <v>91</v>
       </c>
       <c r="K489" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L489" s="6">
         <f t="shared" si="16"/>
@@ -45009,7 +45009,7 @@
       <c r="I490" s="5"/>
       <c r="J490" s="5"/>
       <c r="K490" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L490" s="6">
         <f t="shared" si="16"/>
@@ -45069,7 +45069,7 @@
       </c>
       <c r="J491" s="5"/>
       <c r="K491" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L491" s="6">
         <f t="shared" si="16"/>
@@ -45141,7 +45141,7 @@
       </c>
       <c r="J492" s="5"/>
       <c r="K492" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L492" s="6">
         <f t="shared" si="16"/>
@@ -45211,7 +45211,7 @@
         <v>49</v>
       </c>
       <c r="K493" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L493" s="6">
         <f t="shared" si="16"/>
@@ -45283,7 +45283,7 @@
       <c r="I494" s="5"/>
       <c r="J494" s="5"/>
       <c r="K494" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L494" s="6">
         <f t="shared" si="16"/>
@@ -45341,7 +45341,7 @@
       <c r="I495" s="5"/>
       <c r="J495" s="5"/>
       <c r="K495" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L495" s="6">
         <f t="shared" si="16"/>
@@ -45398,16 +45398,16 @@
         <v>47</v>
       </c>
       <c r="H496" s="5" t="s">
-        <v>1882</v>
+        <v>1881</v>
       </c>
       <c r="I496" s="5" t="s">
         <v>71</v>
       </c>
       <c r="J496" s="5" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="K496" s="18" t="s">
-        <v>1882</v>
+        <v>1881</v>
       </c>
       <c r="L496" s="6">
         <f t="shared" si="16"/>
@@ -45419,7 +45419,7 @@
       </c>
       <c r="N496" s="5"/>
       <c r="O496" s="5" t="s">
-        <v>1883</v>
+        <v>1882</v>
       </c>
       <c r="P496" s="5" t="s">
         <v>128</v>
@@ -45438,7 +45438,7 @@
         <v>51</v>
       </c>
       <c r="X496" s="5" t="s">
-        <v>1882</v>
+        <v>1881</v>
       </c>
       <c r="Y496" s="5" t="s">
         <v>47</v>
@@ -45469,7 +45469,7 @@
         <v>71</v>
       </c>
       <c r="K497" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L497" s="6">
         <f t="shared" si="16"/>
@@ -45533,7 +45533,7 @@
       <c r="I498" s="5"/>
       <c r="J498" s="5"/>
       <c r="K498" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L498" s="6">
         <f t="shared" si="16"/>
@@ -45597,7 +45597,7 @@
         <v>91</v>
       </c>
       <c r="K499" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L499" s="6">
         <f t="shared" si="16"/>
@@ -45659,7 +45659,7 @@
         <v>72</v>
       </c>
       <c r="K500" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L500" s="6">
         <f t="shared" si="16"/>
@@ -45719,7 +45719,7 @@
       <c r="I501" s="5"/>
       <c r="J501" s="5"/>
       <c r="K501" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L501" s="6">
         <f t="shared" si="16"/>
@@ -45779,7 +45779,7 @@
         <v>1460</v>
       </c>
       <c r="K502" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L502" s="6">
         <f t="shared" si="16"/>
@@ -45837,7 +45837,7 @@
       <c r="I503" s="5"/>
       <c r="J503" s="5"/>
       <c r="K503" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L503" s="6">
         <f t="shared" si="16"/>
@@ -45897,7 +45897,7 @@
       <c r="I504" s="5"/>
       <c r="J504" s="5"/>
       <c r="K504" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L504" s="6">
         <f t="shared" si="16"/>
@@ -45953,7 +45953,7 @@
       <c r="I505" s="5"/>
       <c r="J505" s="5"/>
       <c r="K505" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L505" s="6">
         <f t="shared" si="16"/>
@@ -46013,7 +46013,7 @@
       </c>
       <c r="J506" s="5"/>
       <c r="K506" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L506" s="6">
         <f t="shared" si="16"/>
@@ -46075,7 +46075,7 @@
         <v>1472</v>
       </c>
       <c r="K507" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L507" s="6">
         <f t="shared" si="16"/>
@@ -46141,7 +46141,7 @@
       </c>
       <c r="J508" s="5"/>
       <c r="K508" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L508" s="6">
         <f t="shared" si="16"/>
@@ -46199,7 +46199,7 @@
       <c r="I509" s="5"/>
       <c r="J509" s="5"/>
       <c r="K509" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L509" s="6">
         <f t="shared" si="16"/>
@@ -46256,7 +46256,7 @@
         <v>57</v>
       </c>
       <c r="H510" s="5" t="s">
-        <v>1967</v>
+        <v>1966</v>
       </c>
       <c r="I510" s="5" t="s">
         <v>119</v>
@@ -46265,7 +46265,7 @@
         <v>49</v>
       </c>
       <c r="K510" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L510" s="6">
         <f t="shared" si="16"/>
@@ -46277,7 +46277,7 @@
       </c>
       <c r="N510" s="5"/>
       <c r="O510" s="5" t="s">
-        <v>1968</v>
+        <v>1967</v>
       </c>
       <c r="P510" s="5" t="s">
         <v>43</v>
@@ -46323,7 +46323,7 @@
       </c>
       <c r="J511" s="5"/>
       <c r="K511" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L511" s="6">
         <f t="shared" si="16"/>
@@ -46391,7 +46391,7 @@
         <v>71</v>
       </c>
       <c r="K512" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L512" s="6">
         <f t="shared" si="16"/>
@@ -46451,7 +46451,7 @@
       </c>
       <c r="J513" s="5"/>
       <c r="K513" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L513" s="6">
         <f t="shared" si="16"/>
@@ -46507,7 +46507,7 @@
       <c r="I514" s="5"/>
       <c r="J514" s="5"/>
       <c r="K514" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L514" s="6">
         <f t="shared" si="16"/>
@@ -46573,7 +46573,7 @@
         <v>193</v>
       </c>
       <c r="K515" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L515" s="6">
         <f t="shared" si="16"/>
@@ -46633,7 +46633,7 @@
       <c r="I516" s="5"/>
       <c r="J516" s="5"/>
       <c r="K516" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L516" s="6">
         <f t="shared" si="16"/>
@@ -46695,7 +46695,7 @@
         <v>91</v>
       </c>
       <c r="K517" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L517" s="6">
         <f t="shared" si="16"/>
@@ -46707,7 +46707,7 @@
       </c>
       <c r="N517" s="5"/>
       <c r="O517" s="5" t="s">
-        <v>1966</v>
+        <v>1965</v>
       </c>
       <c r="P517" s="5"/>
       <c r="Q517" s="5"/>
@@ -46749,7 +46749,7 @@
       <c r="I518" s="5"/>
       <c r="J518" s="5"/>
       <c r="K518" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L518" s="6">
         <f t="shared" si="16"/>
@@ -46799,7 +46799,7 @@
       <c r="I519" s="5"/>
       <c r="J519" s="5"/>
       <c r="K519" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L519" s="6">
         <f t="shared" si="16"/>
@@ -46849,7 +46849,7 @@
       </c>
       <c r="J520" s="5"/>
       <c r="K520" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L520" s="6">
         <f t="shared" si="16"/>
@@ -46889,7 +46889,7 @@
     </row>
     <row r="521" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A521" s="5" t="s">
-        <v>1961</v>
+        <v>1960</v>
       </c>
       <c r="B521" s="5"/>
       <c r="C521" s="5" t="s">
@@ -46908,14 +46908,14 @@
         <v>57</v>
       </c>
       <c r="H521" s="5" t="s">
-        <v>1881</v>
+        <v>1880</v>
       </c>
       <c r="I521" s="5" t="s">
         <v>72</v>
       </c>
       <c r="J521" s="5"/>
       <c r="K521" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L521" s="6">
         <f t="shared" ref="L521" si="18">IF(A521="","",COUNTA(D521:F521)+COUNTA(G521:G521)+COUNTA(H521:H521)+COUNTA(I521:I521))</f>
@@ -46927,7 +46927,7 @@
       </c>
       <c r="N521" s="5"/>
       <c r="O521" s="5" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="P521" s="5" t="s">
         <v>128</v>
@@ -46985,7 +46985,7 @@
         <v>1500</v>
       </c>
       <c r="K522" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L522" s="6">
         <f t="shared" si="16"/>
@@ -46997,7 +46997,7 @@
       </c>
       <c r="N522" s="5"/>
       <c r="O522" s="5" t="s">
-        <v>1964</v>
+        <v>1963</v>
       </c>
       <c r="P522" s="5" t="s">
         <v>43</v>
@@ -47045,7 +47045,7 @@
       <c r="I523" s="5"/>
       <c r="J523" s="5"/>
       <c r="K523" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L523" s="6">
         <f t="shared" si="16"/>
@@ -47105,7 +47105,7 @@
       </c>
       <c r="J524" s="5"/>
       <c r="K524" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L524" s="6">
         <f t="shared" si="16"/>
@@ -47170,14 +47170,14 @@
         <v>47</v>
       </c>
       <c r="H525" s="5" t="s">
-        <v>1916</v>
+        <v>1915</v>
       </c>
       <c r="I525" s="5" t="s">
         <v>123</v>
       </c>
       <c r="J525" s="5"/>
       <c r="K525" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L525" s="6">
         <f t="shared" si="16"/>
@@ -47233,7 +47233,7 @@
       <c r="I526" s="5"/>
       <c r="J526" s="5"/>
       <c r="K526" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L526" s="6">
         <f t="shared" si="16"/>
@@ -47279,7 +47279,7 @@
       <c r="I527" s="5"/>
       <c r="J527" s="5"/>
       <c r="K527" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L527" s="6">
         <f t="shared" si="16"/>
@@ -47333,7 +47333,7 @@
       <c r="I528" s="5"/>
       <c r="J528" s="5"/>
       <c r="K528" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L528" s="6">
         <f t="shared" si="16"/>
@@ -47399,7 +47399,7 @@
       </c>
       <c r="J529" s="5"/>
       <c r="K529" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L529" s="6">
         <f t="shared" si="16"/>
@@ -47443,7 +47443,7 @@
     </row>
     <row r="530" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A530" s="5" t="s">
-        <v>1861</v>
+        <v>1860</v>
       </c>
       <c r="B530" s="5"/>
       <c r="C530" s="5" t="s">
@@ -47462,7 +47462,7 @@
         <v>47</v>
       </c>
       <c r="H530" s="5" t="s">
-        <v>1860</v>
+        <v>1859</v>
       </c>
       <c r="I530" s="5" t="s">
         <v>71</v>
@@ -47471,7 +47471,7 @@
         <v>91</v>
       </c>
       <c r="K530" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L530" s="6">
         <f t="shared" si="16"/>
@@ -47482,10 +47482,10 @@
         <v>Yes</v>
       </c>
       <c r="N530" s="5" t="s">
-        <v>1963</v>
+        <v>1962</v>
       </c>
       <c r="O530" s="5" t="s">
-        <v>1965</v>
+        <v>1964</v>
       </c>
       <c r="P530" s="5" t="s">
         <v>43</v>
@@ -47509,7 +47509,7 @@
         <v>538</v>
       </c>
       <c r="Y530" s="5" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
       <c r="Z530" s="5" t="s">
         <v>540</v>
@@ -47531,7 +47531,7 @@
       <c r="I531" s="5"/>
       <c r="J531" s="5"/>
       <c r="K531" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L531" s="6">
         <f t="shared" si="16"/>
@@ -47591,7 +47591,7 @@
       </c>
       <c r="J532" s="5"/>
       <c r="K532" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L532" s="6">
         <f t="shared" ref="L532:L595" si="20">IF(A532="","",COUNTA(D532:F532)+COUNTA(G532:G532)+COUNTA(H532:H532)+COUNTA(I532:I532))</f>
@@ -47603,7 +47603,7 @@
       </c>
       <c r="N532" s="5"/>
       <c r="O532" s="5" t="s">
-        <v>1971</v>
+        <v>1970</v>
       </c>
       <c r="P532" s="5" t="s">
         <v>128</v>
@@ -47657,7 +47657,7 @@
       </c>
       <c r="J533" s="5"/>
       <c r="K533" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L533" s="6">
         <f t="shared" si="20"/>
@@ -47731,7 +47731,7 @@
         <v>133</v>
       </c>
       <c r="K534" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L534" s="6">
         <f t="shared" si="20"/>
@@ -47790,7 +47790,7 @@
         <v>57</v>
       </c>
       <c r="H535" s="5" t="s">
-        <v>1881</v>
+        <v>1880</v>
       </c>
       <c r="I535" s="5" t="s">
         <v>123</v>
@@ -47799,7 +47799,7 @@
         <v>49</v>
       </c>
       <c r="K535" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L535" s="6">
         <f t="shared" si="20"/>
@@ -47859,7 +47859,7 @@
       <c r="I536" s="5"/>
       <c r="J536" s="5"/>
       <c r="K536" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L536" s="6">
         <f t="shared" si="20"/>
@@ -47915,7 +47915,7 @@
       <c r="I537" s="5"/>
       <c r="J537" s="5"/>
       <c r="K537" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L537" s="6">
         <f t="shared" si="20"/>
@@ -47974,10 +47974,10 @@
         <v>193</v>
       </c>
       <c r="J538" s="5" t="s">
-        <v>1954</v>
+        <v>1953</v>
       </c>
       <c r="K538" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L538" s="6">
         <f t="shared" si="20"/>
@@ -48033,7 +48033,7 @@
       <c r="I539" s="5"/>
       <c r="J539" s="5"/>
       <c r="K539" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L539" s="6">
         <f t="shared" si="20"/>
@@ -48095,7 +48095,7 @@
       </c>
       <c r="J540" s="5"/>
       <c r="K540" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L540" s="6">
         <f t="shared" si="20"/>
@@ -48107,7 +48107,7 @@
       </c>
       <c r="N540" s="5"/>
       <c r="O540" s="5" t="s">
-        <v>1955</v>
+        <v>1954</v>
       </c>
       <c r="P540" s="5"/>
       <c r="Q540" s="5"/>
@@ -48145,7 +48145,7 @@
       <c r="I541" s="5"/>
       <c r="J541" s="5"/>
       <c r="K541" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L541" s="6">
         <f t="shared" si="20"/>
@@ -48199,7 +48199,7 @@
         <v>91</v>
       </c>
       <c r="K542" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L542" s="6">
         <f t="shared" si="20"/>
@@ -48263,7 +48263,7 @@
       </c>
       <c r="J543" s="5"/>
       <c r="K543" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L543" s="6">
         <f t="shared" si="20"/>
@@ -48313,7 +48313,7 @@
         <v>44</v>
       </c>
       <c r="E544" s="5" t="s">
-        <v>1900</v>
+        <v>1899</v>
       </c>
       <c r="F544" s="5" t="s">
         <v>107</v>
@@ -48329,7 +48329,7 @@
       </c>
       <c r="J544" s="5"/>
       <c r="K544" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L544" s="6">
         <f t="shared" si="20"/>
@@ -48397,7 +48397,7 @@
         <v>595</v>
       </c>
       <c r="K545" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L545" s="6">
         <f t="shared" si="20"/>
@@ -48431,10 +48431,10 @@
     </row>
     <row r="546" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A546" s="5" t="s">
+        <v>1896</v>
+      </c>
+      <c r="B546" s="5" t="s">
         <v>1897</v>
-      </c>
-      <c r="B546" s="5" t="s">
-        <v>1898</v>
       </c>
       <c r="C546" s="5" t="s">
         <v>43</v>
@@ -48459,7 +48459,7 @@
       </c>
       <c r="J546" s="5"/>
       <c r="K546" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L546" s="6">
         <f t="shared" si="20"/>
@@ -48471,7 +48471,7 @@
       </c>
       <c r="N546" s="5"/>
       <c r="O546" s="5" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="P546" s="5"/>
       <c r="Q546" s="5"/>
@@ -48501,7 +48501,7 @@
       <c r="I547" s="5"/>
       <c r="J547" s="5"/>
       <c r="K547" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L547" s="6">
         <f t="shared" si="20"/>
@@ -48549,7 +48549,7 @@
       <c r="I548" s="5"/>
       <c r="J548" s="5"/>
       <c r="K548" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L548" s="6">
         <f t="shared" si="20"/>
@@ -48601,7 +48601,7 @@
       <c r="I549" s="5"/>
       <c r="J549" s="5"/>
       <c r="K549" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L549" s="6">
         <f t="shared" si="20"/>
@@ -48653,7 +48653,7 @@
       <c r="I550" s="5"/>
       <c r="J550" s="5"/>
       <c r="K550" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L550" s="6">
         <f t="shared" si="20"/>
@@ -48715,7 +48715,7 @@
       </c>
       <c r="J551" s="5"/>
       <c r="K551" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L551" s="6">
         <f t="shared" si="20"/>
@@ -48727,7 +48727,7 @@
       </c>
       <c r="N551" s="5"/>
       <c r="O551" s="5" t="s">
-        <v>1956</v>
+        <v>1955</v>
       </c>
       <c r="P551" s="5"/>
       <c r="Q551" s="5"/>
@@ -48771,7 +48771,7 @@
       <c r="I552" s="5"/>
       <c r="J552" s="5"/>
       <c r="K552" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L552" s="6">
         <f t="shared" si="20"/>
@@ -48827,7 +48827,7 @@
       <c r="I553" s="5"/>
       <c r="J553" s="5"/>
       <c r="K553" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L553" s="6">
         <f t="shared" si="20"/>
@@ -48887,7 +48887,7 @@
       </c>
       <c r="J554" s="5"/>
       <c r="K554" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L554" s="6">
         <f t="shared" si="20"/>
@@ -48951,7 +48951,7 @@
       </c>
       <c r="J555" s="5"/>
       <c r="K555" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L555" s="6">
         <f t="shared" si="20"/>
@@ -48993,7 +48993,7 @@
     </row>
     <row r="556" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A556" s="5" t="s">
-        <v>1947</v>
+        <v>1946</v>
       </c>
       <c r="B556" s="5"/>
       <c r="C556" s="5" t="s">
@@ -49012,7 +49012,7 @@
         <v>47</v>
       </c>
       <c r="H556" s="5" t="s">
-        <v>1934</v>
+        <v>1933</v>
       </c>
       <c r="I556" s="5" t="s">
         <v>91</v>
@@ -49021,7 +49021,7 @@
         <v>119</v>
       </c>
       <c r="K556" s="18" t="s">
-        <v>1943</v>
+        <v>1942</v>
       </c>
       <c r="L556" s="6">
         <f t="shared" si="20"/>
@@ -49033,7 +49033,7 @@
       </c>
       <c r="N556" s="5"/>
       <c r="O556" s="5" t="s">
-        <v>1948</v>
+        <v>1947</v>
       </c>
       <c r="P556" s="5" t="s">
         <v>105</v>
@@ -49069,7 +49069,7 @@
       <c r="I557" s="5"/>
       <c r="J557" s="5"/>
       <c r="K557" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L557" s="6">
         <f t="shared" si="20"/>
@@ -49127,7 +49127,7 @@
       </c>
       <c r="J558" s="5"/>
       <c r="K558" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L558" s="6">
         <f t="shared" si="20"/>
@@ -49191,7 +49191,7 @@
       </c>
       <c r="J559" s="5"/>
       <c r="K559" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L559" s="6">
         <f t="shared" si="20"/>
@@ -49237,7 +49237,7 @@
     </row>
     <row r="560" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A560" s="5" t="s">
-        <v>1893</v>
+        <v>1892</v>
       </c>
       <c r="B560" s="5" t="s">
         <v>730</v>
@@ -49258,7 +49258,7 @@
         <v>57</v>
       </c>
       <c r="H560" s="5" t="s">
-        <v>1860</v>
+        <v>1859</v>
       </c>
       <c r="I560" s="5" t="s">
         <v>72</v>
@@ -49267,7 +49267,7 @@
         <v>71</v>
       </c>
       <c r="K560" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L560" s="6">
         <f t="shared" si="20"/>
@@ -49278,10 +49278,10 @@
         <v>Yes</v>
       </c>
       <c r="N560" s="5" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
       <c r="O560" s="5" t="s">
-        <v>1892</v>
+        <v>1891</v>
       </c>
       <c r="P560" s="5"/>
       <c r="Q560" s="5"/>
@@ -49325,7 +49325,7 @@
       <c r="I561" s="5"/>
       <c r="J561" s="5"/>
       <c r="K561" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L561" s="6">
         <f t="shared" si="20"/>
@@ -49387,7 +49387,7 @@
       </c>
       <c r="J562" s="5"/>
       <c r="K562" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L562" s="6">
         <f t="shared" si="20"/>
@@ -49461,7 +49461,7 @@
         <v>91</v>
       </c>
       <c r="K563" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L563" s="6">
         <f t="shared" si="20"/>
@@ -49523,7 +49523,7 @@
         <v>91</v>
       </c>
       <c r="K564" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L564" s="6">
         <f t="shared" si="20"/>
@@ -49579,7 +49579,7 @@
       <c r="I565" s="5"/>
       <c r="J565" s="5"/>
       <c r="K565" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L565" s="6">
         <f t="shared" si="20"/>
@@ -49631,7 +49631,7 @@
       <c r="I566" s="5"/>
       <c r="J566" s="5"/>
       <c r="K566" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L566" s="6">
         <f t="shared" si="20"/>
@@ -49685,7 +49685,7 @@
       </c>
       <c r="J567" s="5"/>
       <c r="K567" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L567" s="6">
         <f t="shared" si="20"/>
@@ -49741,7 +49741,7 @@
       <c r="I568" s="5"/>
       <c r="J568" s="5"/>
       <c r="K568" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L568" s="6">
         <f t="shared" si="20"/>
@@ -49807,7 +49807,7 @@
         <v>1579</v>
       </c>
       <c r="K569" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L569" s="6">
         <f t="shared" si="20"/>
@@ -49873,7 +49873,7 @@
       </c>
       <c r="J570" s="5"/>
       <c r="K570" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L570" s="6">
         <f t="shared" si="20"/>
@@ -49931,7 +49931,7 @@
       <c r="I571" s="5"/>
       <c r="J571" s="5"/>
       <c r="K571" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L571" s="6">
         <f t="shared" si="20"/>
@@ -49981,7 +49981,7 @@
       <c r="I572" s="5"/>
       <c r="J572" s="5"/>
       <c r="K572" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L572" s="6">
         <f t="shared" si="20"/>
@@ -50037,7 +50037,7 @@
       </c>
       <c r="J573" s="5"/>
       <c r="K573" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L573" s="6">
         <f t="shared" si="20"/>
@@ -50095,7 +50095,7 @@
       <c r="I574" s="5"/>
       <c r="J574" s="5"/>
       <c r="K574" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L574" s="6">
         <f t="shared" si="20"/>
@@ -50157,7 +50157,7 @@
       </c>
       <c r="J575" s="5"/>
       <c r="K575" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L575" s="6">
         <f t="shared" si="20"/>
@@ -50221,7 +50221,7 @@
       </c>
       <c r="J576" s="5"/>
       <c r="K576" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L576" s="6">
         <f t="shared" si="20"/>
@@ -50289,7 +50289,7 @@
         <v>193</v>
       </c>
       <c r="K577" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L577" s="6">
         <f t="shared" si="20"/>
@@ -50355,7 +50355,7 @@
         <v>71</v>
       </c>
       <c r="K578" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L578" s="6">
         <f t="shared" si="20"/>
@@ -50415,7 +50415,7 @@
         <v>1602</v>
       </c>
       <c r="K579" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L579" s="6">
         <f t="shared" si="20"/>
@@ -50485,7 +50485,7 @@
       </c>
       <c r="J580" s="5"/>
       <c r="K580" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L580" s="6">
         <f t="shared" si="20"/>
@@ -50551,7 +50551,7 @@
       <c r="I581" s="5"/>
       <c r="J581" s="5"/>
       <c r="K581" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L581" s="6">
         <f t="shared" si="20"/>
@@ -50615,7 +50615,7 @@
       </c>
       <c r="J582" s="5"/>
       <c r="K582" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L582" s="6">
         <f t="shared" si="20"/>
@@ -50672,14 +50672,14 @@
         <v>47</v>
       </c>
       <c r="H583" s="5" t="s">
-        <v>1858</v>
+        <v>1857</v>
       </c>
       <c r="I583" s="5" t="s">
         <v>49</v>
       </c>
       <c r="J583" s="5"/>
       <c r="K583" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L583" s="6">
         <f t="shared" si="20"/>
@@ -50745,7 +50745,7 @@
       <c r="I584" s="5"/>
       <c r="J584" s="5"/>
       <c r="K584" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L584" s="6">
         <f t="shared" si="20"/>
@@ -50756,10 +50756,10 @@
         <v>No</v>
       </c>
       <c r="N584" s="5" t="s">
-        <v>1886</v>
+        <v>1885</v>
       </c>
       <c r="O584" s="5" t="s">
-        <v>1885</v>
+        <v>1884</v>
       </c>
       <c r="P584" s="5" t="s">
         <v>43</v>
@@ -50805,7 +50805,7 @@
         <v>1618</v>
       </c>
       <c r="K585" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L585" s="6">
         <f t="shared" si="20"/>
@@ -50871,7 +50871,7 @@
       </c>
       <c r="J586" s="5"/>
       <c r="K586" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L586" s="6">
         <f t="shared" si="20"/>
@@ -50935,7 +50935,7 @@
       <c r="I587" s="5"/>
       <c r="J587" s="5"/>
       <c r="K587" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L587" s="6">
         <f t="shared" si="20"/>
@@ -50987,7 +50987,7 @@
       <c r="I588" s="5"/>
       <c r="J588" s="5"/>
       <c r="K588" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L588" s="6">
         <f t="shared" si="20"/>
@@ -51043,7 +51043,7 @@
       </c>
       <c r="J589" s="5"/>
       <c r="K589" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L589" s="6">
         <f t="shared" si="20"/>
@@ -51107,7 +51107,7 @@
         <v>193</v>
       </c>
       <c r="K590" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L590" s="6">
         <f t="shared" si="20"/>
@@ -51175,7 +51175,7 @@
         <v>1634</v>
       </c>
       <c r="K591" s="18" t="s">
-        <v>1932</v>
+        <v>1931</v>
       </c>
       <c r="L591" s="6">
         <f t="shared" si="20"/>
@@ -51231,7 +51231,7 @@
       <c r="I592" s="5"/>
       <c r="J592" s="5"/>
       <c r="K592" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L592" s="6">
         <f t="shared" si="20"/>
@@ -51295,7 +51295,7 @@
         <v>178</v>
       </c>
       <c r="K593" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L593" s="6">
         <f t="shared" si="20"/>
@@ -51355,7 +51355,7 @@
       <c r="I594" s="5"/>
       <c r="J594" s="5"/>
       <c r="K594" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L594" s="6">
         <f t="shared" si="20"/>
@@ -51407,7 +51407,7 @@
       <c r="I595" s="5"/>
       <c r="J595" s="5"/>
       <c r="K595" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L595" s="6">
         <f t="shared" si="20"/>
@@ -51465,7 +51465,7 @@
       </c>
       <c r="J596" s="5"/>
       <c r="K596" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L596" s="6">
         <f t="shared" ref="L596:L660" si="22">IF(A596="","",COUNTA(D596:F596)+COUNTA(G596:G596)+COUNTA(H596:H596)+COUNTA(I596:I596))</f>
@@ -51523,7 +51523,7 @@
       <c r="I597" s="5"/>
       <c r="J597" s="5"/>
       <c r="K597" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L597" s="6">
         <f t="shared" si="22"/>
@@ -51578,7 +51578,7 @@
         <v>47</v>
       </c>
       <c r="H598" s="5" t="s">
-        <v>1858</v>
+        <v>1857</v>
       </c>
       <c r="I598" s="5" t="s">
         <v>91</v>
@@ -51587,7 +51587,7 @@
         <v>49</v>
       </c>
       <c r="K598" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L598" s="6">
         <f t="shared" si="22"/>
@@ -51599,7 +51599,7 @@
       </c>
       <c r="N598" s="5"/>
       <c r="O598" s="5" t="s">
-        <v>1957</v>
+        <v>1956</v>
       </c>
       <c r="P598" s="5" t="s">
         <v>128</v>
@@ -51625,7 +51625,7 @@
     </row>
     <row r="599" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A599" s="5" t="s">
-        <v>1959</v>
+        <v>1958</v>
       </c>
       <c r="B599" s="5"/>
       <c r="C599" s="5" t="s">
@@ -51651,7 +51651,7 @@
       </c>
       <c r="J599" s="5"/>
       <c r="K599" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L599" s="6">
         <f t="shared" ref="L599" si="23">IF(A599="","",COUNTA(D599:F599)+COUNTA(G599:G599)+COUNTA(H599:H599)+COUNTA(I599:I599))</f>
@@ -51663,7 +51663,7 @@
       </c>
       <c r="N599" s="5"/>
       <c r="O599" s="5" t="s">
-        <v>1960</v>
+        <v>1959</v>
       </c>
       <c r="P599" s="5"/>
       <c r="Q599" s="5"/>
@@ -51717,7 +51717,7 @@
       </c>
       <c r="J600" s="5"/>
       <c r="K600" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L600" s="6">
         <f t="shared" si="22"/>
@@ -51729,7 +51729,7 @@
       </c>
       <c r="N600" s="5"/>
       <c r="O600" s="5" t="s">
-        <v>1958</v>
+        <v>1957</v>
       </c>
       <c r="P600" s="5"/>
       <c r="Q600" s="5"/>
@@ -51783,7 +51783,7 @@
       </c>
       <c r="J601" s="5"/>
       <c r="K601" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L601" s="6">
         <f t="shared" si="22"/>
@@ -51839,7 +51839,7 @@
       <c r="I602" s="5"/>
       <c r="J602" s="5"/>
       <c r="K602" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L602" s="6">
         <f t="shared" si="22"/>
@@ -51889,7 +51889,7 @@
       <c r="I603" s="5"/>
       <c r="J603" s="5"/>
       <c r="K603" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L603" s="6">
         <f t="shared" si="22"/>
@@ -51943,7 +51943,7 @@
         <v>71</v>
       </c>
       <c r="K604" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L604" s="6">
         <f t="shared" si="22"/>
@@ -51999,7 +51999,7 @@
       <c r="I605" s="5"/>
       <c r="J605" s="5"/>
       <c r="K605" s="18" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="L605" s="6">
         <f t="shared" si="22"/>

--- a/data/parahumandle_design.xlsx
+++ b/data/parahumandle_design.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Research\Worm Wordle clone\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC7D27AB-130B-499F-9F58-AAB2E52F8E1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C67D0DA2-235B-40E1-BBA6-65D0D45EBDB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18654" uniqueCount="1974">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10550" uniqueCount="1975">
   <si>
     <t>Parahumandle – design workbook</t>
   </si>
@@ -5974,6 +5974,9 @@
   </si>
   <si>
     <t>Sanya</t>
+  </si>
+  <si>
+    <t>Can create and control create globs of superheated glass. Flies in a bubble of superheated air.</t>
   </si>
 </sst>
 </file>
@@ -15389,7 +15392,9 @@
       <c r="P2" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="Q2" s="5"/>
+      <c r="Q2" s="5">
+        <v>17.8</v>
+      </c>
       <c r="R2" s="5" t="s">
         <v>49</v>
       </c>
@@ -25970,7 +25975,9 @@
         <v>Yes</v>
       </c>
       <c r="N172" s="5"/>
-      <c r="O172" s="5"/>
+      <c r="O172" s="5" t="s">
+        <v>1974</v>
+      </c>
       <c r="P172" s="5" t="s">
         <v>128</v>
       </c>
@@ -50871,7 +50878,7 @@
         <v>57</v>
       </c>
       <c r="H586" s="5" t="s">
-        <v>83</v>
+        <v>1878</v>
       </c>
       <c r="I586" s="5" t="s">
         <v>91</v>

--- a/data/parahumandle_design.xlsx
+++ b/data/parahumandle_design.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Research\Worm Wordle clone\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10C65C7E-99B6-4CF1-9706-F41574ACA41E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B1C082B-5989-48EF-8F4B-1DEA216C92B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15664,9 +15664,11 @@
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="D5" s="5"/>
+        <v>43</v>
+      </c>
+      <c r="D5" s="5">
+        <v>25.5</v>
+      </c>
       <c r="E5" s="5" t="s">
         <v>76</v>
       </c>
@@ -15872,7 +15874,9 @@
       <c r="C8" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="D8" s="5"/>
+      <c r="D8" s="5">
+        <v>28.5</v>
+      </c>
       <c r="E8" s="5" t="s">
         <v>44</v>
       </c>
@@ -19645,7 +19649,9 @@
       <c r="C67" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="D67" s="5"/>
+      <c r="D67" s="5">
+        <v>26.3</v>
+      </c>
       <c r="E67" s="5" t="s">
         <v>44</v>
       </c>
@@ -19895,7 +19901,9 @@
       <c r="C71" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="D71" s="5"/>
+      <c r="D71" s="5">
+        <v>10.6</v>
+      </c>
       <c r="E71" s="5" t="s">
         <v>44</v>
       </c>
@@ -20955,7 +20963,7 @@
       </c>
       <c r="B89" s="5"/>
       <c r="C89" s="5" t="s">
-        <v>128</v>
+        <v>318</v>
       </c>
       <c r="D89" s="5" t="s">
         <v>319</v>
@@ -22487,7 +22495,9 @@
       <c r="C113" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="D113" s="5"/>
+      <c r="D113" s="5">
+        <v>21.6</v>
+      </c>
       <c r="E113" s="5" t="s">
         <v>44</v>
       </c>
@@ -25471,7 +25481,7 @@
       </c>
       <c r="B159" s="5"/>
       <c r="C159" s="5" t="s">
-        <v>128</v>
+        <v>318</v>
       </c>
       <c r="D159" s="5" t="s">
         <v>1912</v>
@@ -27771,7 +27781,7 @@
       </c>
       <c r="B197" s="5"/>
       <c r="C197" s="5" t="s">
-        <v>128</v>
+        <v>318</v>
       </c>
       <c r="D197" s="5" t="s">
         <v>319</v>
@@ -56004,7 +56014,7 @@
         <v/>
       </c>
       <c r="N704" s="6" t="str">
-        <f t="shared" ref="N704:N767" si="25">IF(A704="","",IF(AND(M704=6,UPPER(S704)&lt;&gt;"Y",C704&lt;&gt;""),"Yes","No"))</f>
+        <f t="shared" ref="N704:N713" si="25">IF(A704="","",IF(AND(M704=6,UPPER(S704)&lt;&gt;"Y",C704&lt;&gt;""),"Yes","No"))</f>
         <v/>
       </c>
       <c r="O704" s="5"/>
@@ -56323,7 +56333,7 @@
       <sortCondition ref="A1:A713"/>
     </sortState>
   </autoFilter>
-  <conditionalFormatting sqref="C23:D23 D2:D202 N2:Q713 D204:D713">
+  <conditionalFormatting sqref="D2:D202 N2:Q713 C23:D23 D204:D713">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"Yes"</formula>
     </cfRule>
@@ -56349,7 +56359,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>C2:D22 C203 C24:D202 C204:D713</xm:sqref>
+          <xm:sqref>C204:D713 C203 C24:D202 C2:D22</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0100-000001000000}">
           <x14:formula1>

--- a/data/parahumandle_design.xlsx
+++ b/data/parahumandle_design.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Research\Worm Wordle clone\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B1C082B-5989-48EF-8F4B-1DEA216C92B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FFF058A-B9D9-4D62-8F09-655B0FE6E4DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10759" uniqueCount="2017">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10765" uniqueCount="2018">
   <si>
     <t>Parahumandle – design workbook</t>
   </si>
@@ -6103,6 +6103,9 @@
   </si>
   <si>
     <t>Capable of flight and can turn himself and his gear into a living projectile, unable to change course.</t>
+  </si>
+  <si>
+    <t>x.1</t>
   </si>
 </sst>
 </file>
@@ -25245,7 +25248,7 @@
       </c>
       <c r="B155" s="5"/>
       <c r="C155" s="5" t="s">
-        <v>70</v>
+        <v>43</v>
       </c>
       <c r="D155" s="5"/>
       <c r="E155" s="5"/>
@@ -25307,9 +25310,11 @@
       </c>
       <c r="B156" s="5"/>
       <c r="C156" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="D156" s="5"/>
+        <v>128</v>
+      </c>
+      <c r="D156" s="5" t="s">
+        <v>2017</v>
+      </c>
       <c r="E156" s="5" t="s">
         <v>76</v>
       </c>
@@ -25319,7 +25324,9 @@
       <c r="G156" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="H156" s="5"/>
+      <c r="H156" s="5" t="s">
+        <v>57</v>
+      </c>
       <c r="I156" s="5" t="s">
         <v>58</v>
       </c>
@@ -25332,11 +25339,11 @@
       </c>
       <c r="M156" s="6">
         <f t="shared" si="6"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N156" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="O156" s="5"/>
       <c r="P156" s="5" t="s">
@@ -34923,15 +34930,23 @@
       </c>
       <c r="B314" s="5"/>
       <c r="C314" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="D314" s="5"/>
+        <v>128</v>
+      </c>
+      <c r="D314" s="5" t="s">
+        <v>2017</v>
+      </c>
       <c r="E314" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="F314" s="5"/>
-      <c r="G314" s="5"/>
-      <c r="H314" s="5"/>
+      <c r="F314" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="G314" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="H314" s="5" t="s">
+        <v>57</v>
+      </c>
       <c r="I314" s="5" t="s">
         <v>58</v>
       </c>
@@ -34944,11 +34959,11 @@
       </c>
       <c r="M314" s="6">
         <f t="shared" si="10"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N314" s="6" t="str">
         <f t="shared" si="9"/>
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="O314" s="5"/>
       <c r="P314" s="5" t="s">
@@ -56359,7 +56374,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>C204:D713 C203 C24:D202 C2:D22</xm:sqref>
+          <xm:sqref>C24:D202 C203 C2:D22 C204:D713</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0100-000001000000}">
           <x14:formula1>
@@ -56489,11 +56504,11 @@
       </c>
       <c r="E3" s="8">
         <f>COUNTA(Roster!F2:F713)</f>
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F3" s="9">
         <f>IF(COUNTA(Roster!A2:A713)=0,0,E3/COUNTA(Roster!A2:A713))</f>
-        <v>0.58471760797342198</v>
+        <v>0.58637873754152825</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -56511,11 +56526,11 @@
       </c>
       <c r="E4" s="8">
         <f>COUNTA(Roster!G2:G713)</f>
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F4" s="9">
         <f>IF(COUNTA(Roster!A2:A713)=0,0,E4/COUNTA(Roster!A2:A713))</f>
-        <v>0.56810631229235875</v>
+        <v>0.56976744186046513</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -56533,11 +56548,11 @@
       </c>
       <c r="E5" s="8">
         <f>COUNTA(Roster!H2:H713)</f>
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="F5" s="9">
         <f>IF(COUNTA(Roster!A2:A713)=0,0,E5/COUNTA(Roster!A2:A713))</f>
-        <v>0.66279069767441856</v>
+        <v>0.66611295681063121</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -56952,7 +56967,7 @@
       </c>
       <c r="B11" s="8">
         <f>COUNTIF(Roster!N2:N713,"Yes")</f>
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C11" s="8" t="s">
         <v>1713</v>
@@ -56964,7 +56979,7 @@
       </c>
       <c r="B12" s="9">
         <f>IF(B5=0,0,B11/B5)</f>
-        <v>1.8333333333333333</v>
+        <v>1.8466666666666667</v>
       </c>
       <c r="C12" s="8" t="s">
         <v>1713</v>
@@ -56976,7 +56991,7 @@
       </c>
       <c r="B13" s="13">
         <f>IFERROR(AVERAGE(Roster!M2:M713),0)</f>
-        <v>3.8787375415282392</v>
+        <v>3.8853820598006643</v>
       </c>
       <c r="C13" s="8" t="s">
         <v>1713</v>

--- a/data/parahumandle_design.xlsx
+++ b/data/parahumandle_design.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Research\Worm Wordle clone\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FFF058A-B9D9-4D62-8F09-655B0FE6E4DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{402D334C-F832-498F-BB2F-6A30B869C516}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10765" uniqueCount="2018">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10769" uniqueCount="2019">
   <si>
     <t>Parahumandle – design workbook</t>
   </si>
@@ -6106,6 +6106,9 @@
   </si>
   <si>
     <t>x.1</t>
+  </si>
+  <si>
+    <t>Alien divinity with immense power who seeks an end to entropy and to grow forever</t>
   </si>
 </sst>
 </file>
@@ -44396,37 +44399,45 @@
         <v>1365</v>
       </c>
       <c r="C470" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="D470" s="5"/>
-      <c r="E470" s="5"/>
+        <v>43</v>
+      </c>
+      <c r="D470" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="E470" s="5" t="s">
+        <v>44</v>
+      </c>
       <c r="F470" s="5" t="s">
         <v>592</v>
       </c>
-      <c r="G470" s="5"/>
+      <c r="G470" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="H470" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="I470" s="5"/>
+      <c r="I470" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="J470" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="K470" s="5" t="s">
         <v>133</v>
       </c>
+      <c r="K470" s="5"/>
       <c r="L470" s="18" t="s">
         <v>1922</v>
       </c>
       <c r="M470" s="6">
         <f t="shared" si="16"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N470" s="6" t="str">
         <f t="shared" si="15"/>
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="O470" s="5"/>
-      <c r="P470" s="5"/>
+      <c r="P470" s="5" t="s">
+        <v>2018</v>
+      </c>
       <c r="Q470" s="5"/>
       <c r="R470" s="5" t="s">
         <v>1366</v>
@@ -56365,7 +56376,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>R126 J2:J101 J237:J262 J264:J309 K102 J201:J212 J214:J235 J103:J199 K200 K236 K310 K213 K263 M213:Q213 D102 M102:Q102 D263 M263:Q263 D200 M200:Q200 D236 M236:Q236 D310 M310:Q310 D213 J311:J318 J320:J499 J501:J713</xm:sqref>
+          <xm:sqref>R126 J2:J101 J237:J262 J264:J309 K102 J201:J212 J214:J235 J103:J199 K200 K236 K310 K213 K263 M213:Q213 D102 M102:Q102 D263 M263:Q263 D200 M200:Q200 D236 M236:Q236 D310 M310:Q310 D213 J311:J318 J501:J713 J320:J469 J471:J499</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0100-000000000000}">
           <x14:formula1>
@@ -56482,11 +56493,11 @@
       </c>
       <c r="E2" s="8">
         <f>COUNTA(Roster!E2:E713)</f>
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="F2" s="9">
         <f>IF(COUNTA(Roster!A2:A713)=0,0,E2/COUNTA(Roster!A2:A713))</f>
-        <v>0.63455149501661134</v>
+        <v>0.63621262458471761</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -56526,11 +56537,11 @@
       </c>
       <c r="E4" s="8">
         <f>COUNTA(Roster!G2:G713)</f>
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F4" s="9">
         <f>IF(COUNTA(Roster!A2:A713)=0,0,E4/COUNTA(Roster!A2:A713))</f>
-        <v>0.56976744186046513</v>
+        <v>0.5714285714285714</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -56570,11 +56581,11 @@
       </c>
       <c r="E6" s="8">
         <f>COUNTA(Roster!I2:I713)</f>
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="F6" s="9">
         <f>IF(COUNTA(Roster!A2:A713)=0,0,E6/COUNTA(Roster!A2:A713))</f>
-        <v>0.81229235880398676</v>
+        <v>0.81395348837209303</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
@@ -56687,11 +56698,11 @@
       </c>
       <c r="C5" s="6">
         <f>COUNTIF(Roster!$J$2:$J$713,A5)</f>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D5" s="10">
         <f t="shared" si="0"/>
-        <v>5.1212938005390833E-2</v>
+        <v>4.8517520215633422E-2</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -56799,11 +56810,11 @@
       </c>
       <c r="C12" s="6">
         <f>COUNTIF(Roster!$J$2:$J$713,A12)</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D12" s="10">
         <f t="shared" si="0"/>
-        <v>4.0431266846361183E-2</v>
+        <v>4.3126684636118601E-2</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -56967,7 +56978,7 @@
       </c>
       <c r="B11" s="8">
         <f>COUNTIF(Roster!N2:N713,"Yes")</f>
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C11" s="8" t="s">
         <v>1713</v>
@@ -56979,7 +56990,7 @@
       </c>
       <c r="B12" s="9">
         <f>IF(B5=0,0,B11/B5)</f>
-        <v>1.8466666666666667</v>
+        <v>1.8533333333333333</v>
       </c>
       <c r="C12" s="8" t="s">
         <v>1713</v>
@@ -56991,7 +57002,7 @@
       </c>
       <c r="B13" s="13">
         <f>IFERROR(AVERAGE(Roster!M2:M713),0)</f>
-        <v>3.8853820598006643</v>
+        <v>3.8903654485049834</v>
       </c>
       <c r="C13" s="8" t="s">
         <v>1713</v>

--- a/data/parahumandle_design.xlsx
+++ b/data/parahumandle_design.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Research\Worm Wordle clone\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{427CE6EC-3310-4197-A30A-632E443D55AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D3005B0-48DD-47BB-BB60-98CC5A36DFD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -48876,7 +48876,7 @@
         <v>46</v>
       </c>
       <c r="H541" s="5" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="I541" s="5" t="s">
         <v>312</v>
